--- a/Aepms-backend/data/Engine_Performance_Data.xlsx
+++ b/Aepms-backend/data/Engine_Performance_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ozellar Project\Aepms-backend\iso-performance-backend\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GOKUL\Desktop\Ozellar_project\Aepms-backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C9652E-B1CF-47DA-89DF-3420D00920D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FA3AE40-7B43-445A-97BE-D9C2196EEDBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="vessel_info" sheetId="1" r:id="rId1"/>
@@ -19,17 +19,26 @@
     <sheet name="monthly_report_header" sheetId="6" r:id="rId4"/>
     <sheet name="monthly_report_details_jsonb" sheetId="7" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2172" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2153" uniqueCount="218">
   <si>
     <t>hull_no</t>
   </si>
@@ -598,12 +607,6 @@
     <t>SE6S60-0086-YAMUNA</t>
   </si>
   <si>
-    <t>GCL Mahanadhi</t>
-  </si>
-  <si>
-    <t>SE6S60-0086-MAHANADHI</t>
-  </si>
-  <si>
     <t>AM Tarang</t>
   </si>
   <si>
@@ -643,9 +646,6 @@
     <t>KAA006637-KIRTI</t>
   </si>
   <si>
-    <t>Column1</t>
-  </si>
-  <si>
     <t>csr_power_kw</t>
   </si>
   <si>
@@ -653,6 +653,45 @@
   </si>
   <si>
     <t>barred_speed_rpm_end</t>
+  </si>
+  <si>
+    <t>kg/cm²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T. Takemoto </t>
+  </si>
+  <si>
+    <t>TEST RESULTS of SHOP TRIAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TE3X63 </t>
+  </si>
+  <si>
+    <t>TSUNEISHI</t>
+  </si>
+  <si>
+    <t>MITSUI MAN B&amp;W</t>
+  </si>
+  <si>
+    <t>6S60ME-C8.2</t>
+  </si>
+  <si>
+    <t>MESSERS</t>
+  </si>
+  <si>
+    <t>AM UMANG</t>
+  </si>
+  <si>
+    <t>SE6S60-0086-UMANG</t>
+  </si>
+  <si>
+    <t>mcr_limit_unit</t>
+  </si>
+  <si>
+    <t>mcr_limit_percentage</t>
+  </si>
+  <si>
+    <t>mcr_limit</t>
   </si>
 </sst>
 </file>
@@ -668,12 +707,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -688,9 +733,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -709,42 +758,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:X1048576" totalsRowShown="0">
-  <autoFilter ref="A1:X1048576" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="vessel_id (PK)"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="vessel_name (NOT NULL)"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="imo_number (UNIQUE)"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="engine_no (UNIQUE, NOT NULL)"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="hull_no"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="owner"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="shipyard"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="engine_maker"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="engine_type"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="engine_model"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="number_of_cylinders"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="propeller_pitch_mm"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="propeller_pitch_mm_Unit"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="sfoc_target_gm_kwh"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="sfoc_target_gm_kwh_Unit"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="mcr_power_kw"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="mcr_power_kw_Unit"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="mcr_rpm"/>
-    <tableColumn id="23" xr3:uid="{7A026D6B-9313-46F4-9D22-30EBB2B9B025}" name="mcr_rpm_Unit"/>
-    <tableColumn id="26" xr3:uid="{1E5999CB-3D01-4F88-AD4A-BCB43E53C287}" name="csr_power_kw"/>
-    <tableColumn id="25" xr3:uid="{41F40D24-103B-40E3-B088-665F77D365AF}" name="barred_speed_rpm_start"/>
-    <tableColumn id="24" xr3:uid="{7C7D6C02-16B7-441A-94E8-B409DA35AAE3}" name="barred_speed_rpm_end"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="created_at"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="updated_at"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Column2"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:Q1048576" totalsRowShown="0">
-  <autoFilter ref="A1:Q1048576" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:Q1048575" totalsRowShown="0">
+  <autoFilter ref="A1:Q1048575" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="session_id (PK)"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="engine_no (FK, NOT NULL)"/>
@@ -768,9 +783,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table3" displayName="Table3" ref="A1:BT1048576" totalsRowShown="0">
-  <autoFilter ref="A1:BT1048576" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table3" displayName="Table3" ref="A1:BT1048569" totalsRowShown="0">
+  <autoFilter ref="A1:BT1048569" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="72">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="performance_data_id (PK)"/>
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0200-000049000000}" name="engine_no (UNIQUE, NOT NULL)"/>
@@ -849,7 +864,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Table6" displayName="Table6" ref="A1:AT1048576" totalsRowShown="0">
   <autoFilter ref="A1:AT1048576" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="46">
@@ -905,9 +920,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -945,7 +960,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1051,7 +1066,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1193,7 +1208,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1201,31 +1216,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AB9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7265625" customWidth="1"/>
-    <col min="2" max="2" width="29.54296875" customWidth="1"/>
-    <col min="3" max="3" width="25.453125" customWidth="1"/>
-    <col min="4" max="4" width="31.1796875" customWidth="1"/>
-    <col min="5" max="5" width="9.81640625" customWidth="1"/>
-    <col min="7" max="7" width="22.1796875" customWidth="1"/>
-    <col min="8" max="8" width="15.81640625" customWidth="1"/>
-    <col min="9" max="9" width="14.26953125" customWidth="1"/>
-    <col min="10" max="10" width="20.26953125" customWidth="1"/>
+    <col min="1" max="1" width="18.77734375" customWidth="1"/>
+    <col min="2" max="2" width="29.5546875" customWidth="1"/>
+    <col min="3" max="3" width="25.44140625" customWidth="1"/>
+    <col min="4" max="4" width="31.21875" customWidth="1"/>
+    <col min="5" max="5" width="16.88671875" customWidth="1"/>
+    <col min="7" max="7" width="22.21875" customWidth="1"/>
+    <col min="8" max="8" width="15.77734375" customWidth="1"/>
+    <col min="9" max="9" width="14.21875" customWidth="1"/>
+    <col min="10" max="10" width="20.21875" customWidth="1"/>
     <col min="11" max="11" width="22" customWidth="1"/>
-    <col min="12" max="12" width="21.26953125" customWidth="1"/>
+    <col min="12" max="12" width="21.21875" customWidth="1"/>
     <col min="13" max="13" width="23" customWidth="1"/>
-    <col min="14" max="14" width="16.7265625" customWidth="1"/>
+    <col min="14" max="14" width="16.77734375" customWidth="1"/>
     <col min="15" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="12.54296875" customWidth="1"/>
-    <col min="17" max="17" width="13.26953125" customWidth="1"/>
-    <col min="18" max="18" width="24.90625" customWidth="1"/>
-    <col min="19" max="22" width="14.54296875" customWidth="1"/>
-    <col min="24" max="24" width="11.26953125" customWidth="1"/>
+    <col min="16" max="16" width="12.5546875" customWidth="1"/>
+    <col min="17" max="17" width="13.21875" customWidth="1"/>
+    <col min="18" max="18" width="24.88671875" customWidth="1"/>
+    <col min="19" max="20" width="14.5546875" customWidth="1"/>
+    <col min="21" max="21" width="29.44140625" customWidth="1"/>
+    <col min="22" max="22" width="21.21875" customWidth="1"/>
+    <col min="23" max="24" width="14.5546875" customWidth="1"/>
+    <col min="25" max="25" width="19" customWidth="1"/>
+    <col min="26" max="26" width="16.21875" customWidth="1"/>
+    <col min="28" max="28" width="11.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>23</v>
       </c>
@@ -1284,22 +1304,34 @@
         <v>127</v>
       </c>
       <c r="T1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="U1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="V1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="W1" t="s">
+        <v>217</v>
+      </c>
+      <c r="X1" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>216</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA1" t="s">
         <v>11</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AB1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>13</v>
       </c>
@@ -1360,8 +1392,20 @@
       <c r="V2">
         <v>50</v>
       </c>
+      <c r="W2">
+        <v>8698.74</v>
+      </c>
+      <c r="X2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y2">
+        <v>64.150000000000006</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>178</v>
       </c>
@@ -1422,8 +1466,20 @@
       <c r="V3">
         <v>50</v>
       </c>
+      <c r="W3">
+        <v>8861.4599999999991</v>
+      </c>
+      <c r="X3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y3">
+        <v>65.349999999999994</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>181</v>
       </c>
@@ -1484,8 +1540,20 @@
       <c r="V4">
         <v>50</v>
       </c>
+      <c r="W4">
+        <v>8861.4599999999991</v>
+      </c>
+      <c r="X4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y4">
+        <v>65.349999999999994</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>185</v>
       </c>
@@ -1546,8 +1614,20 @@
       <c r="V5">
         <v>50</v>
       </c>
+      <c r="W5">
+        <v>8637.7199999999993</v>
+      </c>
+      <c r="X5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y5">
+        <v>63.7</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>187</v>
       </c>
@@ -1608,34 +1688,46 @@
       <c r="V6">
         <v>50</v>
       </c>
+      <c r="W6">
+        <v>8651.2800000000007</v>
+      </c>
+      <c r="X6" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y6">
+        <v>63.8</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>189</v>
       </c>
       <c r="C7">
-        <v>9481673</v>
+        <v>9832913</v>
       </c>
       <c r="D7" t="s">
+        <v>198</v>
+      </c>
+      <c r="E7" t="s">
         <v>190</v>
       </c>
-      <c r="E7" t="s">
-        <v>183</v>
-      </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>191</v>
       </c>
       <c r="G7" t="s">
-        <v>17</v>
+        <v>192</v>
       </c>
       <c r="H7" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="I7" t="s">
-        <v>123</v>
+        <v>194</v>
       </c>
       <c r="J7" t="s">
-        <v>123</v>
+        <v>194</v>
       </c>
       <c r="K7">
         <v>6</v>
@@ -1650,54 +1742,66 @@
         <v>20</v>
       </c>
       <c r="P7">
-        <v>13560</v>
+        <v>15748</v>
       </c>
       <c r="Q7" t="s">
         <v>21</v>
       </c>
       <c r="R7">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="S7" t="s">
         <v>22</v>
       </c>
       <c r="T7">
-        <v>12204</v>
+        <v>11811</v>
       </c>
       <c r="U7">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="V7">
-        <v>50</v>
+        <v>43</v>
+      </c>
+      <c r="W7">
+        <v>12770.63</v>
+      </c>
+      <c r="X7" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y7">
+        <v>81.09</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>171</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
+        <v>200</v>
+      </c>
+      <c r="C8">
+        <v>9832925</v>
+      </c>
+      <c r="D8" t="s">
+        <v>201</v>
+      </c>
+      <c r="E8" t="s">
+        <v>190</v>
+      </c>
+      <c r="F8" t="s">
         <v>191</v>
       </c>
-      <c r="C8">
-        <v>9832913</v>
-      </c>
-      <c r="D8" t="s">
-        <v>200</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
         <v>192</v>
       </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
         <v>193</v>
       </c>
-      <c r="G8" t="s">
+      <c r="I8" t="s">
         <v>194</v>
       </c>
-      <c r="H8" t="s">
-        <v>195</v>
-      </c>
-      <c r="I8" t="s">
-        <v>196</v>
-      </c>
       <c r="J8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K8">
         <v>6</v>
@@ -1732,34 +1836,46 @@
       <c r="V8">
         <v>43</v>
       </c>
+      <c r="W8">
+        <v>12701</v>
+      </c>
+      <c r="X8" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y8">
+        <v>80.650000000000006</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="C9">
-        <v>9832925</v>
-      </c>
-      <c r="D9" t="s">
-        <v>203</v>
-      </c>
-      <c r="E9" t="s">
-        <v>192</v>
+        <v>9792058</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1576</v>
       </c>
       <c r="F9" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="G9" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="H9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="I9" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="J9" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="K9">
         <v>6</v>
@@ -1768,63 +1884,66 @@
         <v>19</v>
       </c>
       <c r="N9">
-        <v>172.5</v>
+        <v>159.19999999999999</v>
       </c>
       <c r="O9" t="s">
         <v>20</v>
       </c>
       <c r="P9">
-        <v>15748</v>
+        <v>9660</v>
       </c>
       <c r="Q9" t="s">
         <v>21</v>
       </c>
       <c r="R9">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="S9" t="s">
         <v>22</v>
       </c>
       <c r="T9">
-        <v>11811</v>
-      </c>
-      <c r="U9">
-        <v>35</v>
-      </c>
-      <c r="V9">
-        <v>43</v>
+        <v>7300</v>
+      </c>
+      <c r="W9">
+        <v>9660</v>
+      </c>
+      <c r="X9" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y9">
+        <v>100</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.26953125" customWidth="1"/>
-    <col min="2" max="2" width="26.26953125" customWidth="1"/>
-    <col min="3" max="3" width="22.26953125" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" customWidth="1"/>
-    <col min="5" max="5" width="15.54296875" customWidth="1"/>
+    <col min="1" max="1" width="21.21875" customWidth="1"/>
+    <col min="2" max="2" width="26.21875" customWidth="1"/>
+    <col min="3" max="3" width="22.21875" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" customWidth="1"/>
+    <col min="5" max="5" width="15.5546875" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="7" width="21.81640625" customWidth="1"/>
-    <col min="8" max="8" width="45.54296875" customWidth="1"/>
-    <col min="9" max="9" width="30.26953125" customWidth="1"/>
+    <col min="7" max="7" width="21.77734375" customWidth="1"/>
+    <col min="8" max="8" width="45.5546875" customWidth="1"/>
+    <col min="9" max="9" width="30.21875" customWidth="1"/>
     <col min="10" max="10" width="24" customWidth="1"/>
-    <col min="11" max="11" width="10.26953125" customWidth="1"/>
-    <col min="13" max="13" width="12.54296875" customWidth="1"/>
-    <col min="14" max="14" width="13.26953125" customWidth="1"/>
+    <col min="11" max="11" width="10.21875" customWidth="1"/>
+    <col min="13" max="13" width="12.5546875" customWidth="1"/>
+    <col min="14" max="14" width="30.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -1877,7 +1996,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>14</v>
       </c>
@@ -1921,7 +2040,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>180</v>
       </c>
@@ -1962,7 +2081,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>182</v>
       </c>
@@ -2003,7 +2122,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>186</v>
       </c>
@@ -2044,7 +2163,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>188</v>
       </c>
@@ -2085,50 +2204,53 @@
         <v>137</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="C7" s="1">
-        <v>40518</v>
+        <v>43461</v>
       </c>
       <c r="D7" t="s">
         <v>131</v>
       </c>
       <c r="E7" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="F7" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="G7" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I7" t="s">
         <v>135</v>
       </c>
       <c r="J7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K7" t="s">
         <v>135</v>
       </c>
       <c r="L7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M7" t="s">
         <v>135</v>
+      </c>
+      <c r="N7" t="s">
+        <v>137</v>
       </c>
       <c r="O7" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C8" s="1">
         <v>43461</v>
@@ -2137,13 +2259,13 @@
         <v>131</v>
       </c>
       <c r="E8" t="s">
+        <v>195</v>
+      </c>
+      <c r="F8" t="s">
+        <v>199</v>
+      </c>
+      <c r="G8" t="s">
         <v>197</v>
-      </c>
-      <c r="F8" t="s">
-        <v>198</v>
-      </c>
-      <c r="G8" t="s">
-        <v>199</v>
       </c>
       <c r="H8">
         <v>6</v>
@@ -2158,7 +2280,7 @@
         <v>135</v>
       </c>
       <c r="L8">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M8" t="s">
         <v>135</v>
@@ -2170,45 +2292,30 @@
         <v>137</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="B9" t="s">
-        <v>203</v>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>214</v>
       </c>
       <c r="C9" s="1">
-        <v>43461</v>
+        <v>42788</v>
       </c>
       <c r="D9" t="s">
         <v>131</v>
       </c>
       <c r="E9" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="F9" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="G9" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="H9">
-        <v>6</v>
-      </c>
-      <c r="I9" t="s">
-        <v>135</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>44</v>
-      </c>
-      <c r="K9" t="s">
-        <v>135</v>
-      </c>
-      <c r="L9">
-        <v>42</v>
-      </c>
-      <c r="M9" t="s">
-        <v>135</v>
-      </c>
-      <c r="N9" t="s">
-        <v>137</v>
+        <v>45</v>
       </c>
       <c r="O9" t="s">
         <v>137</v>
@@ -2225,52 +2332,82 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:BT55"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:BT54"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="26.26953125" customWidth="1"/>
-    <col min="3" max="3" width="26.1796875" customWidth="1"/>
-    <col min="4" max="4" width="28.54296875" customWidth="1"/>
-    <col min="5" max="5" width="26.7265625" customWidth="1"/>
-    <col min="6" max="6" width="30.453125" customWidth="1"/>
-    <col min="7" max="7" width="20.26953125" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="24.7265625" customWidth="1"/>
-    <col min="10" max="10" width="26.81640625" customWidth="1"/>
-    <col min="11" max="11" width="17.453125" customWidth="1"/>
-    <col min="12" max="12" width="24.26953125" customWidth="1"/>
-    <col min="13" max="13" width="28.453125" customWidth="1"/>
-    <col min="14" max="14" width="30.81640625" customWidth="1"/>
+    <col min="1" max="3" width="26.21875" customWidth="1"/>
+    <col min="4" max="4" width="28.5546875" customWidth="1"/>
+    <col min="5" max="5" width="26.77734375" customWidth="1"/>
+    <col min="6" max="6" width="30.44140625" customWidth="1"/>
+    <col min="7" max="7" width="42.109375" customWidth="1"/>
+    <col min="8" max="8" width="29.5546875" customWidth="1"/>
+    <col min="9" max="9" width="24.77734375" customWidth="1"/>
+    <col min="10" max="10" width="26.77734375" customWidth="1"/>
+    <col min="11" max="11" width="41.109375" customWidth="1"/>
+    <col min="12" max="12" width="33.109375" customWidth="1"/>
+    <col min="13" max="13" width="28.44140625" customWidth="1"/>
+    <col min="14" max="14" width="30.77734375" customWidth="1"/>
     <col min="15" max="15" width="27" customWidth="1"/>
-    <col min="16" max="16" width="29.7265625" customWidth="1"/>
-    <col min="17" max="17" width="32.1796875" customWidth="1"/>
-    <col min="18" max="18" width="32.7265625" customWidth="1"/>
-    <col min="19" max="19" width="21.7265625" customWidth="1"/>
-    <col min="20" max="20" width="23" customWidth="1"/>
-    <col min="21" max="21" width="31.54296875" customWidth="1"/>
-    <col min="22" max="22" width="22.7265625" customWidth="1"/>
-    <col min="23" max="23" width="36.81640625" customWidth="1"/>
-    <col min="24" max="24" width="24.1796875" customWidth="1"/>
-    <col min="25" max="25" width="27.7265625" customWidth="1"/>
-    <col min="26" max="26" width="29.26953125" customWidth="1"/>
-    <col min="27" max="27" width="34.453125" customWidth="1"/>
-    <col min="28" max="28" width="30.54296875" customWidth="1"/>
-    <col min="29" max="29" width="30" customWidth="1"/>
-    <col min="30" max="30" width="25.26953125" customWidth="1"/>
-    <col min="31" max="31" width="26.54296875" customWidth="1"/>
-    <col min="32" max="32" width="35.1796875" customWidth="1"/>
-    <col min="33" max="33" width="32.81640625" customWidth="1"/>
-    <col min="34" max="34" width="30.453125" customWidth="1"/>
-    <col min="35" max="35" width="21" customWidth="1"/>
-    <col min="36" max="36" width="27.81640625" customWidth="1"/>
+    <col min="16" max="16" width="29.77734375" customWidth="1"/>
+    <col min="17" max="17" width="32.21875" customWidth="1"/>
+    <col min="18" max="18" width="32.77734375" customWidth="1"/>
+    <col min="19" max="19" width="36.109375" customWidth="1"/>
+    <col min="20" max="20" width="36.21875" customWidth="1"/>
+    <col min="21" max="21" width="31.77734375" customWidth="1"/>
+    <col min="22" max="22" width="51.44140625" customWidth="1"/>
+    <col min="23" max="23" width="36.77734375" customWidth="1"/>
+    <col min="24" max="24" width="43.6640625" customWidth="1"/>
+    <col min="25" max="25" width="27.77734375" customWidth="1"/>
+    <col min="26" max="26" width="32.109375" customWidth="1"/>
+    <col min="27" max="27" width="30.77734375" customWidth="1"/>
+    <col min="28" max="28" width="53.77734375" customWidth="1"/>
+    <col min="29" max="29" width="42.77734375" customWidth="1"/>
+    <col min="30" max="30" width="39.21875" customWidth="1"/>
+    <col min="31" max="31" width="38.33203125" customWidth="1"/>
+    <col min="32" max="32" width="39.5546875" customWidth="1"/>
+    <col min="33" max="33" width="32.77734375" customWidth="1"/>
+    <col min="34" max="34" width="30.44140625" customWidth="1"/>
+    <col min="35" max="35" width="25.6640625" customWidth="1"/>
+    <col min="36" max="36" width="27.77734375" customWidth="1"/>
     <col min="37" max="37" width="32" customWidth="1"/>
-    <col min="38" max="38" width="12.54296875" customWidth="1"/>
-    <col min="39" max="39" width="13.26953125" customWidth="1"/>
-    <col min="60" max="60" width="37.7265625" customWidth="1"/>
-    <col min="61" max="61" width="23.26953125" customWidth="1"/>
+    <col min="38" max="38" width="34.88671875" customWidth="1"/>
+    <col min="39" max="39" width="27.109375" customWidth="1"/>
+    <col min="40" max="40" width="30.88671875" customWidth="1"/>
+    <col min="41" max="41" width="41.109375" customWidth="1"/>
+    <col min="42" max="42" width="75.21875" customWidth="1"/>
+    <col min="43" max="43" width="51" customWidth="1"/>
+    <col min="44" max="44" width="43.77734375" customWidth="1"/>
+    <col min="45" max="45" width="58.33203125" customWidth="1"/>
+    <col min="46" max="46" width="47.5546875" customWidth="1"/>
+    <col min="47" max="47" width="38.44140625" customWidth="1"/>
+    <col min="48" max="48" width="42.33203125" customWidth="1"/>
+    <col min="49" max="49" width="46.21875" customWidth="1"/>
+    <col min="50" max="50" width="42.109375" customWidth="1"/>
+    <col min="51" max="51" width="40.44140625" customWidth="1"/>
+    <col min="52" max="52" width="50.109375" customWidth="1"/>
+    <col min="53" max="53" width="54" customWidth="1"/>
+    <col min="54" max="54" width="47.88671875" customWidth="1"/>
+    <col min="55" max="55" width="46" customWidth="1"/>
+    <col min="56" max="56" width="38.21875" customWidth="1"/>
+    <col min="57" max="57" width="46.44140625" customWidth="1"/>
+    <col min="58" max="58" width="50.109375" customWidth="1"/>
+    <col min="59" max="59" width="44.44140625" customWidth="1"/>
+    <col min="60" max="60" width="41.88671875" customWidth="1"/>
+    <col min="61" max="61" width="42.6640625" customWidth="1"/>
+    <col min="62" max="62" width="37.5546875" customWidth="1"/>
+    <col min="63" max="63" width="32.21875" customWidth="1"/>
+    <col min="64" max="64" width="33.88671875" customWidth="1"/>
+    <col min="65" max="65" width="48.109375" customWidth="1"/>
+    <col min="66" max="66" width="39.77734375" customWidth="1"/>
+    <col min="67" max="67" width="36.21875" customWidth="1"/>
+    <col min="68" max="68" width="36.88671875" customWidth="1"/>
+    <col min="69" max="69" width="46.6640625" customWidth="1"/>
+    <col min="70" max="70" width="37.6640625" customWidth="1"/>
+    <col min="71" max="71" width="38.5546875" customWidth="1"/>
+    <col min="72" max="72" width="48.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:72" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>70</v>
       </c>
@@ -2488,7 +2625,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:72" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>14</v>
       </c>
@@ -2694,7 +2831,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="3" spans="1:72" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>14</v>
       </c>
@@ -2900,7 +3037,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="4" spans="1:72" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>14</v>
       </c>
@@ -3106,7 +3243,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="5" spans="1:72" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>14</v>
       </c>
@@ -3312,7 +3449,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="6" spans="1:72" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>14</v>
       </c>
@@ -3518,7 +3655,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="7" spans="1:72" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>14</v>
       </c>
@@ -3724,7 +3861,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="8" spans="1:72" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>14</v>
       </c>
@@ -3930,7 +4067,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="9" spans="1:72" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>180</v>
       </c>
@@ -4136,7 +4273,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="10" spans="1:72" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>180</v>
       </c>
@@ -4342,7 +4479,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="11" spans="1:72" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>180</v>
       </c>
@@ -4548,7 +4685,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="12" spans="1:72" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>180</v>
       </c>
@@ -4754,7 +4891,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="13" spans="1:72" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>180</v>
       </c>
@@ -4960,7 +5097,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="14" spans="1:72" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>180</v>
       </c>
@@ -5166,7 +5303,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="15" spans="1:72" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>180</v>
       </c>
@@ -5372,7 +5509,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="16" spans="1:72" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>182</v>
       </c>
@@ -5578,7 +5715,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="17" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>182</v>
       </c>
@@ -5784,7 +5921,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="18" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>182</v>
       </c>
@@ -5990,7 +6127,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="19" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>182</v>
       </c>
@@ -6196,7 +6333,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="20" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>182</v>
       </c>
@@ -6402,7 +6539,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="21" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>182</v>
       </c>
@@ -6608,7 +6745,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="22" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>182</v>
       </c>
@@ -6814,7 +6951,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="23" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>186</v>
       </c>
@@ -7020,7 +7157,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="24" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>186</v>
       </c>
@@ -7226,7 +7363,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="25" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>186</v>
       </c>
@@ -7432,7 +7569,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="26" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>186</v>
       </c>
@@ -7638,7 +7775,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="27" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>186</v>
       </c>
@@ -7844,7 +7981,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="28" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>186</v>
       </c>
@@ -8050,7 +8187,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="29" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>186</v>
       </c>
@@ -8256,7 +8393,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="30" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>188</v>
       </c>
@@ -8462,7 +8599,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="31" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>188</v>
       </c>
@@ -8668,7 +8805,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="32" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>188</v>
       </c>
@@ -8874,7 +9011,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="33" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>188</v>
       </c>
@@ -9080,7 +9217,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="34" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>188</v>
       </c>
@@ -9286,7 +9423,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="35" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>188</v>
       </c>
@@ -9492,7 +9629,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="36" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>188</v>
       </c>
@@ -9698,9 +9835,9 @@
         <v>173</v>
       </c>
     </row>
-    <row r="37" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D37">
         <v>25</v>
@@ -9712,25 +9849,25 @@
         <v>1</v>
       </c>
       <c r="G37">
-        <v>3390</v>
+        <v>3937</v>
       </c>
       <c r="H37" t="s">
         <v>21</v>
       </c>
       <c r="I37">
-        <v>66.099999999999994</v>
+        <v>47.2</v>
       </c>
       <c r="J37" t="s">
         <v>22</v>
       </c>
       <c r="K37">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="L37" t="s">
         <v>135</v>
       </c>
       <c r="M37">
-        <v>21</v>
+        <v>13.6</v>
       </c>
       <c r="N37" t="s">
         <v>171</v>
@@ -9742,139 +9879,133 @@
         <v>172</v>
       </c>
       <c r="Q37">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="R37" t="s">
         <v>135</v>
       </c>
       <c r="S37">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="T37" t="s">
         <v>135</v>
       </c>
       <c r="U37">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V37" t="s">
         <v>173</v>
       </c>
       <c r="W37">
-        <v>75.3</v>
+        <v>116</v>
       </c>
       <c r="X37" t="s">
         <v>174</v>
       </c>
       <c r="Y37">
-        <v>50.2</v>
+        <v>76</v>
       </c>
       <c r="Z37" t="s">
         <v>174</v>
       </c>
-      <c r="AA37">
-        <v>7.56</v>
-      </c>
       <c r="AB37" t="s">
         <v>174</v>
       </c>
       <c r="AC37">
-        <v>48.8</v>
+        <v>43</v>
       </c>
       <c r="AD37" t="s">
-        <v>19</v>
+        <v>171</v>
       </c>
       <c r="AE37">
-        <v>279.2</v>
+        <v>174</v>
       </c>
       <c r="AF37" t="s">
         <v>135</v>
       </c>
       <c r="AG37">
-        <v>310</v>
+        <v>211</v>
       </c>
       <c r="AH37" t="s">
         <v>135</v>
       </c>
       <c r="AI37">
-        <v>250</v>
+        <v>171</v>
       </c>
       <c r="AJ37" t="s">
         <v>135</v>
       </c>
       <c r="AK37">
-        <v>5.9</v>
+        <v>5.7590000000000003</v>
       </c>
       <c r="AL37" t="s">
         <v>175</v>
       </c>
       <c r="AM37">
-        <v>0.51</v>
+        <v>0.38</v>
       </c>
       <c r="AN37" t="s">
         <v>174</v>
-      </c>
-      <c r="AO37">
-        <v>0.41</v>
       </c>
       <c r="AP37" t="s">
         <v>176</v>
       </c>
       <c r="AQ37">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="AR37" t="s">
         <v>135</v>
       </c>
       <c r="AS37">
-        <v>652.79999999999995</v>
+        <v>676</v>
       </c>
       <c r="AT37" t="s">
         <v>177</v>
       </c>
       <c r="AU37">
-        <v>192.6</v>
+        <v>173.7</v>
       </c>
       <c r="AV37" t="s">
         <v>20</v>
       </c>
       <c r="AW37">
-        <v>71.8</v>
+        <v>116</v>
       </c>
       <c r="AX37" t="s">
         <v>174</v>
       </c>
       <c r="AY37">
-        <v>46.8</v>
+        <v>76</v>
       </c>
       <c r="AZ37" t="s">
         <v>174</v>
       </c>
       <c r="BA37">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BB37" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="BC37">
-        <v>334.7</v>
+        <v>211</v>
       </c>
       <c r="BD37" t="s">
         <v>135</v>
       </c>
       <c r="BE37">
-        <v>278.5</v>
+        <v>171</v>
       </c>
       <c r="BF37" t="s">
         <v>135</v>
       </c>
       <c r="BG37">
-        <v>6</v>
+        <v>5.7590000000000003</v>
       </c>
       <c r="BH37" t="s">
         <v>175</v>
       </c>
       <c r="BI37">
-        <v>192.7</v>
+        <v>173.7</v>
       </c>
       <c r="BJ37" t="s">
         <v>20</v>
@@ -9904,9 +10035,9 @@
         <v>173</v>
       </c>
     </row>
-    <row r="38" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D38">
         <v>50</v>
@@ -9918,25 +10049,25 @@
         <v>2</v>
       </c>
       <c r="G38">
-        <v>6780</v>
+        <v>7874</v>
       </c>
       <c r="H38" t="s">
         <v>21</v>
       </c>
       <c r="I38">
-        <v>83.3</v>
+        <v>59.5</v>
       </c>
       <c r="J38" t="s">
         <v>22</v>
       </c>
       <c r="K38">
-        <v>6</v>
+        <v>9.9</v>
       </c>
       <c r="L38" t="s">
         <v>135</v>
       </c>
       <c r="M38">
-        <v>30</v>
+        <v>11.9</v>
       </c>
       <c r="N38" t="s">
         <v>171</v>
@@ -9948,139 +10079,133 @@
         <v>172</v>
       </c>
       <c r="Q38">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="R38" t="s">
         <v>135</v>
       </c>
       <c r="S38">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T38" t="s">
         <v>135</v>
       </c>
       <c r="U38">
-        <v>120</v>
+        <v>33</v>
       </c>
       <c r="V38" t="s">
         <v>173</v>
       </c>
       <c r="W38">
-        <v>111</v>
+        <v>159</v>
       </c>
       <c r="X38" t="s">
         <v>174</v>
       </c>
       <c r="Y38">
-        <v>85.2</v>
+        <v>119</v>
       </c>
       <c r="Z38" t="s">
         <v>174</v>
       </c>
-      <c r="AA38">
-        <v>12</v>
-      </c>
       <c r="AB38" t="s">
         <v>174</v>
       </c>
       <c r="AC38">
-        <v>64.8</v>
+        <v>65</v>
       </c>
       <c r="AD38" t="s">
-        <v>19</v>
+        <v>171</v>
       </c>
       <c r="AE38">
-        <v>263.3</v>
+        <v>242</v>
       </c>
       <c r="AF38" t="s">
         <v>135</v>
       </c>
       <c r="AG38">
-        <v>335</v>
+        <v>278</v>
       </c>
       <c r="AH38" t="s">
         <v>135</v>
       </c>
       <c r="AI38">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="AJ38" t="s">
         <v>135</v>
       </c>
       <c r="AK38">
-        <v>10</v>
+        <v>9.2200000000000006</v>
       </c>
       <c r="AL38" t="s">
         <v>175</v>
       </c>
       <c r="AM38">
-        <v>1.53</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="AN38" t="s">
         <v>174</v>
-      </c>
-      <c r="AO38">
-        <v>1.33</v>
       </c>
       <c r="AP38" t="s">
         <v>176</v>
       </c>
       <c r="AQ38">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AR38" t="s">
         <v>135</v>
       </c>
       <c r="AS38">
-        <v>1197.5999999999999</v>
+        <v>1292</v>
       </c>
       <c r="AT38" t="s">
         <v>177</v>
       </c>
       <c r="AU38">
-        <v>176.6</v>
+        <v>165.4</v>
       </c>
       <c r="AV38" t="s">
         <v>20</v>
       </c>
       <c r="AW38">
-        <v>105</v>
+        <v>159</v>
       </c>
       <c r="AX38" t="s">
         <v>174</v>
       </c>
       <c r="AY38">
-        <v>78.5</v>
+        <v>119</v>
       </c>
       <c r="AZ38" t="s">
         <v>174</v>
       </c>
       <c r="BA38">
-        <v>1.31</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="BB38" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="BC38">
-        <v>359.9</v>
+        <v>278</v>
       </c>
       <c r="BD38" t="s">
         <v>135</v>
       </c>
       <c r="BE38">
-        <v>247.1</v>
+        <v>190</v>
       </c>
       <c r="BF38" t="s">
         <v>135</v>
       </c>
       <c r="BG38">
-        <v>10</v>
+        <v>9.2200000000000006</v>
       </c>
       <c r="BH38" t="s">
         <v>175</v>
       </c>
       <c r="BI38">
-        <v>176.4</v>
+        <v>165.4</v>
       </c>
       <c r="BJ38" t="s">
         <v>20</v>
@@ -10098,21 +10223,21 @@
         <v>135</v>
       </c>
       <c r="BO38">
-        <v>27.4</v>
+        <v>33.5</v>
       </c>
       <c r="BP38" t="s">
         <v>135</v>
       </c>
       <c r="BQ38">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="BR38" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="39" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D39">
         <v>75</v>
@@ -10124,139 +10249,133 @@
         <v>3</v>
       </c>
       <c r="G39">
-        <v>10170</v>
+        <v>11811</v>
       </c>
       <c r="H39" t="s">
         <v>21</v>
       </c>
       <c r="I39">
-        <v>95.4</v>
+        <v>68.099999999999994</v>
       </c>
       <c r="J39" t="s">
         <v>22</v>
       </c>
       <c r="K39">
-        <v>7</v>
+        <v>10.4</v>
       </c>
       <c r="L39" t="s">
         <v>135</v>
       </c>
       <c r="M39">
-        <v>30</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="N39" t="s">
         <v>171</v>
       </c>
       <c r="O39">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="P39" t="s">
         <v>172</v>
       </c>
       <c r="Q39">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="R39" t="s">
         <v>135</v>
       </c>
       <c r="S39">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="T39" t="s">
         <v>135</v>
       </c>
       <c r="U39">
-        <v>160</v>
+        <v>43</v>
       </c>
       <c r="V39" t="s">
         <v>173</v>
       </c>
       <c r="W39">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="X39" t="s">
         <v>174</v>
       </c>
       <c r="Y39">
-        <v>120.7</v>
+        <v>135</v>
       </c>
       <c r="Z39" t="s">
         <v>174</v>
       </c>
-      <c r="AA39">
-        <v>15.72</v>
-      </c>
       <c r="AB39" t="s">
         <v>174</v>
       </c>
       <c r="AC39">
-        <v>79.3</v>
+        <v>84</v>
       </c>
       <c r="AD39" t="s">
-        <v>19</v>
+        <v>171</v>
       </c>
       <c r="AE39">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="AF39" t="s">
         <v>135</v>
       </c>
       <c r="AG39">
-        <v>370</v>
+        <v>317</v>
       </c>
       <c r="AH39" t="s">
         <v>135</v>
       </c>
       <c r="AI39">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="AJ39" t="s">
         <v>135</v>
       </c>
       <c r="AK39">
-        <v>11.4</v>
+        <v>11.48</v>
       </c>
       <c r="AL39" t="s">
         <v>175</v>
       </c>
       <c r="AM39">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="AN39" t="s">
         <v>174</v>
-      </c>
-      <c r="AO39">
-        <v>2.2000000000000002</v>
       </c>
       <c r="AP39" t="s">
         <v>176</v>
       </c>
       <c r="AQ39">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AR39" t="s">
         <v>135</v>
       </c>
       <c r="AS39">
-        <v>1725.6</v>
+        <v>1932</v>
       </c>
       <c r="AT39" t="s">
         <v>177</v>
       </c>
       <c r="AU39">
-        <v>169.7</v>
+        <v>164.5</v>
       </c>
       <c r="AV39" t="s">
         <v>20</v>
       </c>
       <c r="AW39">
-        <v>137.30000000000001</v>
+        <v>175</v>
       </c>
       <c r="AX39" t="s">
         <v>174</v>
       </c>
       <c r="AY39">
-        <v>111.4</v>
+        <v>135</v>
       </c>
       <c r="AZ39" t="s">
         <v>174</v>
@@ -10265,28 +10384,28 @@
         <v>2.12</v>
       </c>
       <c r="BB39" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="BC39">
-        <v>397.5</v>
+        <v>317</v>
       </c>
       <c r="BD39" t="s">
         <v>135</v>
       </c>
       <c r="BE39">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="BF39" t="s">
         <v>135</v>
       </c>
       <c r="BG39">
-        <v>11.4</v>
+        <v>11.48</v>
       </c>
       <c r="BH39" t="s">
         <v>175</v>
       </c>
       <c r="BI39">
-        <v>169.3</v>
+        <v>164.5</v>
       </c>
       <c r="BJ39" t="s">
         <v>20</v>
@@ -10304,24 +10423,24 @@
         <v>135</v>
       </c>
       <c r="BO39">
-        <v>31.2</v>
+        <v>33.5</v>
       </c>
       <c r="BP39" t="s">
         <v>135</v>
       </c>
       <c r="BQ39">
-        <v>179</v>
+        <v>25</v>
       </c>
       <c r="BR39" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="40" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D40">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E40" t="s">
         <v>171</v>
@@ -10330,169 +10449,163 @@
         <v>4</v>
       </c>
       <c r="G40">
-        <v>12204</v>
+        <v>15748</v>
       </c>
       <c r="H40" t="s">
         <v>21</v>
       </c>
       <c r="I40">
-        <v>101.4</v>
+        <v>75</v>
       </c>
       <c r="J40" t="s">
         <v>22</v>
       </c>
       <c r="K40">
-        <v>7</v>
+        <v>11.2</v>
       </c>
       <c r="L40" t="s">
         <v>135</v>
       </c>
       <c r="M40">
-        <v>30</v>
+        <v>10.4</v>
       </c>
       <c r="N40" t="s">
         <v>171</v>
       </c>
       <c r="O40">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="P40" t="s">
         <v>172</v>
       </c>
       <c r="Q40">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="R40" t="s">
         <v>135</v>
       </c>
       <c r="S40">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="T40" t="s">
         <v>135</v>
       </c>
       <c r="U40">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="V40" t="s">
         <v>173</v>
       </c>
       <c r="W40">
-        <v>160.19999999999999</v>
+        <v>176</v>
       </c>
       <c r="X40" t="s">
         <v>174</v>
       </c>
       <c r="Y40">
-        <v>139.80000000000001</v>
+        <v>150</v>
       </c>
       <c r="Z40" t="s">
         <v>174</v>
       </c>
-      <c r="AA40">
-        <v>17.75</v>
-      </c>
       <c r="AB40" t="s">
         <v>174</v>
       </c>
       <c r="AC40">
-        <v>90.5</v>
+        <v>100</v>
       </c>
       <c r="AD40" t="s">
-        <v>19</v>
+        <v>171</v>
       </c>
       <c r="AE40">
-        <v>305.8</v>
+        <v>340</v>
       </c>
       <c r="AF40" t="s">
         <v>135</v>
       </c>
       <c r="AG40">
-        <v>410</v>
+        <v>380</v>
       </c>
       <c r="AH40" t="s">
         <v>135</v>
       </c>
       <c r="AI40">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="AJ40" t="s">
         <v>135</v>
       </c>
       <c r="AK40">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="AL40" t="s">
         <v>175</v>
       </c>
       <c r="AM40">
-        <v>2.91</v>
+        <v>2.79</v>
       </c>
       <c r="AN40" t="s">
         <v>174</v>
-      </c>
-      <c r="AO40">
-        <v>2.71</v>
       </c>
       <c r="AP40" t="s">
         <v>176</v>
       </c>
       <c r="AQ40">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AR40" t="s">
         <v>135</v>
       </c>
       <c r="AS40">
-        <v>2098.1999999999998</v>
+        <v>2664</v>
       </c>
       <c r="AT40" t="s">
         <v>177</v>
       </c>
       <c r="AU40">
-        <v>171.9</v>
+        <v>169.9</v>
       </c>
       <c r="AV40" t="s">
         <v>20</v>
       </c>
       <c r="AW40">
-        <v>151.6</v>
+        <v>176</v>
       </c>
       <c r="AX40" t="s">
         <v>174</v>
       </c>
       <c r="AY40">
-        <v>129.19999999999999</v>
+        <v>150</v>
       </c>
       <c r="AZ40" t="s">
         <v>174</v>
       </c>
       <c r="BA40">
-        <v>2.59</v>
+        <v>2.79</v>
       </c>
       <c r="BB40" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="BC40">
-        <v>440.8</v>
+        <v>380</v>
       </c>
       <c r="BD40" t="s">
         <v>135</v>
       </c>
       <c r="BE40">
-        <v>255.1</v>
+        <v>219</v>
       </c>
       <c r="BF40" t="s">
         <v>135</v>
       </c>
       <c r="BG40">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="BH40" t="s">
         <v>175</v>
       </c>
       <c r="BI40">
-        <v>171.3</v>
+        <v>169.9</v>
       </c>
       <c r="BJ40" t="s">
         <v>20</v>
@@ -10510,21 +10623,21 @@
         <v>135</v>
       </c>
       <c r="BO40">
-        <v>34.4</v>
+        <v>33.5</v>
       </c>
       <c r="BP40" t="s">
         <v>135</v>
       </c>
       <c r="BQ40">
-        <v>248</v>
+        <v>25</v>
       </c>
       <c r="BR40" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="41" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D41">
         <v>100</v>
@@ -10536,169 +10649,163 @@
         <v>5</v>
       </c>
       <c r="G41">
-        <v>13560</v>
+        <v>15748</v>
       </c>
       <c r="H41" t="s">
         <v>21</v>
       </c>
       <c r="I41">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="J41" t="s">
         <v>22</v>
       </c>
       <c r="K41">
-        <v>7</v>
+        <v>11.4</v>
       </c>
       <c r="L41" t="s">
         <v>135</v>
       </c>
       <c r="M41">
-        <v>30</v>
+        <v>10.6</v>
       </c>
       <c r="N41" t="s">
         <v>171</v>
       </c>
       <c r="O41">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="P41" t="s">
         <v>172</v>
       </c>
       <c r="Q41">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="R41" t="s">
         <v>135</v>
       </c>
       <c r="S41">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="T41" t="s">
         <v>135</v>
       </c>
       <c r="U41">
-        <v>220</v>
+        <v>53</v>
       </c>
       <c r="V41" t="s">
         <v>173</v>
       </c>
       <c r="W41">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="X41" t="s">
         <v>174</v>
       </c>
       <c r="Y41">
-        <v>154.80000000000001</v>
+        <v>150</v>
       </c>
       <c r="Z41" t="s">
         <v>174</v>
       </c>
-      <c r="AA41">
-        <v>19.04</v>
-      </c>
       <c r="AB41" t="s">
         <v>174</v>
       </c>
       <c r="AC41">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AD41" t="s">
-        <v>19</v>
+        <v>171</v>
       </c>
       <c r="AE41">
-        <v>308.3</v>
+        <v>353</v>
       </c>
       <c r="AF41" t="s">
         <v>135</v>
       </c>
       <c r="AG41">
-        <v>415</v>
+        <v>386</v>
       </c>
       <c r="AH41" t="s">
         <v>135</v>
       </c>
       <c r="AI41">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="AJ41" t="s">
         <v>135</v>
       </c>
       <c r="AK41">
-        <v>12.7</v>
+        <v>12.78</v>
       </c>
       <c r="AL41" t="s">
         <v>175</v>
       </c>
       <c r="AM41">
-        <v>3.31</v>
+        <v>2.88</v>
       </c>
       <c r="AN41" t="s">
         <v>174</v>
-      </c>
-      <c r="AO41">
-        <v>3.11</v>
       </c>
       <c r="AP41" t="s">
         <v>176</v>
       </c>
       <c r="AQ41">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AR41" t="s">
         <v>135</v>
       </c>
       <c r="AS41">
-        <v>2359.8000000000002</v>
+        <v>2664</v>
       </c>
       <c r="AT41" t="s">
         <v>177</v>
       </c>
       <c r="AU41">
-        <v>174</v>
+        <v>169.9</v>
       </c>
       <c r="AV41" t="s">
         <v>20</v>
       </c>
       <c r="AW41">
-        <v>151.1</v>
+        <v>176</v>
       </c>
       <c r="AX41" t="s">
         <v>174</v>
       </c>
       <c r="AY41">
-        <v>142.6</v>
+        <v>150</v>
       </c>
       <c r="AZ41" t="s">
         <v>174</v>
       </c>
       <c r="BA41">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="BB41" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="BC41">
-        <v>447.2</v>
+        <v>386</v>
       </c>
       <c r="BD41" t="s">
         <v>135</v>
       </c>
       <c r="BE41">
-        <v>267.2</v>
+        <v>221</v>
       </c>
       <c r="BF41" t="s">
         <v>135</v>
       </c>
       <c r="BG41">
-        <v>12.7</v>
+        <v>12.78</v>
       </c>
       <c r="BH41" t="s">
         <v>175</v>
       </c>
       <c r="BI41">
-        <v>173.5</v>
+        <v>169.9</v>
       </c>
       <c r="BJ41" t="s">
         <v>20</v>
@@ -10716,24 +10823,24 @@
         <v>135</v>
       </c>
       <c r="BO41">
-        <v>37</v>
+        <v>33.5</v>
       </c>
       <c r="BP41" t="s">
         <v>135</v>
       </c>
       <c r="BQ41">
-        <v>300</v>
+        <v>25</v>
       </c>
       <c r="BR41" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="42" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D42">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E42" t="s">
         <v>171</v>
@@ -10742,25 +10849,25 @@
         <v>6</v>
       </c>
       <c r="G42">
-        <v>13560</v>
+        <v>17323</v>
       </c>
       <c r="H42" t="s">
         <v>21</v>
       </c>
       <c r="I42">
-        <v>105</v>
+        <v>77.400000000000006</v>
       </c>
       <c r="J42" t="s">
         <v>22</v>
       </c>
       <c r="K42">
-        <v>7</v>
+        <v>11.4</v>
       </c>
       <c r="L42" t="s">
         <v>135</v>
       </c>
       <c r="M42">
-        <v>30</v>
+        <v>11.7</v>
       </c>
       <c r="N42" t="s">
         <v>171</v>
@@ -10772,139 +10879,133 @@
         <v>172</v>
       </c>
       <c r="Q42">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="R42" t="s">
         <v>135</v>
       </c>
       <c r="S42">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T42" t="s">
         <v>135</v>
       </c>
       <c r="U42">
-        <v>240</v>
+        <v>55</v>
       </c>
       <c r="V42" t="s">
         <v>173</v>
       </c>
       <c r="W42">
-        <v>160.30000000000001</v>
+        <v>185</v>
       </c>
       <c r="X42" t="s">
         <v>174</v>
       </c>
       <c r="Y42">
-        <v>154.5</v>
+        <v>173</v>
       </c>
       <c r="Z42" t="s">
         <v>174</v>
       </c>
-      <c r="AA42">
-        <v>19.04</v>
-      </c>
       <c r="AB42" t="s">
         <v>174</v>
       </c>
       <c r="AC42">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="AD42" t="s">
-        <v>19</v>
+        <v>171</v>
       </c>
       <c r="AE42">
-        <v>308.3</v>
+        <v>364</v>
       </c>
       <c r="AF42" t="s">
         <v>135</v>
       </c>
       <c r="AG42">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="AH42" t="s">
         <v>135</v>
       </c>
       <c r="AI42">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AJ42" t="s">
         <v>135</v>
       </c>
       <c r="AK42">
-        <v>12.9</v>
+        <v>13.12</v>
       </c>
       <c r="AL42" t="s">
         <v>175</v>
       </c>
       <c r="AM42">
-        <v>3.31</v>
+        <v>3.12</v>
       </c>
       <c r="AN42" t="s">
         <v>174</v>
-      </c>
-      <c r="AO42">
-        <v>3.11</v>
       </c>
       <c r="AP42" t="s">
         <v>176</v>
       </c>
       <c r="AQ42">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AR42" t="s">
         <v>135</v>
       </c>
       <c r="AS42">
-        <v>2388</v>
+        <v>2980</v>
       </c>
       <c r="AT42" t="s">
         <v>177</v>
       </c>
       <c r="AU42">
-        <v>176.1</v>
+        <v>172.1</v>
       </c>
       <c r="AV42" t="s">
         <v>20</v>
       </c>
       <c r="AW42">
-        <v>151.9</v>
+        <v>185</v>
       </c>
       <c r="AX42" t="s">
         <v>174</v>
       </c>
       <c r="AY42">
-        <v>142.9</v>
+        <v>173</v>
       </c>
       <c r="AZ42" t="s">
         <v>174</v>
       </c>
       <c r="BA42">
-        <v>2.96</v>
+        <v>3.12</v>
       </c>
       <c r="BB42" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="BC42">
-        <v>450</v>
+        <v>405</v>
       </c>
       <c r="BD42" t="s">
         <v>135</v>
       </c>
       <c r="BE42">
-        <v>259.39999999999998</v>
+        <v>232</v>
       </c>
       <c r="BF42" t="s">
         <v>135</v>
       </c>
       <c r="BG42">
-        <v>12.9</v>
+        <v>13.12</v>
       </c>
       <c r="BH42" t="s">
         <v>175</v>
       </c>
       <c r="BI42">
-        <v>175.6</v>
+        <v>172.1</v>
       </c>
       <c r="BJ42" t="s">
         <v>20</v>
@@ -10922,51 +11023,51 @@
         <v>135</v>
       </c>
       <c r="BO42">
-        <v>37</v>
+        <v>33.5</v>
       </c>
       <c r="BP42" t="s">
         <v>135</v>
       </c>
       <c r="BQ42">
-        <v>300</v>
+        <v>25</v>
       </c>
       <c r="BR42" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="43" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="D43">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c r="E43" t="s">
         <v>171</v>
       </c>
       <c r="F43">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G43">
-        <v>14916</v>
+        <v>3937</v>
       </c>
       <c r="H43" t="s">
         <v>21</v>
       </c>
       <c r="I43">
-        <v>108.4</v>
+        <v>47.2</v>
       </c>
       <c r="J43" t="s">
         <v>22</v>
       </c>
       <c r="K43">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="L43" t="s">
         <v>135</v>
       </c>
       <c r="M43">
-        <v>30</v>
+        <v>13.6</v>
       </c>
       <c r="N43" t="s">
         <v>171</v>
@@ -10978,139 +11079,133 @@
         <v>172</v>
       </c>
       <c r="Q43">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="R43" t="s">
         <v>135</v>
       </c>
       <c r="S43">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="T43" t="s">
         <v>135</v>
       </c>
       <c r="U43">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="V43" t="s">
         <v>173</v>
       </c>
       <c r="W43">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="X43" t="s">
         <v>174</v>
       </c>
       <c r="Y43">
-        <v>161.69999999999999</v>
+        <v>76</v>
       </c>
       <c r="Z43" t="s">
         <v>174</v>
       </c>
-      <c r="AA43">
-        <v>20.29</v>
-      </c>
       <c r="AB43" t="s">
         <v>174</v>
       </c>
       <c r="AC43">
-        <v>105.2</v>
+        <v>43</v>
       </c>
       <c r="AD43" t="s">
-        <v>19</v>
+        <v>171</v>
       </c>
       <c r="AE43">
-        <v>340.8</v>
+        <v>174</v>
       </c>
       <c r="AF43" t="s">
         <v>135</v>
       </c>
       <c r="AG43">
-        <v>450</v>
+        <v>211</v>
       </c>
       <c r="AH43" t="s">
         <v>135</v>
       </c>
       <c r="AI43">
-        <v>250</v>
+        <v>171</v>
       </c>
       <c r="AJ43" t="s">
         <v>135</v>
       </c>
       <c r="AK43">
-        <v>13.6</v>
+        <v>5.7590000000000003</v>
       </c>
       <c r="AL43" t="s">
         <v>175</v>
       </c>
       <c r="AM43">
-        <v>3.61</v>
+        <v>0.38</v>
       </c>
       <c r="AN43" t="s">
         <v>174</v>
-      </c>
-      <c r="AO43">
-        <v>3.31</v>
       </c>
       <c r="AP43" t="s">
         <v>176</v>
       </c>
       <c r="AQ43">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="AR43" t="s">
         <v>135</v>
       </c>
       <c r="AS43">
-        <v>2652</v>
+        <v>676</v>
       </c>
       <c r="AT43" t="s">
         <v>177</v>
       </c>
       <c r="AU43">
-        <v>177.8</v>
+        <v>173.7</v>
       </c>
       <c r="AV43" t="s">
         <v>20</v>
       </c>
       <c r="AW43">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="AX43" t="s">
         <v>174</v>
       </c>
       <c r="AY43">
-        <v>148.80000000000001</v>
+        <v>76</v>
       </c>
       <c r="AZ43" t="s">
         <v>174</v>
       </c>
       <c r="BA43">
-        <v>3.22</v>
+        <v>0.38</v>
       </c>
       <c r="BB43" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="BC43">
-        <v>485.5</v>
+        <v>211</v>
       </c>
       <c r="BD43" t="s">
         <v>135</v>
       </c>
       <c r="BE43">
-        <v>284.60000000000002</v>
+        <v>171</v>
       </c>
       <c r="BF43" t="s">
         <v>135</v>
       </c>
       <c r="BG43">
-        <v>13.5</v>
+        <v>5.7590000000000003</v>
       </c>
       <c r="BH43" t="s">
         <v>175</v>
       </c>
       <c r="BI43">
-        <v>177.2</v>
+        <v>173.7</v>
       </c>
       <c r="BJ43" t="s">
         <v>20</v>
@@ -11128,51 +11223,51 @@
         <v>135</v>
       </c>
       <c r="BO43">
-        <v>39.9</v>
+        <v>33.5</v>
       </c>
       <c r="BP43" t="s">
         <v>135</v>
       </c>
       <c r="BQ43">
-        <v>355</v>
+        <v>25</v>
       </c>
       <c r="BR43" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="44" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D44">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E44" t="s">
         <v>171</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44">
-        <v>3937</v>
+        <v>7874</v>
       </c>
       <c r="H44" t="s">
         <v>21</v>
       </c>
       <c r="I44">
-        <v>47.2</v>
+        <v>59.5</v>
       </c>
       <c r="J44" t="s">
         <v>22</v>
       </c>
       <c r="K44">
-        <v>8.1</v>
+        <v>9.9</v>
       </c>
       <c r="L44" t="s">
         <v>135</v>
       </c>
       <c r="M44">
-        <v>13.6</v>
+        <v>11.9</v>
       </c>
       <c r="N44" t="s">
         <v>171</v>
@@ -11184,31 +11279,31 @@
         <v>172</v>
       </c>
       <c r="Q44">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="R44" t="s">
         <v>135</v>
       </c>
       <c r="S44">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="T44" t="s">
         <v>135</v>
       </c>
       <c r="U44">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="V44" t="s">
         <v>173</v>
       </c>
       <c r="W44">
-        <v>116</v>
+        <v>159</v>
       </c>
       <c r="X44" t="s">
         <v>174</v>
       </c>
       <c r="Y44">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="Z44" t="s">
         <v>174</v>
@@ -11217,37 +11312,37 @@
         <v>174</v>
       </c>
       <c r="AC44">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="AD44" t="s">
         <v>171</v>
       </c>
       <c r="AE44">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="AF44" t="s">
         <v>135</v>
       </c>
       <c r="AG44">
-        <v>211</v>
+        <v>278</v>
       </c>
       <c r="AH44" t="s">
         <v>135</v>
       </c>
       <c r="AI44">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="AJ44" t="s">
         <v>135</v>
       </c>
       <c r="AK44">
-        <v>5.7590000000000003</v>
+        <v>9.2200000000000006</v>
       </c>
       <c r="AL44" t="s">
         <v>175</v>
       </c>
       <c r="AM44">
-        <v>0.38</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="AN44" t="s">
         <v>174</v>
@@ -11256,61 +11351,61 @@
         <v>176</v>
       </c>
       <c r="AQ44">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AR44" t="s">
         <v>135</v>
       </c>
       <c r="AS44">
-        <v>676</v>
+        <v>1292</v>
       </c>
       <c r="AT44" t="s">
         <v>177</v>
       </c>
       <c r="AU44">
-        <v>173.7</v>
+        <v>165.4</v>
       </c>
       <c r="AV44" t="s">
         <v>20</v>
       </c>
       <c r="AW44">
-        <v>116</v>
+        <v>159</v>
       </c>
       <c r="AX44" t="s">
         <v>174</v>
       </c>
       <c r="AY44">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="AZ44" t="s">
         <v>174</v>
       </c>
       <c r="BA44">
-        <v>0.38</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="BB44" t="s">
         <v>174</v>
       </c>
       <c r="BC44">
-        <v>211</v>
+        <v>278</v>
       </c>
       <c r="BD44" t="s">
         <v>135</v>
       </c>
       <c r="BE44">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="BF44" t="s">
         <v>135</v>
       </c>
       <c r="BG44">
-        <v>5.7590000000000003</v>
+        <v>9.2200000000000006</v>
       </c>
       <c r="BH44" t="s">
         <v>175</v>
       </c>
       <c r="BI44">
-        <v>173.7</v>
+        <v>165.4</v>
       </c>
       <c r="BJ44" t="s">
         <v>20</v>
@@ -11340,45 +11435,45 @@
         <v>173</v>
       </c>
     </row>
-    <row r="45" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D45">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E45" t="s">
         <v>171</v>
       </c>
       <c r="F45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G45">
-        <v>7874</v>
+        <v>11811</v>
       </c>
       <c r="H45" t="s">
         <v>21</v>
       </c>
       <c r="I45">
-        <v>59.5</v>
+        <v>68.099999999999994</v>
       </c>
       <c r="J45" t="s">
         <v>22</v>
       </c>
       <c r="K45">
-        <v>9.9</v>
+        <v>10.4</v>
       </c>
       <c r="L45" t="s">
         <v>135</v>
       </c>
       <c r="M45">
-        <v>11.9</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="N45" t="s">
         <v>171</v>
       </c>
       <c r="O45">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="P45" t="s">
         <v>172</v>
@@ -11390,25 +11485,25 @@
         <v>135</v>
       </c>
       <c r="S45">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="T45" t="s">
         <v>135</v>
       </c>
       <c r="U45">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="V45" t="s">
         <v>173</v>
       </c>
       <c r="W45">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="X45" t="s">
         <v>174</v>
       </c>
       <c r="Y45">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="Z45" t="s">
         <v>174</v>
@@ -11417,19 +11512,19 @@
         <v>174</v>
       </c>
       <c r="AC45">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="AD45" t="s">
         <v>171</v>
       </c>
       <c r="AE45">
-        <v>242</v>
+        <v>285</v>
       </c>
       <c r="AF45" t="s">
         <v>135</v>
       </c>
       <c r="AG45">
-        <v>278</v>
+        <v>317</v>
       </c>
       <c r="AH45" t="s">
         <v>135</v>
@@ -11441,13 +11536,13 @@
         <v>135</v>
       </c>
       <c r="AK45">
-        <v>9.2200000000000006</v>
+        <v>11.48</v>
       </c>
       <c r="AL45" t="s">
         <v>175</v>
       </c>
       <c r="AM45">
-        <v>1.1499999999999999</v>
+        <v>2.12</v>
       </c>
       <c r="AN45" t="s">
         <v>174</v>
@@ -11462,37 +11557,37 @@
         <v>135</v>
       </c>
       <c r="AS45">
-        <v>1292</v>
+        <v>1932</v>
       </c>
       <c r="AT45" t="s">
         <v>177</v>
       </c>
       <c r="AU45">
-        <v>165.4</v>
+        <v>164.5</v>
       </c>
       <c r="AV45" t="s">
         <v>20</v>
       </c>
       <c r="AW45">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="AX45" t="s">
         <v>174</v>
       </c>
       <c r="AY45">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="AZ45" t="s">
         <v>174</v>
       </c>
       <c r="BA45">
-        <v>1.1499999999999999</v>
+        <v>2.12</v>
       </c>
       <c r="BB45" t="s">
         <v>174</v>
       </c>
       <c r="BC45">
-        <v>278</v>
+        <v>317</v>
       </c>
       <c r="BD45" t="s">
         <v>135</v>
@@ -11504,13 +11599,13 @@
         <v>135</v>
       </c>
       <c r="BG45">
-        <v>9.2200000000000006</v>
+        <v>11.48</v>
       </c>
       <c r="BH45" t="s">
         <v>175</v>
       </c>
       <c r="BI45">
-        <v>165.4</v>
+        <v>164.5</v>
       </c>
       <c r="BJ45" t="s">
         <v>20</v>
@@ -11540,45 +11635,45 @@
         <v>173</v>
       </c>
     </row>
-    <row r="46" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D46">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E46" t="s">
         <v>171</v>
       </c>
       <c r="F46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G46">
-        <v>11811</v>
+        <v>15748</v>
       </c>
       <c r="H46" t="s">
         <v>21</v>
       </c>
       <c r="I46">
-        <v>68.099999999999994</v>
+        <v>75</v>
       </c>
       <c r="J46" t="s">
         <v>22</v>
       </c>
       <c r="K46">
+        <v>11.2</v>
+      </c>
+      <c r="L46" t="s">
+        <v>135</v>
+      </c>
+      <c r="M46">
         <v>10.4</v>
-      </c>
-      <c r="L46" t="s">
-        <v>135</v>
-      </c>
-      <c r="M46">
-        <v>10.199999999999999</v>
       </c>
       <c r="N46" t="s">
         <v>171</v>
       </c>
       <c r="O46">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="P46" t="s">
         <v>172</v>
@@ -11590,25 +11685,25 @@
         <v>135</v>
       </c>
       <c r="S46">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="T46" t="s">
         <v>135</v>
       </c>
       <c r="U46">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="V46" t="s">
         <v>173</v>
       </c>
       <c r="W46">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="X46" t="s">
         <v>174</v>
       </c>
       <c r="Y46">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="Z46" t="s">
         <v>174</v>
@@ -11617,37 +11712,37 @@
         <v>174</v>
       </c>
       <c r="AC46">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="AD46" t="s">
         <v>171</v>
       </c>
       <c r="AE46">
-        <v>285</v>
+        <v>340</v>
       </c>
       <c r="AF46" t="s">
         <v>135</v>
       </c>
       <c r="AG46">
-        <v>317</v>
+        <v>380</v>
       </c>
       <c r="AH46" t="s">
         <v>135</v>
       </c>
       <c r="AI46">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="AJ46" t="s">
         <v>135</v>
       </c>
       <c r="AK46">
-        <v>11.48</v>
+        <v>12.7</v>
       </c>
       <c r="AL46" t="s">
         <v>175</v>
       </c>
       <c r="AM46">
-        <v>2.12</v>
+        <v>2.79</v>
       </c>
       <c r="AN46" t="s">
         <v>174</v>
@@ -11662,55 +11757,55 @@
         <v>135</v>
       </c>
       <c r="AS46">
-        <v>1932</v>
+        <v>2664</v>
       </c>
       <c r="AT46" t="s">
         <v>177</v>
       </c>
       <c r="AU46">
-        <v>164.5</v>
+        <v>169.9</v>
       </c>
       <c r="AV46" t="s">
         <v>20</v>
       </c>
       <c r="AW46">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AX46" t="s">
         <v>174</v>
       </c>
       <c r="AY46">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="AZ46" t="s">
         <v>174</v>
       </c>
       <c r="BA46">
-        <v>2.12</v>
+        <v>2.79</v>
       </c>
       <c r="BB46" t="s">
         <v>174</v>
       </c>
       <c r="BC46">
-        <v>317</v>
+        <v>380</v>
       </c>
       <c r="BD46" t="s">
         <v>135</v>
       </c>
       <c r="BE46">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="BF46" t="s">
         <v>135</v>
       </c>
       <c r="BG46">
-        <v>11.48</v>
+        <v>12.7</v>
       </c>
       <c r="BH46" t="s">
         <v>175</v>
       </c>
       <c r="BI46">
-        <v>164.5</v>
+        <v>169.9</v>
       </c>
       <c r="BJ46" t="s">
         <v>20</v>
@@ -11740,9 +11835,9 @@
         <v>173</v>
       </c>
     </row>
-    <row r="47" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D47">
         <v>100</v>
@@ -11751,7 +11846,7 @@
         <v>171</v>
       </c>
       <c r="F47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G47">
         <v>15748</v>
@@ -11766,13 +11861,13 @@
         <v>22</v>
       </c>
       <c r="K47">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="L47" t="s">
         <v>135</v>
       </c>
       <c r="M47">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="N47" t="s">
         <v>171</v>
@@ -11790,13 +11885,13 @@
         <v>135</v>
       </c>
       <c r="S47">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T47" t="s">
         <v>135</v>
       </c>
       <c r="U47">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="V47" t="s">
         <v>173</v>
@@ -11823,31 +11918,31 @@
         <v>171</v>
       </c>
       <c r="AE47">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="AF47" t="s">
         <v>135</v>
       </c>
       <c r="AG47">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="AH47" t="s">
         <v>135</v>
       </c>
       <c r="AI47">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AJ47" t="s">
         <v>135</v>
       </c>
       <c r="AK47">
-        <v>12.7</v>
+        <v>12.78</v>
       </c>
       <c r="AL47" t="s">
         <v>175</v>
       </c>
       <c r="AM47">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="AN47" t="s">
         <v>174</v>
@@ -11886,25 +11981,25 @@
         <v>174</v>
       </c>
       <c r="BA47">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="BB47" t="s">
         <v>174</v>
       </c>
       <c r="BC47">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="BD47" t="s">
         <v>135</v>
       </c>
       <c r="BE47">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="BF47" t="s">
         <v>135</v>
       </c>
       <c r="BG47">
-        <v>12.7</v>
+        <v>12.78</v>
       </c>
       <c r="BH47" t="s">
         <v>175</v>
@@ -11940,27 +12035,27 @@
         <v>173</v>
       </c>
     </row>
-    <row r="48" spans="2:70" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D48">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E48" t="s">
         <v>171</v>
       </c>
       <c r="F48">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G48">
-        <v>15748</v>
+        <v>17323</v>
       </c>
       <c r="H48" t="s">
         <v>21</v>
       </c>
       <c r="I48">
-        <v>75</v>
+        <v>77.400000000000006</v>
       </c>
       <c r="J48" t="s">
         <v>22</v>
@@ -11972,7 +12067,7 @@
         <v>135</v>
       </c>
       <c r="M48">
-        <v>10.6</v>
+        <v>11.7</v>
       </c>
       <c r="N48" t="s">
         <v>171</v>
@@ -11990,25 +12085,25 @@
         <v>135</v>
       </c>
       <c r="S48">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="T48" t="s">
         <v>135</v>
       </c>
       <c r="U48">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="V48" t="s">
         <v>173</v>
       </c>
       <c r="W48">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="X48" t="s">
         <v>174</v>
       </c>
       <c r="Y48">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="Z48" t="s">
         <v>174</v>
@@ -12017,37 +12112,37 @@
         <v>174</v>
       </c>
       <c r="AC48">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="AD48" t="s">
         <v>171</v>
       </c>
       <c r="AE48">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="AF48" t="s">
         <v>135</v>
       </c>
       <c r="AG48">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="AH48" t="s">
         <v>135</v>
       </c>
       <c r="AI48">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="AJ48" t="s">
         <v>135</v>
       </c>
       <c r="AK48">
-        <v>12.78</v>
+        <v>13.12</v>
       </c>
       <c r="AL48" t="s">
         <v>175</v>
       </c>
       <c r="AM48">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="AN48" t="s">
         <v>174</v>
@@ -12062,55 +12157,55 @@
         <v>135</v>
       </c>
       <c r="AS48">
-        <v>2664</v>
+        <v>2980</v>
       </c>
       <c r="AT48" t="s">
         <v>177</v>
       </c>
       <c r="AU48">
-        <v>169.9</v>
+        <v>172.1</v>
       </c>
       <c r="AV48" t="s">
         <v>20</v>
       </c>
       <c r="AW48">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="AX48" t="s">
         <v>174</v>
       </c>
       <c r="AY48">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="AZ48" t="s">
         <v>174</v>
       </c>
       <c r="BA48">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="BB48" t="s">
         <v>174</v>
       </c>
       <c r="BC48">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="BD48" t="s">
         <v>135</v>
       </c>
       <c r="BE48">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="BF48" t="s">
         <v>135</v>
       </c>
       <c r="BG48">
-        <v>12.78</v>
+        <v>13.12</v>
       </c>
       <c r="BH48" t="s">
         <v>175</v>
       </c>
       <c r="BI48">
-        <v>169.9</v>
+        <v>172.1</v>
       </c>
       <c r="BJ48" t="s">
         <v>20</v>
@@ -12140,75 +12235,75 @@
         <v>173</v>
       </c>
     </row>
-    <row r="49" spans="2:70" x14ac:dyDescent="0.35">
-      <c r="B49" t="s">
-        <v>200</v>
+    <row r="49" spans="2:70" x14ac:dyDescent="0.3">
+      <c r="B49" s="3" t="s">
+        <v>214</v>
       </c>
       <c r="D49">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c r="E49" t="s">
         <v>171</v>
       </c>
       <c r="F49">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G49">
-        <v>17323</v>
+        <v>2420</v>
       </c>
       <c r="H49" t="s">
         <v>21</v>
       </c>
       <c r="I49">
-        <v>77.400000000000006</v>
+        <v>56.1</v>
       </c>
       <c r="J49" t="s">
         <v>22</v>
       </c>
       <c r="K49">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="L49" t="s">
         <v>135</v>
       </c>
       <c r="M49">
-        <v>11.7</v>
+        <v>72.400000000000006</v>
       </c>
       <c r="N49" t="s">
         <v>171</v>
       </c>
       <c r="O49">
-        <v>1021</v>
+        <v>1002</v>
       </c>
       <c r="P49" t="s">
         <v>172</v>
       </c>
       <c r="Q49">
-        <v>42</v>
+        <v>15.2</v>
       </c>
       <c r="R49" t="s">
         <v>135</v>
       </c>
       <c r="S49">
-        <v>43</v>
+        <v>35.9</v>
       </c>
       <c r="T49" t="s">
         <v>135</v>
       </c>
       <c r="U49">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="V49" t="s">
         <v>173</v>
       </c>
       <c r="W49">
-        <v>185</v>
+        <v>104.8</v>
       </c>
       <c r="X49" t="s">
         <v>174</v>
       </c>
       <c r="Y49">
-        <v>173</v>
+        <v>68.2</v>
       </c>
       <c r="Z49" t="s">
         <v>174</v>
@@ -12217,100 +12312,103 @@
         <v>174</v>
       </c>
       <c r="AC49">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="AD49" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
       <c r="AE49">
-        <v>364</v>
+        <v>219</v>
       </c>
       <c r="AF49" t="s">
         <v>135</v>
       </c>
       <c r="AG49">
-        <v>405</v>
+        <v>212</v>
       </c>
       <c r="AH49" t="s">
         <v>135</v>
       </c>
       <c r="AI49">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="AJ49" t="s">
         <v>135</v>
       </c>
       <c r="AK49">
-        <v>13.12</v>
+        <v>6.9</v>
       </c>
       <c r="AL49" t="s">
         <v>175</v>
       </c>
       <c r="AM49">
-        <v>3.12</v>
+        <v>0.44</v>
       </c>
       <c r="AN49" t="s">
         <v>174</v>
       </c>
+      <c r="AO49">
+        <v>0.38</v>
+      </c>
       <c r="AP49" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="AQ49">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="AR49" t="s">
         <v>135</v>
       </c>
       <c r="AS49">
-        <v>2980</v>
+        <v>443.3</v>
       </c>
       <c r="AT49" t="s">
         <v>177</v>
       </c>
       <c r="AU49">
-        <v>172.1</v>
+        <v>183.2</v>
       </c>
       <c r="AV49" t="s">
         <v>20</v>
       </c>
       <c r="AW49">
-        <v>185</v>
+        <v>102.5</v>
       </c>
       <c r="AX49" t="s">
         <v>174</v>
       </c>
       <c r="AY49">
-        <v>173</v>
+        <v>66.2</v>
       </c>
       <c r="AZ49" t="s">
         <v>174</v>
       </c>
       <c r="BA49">
-        <v>3.12</v>
+        <v>0.43</v>
       </c>
       <c r="BB49" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="BC49">
-        <v>405</v>
+        <v>217</v>
       </c>
       <c r="BD49" t="s">
         <v>135</v>
       </c>
       <c r="BE49">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="BF49" t="s">
         <v>135</v>
       </c>
       <c r="BG49">
-        <v>13.12</v>
+        <v>6.79</v>
       </c>
       <c r="BH49" t="s">
         <v>175</v>
       </c>
       <c r="BI49">
-        <v>172.1</v>
+        <v>181</v>
       </c>
       <c r="BJ49" t="s">
         <v>20</v>
@@ -12328,87 +12426,84 @@
         <v>135</v>
       </c>
       <c r="BO49">
-        <v>33.5</v>
+        <v>25</v>
       </c>
       <c r="BP49" t="s">
         <v>135</v>
-      </c>
-      <c r="BQ49">
-        <v>25</v>
       </c>
       <c r="BR49" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="50" spans="2:70" x14ac:dyDescent="0.35">
-      <c r="B50" t="s">
-        <v>203</v>
+    <row r="50" spans="2:70" x14ac:dyDescent="0.3">
+      <c r="B50" s="3" t="s">
+        <v>214</v>
       </c>
       <c r="D50">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E50" t="s">
         <v>171</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G50">
-        <v>3937</v>
+        <v>4843</v>
       </c>
       <c r="H50" t="s">
         <v>21</v>
       </c>
       <c r="I50">
-        <v>47.2</v>
+        <v>70.599999999999994</v>
       </c>
       <c r="J50" t="s">
         <v>22</v>
       </c>
       <c r="K50">
-        <v>8.1</v>
+        <v>6.5</v>
       </c>
       <c r="L50" t="s">
         <v>135</v>
       </c>
       <c r="M50">
-        <v>13.6</v>
+        <v>73</v>
       </c>
       <c r="N50" t="s">
         <v>171</v>
       </c>
       <c r="O50">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="P50" t="s">
         <v>172</v>
       </c>
       <c r="Q50">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="R50" t="s">
         <v>135</v>
       </c>
       <c r="S50">
-        <v>28</v>
+        <v>29.1</v>
       </c>
       <c r="T50" t="s">
         <v>135</v>
       </c>
       <c r="U50">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="V50" t="s">
         <v>173</v>
       </c>
       <c r="W50">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="X50" t="s">
         <v>174</v>
       </c>
       <c r="Y50">
-        <v>76</v>
+        <v>110.8</v>
       </c>
       <c r="Z50" t="s">
         <v>174</v>
@@ -12417,100 +12512,103 @@
         <v>174</v>
       </c>
       <c r="AC50">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="AD50" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
       <c r="AE50">
-        <v>174</v>
+        <v>240</v>
       </c>
       <c r="AF50" t="s">
         <v>135</v>
       </c>
       <c r="AG50">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="AH50" t="s">
         <v>135</v>
       </c>
       <c r="AI50">
-        <v>171</v>
+        <v>212</v>
       </c>
       <c r="AJ50" t="s">
         <v>135</v>
       </c>
       <c r="AK50">
-        <v>5.7590000000000003</v>
+        <v>10.3</v>
       </c>
       <c r="AL50" t="s">
         <v>175</v>
       </c>
       <c r="AM50">
-        <v>0.38</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="AN50" t="s">
         <v>174</v>
       </c>
+      <c r="AO50">
+        <v>1.06</v>
+      </c>
       <c r="AP50" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="AQ50">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="AR50" t="s">
         <v>135</v>
       </c>
       <c r="AS50">
-        <v>676</v>
+        <v>832.5</v>
       </c>
       <c r="AT50" t="s">
         <v>177</v>
       </c>
       <c r="AU50">
-        <v>173.7</v>
+        <v>171.9</v>
       </c>
       <c r="AV50" t="s">
         <v>20</v>
       </c>
       <c r="AW50">
-        <v>116</v>
+        <v>135.4</v>
       </c>
       <c r="AX50" t="s">
         <v>174</v>
       </c>
       <c r="AY50">
-        <v>76</v>
+        <v>105.9</v>
       </c>
       <c r="AZ50" t="s">
         <v>174</v>
       </c>
       <c r="BA50">
-        <v>0.38</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="BB50" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="BC50">
-        <v>211</v>
+        <v>311</v>
       </c>
       <c r="BD50" t="s">
         <v>135</v>
       </c>
       <c r="BE50">
-        <v>171</v>
+        <v>220</v>
       </c>
       <c r="BF50" t="s">
         <v>135</v>
       </c>
       <c r="BG50">
-        <v>5.7590000000000003</v>
+        <v>10.039999999999999</v>
       </c>
       <c r="BH50" t="s">
         <v>175</v>
       </c>
       <c r="BI50">
-        <v>173.7</v>
+        <v>170.1</v>
       </c>
       <c r="BJ50" t="s">
         <v>20</v>
@@ -12528,87 +12626,84 @@
         <v>135</v>
       </c>
       <c r="BO50">
-        <v>33.5</v>
+        <v>25</v>
       </c>
       <c r="BP50" t="s">
         <v>135</v>
-      </c>
-      <c r="BQ50">
-        <v>25</v>
       </c>
       <c r="BR50" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="51" spans="2:70" x14ac:dyDescent="0.35">
-      <c r="B51" t="s">
-        <v>203</v>
+    <row r="51" spans="2:70" x14ac:dyDescent="0.3">
+      <c r="B51" s="3" t="s">
+        <v>214</v>
       </c>
       <c r="D51">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E51" t="s">
         <v>171</v>
       </c>
       <c r="F51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G51">
-        <v>7874</v>
+        <v>6289</v>
       </c>
       <c r="H51" t="s">
         <v>21</v>
       </c>
       <c r="I51">
-        <v>59.5</v>
+        <v>77.099999999999994</v>
       </c>
       <c r="J51" t="s">
         <v>22</v>
       </c>
       <c r="K51">
-        <v>9.9</v>
+        <v>7</v>
       </c>
       <c r="L51" t="s">
         <v>135</v>
       </c>
       <c r="M51">
-        <v>11.9</v>
+        <v>67.8</v>
       </c>
       <c r="N51" t="s">
         <v>171</v>
       </c>
       <c r="O51">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="P51" t="s">
         <v>172</v>
       </c>
       <c r="Q51">
-        <v>42</v>
+        <v>10.3</v>
       </c>
       <c r="R51" t="s">
         <v>135</v>
       </c>
       <c r="S51">
-        <v>32</v>
+        <v>30.5</v>
       </c>
       <c r="T51" t="s">
         <v>135</v>
       </c>
       <c r="U51">
-        <v>33</v>
+        <v>160</v>
       </c>
       <c r="V51" t="s">
         <v>173</v>
       </c>
       <c r="W51">
-        <v>159</v>
+        <v>156.5</v>
       </c>
       <c r="X51" t="s">
         <v>174</v>
       </c>
       <c r="Y51">
-        <v>119</v>
+        <v>130.80000000000001</v>
       </c>
       <c r="Z51" t="s">
         <v>174</v>
@@ -12617,100 +12712,103 @@
         <v>174</v>
       </c>
       <c r="AC51">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="AD51" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
       <c r="AE51">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="AF51" t="s">
         <v>135</v>
       </c>
       <c r="AG51">
-        <v>278</v>
+        <v>322</v>
       </c>
       <c r="AH51" t="s">
         <v>135</v>
       </c>
       <c r="AI51">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="AJ51" t="s">
         <v>135</v>
       </c>
       <c r="AK51">
-        <v>9.2200000000000006</v>
+        <v>12.1</v>
       </c>
       <c r="AL51" t="s">
         <v>175</v>
       </c>
       <c r="AM51">
-        <v>1.1499999999999999</v>
+        <v>1.74</v>
       </c>
       <c r="AN51" t="s">
         <v>174</v>
       </c>
+      <c r="AO51">
+        <v>1.66</v>
+      </c>
       <c r="AP51" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="AQ51">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="AR51" t="s">
         <v>135</v>
       </c>
       <c r="AS51">
-        <v>1292</v>
+        <v>1062.8</v>
       </c>
       <c r="AT51" t="s">
         <v>177</v>
       </c>
       <c r="AU51">
-        <v>165.4</v>
+        <v>169</v>
       </c>
       <c r="AV51" t="s">
         <v>20</v>
       </c>
       <c r="AW51">
-        <v>159</v>
+        <v>151.4</v>
       </c>
       <c r="AX51" t="s">
         <v>174</v>
       </c>
       <c r="AY51">
-        <v>119</v>
+        <v>125.1</v>
       </c>
       <c r="AZ51" t="s">
         <v>174</v>
       </c>
       <c r="BA51">
-        <v>1.1499999999999999</v>
+        <v>1.68</v>
       </c>
       <c r="BB51" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="BC51">
-        <v>278</v>
+        <v>329</v>
       </c>
       <c r="BD51" t="s">
         <v>135</v>
       </c>
       <c r="BE51">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="BF51" t="s">
         <v>135</v>
       </c>
       <c r="BG51">
-        <v>9.2200000000000006</v>
+        <v>11.8</v>
       </c>
       <c r="BH51" t="s">
         <v>175</v>
       </c>
       <c r="BI51">
-        <v>165.4</v>
+        <v>167.2</v>
       </c>
       <c r="BJ51" t="s">
         <v>20</v>
@@ -12728,87 +12826,84 @@
         <v>135</v>
       </c>
       <c r="BO51">
-        <v>33.5</v>
+        <v>25</v>
       </c>
       <c r="BP51" t="s">
         <v>135</v>
-      </c>
-      <c r="BQ51">
-        <v>25</v>
       </c>
       <c r="BR51" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="52" spans="2:70" x14ac:dyDescent="0.35">
-      <c r="B52" t="s">
-        <v>203</v>
+    <row r="52" spans="2:70" x14ac:dyDescent="0.3">
+      <c r="B52" s="3" t="s">
+        <v>214</v>
       </c>
       <c r="D52">
-        <v>75</v>
+        <v>75.599999999999994</v>
       </c>
       <c r="E52" t="s">
         <v>171</v>
       </c>
       <c r="F52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G52">
-        <v>11811</v>
+        <v>7312</v>
       </c>
       <c r="H52" t="s">
         <v>21</v>
       </c>
       <c r="I52">
-        <v>68.099999999999994</v>
+        <v>81.099999999999994</v>
       </c>
       <c r="J52" t="s">
         <v>22</v>
       </c>
       <c r="K52">
-        <v>10.4</v>
+        <v>8</v>
       </c>
       <c r="L52" t="s">
         <v>135</v>
       </c>
       <c r="M52">
-        <v>10.199999999999999</v>
+        <v>68.400000000000006</v>
       </c>
       <c r="N52" t="s">
         <v>171</v>
       </c>
       <c r="O52">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="P52" t="s">
         <v>172</v>
       </c>
       <c r="Q52">
-        <v>42</v>
+        <v>11.6</v>
       </c>
       <c r="R52" t="s">
         <v>135</v>
       </c>
       <c r="S52">
-        <v>36</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="T52" t="s">
         <v>135</v>
       </c>
       <c r="U52">
-        <v>43</v>
+        <v>203</v>
       </c>
       <c r="V52" t="s">
         <v>173</v>
       </c>
       <c r="W52">
-        <v>175</v>
+        <v>167.2</v>
       </c>
       <c r="X52" t="s">
         <v>174</v>
       </c>
       <c r="Y52">
-        <v>135</v>
+        <v>136.69999999999999</v>
       </c>
       <c r="Z52" t="s">
         <v>174</v>
@@ -12817,100 +12912,103 @@
         <v>174</v>
       </c>
       <c r="AC52">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD52" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
       <c r="AE52">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="AF52" t="s">
         <v>135</v>
       </c>
       <c r="AG52">
-        <v>317</v>
+        <v>342</v>
       </c>
       <c r="AH52" t="s">
         <v>135</v>
       </c>
       <c r="AI52">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AJ52" t="s">
         <v>135</v>
       </c>
       <c r="AK52">
-        <v>11.48</v>
+        <v>13</v>
       </c>
       <c r="AL52" t="s">
         <v>175</v>
       </c>
       <c r="AM52">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AN52" t="s">
         <v>174</v>
       </c>
+      <c r="AO52">
+        <v>2.06</v>
+      </c>
       <c r="AP52" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="AQ52">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AR52" t="s">
         <v>135</v>
       </c>
       <c r="AS52">
-        <v>1932</v>
+        <v>1226.9000000000001</v>
       </c>
       <c r="AT52" t="s">
         <v>177</v>
       </c>
       <c r="AU52">
-        <v>164.5</v>
+        <v>167.8</v>
       </c>
       <c r="AV52" t="s">
         <v>20</v>
       </c>
       <c r="AW52">
-        <v>175</v>
+        <v>162.30000000000001</v>
       </c>
       <c r="AX52" t="s">
         <v>174</v>
       </c>
       <c r="AY52">
-        <v>135</v>
+        <v>131.30000000000001</v>
       </c>
       <c r="AZ52" t="s">
         <v>174</v>
       </c>
       <c r="BA52">
-        <v>2.12</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="BB52" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="BC52">
-        <v>317</v>
+        <v>349</v>
       </c>
       <c r="BD52" t="s">
         <v>135</v>
       </c>
       <c r="BE52">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="BF52" t="s">
         <v>135</v>
       </c>
       <c r="BG52">
-        <v>11.48</v>
+        <v>12.7</v>
       </c>
       <c r="BH52" t="s">
         <v>175</v>
       </c>
       <c r="BI52">
-        <v>164.5</v>
+        <v>166</v>
       </c>
       <c r="BJ52" t="s">
         <v>20</v>
@@ -12928,87 +13026,84 @@
         <v>135</v>
       </c>
       <c r="BO52">
-        <v>33.5</v>
+        <v>25</v>
       </c>
       <c r="BP52" t="s">
         <v>135</v>
-      </c>
-      <c r="BQ52">
-        <v>25</v>
       </c>
       <c r="BR52" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="53" spans="2:70" x14ac:dyDescent="0.35">
-      <c r="B53" t="s">
-        <v>203</v>
+    <row r="53" spans="2:70" x14ac:dyDescent="0.3">
+      <c r="B53" s="3" t="s">
+        <v>214</v>
       </c>
       <c r="D53">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E53" t="s">
         <v>171</v>
       </c>
       <c r="F53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G53">
-        <v>15748</v>
+        <v>8227</v>
       </c>
       <c r="H53" t="s">
         <v>21</v>
       </c>
       <c r="I53">
-        <v>75</v>
+        <v>84.3</v>
       </c>
       <c r="J53" t="s">
         <v>22</v>
       </c>
       <c r="K53">
-        <v>11.2</v>
+        <v>10.5</v>
       </c>
       <c r="L53" t="s">
         <v>135</v>
       </c>
       <c r="M53">
-        <v>10.4</v>
+        <v>49.6</v>
       </c>
       <c r="N53" t="s">
         <v>171</v>
       </c>
       <c r="O53">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="P53" t="s">
         <v>172</v>
       </c>
       <c r="Q53">
-        <v>42</v>
+        <v>12.8</v>
       </c>
       <c r="R53" t="s">
         <v>135</v>
       </c>
       <c r="S53">
-        <v>40</v>
+        <v>35.6</v>
       </c>
       <c r="T53" t="s">
         <v>135</v>
       </c>
       <c r="U53">
-        <v>50</v>
+        <v>255</v>
       </c>
       <c r="V53" t="s">
         <v>173</v>
       </c>
       <c r="W53">
-        <v>176</v>
+        <v>169.2</v>
       </c>
       <c r="X53" t="s">
         <v>174</v>
       </c>
       <c r="Y53">
-        <v>150</v>
+        <v>147.80000000000001</v>
       </c>
       <c r="Z53" t="s">
         <v>174</v>
@@ -13017,100 +13112,103 @@
         <v>174</v>
       </c>
       <c r="AC53">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AD53" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
       <c r="AE53">
-        <v>340</v>
+        <v>293</v>
       </c>
       <c r="AF53" t="s">
         <v>135</v>
       </c>
       <c r="AG53">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="AH53" t="s">
         <v>135</v>
       </c>
       <c r="AI53">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="AJ53" t="s">
         <v>135</v>
       </c>
       <c r="AK53">
-        <v>12.7</v>
+        <v>13.75</v>
       </c>
       <c r="AL53" t="s">
         <v>175</v>
       </c>
       <c r="AM53">
-        <v>2.79</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="AN53" t="s">
         <v>174</v>
       </c>
+      <c r="AO53">
+        <v>2.39</v>
+      </c>
       <c r="AP53" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="AQ53">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="AR53" t="s">
         <v>135</v>
       </c>
       <c r="AS53">
-        <v>2664</v>
+        <v>1395.3</v>
       </c>
       <c r="AT53" t="s">
         <v>177</v>
       </c>
       <c r="AU53">
-        <v>169.9</v>
+        <v>169.6</v>
       </c>
       <c r="AV53" t="s">
         <v>20</v>
       </c>
       <c r="AW53">
-        <v>176</v>
+        <v>164.7</v>
       </c>
       <c r="AX53" t="s">
         <v>174</v>
       </c>
       <c r="AY53">
-        <v>150</v>
+        <v>142.5</v>
       </c>
       <c r="AZ53" t="s">
         <v>174</v>
       </c>
       <c r="BA53">
-        <v>2.79</v>
+        <v>2.4</v>
       </c>
       <c r="BB53" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="BC53">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="BD53" t="s">
         <v>135</v>
       </c>
       <c r="BE53">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="BF53" t="s">
         <v>135</v>
       </c>
       <c r="BG53">
-        <v>12.7</v>
+        <v>13.47</v>
       </c>
       <c r="BH53" t="s">
         <v>175</v>
       </c>
       <c r="BI53">
-        <v>169.9</v>
+        <v>167.8</v>
       </c>
       <c r="BJ53" t="s">
         <v>20</v>
@@ -13128,21 +13226,18 @@
         <v>135</v>
       </c>
       <c r="BO53">
-        <v>33.5</v>
+        <v>25</v>
       </c>
       <c r="BP53" t="s">
         <v>135</v>
-      </c>
-      <c r="BQ53">
-        <v>25</v>
       </c>
       <c r="BR53" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="54" spans="2:70" x14ac:dyDescent="0.35">
-      <c r="B54" t="s">
-        <v>203</v>
+    <row r="54" spans="2:70" x14ac:dyDescent="0.3">
+      <c r="B54" s="3" t="s">
+        <v>214</v>
       </c>
       <c r="D54">
         <v>100</v>
@@ -13151,64 +13246,64 @@
         <v>171</v>
       </c>
       <c r="F54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G54">
-        <v>15748</v>
+        <v>9671</v>
       </c>
       <c r="H54" t="s">
         <v>21</v>
       </c>
       <c r="I54">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="J54" t="s">
         <v>22</v>
       </c>
       <c r="K54">
-        <v>11.4</v>
+        <v>9</v>
       </c>
       <c r="L54" t="s">
         <v>135</v>
       </c>
       <c r="M54">
-        <v>10.6</v>
+        <v>69.599999999999994</v>
       </c>
       <c r="N54" t="s">
         <v>171</v>
       </c>
       <c r="O54">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="P54" t="s">
         <v>172</v>
       </c>
       <c r="Q54">
-        <v>42</v>
+        <v>13.7</v>
       </c>
       <c r="R54" t="s">
         <v>135</v>
       </c>
       <c r="S54">
-        <v>41</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="T54" t="s">
         <v>135</v>
       </c>
       <c r="U54">
-        <v>53</v>
+        <v>335</v>
       </c>
       <c r="V54" t="s">
         <v>173</v>
       </c>
       <c r="W54">
-        <v>176</v>
+        <v>170.3</v>
       </c>
       <c r="X54" t="s">
         <v>174</v>
       </c>
       <c r="Y54">
-        <v>150</v>
+        <v>153.80000000000001</v>
       </c>
       <c r="Z54" t="s">
         <v>174</v>
@@ -13220,97 +13315,100 @@
         <v>100</v>
       </c>
       <c r="AD54" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
       <c r="AE54">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="AF54" t="s">
         <v>135</v>
       </c>
       <c r="AG54">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="AH54" t="s">
         <v>135</v>
       </c>
       <c r="AI54">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AJ54" t="s">
         <v>135</v>
       </c>
       <c r="AK54">
-        <v>12.78</v>
+        <v>14.7</v>
       </c>
       <c r="AL54" t="s">
         <v>175</v>
       </c>
       <c r="AM54">
-        <v>2.88</v>
+        <v>3.01</v>
       </c>
       <c r="AN54" t="s">
         <v>174</v>
       </c>
+      <c r="AO54">
+        <v>2.92</v>
+      </c>
       <c r="AP54" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="AQ54">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="AR54" t="s">
         <v>135</v>
       </c>
       <c r="AS54">
-        <v>2664</v>
+        <v>1658.6</v>
       </c>
       <c r="AT54" t="s">
         <v>177</v>
       </c>
       <c r="AU54">
-        <v>169.9</v>
+        <v>171.5</v>
       </c>
       <c r="AV54" t="s">
         <v>20</v>
       </c>
       <c r="AW54">
-        <v>176</v>
+        <v>166.1</v>
       </c>
       <c r="AX54" t="s">
         <v>174</v>
       </c>
       <c r="AY54">
-        <v>150</v>
+        <v>148.69999999999999</v>
       </c>
       <c r="AZ54" t="s">
         <v>174</v>
       </c>
       <c r="BA54">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="BB54" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="BC54">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="BD54" t="s">
         <v>135</v>
       </c>
       <c r="BE54">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="BF54" t="s">
         <v>135</v>
       </c>
       <c r="BG54">
-        <v>12.78</v>
+        <v>14.42</v>
       </c>
       <c r="BH54" t="s">
         <v>175</v>
       </c>
       <c r="BI54">
-        <v>169.9</v>
+        <v>169.6</v>
       </c>
       <c r="BJ54" t="s">
         <v>20</v>
@@ -13328,215 +13426,12 @@
         <v>135</v>
       </c>
       <c r="BO54">
-        <v>33.5</v>
+        <v>25</v>
       </c>
       <c r="BP54" t="s">
         <v>135</v>
       </c>
-      <c r="BQ54">
-        <v>25</v>
-      </c>
       <c r="BR54" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="55" spans="2:70" x14ac:dyDescent="0.35">
-      <c r="B55" t="s">
-        <v>203</v>
-      </c>
-      <c r="D55">
-        <v>110</v>
-      </c>
-      <c r="E55" t="s">
-        <v>171</v>
-      </c>
-      <c r="F55">
-        <v>6</v>
-      </c>
-      <c r="G55">
-        <v>17323</v>
-      </c>
-      <c r="H55" t="s">
-        <v>21</v>
-      </c>
-      <c r="I55">
-        <v>77.400000000000006</v>
-      </c>
-      <c r="J55" t="s">
-        <v>22</v>
-      </c>
-      <c r="K55">
-        <v>11.4</v>
-      </c>
-      <c r="L55" t="s">
-        <v>135</v>
-      </c>
-      <c r="M55">
-        <v>11.7</v>
-      </c>
-      <c r="N55" t="s">
-        <v>171</v>
-      </c>
-      <c r="O55">
-        <v>1021</v>
-      </c>
-      <c r="P55" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q55">
-        <v>42</v>
-      </c>
-      <c r="R55" t="s">
-        <v>135</v>
-      </c>
-      <c r="S55">
-        <v>43</v>
-      </c>
-      <c r="T55" t="s">
-        <v>135</v>
-      </c>
-      <c r="U55">
-        <v>55</v>
-      </c>
-      <c r="V55" t="s">
-        <v>173</v>
-      </c>
-      <c r="W55">
-        <v>185</v>
-      </c>
-      <c r="X55" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y55">
-        <v>173</v>
-      </c>
-      <c r="Z55" t="s">
-        <v>174</v>
-      </c>
-      <c r="AB55" t="s">
-        <v>174</v>
-      </c>
-      <c r="AC55">
-        <v>106</v>
-      </c>
-      <c r="AD55" t="s">
-        <v>171</v>
-      </c>
-      <c r="AE55">
-        <v>364</v>
-      </c>
-      <c r="AF55" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG55">
-        <v>405</v>
-      </c>
-      <c r="AH55" t="s">
-        <v>135</v>
-      </c>
-      <c r="AI55">
-        <v>232</v>
-      </c>
-      <c r="AJ55" t="s">
-        <v>135</v>
-      </c>
-      <c r="AK55">
-        <v>13.12</v>
-      </c>
-      <c r="AL55" t="s">
-        <v>175</v>
-      </c>
-      <c r="AM55">
-        <v>3.12</v>
-      </c>
-      <c r="AN55" t="s">
-        <v>174</v>
-      </c>
-      <c r="AP55" t="s">
-        <v>176</v>
-      </c>
-      <c r="AQ55">
-        <v>42</v>
-      </c>
-      <c r="AR55" t="s">
-        <v>135</v>
-      </c>
-      <c r="AS55">
-        <v>2980</v>
-      </c>
-      <c r="AT55" t="s">
-        <v>177</v>
-      </c>
-      <c r="AU55">
-        <v>172.1</v>
-      </c>
-      <c r="AV55" t="s">
-        <v>20</v>
-      </c>
-      <c r="AW55">
-        <v>185</v>
-      </c>
-      <c r="AX55" t="s">
-        <v>174</v>
-      </c>
-      <c r="AY55">
-        <v>173</v>
-      </c>
-      <c r="AZ55" t="s">
-        <v>174</v>
-      </c>
-      <c r="BA55">
-        <v>3.12</v>
-      </c>
-      <c r="BB55" t="s">
-        <v>174</v>
-      </c>
-      <c r="BC55">
-        <v>405</v>
-      </c>
-      <c r="BD55" t="s">
-        <v>135</v>
-      </c>
-      <c r="BE55">
-        <v>232</v>
-      </c>
-      <c r="BF55" t="s">
-        <v>135</v>
-      </c>
-      <c r="BG55">
-        <v>13.12</v>
-      </c>
-      <c r="BH55" t="s">
-        <v>175</v>
-      </c>
-      <c r="BI55">
-        <v>172.1</v>
-      </c>
-      <c r="BJ55" t="s">
-        <v>20</v>
-      </c>
-      <c r="BK55">
-        <v>1000</v>
-      </c>
-      <c r="BL55" t="s">
-        <v>172</v>
-      </c>
-      <c r="BM55">
-        <v>25</v>
-      </c>
-      <c r="BN55" t="s">
-        <v>135</v>
-      </c>
-      <c r="BO55">
-        <v>33.5</v>
-      </c>
-      <c r="BP55" t="s">
-        <v>135</v>
-      </c>
-      <c r="BQ55">
-        <v>25</v>
-      </c>
-      <c r="BR55" t="s">
         <v>173</v>
       </c>
     </row>
@@ -13552,55 +13447,54 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AT1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.54296875" customWidth="1"/>
-    <col min="2" max="2" width="26.26953125" customWidth="1"/>
-    <col min="3" max="3" width="26.1796875" customWidth="1"/>
-    <col min="4" max="4" width="24.26953125" customWidth="1"/>
+    <col min="1" max="1" width="15.5546875" customWidth="1"/>
+    <col min="2" max="3" width="26.21875" customWidth="1"/>
+    <col min="4" max="4" width="24.21875" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="19.1796875" customWidth="1"/>
-    <col min="7" max="7" width="22.26953125" customWidth="1"/>
-    <col min="8" max="8" width="33.81640625" customWidth="1"/>
-    <col min="9" max="9" width="14.81640625" customWidth="1"/>
-    <col min="10" max="10" width="14.54296875" customWidth="1"/>
-    <col min="11" max="11" width="16.26953125" customWidth="1"/>
-    <col min="12" max="12" width="18.54296875" customWidth="1"/>
-    <col min="13" max="13" width="15.81640625" customWidth="1"/>
-    <col min="14" max="14" width="28.81640625" customWidth="1"/>
-    <col min="15" max="15" width="21.453125" customWidth="1"/>
-    <col min="16" max="16" width="17.81640625" customWidth="1"/>
-    <col min="18" max="18" width="9.453125" customWidth="1"/>
+    <col min="6" max="6" width="19.21875" customWidth="1"/>
+    <col min="7" max="7" width="22.21875" customWidth="1"/>
+    <col min="8" max="8" width="33.77734375" customWidth="1"/>
+    <col min="9" max="9" width="14.77734375" customWidth="1"/>
+    <col min="10" max="10" width="14.5546875" customWidth="1"/>
+    <col min="11" max="11" width="16.21875" customWidth="1"/>
+    <col min="12" max="12" width="18.5546875" customWidth="1"/>
+    <col min="13" max="13" width="15.77734375" customWidth="1"/>
+    <col min="14" max="14" width="28.77734375" customWidth="1"/>
+    <col min="15" max="15" width="21.44140625" customWidth="1"/>
+    <col min="16" max="16" width="17.77734375" customWidth="1"/>
+    <col min="18" max="18" width="9.44140625" customWidth="1"/>
     <col min="19" max="19" width="11" customWidth="1"/>
-    <col min="20" max="20" width="18.81640625" customWidth="1"/>
+    <col min="20" max="20" width="18.77734375" customWidth="1"/>
     <col min="21" max="21" width="18" customWidth="1"/>
     <col min="22" max="22" width="28" customWidth="1"/>
-    <col min="23" max="23" width="13.1796875" customWidth="1"/>
-    <col min="24" max="24" width="11.54296875" customWidth="1"/>
-    <col min="25" max="25" width="10.26953125" customWidth="1"/>
-    <col min="27" max="27" width="10.54296875" customWidth="1"/>
-    <col min="28" max="28" width="29.26953125" customWidth="1"/>
-    <col min="29" max="29" width="19.81640625" customWidth="1"/>
-    <col min="30" max="30" width="22.54296875" customWidth="1"/>
-    <col min="31" max="31" width="15.7265625" customWidth="1"/>
-    <col min="32" max="32" width="15.453125" customWidth="1"/>
-    <col min="33" max="33" width="20.26953125" customWidth="1"/>
-    <col min="34" max="34" width="14.1796875" customWidth="1"/>
-    <col min="35" max="35" width="12.26953125" customWidth="1"/>
-    <col min="36" max="36" width="13.26953125" customWidth="1"/>
-    <col min="37" max="37" width="25.26953125" customWidth="1"/>
-    <col min="38" max="38" width="26.26953125" customWidth="1"/>
-    <col min="39" max="39" width="15.1796875" customWidth="1"/>
-    <col min="40" max="40" width="22.54296875" customWidth="1"/>
-    <col min="41" max="41" width="15.54296875" customWidth="1"/>
-    <col min="42" max="42" width="12.81640625" customWidth="1"/>
-    <col min="43" max="43" width="13.54296875" customWidth="1"/>
-    <col min="44" max="44" width="15.26953125" customWidth="1"/>
-    <col min="45" max="45" width="12.54296875" customWidth="1"/>
-    <col min="46" max="46" width="13.26953125" customWidth="1"/>
+    <col min="23" max="23" width="13.21875" customWidth="1"/>
+    <col min="24" max="24" width="11.5546875" customWidth="1"/>
+    <col min="25" max="25" width="10.21875" customWidth="1"/>
+    <col min="27" max="27" width="10.5546875" customWidth="1"/>
+    <col min="28" max="28" width="29.21875" customWidth="1"/>
+    <col min="29" max="29" width="19.77734375" customWidth="1"/>
+    <col min="30" max="30" width="22.5546875" customWidth="1"/>
+    <col min="31" max="31" width="15.77734375" customWidth="1"/>
+    <col min="32" max="32" width="15.44140625" customWidth="1"/>
+    <col min="33" max="33" width="20.21875" customWidth="1"/>
+    <col min="34" max="34" width="14.21875" customWidth="1"/>
+    <col min="35" max="35" width="12.21875" customWidth="1"/>
+    <col min="36" max="36" width="13.21875" customWidth="1"/>
+    <col min="37" max="37" width="25.21875" customWidth="1"/>
+    <col min="38" max="38" width="26.21875" customWidth="1"/>
+    <col min="39" max="39" width="15.21875" customWidth="1"/>
+    <col min="40" max="40" width="22.5546875" customWidth="1"/>
+    <col min="41" max="41" width="15.5546875" customWidth="1"/>
+    <col min="42" max="42" width="12.77734375" customWidth="1"/>
+    <col min="43" max="43" width="13.5546875" customWidth="1"/>
+    <col min="44" max="44" width="15.21875" customWidth="1"/>
+    <col min="45" max="45" width="12.5546875" customWidth="1"/>
+    <col min="46" max="46" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>75</v>
       </c>
@@ -13751,9 +13645,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>118</v>
       </c>

--- a/Aepms-backend/data/Engine_Performance_Data.xlsx
+++ b/Aepms-backend/data/Engine_Performance_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GOKUL\Desktop\Ozellar_project\Aepms-backend\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GOKUL\Desktop\WORKPLACE\Workplace\Aepms-backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FA3AE40-7B43-445A-97BE-D9C2196EEDBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1ED77D-5904-4AE2-A294-C4F5C92A510E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="vessel_info" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2153" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2920" uniqueCount="247">
   <si>
     <t>hull_no</t>
   </si>
@@ -692,14 +692,109 @@
   </si>
   <si>
     <t>mcr_limit</t>
+  </si>
+  <si>
+    <t>SE5S50-0063</t>
+  </si>
+  <si>
+    <t>AMNS POLAR</t>
+  </si>
+  <si>
+    <t>SF080102</t>
+  </si>
+  <si>
+    <t>PZM</t>
+  </si>
+  <si>
+    <t>SANFU</t>
+  </si>
+  <si>
+    <t>MAN B&amp;W</t>
+  </si>
+  <si>
+    <t>kg/cm2</t>
+  </si>
+  <si>
+    <t>GCL SARASWATI</t>
+  </si>
+  <si>
+    <t>Messrs. NYK Line</t>
+  </si>
+  <si>
+    <t>Oshima Shipbuilding Co., Ltd.</t>
+  </si>
+  <si>
+    <t>Mitsubishi Heavy Industries, Ltd.</t>
+  </si>
+  <si>
+    <t>Mitsubishi 6UEC60LS II</t>
+  </si>
+  <si>
+    <t>6UEC60LS II (IMO-Nox Tier I)</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>GCL FOS</t>
+  </si>
+  <si>
+    <t>6S70MC-C</t>
+  </si>
+  <si>
+    <t>MITSUI ENGINEERING &amp; SHIPBUILDING CO., LTD.</t>
+  </si>
+  <si>
+    <t>MESSRS. KOTOBUKI KAIUN CO., LTD.</t>
+  </si>
+  <si>
+    <t>AMNSI STALLION</t>
+  </si>
+  <si>
+    <t>BC8.2-2</t>
+  </si>
+  <si>
+    <t>Qingdao Beihai Shipbuilding Heavy Industry C</t>
+  </si>
+  <si>
+    <t>Hebei Ocean Shipping Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>5RT-flex58T-D</t>
+  </si>
+  <si>
+    <t>DALIAN MARINE DIESEL CO.,LTD (DMD-WÄRTSILÄ)</t>
+  </si>
+  <si>
+    <t>AMNS TUFMAX</t>
+  </si>
+  <si>
+    <t>SF080103</t>
+  </si>
+  <si>
+    <t>Taizhou Sanfu Ship Engineering</t>
+  </si>
+  <si>
+    <t>5S50MC-C</t>
+  </si>
+  <si>
+    <t>STX Dalian Engine Co.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -733,13 +828,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -784,8 +882,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table3" displayName="Table3" ref="A1:BT1048569" totalsRowShown="0">
-  <autoFilter ref="A1:BT1048569" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table3" displayName="Table3" ref="A1:BT1048576" totalsRowShown="0">
+  <autoFilter ref="A1:BT1048576" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="72">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="performance_data_id (PK)"/>
     <tableColumn id="73" xr3:uid="{00000000-0010-0000-0200-000049000000}" name="engine_no (UNIQUE, NOT NULL)"/>
@@ -1216,7 +1314,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB9"/>
+  <dimension ref="A1:AB18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.77734375" customWidth="1"/>
@@ -1224,10 +1322,11 @@
     <col min="3" max="3" width="25.44140625" customWidth="1"/>
     <col min="4" max="4" width="31.21875" customWidth="1"/>
     <col min="5" max="5" width="16.88671875" customWidth="1"/>
-    <col min="7" max="7" width="22.21875" customWidth="1"/>
-    <col min="8" max="8" width="15.77734375" customWidth="1"/>
-    <col min="9" max="9" width="14.21875" customWidth="1"/>
-    <col min="10" max="10" width="20.21875" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="27.33203125" customWidth="1"/>
+    <col min="9" max="9" width="19.88671875" customWidth="1"/>
+    <col min="10" max="10" width="24.5546875" customWidth="1"/>
     <col min="11" max="11" width="22" customWidth="1"/>
     <col min="12" max="12" width="21.21875" customWidth="1"/>
     <col min="13" max="13" width="23" customWidth="1"/>
@@ -1915,6 +2014,333 @@
       </c>
       <c r="Z9" t="s">
         <v>171</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>219</v>
+      </c>
+      <c r="C10">
+        <v>9521813</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F10" t="s">
+        <v>221</v>
+      </c>
+      <c r="G10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H10" t="s">
+        <v>246</v>
+      </c>
+      <c r="I10" t="s">
+        <v>245</v>
+      </c>
+      <c r="J10" t="s">
+        <v>218</v>
+      </c>
+      <c r="K10">
+        <v>5</v>
+      </c>
+      <c r="M10" t="s">
+        <v>19</v>
+      </c>
+      <c r="N10">
+        <v>168.37</v>
+      </c>
+      <c r="O10" t="s">
+        <v>20</v>
+      </c>
+      <c r="P10">
+        <v>6570</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>21</v>
+      </c>
+      <c r="R10">
+        <v>127</v>
+      </c>
+      <c r="S10" t="s">
+        <v>22</v>
+      </c>
+      <c r="T10">
+        <v>5585</v>
+      </c>
+      <c r="Y10">
+        <v>100</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="D11" s="3"/>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="D12" s="3"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>236</v>
+      </c>
+      <c r="C13">
+        <v>9628910</v>
+      </c>
+      <c r="D13">
+        <v>774</v>
+      </c>
+      <c r="E13" t="s">
+        <v>237</v>
+      </c>
+      <c r="F13" t="s">
+        <v>239</v>
+      </c>
+      <c r="G13" t="s">
+        <v>238</v>
+      </c>
+      <c r="H13" t="s">
+        <v>241</v>
+      </c>
+      <c r="I13" t="s">
+        <v>240</v>
+      </c>
+      <c r="J13" t="s">
+        <v>240</v>
+      </c>
+      <c r="K13">
+        <v>5</v>
+      </c>
+      <c r="M13" t="s">
+        <v>19</v>
+      </c>
+      <c r="N13" t="s">
+        <v>231</v>
+      </c>
+      <c r="O13" t="s">
+        <v>20</v>
+      </c>
+      <c r="P13">
+        <v>9760</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>21</v>
+      </c>
+      <c r="R13">
+        <v>92.9</v>
+      </c>
+      <c r="S13" t="s">
+        <v>22</v>
+      </c>
+      <c r="T13" t="s">
+        <v>231</v>
+      </c>
+      <c r="U13" t="s">
+        <v>231</v>
+      </c>
+      <c r="V13" t="s">
+        <v>231</v>
+      </c>
+      <c r="W13" t="s">
+        <v>231</v>
+      </c>
+      <c r="X13" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>231</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>242</v>
+      </c>
+      <c r="C14">
+        <v>9486295</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="G14" t="s">
+        <v>244</v>
+      </c>
+      <c r="H14" t="s">
+        <v>223</v>
+      </c>
+      <c r="I14" t="s">
+        <v>245</v>
+      </c>
+      <c r="J14" t="s">
+        <v>245</v>
+      </c>
+      <c r="K14">
+        <v>5</v>
+      </c>
+      <c r="M14" t="s">
+        <v>19</v>
+      </c>
+      <c r="N14">
+        <v>164.6</v>
+      </c>
+      <c r="O14" t="s">
+        <v>20</v>
+      </c>
+      <c r="P14">
+        <v>6570</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R14">
+        <v>127</v>
+      </c>
+      <c r="S14" t="s">
+        <v>22</v>
+      </c>
+      <c r="T14">
+        <v>5510</v>
+      </c>
+      <c r="U14">
+        <v>56</v>
+      </c>
+      <c r="V14">
+        <v>73</v>
+      </c>
+      <c r="W14" t="s">
+        <v>231</v>
+      </c>
+      <c r="X14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>231</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="D15" s="3"/>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="D16" s="3"/>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>225</v>
+      </c>
+      <c r="C17">
+        <v>9644500</v>
+      </c>
+      <c r="D17" s="2">
+        <v>4078</v>
+      </c>
+      <c r="E17" s="2">
+        <v>10701</v>
+      </c>
+      <c r="F17" t="s">
+        <v>226</v>
+      </c>
+      <c r="G17" t="s">
+        <v>227</v>
+      </c>
+      <c r="H17" t="s">
+        <v>228</v>
+      </c>
+      <c r="I17" t="s">
+        <v>229</v>
+      </c>
+      <c r="J17" t="s">
+        <v>230</v>
+      </c>
+      <c r="K17">
+        <v>6</v>
+      </c>
+      <c r="M17" t="s">
+        <v>19</v>
+      </c>
+      <c r="N17">
+        <v>166.6</v>
+      </c>
+      <c r="O17" t="s">
+        <v>20</v>
+      </c>
+      <c r="P17" s="4">
+        <v>12270</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>21</v>
+      </c>
+      <c r="R17">
+        <v>105</v>
+      </c>
+      <c r="S17" t="s">
+        <v>22</v>
+      </c>
+      <c r="T17" s="4">
+        <v>10436</v>
+      </c>
+    </row>
+    <row r="18" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>232</v>
+      </c>
+      <c r="C18">
+        <v>9532082</v>
+      </c>
+      <c r="D18">
+        <v>5933</v>
+      </c>
+      <c r="F18" t="s">
+        <v>235</v>
+      </c>
+      <c r="G18" t="s">
+        <v>234</v>
+      </c>
+      <c r="H18" t="s">
+        <v>210</v>
+      </c>
+      <c r="I18" t="s">
+        <v>233</v>
+      </c>
+      <c r="J18" t="s">
+        <v>233</v>
+      </c>
+      <c r="K18">
+        <v>6</v>
+      </c>
+      <c r="N18">
+        <v>163.69999999999999</v>
+      </c>
+      <c r="O18" t="s">
+        <v>20</v>
+      </c>
+      <c r="P18">
+        <v>16860</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>21</v>
+      </c>
+      <c r="R18">
+        <v>91</v>
+      </c>
+      <c r="S18" t="s">
+        <v>22</v>
+      </c>
+      <c r="T18">
+        <v>14330</v>
       </c>
     </row>
   </sheetData>
@@ -2332,7 +2758,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:BT54"/>
+  <dimension ref="A1:BT73"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="26.21875" customWidth="1"/>
@@ -13435,6 +13861,3435 @@
         <v>173</v>
       </c>
     </row>
+    <row r="55" spans="2:70" x14ac:dyDescent="0.3">
+      <c r="B55" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D55">
+        <v>25</v>
+      </c>
+      <c r="E55" t="s">
+        <v>171</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55">
+        <v>1643</v>
+      </c>
+      <c r="H55" t="s">
+        <v>21</v>
+      </c>
+      <c r="I55">
+        <v>80</v>
+      </c>
+      <c r="J55" t="s">
+        <v>22</v>
+      </c>
+      <c r="K55">
+        <v>14</v>
+      </c>
+      <c r="L55" t="s">
+        <v>135</v>
+      </c>
+      <c r="M55">
+        <v>24</v>
+      </c>
+      <c r="N55" t="s">
+        <v>171</v>
+      </c>
+      <c r="O55">
+        <v>1023</v>
+      </c>
+      <c r="P55" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q55">
+        <v>17</v>
+      </c>
+      <c r="R55" t="s">
+        <v>135</v>
+      </c>
+      <c r="S55">
+        <v>35</v>
+      </c>
+      <c r="T55" t="s">
+        <v>135</v>
+      </c>
+      <c r="U55">
+        <v>40</v>
+      </c>
+      <c r="V55" t="s">
+        <v>173</v>
+      </c>
+      <c r="W55">
+        <v>75</v>
+      </c>
+      <c r="X55" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y55">
+        <v>52</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA55">
+        <v>6.28</v>
+      </c>
+      <c r="AB55" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC55">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="AD55" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE55">
+        <v>251</v>
+      </c>
+      <c r="AF55" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG55">
+        <v>295</v>
+      </c>
+      <c r="AH55" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI55">
+        <v>235</v>
+      </c>
+      <c r="AJ55" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK55">
+        <v>7</v>
+      </c>
+      <c r="AL55" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM55">
+        <v>0.35</v>
+      </c>
+      <c r="AN55" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO55">
+        <v>0.25</v>
+      </c>
+      <c r="AP55" t="s">
+        <v>174</v>
+      </c>
+      <c r="AQ55">
+        <v>26</v>
+      </c>
+      <c r="AR55" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS55">
+        <v>300</v>
+      </c>
+      <c r="AT55" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU55">
+        <v>182.59</v>
+      </c>
+      <c r="AV55" t="s">
+        <v>20</v>
+      </c>
+      <c r="BJ55">
+        <v>183.02</v>
+      </c>
+      <c r="BK55" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="2:70" x14ac:dyDescent="0.3">
+      <c r="B56" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D56">
+        <v>50</v>
+      </c>
+      <c r="E56" t="s">
+        <v>171</v>
+      </c>
+      <c r="F56">
+        <v>2</v>
+      </c>
+      <c r="G56">
+        <v>3285</v>
+      </c>
+      <c r="H56" t="s">
+        <v>21</v>
+      </c>
+      <c r="I56">
+        <v>100.8</v>
+      </c>
+      <c r="J56" t="s">
+        <v>22</v>
+      </c>
+      <c r="K56">
+        <v>14</v>
+      </c>
+      <c r="L56" t="s">
+        <v>135</v>
+      </c>
+      <c r="M56">
+        <v>28</v>
+      </c>
+      <c r="N56" t="s">
+        <v>171</v>
+      </c>
+      <c r="O56">
+        <v>1023</v>
+      </c>
+      <c r="P56" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q56">
+        <v>17</v>
+      </c>
+      <c r="R56" t="s">
+        <v>135</v>
+      </c>
+      <c r="S56">
+        <v>30</v>
+      </c>
+      <c r="T56" t="s">
+        <v>135</v>
+      </c>
+      <c r="U56">
+        <v>90</v>
+      </c>
+      <c r="V56" t="s">
+        <v>173</v>
+      </c>
+      <c r="W56">
+        <v>105.2</v>
+      </c>
+      <c r="X56" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y56">
+        <v>78.400000000000006</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA56">
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="AB56" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC56">
+        <v>46.2</v>
+      </c>
+      <c r="AD56" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE56">
+        <v>271</v>
+      </c>
+      <c r="AF56" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG56">
+        <v>325</v>
+      </c>
+      <c r="AH56" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI56">
+        <v>235</v>
+      </c>
+      <c r="AJ56" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK56">
+        <v>12.6</v>
+      </c>
+      <c r="AL56" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM56">
+        <v>1</v>
+      </c>
+      <c r="AN56" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO56">
+        <v>0.9</v>
+      </c>
+      <c r="AP56" t="s">
+        <v>174</v>
+      </c>
+      <c r="AQ56">
+        <v>26</v>
+      </c>
+      <c r="AR56" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS56">
+        <v>552</v>
+      </c>
+      <c r="AT56" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU56">
+        <v>168.04</v>
+      </c>
+      <c r="AV56" t="s">
+        <v>20</v>
+      </c>
+      <c r="BJ56">
+        <v>168.43</v>
+      </c>
+      <c r="BK56" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" spans="2:70" x14ac:dyDescent="0.3">
+      <c r="B57" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D57">
+        <v>75</v>
+      </c>
+      <c r="E57" t="s">
+        <v>171</v>
+      </c>
+      <c r="F57">
+        <v>3</v>
+      </c>
+      <c r="G57">
+        <v>4928</v>
+      </c>
+      <c r="H57" t="s">
+        <v>21</v>
+      </c>
+      <c r="I57">
+        <v>115.4</v>
+      </c>
+      <c r="J57" t="s">
+        <v>22</v>
+      </c>
+      <c r="K57">
+        <v>16</v>
+      </c>
+      <c r="L57" t="s">
+        <v>135</v>
+      </c>
+      <c r="M57">
+        <v>34</v>
+      </c>
+      <c r="N57" t="s">
+        <v>171</v>
+      </c>
+      <c r="O57">
+        <v>1022</v>
+      </c>
+      <c r="P57" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q57">
+        <v>18</v>
+      </c>
+      <c r="R57" t="s">
+        <v>135</v>
+      </c>
+      <c r="S57">
+        <v>30</v>
+      </c>
+      <c r="T57" t="s">
+        <v>135</v>
+      </c>
+      <c r="U57">
+        <v>126</v>
+      </c>
+      <c r="V57" t="s">
+        <v>173</v>
+      </c>
+      <c r="W57">
+        <v>142.80000000000001</v>
+      </c>
+      <c r="X57" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y57">
+        <v>113.4</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA57">
+        <v>13.06</v>
+      </c>
+      <c r="AB57" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC57">
+        <v>56.4</v>
+      </c>
+      <c r="AD57" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE57">
+        <v>272</v>
+      </c>
+      <c r="AF57" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG57">
+        <v>330</v>
+      </c>
+      <c r="AH57" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI57">
+        <v>210</v>
+      </c>
+      <c r="AJ57" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK57">
+        <v>14.7</v>
+      </c>
+      <c r="AL57" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM57">
+        <v>1.75</v>
+      </c>
+      <c r="AN57" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO57">
+        <v>1.6</v>
+      </c>
+      <c r="AP57" t="s">
+        <v>174</v>
+      </c>
+      <c r="AQ57">
+        <v>26</v>
+      </c>
+      <c r="AR57" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS57">
+        <v>804</v>
+      </c>
+      <c r="AT57" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU57">
+        <v>163.15</v>
+      </c>
+      <c r="AV57" t="s">
+        <v>20</v>
+      </c>
+      <c r="BJ57">
+        <v>163.46</v>
+      </c>
+      <c r="BK57" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="2:70" x14ac:dyDescent="0.3">
+      <c r="B58" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D58">
+        <v>85</v>
+      </c>
+      <c r="E58" t="s">
+        <v>171</v>
+      </c>
+      <c r="F58">
+        <v>4</v>
+      </c>
+      <c r="G58">
+        <v>5585</v>
+      </c>
+      <c r="H58" t="s">
+        <v>21</v>
+      </c>
+      <c r="I58">
+        <v>120.3</v>
+      </c>
+      <c r="J58" t="s">
+        <v>22</v>
+      </c>
+      <c r="K58">
+        <v>17</v>
+      </c>
+      <c r="L58" t="s">
+        <v>135</v>
+      </c>
+      <c r="M58">
+        <v>32</v>
+      </c>
+      <c r="N58" t="s">
+        <v>171</v>
+      </c>
+      <c r="O58">
+        <v>1021</v>
+      </c>
+      <c r="P58" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q58">
+        <v>18</v>
+      </c>
+      <c r="R58" t="s">
+        <v>135</v>
+      </c>
+      <c r="S58">
+        <v>36</v>
+      </c>
+      <c r="T58" t="s">
+        <v>135</v>
+      </c>
+      <c r="V58" t="s">
+        <v>173</v>
+      </c>
+      <c r="W58">
+        <v>152</v>
+      </c>
+      <c r="X58" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y58">
+        <v>124</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA58">
+        <v>14.19</v>
+      </c>
+      <c r="AB58" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC58">
+        <v>60.4</v>
+      </c>
+      <c r="AD58" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE58">
+        <v>281</v>
+      </c>
+      <c r="AF58" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG58">
+        <v>345</v>
+      </c>
+      <c r="AH58" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI58">
+        <v>210</v>
+      </c>
+      <c r="AJ58" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK58">
+        <v>15.6</v>
+      </c>
+      <c r="AL58" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM58">
+        <v>2.15</v>
+      </c>
+      <c r="AN58" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO58">
+        <v>1.95</v>
+      </c>
+      <c r="AP58" t="s">
+        <v>174</v>
+      </c>
+      <c r="AQ58">
+        <v>28</v>
+      </c>
+      <c r="AR58" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS58">
+        <v>919.2</v>
+      </c>
+      <c r="AT58" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU58">
+        <v>164.58</v>
+      </c>
+      <c r="AV58" t="s">
+        <v>20</v>
+      </c>
+      <c r="BJ58">
+        <v>164.66</v>
+      </c>
+      <c r="BK58" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" spans="2:70" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="D59" s="5">
+        <v>100</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="F59" s="5">
+        <v>5</v>
+      </c>
+      <c r="G59" s="5">
+        <v>6570</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I59" s="5">
+        <v>127</v>
+      </c>
+      <c r="J59" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K59" s="5">
+        <v>17</v>
+      </c>
+      <c r="L59" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="M59" s="5">
+        <v>30</v>
+      </c>
+      <c r="N59" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="O59" s="5">
+        <v>1021</v>
+      </c>
+      <c r="P59" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q59" s="5">
+        <v>18</v>
+      </c>
+      <c r="R59" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="S59" s="5">
+        <v>36</v>
+      </c>
+      <c r="T59" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="U59" s="5">
+        <v>220</v>
+      </c>
+      <c r="V59" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="W59" s="5">
+        <v>151.80000000000001</v>
+      </c>
+      <c r="X59" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y59" s="5">
+        <v>148.19999999999999</v>
+      </c>
+      <c r="Z59" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA59" s="5">
+        <v>15.82</v>
+      </c>
+      <c r="AB59" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC59" s="5">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="AD59" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE59" s="5">
+        <v>293</v>
+      </c>
+      <c r="AF59" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG59" s="5">
+        <v>375</v>
+      </c>
+      <c r="AH59" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI59" s="5">
+        <v>220</v>
+      </c>
+      <c r="AJ59" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK59" s="5">
+        <v>17</v>
+      </c>
+      <c r="AL59" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM59" s="5">
+        <v>2.7</v>
+      </c>
+      <c r="AN59" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO59" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="AP59" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AQ59" s="5">
+        <v>28</v>
+      </c>
+      <c r="AR59" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS59" s="5">
+        <v>1107</v>
+      </c>
+      <c r="AT59" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU59" s="5">
+        <v>168.49</v>
+      </c>
+      <c r="AV59" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="BJ59" s="5">
+        <v>168.37</v>
+      </c>
+      <c r="BK59" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" spans="2:70" x14ac:dyDescent="0.3">
+      <c r="B60" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D60">
+        <v>110</v>
+      </c>
+      <c r="E60" t="s">
+        <v>171</v>
+      </c>
+      <c r="F60">
+        <v>6</v>
+      </c>
+      <c r="G60">
+        <v>7227</v>
+      </c>
+      <c r="H60" t="s">
+        <v>21</v>
+      </c>
+      <c r="I60">
+        <v>131.1</v>
+      </c>
+      <c r="J60" t="s">
+        <v>22</v>
+      </c>
+      <c r="K60">
+        <v>17</v>
+      </c>
+      <c r="L60" t="s">
+        <v>135</v>
+      </c>
+      <c r="M60">
+        <v>26</v>
+      </c>
+      <c r="N60" t="s">
+        <v>171</v>
+      </c>
+      <c r="O60">
+        <v>1021</v>
+      </c>
+      <c r="P60" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q60">
+        <v>18</v>
+      </c>
+      <c r="R60" t="s">
+        <v>135</v>
+      </c>
+      <c r="S60">
+        <v>38</v>
+      </c>
+      <c r="T60" t="s">
+        <v>135</v>
+      </c>
+      <c r="U60">
+        <v>240</v>
+      </c>
+      <c r="V60" t="s">
+        <v>173</v>
+      </c>
+      <c r="W60">
+        <v>153.80000000000001</v>
+      </c>
+      <c r="X60" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y60">
+        <v>155.80000000000001</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA60">
+        <v>16.850000000000001</v>
+      </c>
+      <c r="AB60" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC60">
+        <v>69.8</v>
+      </c>
+      <c r="AD60" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE60">
+        <v>304</v>
+      </c>
+      <c r="AF60" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG60">
+        <v>390</v>
+      </c>
+      <c r="AH60" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI60">
+        <v>220</v>
+      </c>
+      <c r="AJ60" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK60">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="AL60" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM60">
+        <v>2.85</v>
+      </c>
+      <c r="AN60" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO60">
+        <v>2.65</v>
+      </c>
+      <c r="AP60" t="s">
+        <v>174</v>
+      </c>
+      <c r="AQ60">
+        <v>29</v>
+      </c>
+      <c r="AR60" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS60">
+        <v>1236</v>
+      </c>
+      <c r="AT60" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU60">
+        <v>171.03</v>
+      </c>
+      <c r="AV60" t="s">
+        <v>20</v>
+      </c>
+      <c r="BJ60">
+        <v>170.8</v>
+      </c>
+      <c r="BK60" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" spans="2:70" x14ac:dyDescent="0.3">
+      <c r="B61" s="3"/>
+    </row>
+    <row r="62" spans="2:70" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="5">
+        <v>774</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D62" s="5">
+        <v>25</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="F62" s="5">
+        <v>1</v>
+      </c>
+      <c r="G62" s="5">
+        <v>2440</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I62" s="5">
+        <v>58</v>
+      </c>
+      <c r="J62" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K62" s="5">
+        <v>13</v>
+      </c>
+      <c r="L62" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="M62" s="5">
+        <v>64</v>
+      </c>
+      <c r="N62" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="O62" s="5">
+        <v>1028</v>
+      </c>
+      <c r="P62" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q62" s="5">
+        <v>14.2</v>
+      </c>
+      <c r="R62" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="S62" s="5">
+        <v>21</v>
+      </c>
+      <c r="T62" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="U62" s="5">
+        <v>17</v>
+      </c>
+      <c r="V62" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="W62" s="5">
+        <v>80.2</v>
+      </c>
+      <c r="X62" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y62" s="5">
+        <v>50.6</v>
+      </c>
+      <c r="Z62" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA62" s="5">
+        <v>7.91</v>
+      </c>
+      <c r="AB62" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC62" s="5">
+        <v>29.5</v>
+      </c>
+      <c r="AD62" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE62" s="5">
+        <v>257</v>
+      </c>
+      <c r="AF62" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG62" s="5">
+        <v>300</v>
+      </c>
+      <c r="AH62" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI62" s="5">
+        <v>240</v>
+      </c>
+      <c r="AJ62" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK62" s="5">
+        <v>6.35</v>
+      </c>
+      <c r="AL62" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM62" s="5">
+        <v>0.33</v>
+      </c>
+      <c r="AN62" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO62" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="AP62" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="AQ62" s="5">
+        <v>18</v>
+      </c>
+      <c r="AR62" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS62" s="5">
+        <v>434.78</v>
+      </c>
+      <c r="AT62" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU62" s="5">
+        <v>178.19</v>
+      </c>
+      <c r="AV62" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW62" s="5">
+        <v>77.5</v>
+      </c>
+      <c r="AX62" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY62" s="5">
+        <v>46.8</v>
+      </c>
+      <c r="AZ62" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA62" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="BB62" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="BC62" s="5">
+        <v>321.5</v>
+      </c>
+      <c r="BD62" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE62" s="5">
+        <v>259.2</v>
+      </c>
+      <c r="BF62" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG62" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH62" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI62" s="5">
+        <v>179.62</v>
+      </c>
+      <c r="BJ62" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK62" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BL62" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM62" s="5">
+        <v>25</v>
+      </c>
+      <c r="BN62" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO62" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="BP62" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ62" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="BR62" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="63" spans="2:70" x14ac:dyDescent="0.3">
+      <c r="B63">
+        <v>774</v>
+      </c>
+      <c r="C63" t="s">
+        <v>231</v>
+      </c>
+      <c r="D63">
+        <v>50</v>
+      </c>
+      <c r="E63" t="s">
+        <v>171</v>
+      </c>
+      <c r="F63">
+        <v>2</v>
+      </c>
+      <c r="G63">
+        <v>4880</v>
+      </c>
+      <c r="H63" t="s">
+        <v>21</v>
+      </c>
+      <c r="I63">
+        <v>74</v>
+      </c>
+      <c r="J63" t="s">
+        <v>22</v>
+      </c>
+      <c r="K63">
+        <v>14</v>
+      </c>
+      <c r="L63" t="s">
+        <v>135</v>
+      </c>
+      <c r="M63">
+        <v>65</v>
+      </c>
+      <c r="N63" t="s">
+        <v>171</v>
+      </c>
+      <c r="O63">
+        <v>1027</v>
+      </c>
+      <c r="P63" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q63">
+        <v>15</v>
+      </c>
+      <c r="R63" t="s">
+        <v>135</v>
+      </c>
+      <c r="S63">
+        <v>19</v>
+      </c>
+      <c r="T63" t="s">
+        <v>135</v>
+      </c>
+      <c r="U63">
+        <v>75</v>
+      </c>
+      <c r="V63" t="s">
+        <v>173</v>
+      </c>
+      <c r="W63">
+        <v>117.8</v>
+      </c>
+      <c r="X63" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y63">
+        <v>77.400000000000006</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA63">
+        <v>12.4</v>
+      </c>
+      <c r="AB63" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC63">
+        <v>44.4</v>
+      </c>
+      <c r="AD63" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE63">
+        <v>270</v>
+      </c>
+      <c r="AF63" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG63">
+        <v>320</v>
+      </c>
+      <c r="AH63" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI63">
+        <v>220</v>
+      </c>
+      <c r="AJ63" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK63">
+        <v>11.35</v>
+      </c>
+      <c r="AL63" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM63">
+        <v>1.18</v>
+      </c>
+      <c r="AN63" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO63" t="s">
+        <v>231</v>
+      </c>
+      <c r="AP63" t="s">
+        <v>224</v>
+      </c>
+      <c r="AQ63">
+        <v>20</v>
+      </c>
+      <c r="AR63" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS63">
+        <v>861.24</v>
+      </c>
+      <c r="AT63" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU63">
+        <v>176.48</v>
+      </c>
+      <c r="AV63" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW63">
+        <v>116.5</v>
+      </c>
+      <c r="AX63" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY63">
+        <v>75.8</v>
+      </c>
+      <c r="AZ63" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA63" t="s">
+        <v>231</v>
+      </c>
+      <c r="BB63" t="s">
+        <v>224</v>
+      </c>
+      <c r="BC63">
+        <v>347.7</v>
+      </c>
+      <c r="BD63" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE63">
+        <v>241.7</v>
+      </c>
+      <c r="BF63" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG63" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH63" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI63">
+        <v>178.08</v>
+      </c>
+      <c r="BJ63" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK63">
+        <v>1000</v>
+      </c>
+      <c r="BL63" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM63">
+        <v>25</v>
+      </c>
+      <c r="BN63" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO63" t="s">
+        <v>231</v>
+      </c>
+      <c r="BP63" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ63" t="s">
+        <v>231</v>
+      </c>
+      <c r="BR63" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="64" spans="2:70" x14ac:dyDescent="0.3">
+      <c r="B64">
+        <v>774</v>
+      </c>
+      <c r="C64" t="s">
+        <v>231</v>
+      </c>
+      <c r="D64">
+        <v>75</v>
+      </c>
+      <c r="E64" t="s">
+        <v>171</v>
+      </c>
+      <c r="F64">
+        <v>3</v>
+      </c>
+      <c r="G64">
+        <v>7320</v>
+      </c>
+      <c r="H64" t="s">
+        <v>21</v>
+      </c>
+      <c r="I64">
+        <v>84</v>
+      </c>
+      <c r="J64" t="s">
+        <v>22</v>
+      </c>
+      <c r="K64">
+        <v>12</v>
+      </c>
+      <c r="L64" t="s">
+        <v>135</v>
+      </c>
+      <c r="M64">
+        <v>62</v>
+      </c>
+      <c r="N64" t="s">
+        <v>171</v>
+      </c>
+      <c r="O64">
+        <v>1027</v>
+      </c>
+      <c r="P64" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q64">
+        <v>15.7</v>
+      </c>
+      <c r="R64" t="s">
+        <v>135</v>
+      </c>
+      <c r="S64">
+        <v>22</v>
+      </c>
+      <c r="T64" t="s">
+        <v>135</v>
+      </c>
+      <c r="U64">
+        <v>140</v>
+      </c>
+      <c r="V64" t="s">
+        <v>173</v>
+      </c>
+      <c r="W64">
+        <v>140.6</v>
+      </c>
+      <c r="X64" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y64">
+        <v>102.6</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA64">
+        <v>16.39</v>
+      </c>
+      <c r="AB64" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC64">
+        <v>57.4</v>
+      </c>
+      <c r="AD64" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE64">
+        <v>295</v>
+      </c>
+      <c r="AF64" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG64">
+        <v>355</v>
+      </c>
+      <c r="AH64" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI64">
+        <v>200</v>
+      </c>
+      <c r="AJ64" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK64">
+        <v>14.372</v>
+      </c>
+      <c r="AL64" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM64">
+        <v>2.23</v>
+      </c>
+      <c r="AN64" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO64" t="s">
+        <v>231</v>
+      </c>
+      <c r="AP64" t="s">
+        <v>224</v>
+      </c>
+      <c r="AQ64">
+        <v>21</v>
+      </c>
+      <c r="AR64" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS64">
+        <v>1228.67</v>
+      </c>
+      <c r="AT64" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU64">
+        <v>172.76</v>
+      </c>
+      <c r="AV64" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW64">
+        <v>139.5</v>
+      </c>
+      <c r="AX64" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY64">
+        <v>101.2</v>
+      </c>
+      <c r="AZ64" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA64" t="s">
+        <v>231</v>
+      </c>
+      <c r="BB64" t="s">
+        <v>224</v>
+      </c>
+      <c r="BC64">
+        <v>381.8</v>
+      </c>
+      <c r="BD64" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE64">
+        <v>220.7</v>
+      </c>
+      <c r="BF64" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG64" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH64" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI64">
+        <v>169.05</v>
+      </c>
+      <c r="BJ64" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK64">
+        <v>1000</v>
+      </c>
+      <c r="BL64" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM64">
+        <v>25</v>
+      </c>
+      <c r="BN64" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO64" t="s">
+        <v>231</v>
+      </c>
+      <c r="BP64" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ64" t="s">
+        <v>231</v>
+      </c>
+      <c r="BR64" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="65" spans="1:72" x14ac:dyDescent="0.3">
+      <c r="B65">
+        <v>774</v>
+      </c>
+      <c r="C65" t="s">
+        <v>231</v>
+      </c>
+      <c r="D65">
+        <v>85</v>
+      </c>
+      <c r="E65" t="s">
+        <v>171</v>
+      </c>
+      <c r="F65">
+        <v>4</v>
+      </c>
+      <c r="G65">
+        <v>8296</v>
+      </c>
+      <c r="H65" t="s">
+        <v>21</v>
+      </c>
+      <c r="I65">
+        <v>88</v>
+      </c>
+      <c r="J65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K65">
+        <v>12</v>
+      </c>
+      <c r="L65" t="s">
+        <v>135</v>
+      </c>
+      <c r="M65">
+        <v>62</v>
+      </c>
+      <c r="N65" t="s">
+        <v>171</v>
+      </c>
+      <c r="O65">
+        <v>1027</v>
+      </c>
+      <c r="P65" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q65">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="R65" t="s">
+        <v>135</v>
+      </c>
+      <c r="S65">
+        <v>27</v>
+      </c>
+      <c r="T65" t="s">
+        <v>135</v>
+      </c>
+      <c r="U65">
+        <v>190</v>
+      </c>
+      <c r="V65" t="s">
+        <v>173</v>
+      </c>
+      <c r="W65">
+        <v>152.19999999999999</v>
+      </c>
+      <c r="X65" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y65">
+        <v>114.6</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA65">
+        <v>17.73</v>
+      </c>
+      <c r="AB65" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC65">
+        <v>61</v>
+      </c>
+      <c r="AD65" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE65">
+        <v>310</v>
+      </c>
+      <c r="AF65" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG65">
+        <v>375</v>
+      </c>
+      <c r="AH65" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI65">
+        <v>205</v>
+      </c>
+      <c r="AJ65" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK65">
+        <v>15.108000000000001</v>
+      </c>
+      <c r="AL65" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM65">
+        <v>2.56</v>
+      </c>
+      <c r="AN65" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO65" t="s">
+        <v>231</v>
+      </c>
+      <c r="AP65" t="s">
+        <v>224</v>
+      </c>
+      <c r="AQ65">
+        <v>22</v>
+      </c>
+      <c r="AR65" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS65">
+        <v>1422.92</v>
+      </c>
+      <c r="AT65" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU65">
+        <v>171.52</v>
+      </c>
+      <c r="AV65" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW65">
+        <v>152.19999999999999</v>
+      </c>
+      <c r="AX65" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY65">
+        <v>111</v>
+      </c>
+      <c r="AZ65" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA65" t="s">
+        <v>231</v>
+      </c>
+      <c r="BB65" t="s">
+        <v>224</v>
+      </c>
+      <c r="BC65">
+        <v>397.1</v>
+      </c>
+      <c r="BD65" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE65">
+        <v>220.9</v>
+      </c>
+      <c r="BF65" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG65" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH65" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI65">
+        <v>172.2</v>
+      </c>
+      <c r="BJ65" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK65">
+        <v>1000</v>
+      </c>
+      <c r="BL65" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM65">
+        <v>25</v>
+      </c>
+      <c r="BN65" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO65" t="s">
+        <v>231</v>
+      </c>
+      <c r="BP65" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ65" t="s">
+        <v>231</v>
+      </c>
+      <c r="BR65" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="66" spans="1:72" x14ac:dyDescent="0.3">
+      <c r="B66">
+        <v>774</v>
+      </c>
+      <c r="C66" t="s">
+        <v>231</v>
+      </c>
+      <c r="D66">
+        <v>100</v>
+      </c>
+      <c r="E66" t="s">
+        <v>171</v>
+      </c>
+      <c r="F66">
+        <v>5</v>
+      </c>
+      <c r="G66">
+        <v>9760</v>
+      </c>
+      <c r="H66" t="s">
+        <v>21</v>
+      </c>
+      <c r="I66">
+        <v>93</v>
+      </c>
+      <c r="J66" t="s">
+        <v>22</v>
+      </c>
+      <c r="K66">
+        <v>12</v>
+      </c>
+      <c r="L66" t="s">
+        <v>135</v>
+      </c>
+      <c r="M66">
+        <v>62</v>
+      </c>
+      <c r="N66" t="s">
+        <v>171</v>
+      </c>
+      <c r="O66">
+        <v>1028</v>
+      </c>
+      <c r="P66" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q66">
+        <v>17</v>
+      </c>
+      <c r="R66" t="s">
+        <v>135</v>
+      </c>
+      <c r="S66">
+        <v>30</v>
+      </c>
+      <c r="T66" t="s">
+        <v>135</v>
+      </c>
+      <c r="U66">
+        <v>250</v>
+      </c>
+      <c r="V66" t="s">
+        <v>173</v>
+      </c>
+      <c r="W66">
+        <v>147.6</v>
+      </c>
+      <c r="X66" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y66">
+        <v>129.6</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA66">
+        <v>19.739999999999998</v>
+      </c>
+      <c r="AB66" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC66">
+        <v>70.5</v>
+      </c>
+      <c r="AD66" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE66">
+        <v>362</v>
+      </c>
+      <c r="AF66" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG66">
+        <v>425</v>
+      </c>
+      <c r="AH66" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI66">
+        <v>230</v>
+      </c>
+      <c r="AJ66" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK66">
+        <v>16.654</v>
+      </c>
+      <c r="AL66" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM66">
+        <v>3.28</v>
+      </c>
+      <c r="AN66" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO66" t="s">
+        <v>231</v>
+      </c>
+      <c r="AP66" t="s">
+        <v>224</v>
+      </c>
+      <c r="AQ66">
+        <v>24</v>
+      </c>
+      <c r="AR66" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS66">
+        <v>1690.14</v>
+      </c>
+      <c r="AT66" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU66">
+        <v>173.17</v>
+      </c>
+      <c r="AV66" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW66">
+        <v>147.6</v>
+      </c>
+      <c r="AX66" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY66">
+        <v>126.2</v>
+      </c>
+      <c r="AZ66" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA66" t="s">
+        <v>231</v>
+      </c>
+      <c r="BB66" t="s">
+        <v>224</v>
+      </c>
+      <c r="BC66">
+        <v>446.8</v>
+      </c>
+      <c r="BD66" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE66">
+        <v>245.6</v>
+      </c>
+      <c r="BF66" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG66" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH66" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI66">
+        <v>173.54</v>
+      </c>
+      <c r="BJ66" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK66">
+        <v>1000</v>
+      </c>
+      <c r="BL66" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM66">
+        <v>25</v>
+      </c>
+      <c r="BN66" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO66" t="s">
+        <v>231</v>
+      </c>
+      <c r="BP66" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ66" t="s">
+        <v>231</v>
+      </c>
+      <c r="BR66" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="67" spans="1:72" x14ac:dyDescent="0.3">
+      <c r="B67">
+        <v>774</v>
+      </c>
+      <c r="C67" t="s">
+        <v>231</v>
+      </c>
+      <c r="D67">
+        <v>110</v>
+      </c>
+      <c r="E67" t="s">
+        <v>171</v>
+      </c>
+      <c r="F67">
+        <v>6</v>
+      </c>
+      <c r="G67">
+        <v>10736</v>
+      </c>
+      <c r="H67" t="s">
+        <v>21</v>
+      </c>
+      <c r="I67">
+        <v>96</v>
+      </c>
+      <c r="J67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K67">
+        <v>13</v>
+      </c>
+      <c r="L67" t="s">
+        <v>135</v>
+      </c>
+      <c r="M67">
+        <v>62</v>
+      </c>
+      <c r="N67" t="s">
+        <v>171</v>
+      </c>
+      <c r="O67">
+        <v>1027</v>
+      </c>
+      <c r="P67" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q67">
+        <v>18</v>
+      </c>
+      <c r="R67" t="s">
+        <v>135</v>
+      </c>
+      <c r="S67">
+        <v>28</v>
+      </c>
+      <c r="T67" t="s">
+        <v>135</v>
+      </c>
+      <c r="U67">
+        <v>285</v>
+      </c>
+      <c r="V67" t="s">
+        <v>173</v>
+      </c>
+      <c r="W67">
+        <v>153.6</v>
+      </c>
+      <c r="X67" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y67">
+        <v>142.80000000000001</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA67">
+        <v>21.03</v>
+      </c>
+      <c r="AB67" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC67">
+        <v>75.3</v>
+      </c>
+      <c r="AD67" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE67">
+        <v>389</v>
+      </c>
+      <c r="AF67" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG67">
+        <v>450</v>
+      </c>
+      <c r="AH67" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI67">
+        <v>245</v>
+      </c>
+      <c r="AJ67" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK67">
+        <v>17.189</v>
+      </c>
+      <c r="AL67" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM67">
+        <v>3.45</v>
+      </c>
+      <c r="AN67" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO67" t="s">
+        <v>231</v>
+      </c>
+      <c r="AP67" t="s">
+        <v>224</v>
+      </c>
+      <c r="AQ67">
+        <v>24</v>
+      </c>
+      <c r="AR67" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS67">
+        <v>1935.48</v>
+      </c>
+      <c r="AT67" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU67">
+        <v>180.28</v>
+      </c>
+      <c r="AV67" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW67">
+        <v>153.6</v>
+      </c>
+      <c r="AX67" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY67">
+        <v>140.80000000000001</v>
+      </c>
+      <c r="AZ67" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA67" t="s">
+        <v>231</v>
+      </c>
+      <c r="BB67" t="s">
+        <v>224</v>
+      </c>
+      <c r="BC67">
+        <v>473.9</v>
+      </c>
+      <c r="BD67" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE67">
+        <v>261</v>
+      </c>
+      <c r="BF67" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG67" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH67" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI67">
+        <v>180.84</v>
+      </c>
+      <c r="BJ67" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK67">
+        <v>1000</v>
+      </c>
+      <c r="BL67" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM67">
+        <v>25</v>
+      </c>
+      <c r="BN67" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO67" t="s">
+        <v>231</v>
+      </c>
+      <c r="BP67" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ67" t="s">
+        <v>231</v>
+      </c>
+      <c r="BR67" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="68" spans="1:72" x14ac:dyDescent="0.3">
+      <c r="B68">
+        <v>774</v>
+      </c>
+      <c r="C68" t="s">
+        <v>231</v>
+      </c>
+      <c r="D68">
+        <v>100</v>
+      </c>
+      <c r="E68" t="s">
+        <v>171</v>
+      </c>
+      <c r="F68">
+        <v>7</v>
+      </c>
+      <c r="G68">
+        <v>9760</v>
+      </c>
+      <c r="H68" t="s">
+        <v>21</v>
+      </c>
+      <c r="I68">
+        <v>93</v>
+      </c>
+      <c r="J68" t="s">
+        <v>22</v>
+      </c>
+      <c r="K68">
+        <v>12</v>
+      </c>
+      <c r="L68" t="s">
+        <v>135</v>
+      </c>
+      <c r="M68">
+        <v>62</v>
+      </c>
+      <c r="N68" t="s">
+        <v>171</v>
+      </c>
+      <c r="O68">
+        <v>1028</v>
+      </c>
+      <c r="P68" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q68">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="R68" t="s">
+        <v>135</v>
+      </c>
+      <c r="S68">
+        <v>30</v>
+      </c>
+      <c r="T68" t="s">
+        <v>135</v>
+      </c>
+      <c r="U68">
+        <v>250</v>
+      </c>
+      <c r="V68" t="s">
+        <v>173</v>
+      </c>
+      <c r="W68">
+        <v>147.80000000000001</v>
+      </c>
+      <c r="X68" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y68">
+        <v>134</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA68">
+        <v>19.739999999999998</v>
+      </c>
+      <c r="AB68" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC68">
+        <v>71</v>
+      </c>
+      <c r="AD68" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE68">
+        <v>364</v>
+      </c>
+      <c r="AF68" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG68">
+        <v>425</v>
+      </c>
+      <c r="AH68" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI68">
+        <v>230</v>
+      </c>
+      <c r="AJ68" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK68">
+        <v>16.622</v>
+      </c>
+      <c r="AL68" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM68">
+        <v>3.26</v>
+      </c>
+      <c r="AN68" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO68" t="s">
+        <v>231</v>
+      </c>
+      <c r="AP68" t="s">
+        <v>224</v>
+      </c>
+      <c r="AQ68">
+        <v>23</v>
+      </c>
+      <c r="AR68" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS68">
+        <v>1698.11</v>
+      </c>
+      <c r="AT68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU68">
+        <v>173.99</v>
+      </c>
+      <c r="AV68" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW68">
+        <v>147.80000000000001</v>
+      </c>
+      <c r="AX68" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY68">
+        <v>130.80000000000001</v>
+      </c>
+      <c r="AZ68" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA68" t="s">
+        <v>231</v>
+      </c>
+      <c r="BB68" t="s">
+        <v>224</v>
+      </c>
+      <c r="BC68">
+        <v>446.3</v>
+      </c>
+      <c r="BD68" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE68">
+        <v>245.1</v>
+      </c>
+      <c r="BF68" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG68" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH68" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI68">
+        <v>174.34</v>
+      </c>
+      <c r="BJ68" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK68">
+        <v>1000</v>
+      </c>
+      <c r="BL68" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM68">
+        <v>25</v>
+      </c>
+      <c r="BN68" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO68" t="s">
+        <v>231</v>
+      </c>
+      <c r="BP68" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ68" t="s">
+        <v>231</v>
+      </c>
+      <c r="BR68" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="69" spans="1:72" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>231</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C69" t="s">
+        <v>231</v>
+      </c>
+      <c r="D69">
+        <v>50</v>
+      </c>
+      <c r="E69" t="s">
+        <v>171</v>
+      </c>
+      <c r="F69">
+        <v>1</v>
+      </c>
+      <c r="G69" s="4">
+        <v>3135</v>
+      </c>
+      <c r="H69" t="s">
+        <v>21</v>
+      </c>
+      <c r="I69">
+        <v>114</v>
+      </c>
+      <c r="J69" t="s">
+        <v>22</v>
+      </c>
+      <c r="K69">
+        <v>15</v>
+      </c>
+      <c r="L69" t="s">
+        <v>135</v>
+      </c>
+      <c r="M69" t="s">
+        <v>231</v>
+      </c>
+      <c r="N69" t="s">
+        <v>171</v>
+      </c>
+      <c r="O69" t="s">
+        <v>231</v>
+      </c>
+      <c r="P69" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>231</v>
+      </c>
+      <c r="R69" t="s">
+        <v>135</v>
+      </c>
+      <c r="S69">
+        <v>34</v>
+      </c>
+      <c r="T69" t="s">
+        <v>135</v>
+      </c>
+      <c r="U69">
+        <v>80</v>
+      </c>
+      <c r="V69" t="s">
+        <v>173</v>
+      </c>
+      <c r="W69" t="s">
+        <v>231</v>
+      </c>
+      <c r="X69" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>231</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA69" t="s">
+        <v>231</v>
+      </c>
+      <c r="AB69" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC69">
+        <v>43</v>
+      </c>
+      <c r="AD69" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE69">
+        <v>286</v>
+      </c>
+      <c r="AF69" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG69">
+        <v>340</v>
+      </c>
+      <c r="AH69" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI69">
+        <v>250</v>
+      </c>
+      <c r="AJ69" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK69">
+        <v>11.6</v>
+      </c>
+      <c r="AL69" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM69">
+        <v>1</v>
+      </c>
+      <c r="AN69" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO69">
+        <v>0.9</v>
+      </c>
+      <c r="AP69" t="s">
+        <v>174</v>
+      </c>
+      <c r="AQ69">
+        <v>130</v>
+      </c>
+      <c r="AR69" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS69" t="s">
+        <v>231</v>
+      </c>
+      <c r="AT69" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU69" t="s">
+        <v>231</v>
+      </c>
+      <c r="AV69" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW69" t="s">
+        <v>231</v>
+      </c>
+      <c r="AX69" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY69" t="s">
+        <v>231</v>
+      </c>
+      <c r="AZ69" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA69" t="s">
+        <v>231</v>
+      </c>
+      <c r="BB69" t="s">
+        <v>224</v>
+      </c>
+      <c r="BC69" t="s">
+        <v>231</v>
+      </c>
+      <c r="BD69" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE69" t="s">
+        <v>231</v>
+      </c>
+      <c r="BF69" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG69" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH69" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI69" t="s">
+        <v>231</v>
+      </c>
+      <c r="BJ69" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK69" t="s">
+        <v>231</v>
+      </c>
+      <c r="BL69" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM69" t="s">
+        <v>231</v>
+      </c>
+      <c r="BN69" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO69" t="s">
+        <v>231</v>
+      </c>
+      <c r="BP69" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ69" t="s">
+        <v>231</v>
+      </c>
+      <c r="BR69" t="s">
+        <v>173</v>
+      </c>
+      <c r="BS69" t="s">
+        <v>231</v>
+      </c>
+      <c r="BT69" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="70" spans="1:72" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>231</v>
+      </c>
+      <c r="B70" t="s">
+        <v>231</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D70">
+        <v>75</v>
+      </c>
+      <c r="E70" t="s">
+        <v>171</v>
+      </c>
+      <c r="F70">
+        <v>2</v>
+      </c>
+      <c r="G70">
+        <v>4927.5</v>
+      </c>
+      <c r="H70" t="s">
+        <v>21</v>
+      </c>
+      <c r="I70" s="4">
+        <v>120</v>
+      </c>
+      <c r="J70" t="s">
+        <v>22</v>
+      </c>
+      <c r="K70">
+        <v>15</v>
+      </c>
+      <c r="L70" t="s">
+        <v>135</v>
+      </c>
+      <c r="M70" t="s">
+        <v>231</v>
+      </c>
+      <c r="N70" t="s">
+        <v>171</v>
+      </c>
+      <c r="O70" t="s">
+        <v>231</v>
+      </c>
+      <c r="P70" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>231</v>
+      </c>
+      <c r="R70" t="s">
+        <v>135</v>
+      </c>
+      <c r="S70">
+        <v>39</v>
+      </c>
+      <c r="T70" t="s">
+        <v>135</v>
+      </c>
+      <c r="U70">
+        <v>180</v>
+      </c>
+      <c r="V70" t="s">
+        <v>173</v>
+      </c>
+      <c r="W70" t="s">
+        <v>231</v>
+      </c>
+      <c r="X70" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>231</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA70" t="s">
+        <v>231</v>
+      </c>
+      <c r="AB70" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC70">
+        <v>54.8</v>
+      </c>
+      <c r="AD70" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE70">
+        <v>300</v>
+      </c>
+      <c r="AF70" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG70">
+        <v>360</v>
+      </c>
+      <c r="AH70" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI70">
+        <v>238</v>
+      </c>
+      <c r="AJ70" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK70">
+        <v>14.8</v>
+      </c>
+      <c r="AL70" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM70">
+        <v>1.8</v>
+      </c>
+      <c r="AN70" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO70">
+        <v>1.6</v>
+      </c>
+      <c r="AP70" t="s">
+        <v>174</v>
+      </c>
+      <c r="AQ70">
+        <v>130</v>
+      </c>
+      <c r="AR70" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS70" t="s">
+        <v>231</v>
+      </c>
+      <c r="AT70" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU70" t="s">
+        <v>231</v>
+      </c>
+      <c r="AV70" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW70" t="s">
+        <v>231</v>
+      </c>
+      <c r="AX70" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY70" t="s">
+        <v>231</v>
+      </c>
+      <c r="AZ70" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA70" t="s">
+        <v>231</v>
+      </c>
+      <c r="BB70" t="s">
+        <v>224</v>
+      </c>
+      <c r="BC70" t="s">
+        <v>231</v>
+      </c>
+      <c r="BD70" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE70" t="s">
+        <v>231</v>
+      </c>
+      <c r="BF70" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG70" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH70" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI70" t="s">
+        <v>231</v>
+      </c>
+      <c r="BJ70" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK70" t="s">
+        <v>231</v>
+      </c>
+      <c r="BL70" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM70" t="s">
+        <v>231</v>
+      </c>
+      <c r="BN70" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO70" t="s">
+        <v>231</v>
+      </c>
+      <c r="BP70" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ70" t="s">
+        <v>231</v>
+      </c>
+      <c r="BR70" t="s">
+        <v>173</v>
+      </c>
+      <c r="BS70" t="s">
+        <v>231</v>
+      </c>
+      <c r="BT70" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="71" spans="1:72" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>231</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C71" t="s">
+        <v>231</v>
+      </c>
+      <c r="D71">
+        <v>85</v>
+      </c>
+      <c r="E71" t="s">
+        <v>171</v>
+      </c>
+      <c r="F71">
+        <v>3</v>
+      </c>
+      <c r="G71" s="4">
+        <v>5548.3</v>
+      </c>
+      <c r="H71" t="s">
+        <v>21</v>
+      </c>
+      <c r="I71">
+        <v>122</v>
+      </c>
+      <c r="J71" t="s">
+        <v>22</v>
+      </c>
+      <c r="K71">
+        <v>15</v>
+      </c>
+      <c r="L71" t="s">
+        <v>135</v>
+      </c>
+      <c r="M71" t="s">
+        <v>231</v>
+      </c>
+      <c r="N71" t="s">
+        <v>171</v>
+      </c>
+      <c r="O71" t="s">
+        <v>231</v>
+      </c>
+      <c r="P71" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>231</v>
+      </c>
+      <c r="R71" t="s">
+        <v>135</v>
+      </c>
+      <c r="S71">
+        <v>40</v>
+      </c>
+      <c r="T71" t="s">
+        <v>135</v>
+      </c>
+      <c r="U71">
+        <v>210</v>
+      </c>
+      <c r="V71" t="s">
+        <v>173</v>
+      </c>
+      <c r="W71" t="s">
+        <v>231</v>
+      </c>
+      <c r="X71" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>231</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA71" t="s">
+        <v>231</v>
+      </c>
+      <c r="AB71" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC71">
+        <v>60.6</v>
+      </c>
+      <c r="AD71" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE71">
+        <v>301</v>
+      </c>
+      <c r="AF71" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG71">
+        <v>365</v>
+      </c>
+      <c r="AH71" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI71">
+        <v>238</v>
+      </c>
+      <c r="AJ71" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK71">
+        <v>15.4</v>
+      </c>
+      <c r="AL71" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM71">
+        <v>2</v>
+      </c>
+      <c r="AN71" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO71">
+        <v>1.8</v>
+      </c>
+      <c r="AP71" t="s">
+        <v>174</v>
+      </c>
+      <c r="AQ71">
+        <v>130</v>
+      </c>
+      <c r="AR71" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS71" t="s">
+        <v>231</v>
+      </c>
+      <c r="AT71" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU71" t="s">
+        <v>231</v>
+      </c>
+      <c r="AV71" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW71" t="s">
+        <v>231</v>
+      </c>
+      <c r="AX71" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY71" t="s">
+        <v>231</v>
+      </c>
+      <c r="AZ71" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA71" t="s">
+        <v>231</v>
+      </c>
+      <c r="BB71" t="s">
+        <v>224</v>
+      </c>
+      <c r="BC71" t="s">
+        <v>231</v>
+      </c>
+      <c r="BD71" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE71" t="s">
+        <v>231</v>
+      </c>
+      <c r="BF71" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG71" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH71" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI71" t="s">
+        <v>231</v>
+      </c>
+      <c r="BJ71" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK71" t="s">
+        <v>231</v>
+      </c>
+      <c r="BL71" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM71" t="s">
+        <v>231</v>
+      </c>
+      <c r="BN71" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO71" t="s">
+        <v>231</v>
+      </c>
+      <c r="BP71" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ71" t="s">
+        <v>231</v>
+      </c>
+      <c r="BR71" t="s">
+        <v>173</v>
+      </c>
+      <c r="BS71" t="s">
+        <v>231</v>
+      </c>
+      <c r="BT71" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="72" spans="1:72" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>231</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C72" t="s">
+        <v>231</v>
+      </c>
+      <c r="D72">
+        <v>100</v>
+      </c>
+      <c r="E72" t="s">
+        <v>171</v>
+      </c>
+      <c r="F72">
+        <v>4</v>
+      </c>
+      <c r="G72" s="4">
+        <v>6580</v>
+      </c>
+      <c r="H72" t="s">
+        <v>21</v>
+      </c>
+      <c r="I72">
+        <v>127</v>
+      </c>
+      <c r="J72" t="s">
+        <v>22</v>
+      </c>
+      <c r="K72">
+        <v>15</v>
+      </c>
+      <c r="L72" t="s">
+        <v>135</v>
+      </c>
+      <c r="M72" t="s">
+        <v>231</v>
+      </c>
+      <c r="N72" t="s">
+        <v>171</v>
+      </c>
+      <c r="O72" t="s">
+        <v>231</v>
+      </c>
+      <c r="P72" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>231</v>
+      </c>
+      <c r="R72" t="s">
+        <v>135</v>
+      </c>
+      <c r="S72">
+        <v>43</v>
+      </c>
+      <c r="T72" t="s">
+        <v>135</v>
+      </c>
+      <c r="U72">
+        <v>265</v>
+      </c>
+      <c r="V72" t="s">
+        <v>173</v>
+      </c>
+      <c r="W72" t="s">
+        <v>231</v>
+      </c>
+      <c r="X72" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>231</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA72" t="s">
+        <v>231</v>
+      </c>
+      <c r="AB72" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC72">
+        <v>69.400000000000006</v>
+      </c>
+      <c r="AD72" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE72">
+        <v>335.6</v>
+      </c>
+      <c r="AF72" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG72">
+        <v>400</v>
+      </c>
+      <c r="AH72" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI72">
+        <v>245</v>
+      </c>
+      <c r="AJ72" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK72">
+        <v>17.010000000000002</v>
+      </c>
+      <c r="AL72" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM72">
+        <v>2.5</v>
+      </c>
+      <c r="AN72" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO72">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AP72" t="s">
+        <v>174</v>
+      </c>
+      <c r="AQ72">
+        <v>129</v>
+      </c>
+      <c r="AR72" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS72" t="s">
+        <v>231</v>
+      </c>
+      <c r="AT72" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU72" t="s">
+        <v>231</v>
+      </c>
+      <c r="AV72" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW72" t="s">
+        <v>231</v>
+      </c>
+      <c r="AX72" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY72" t="s">
+        <v>231</v>
+      </c>
+      <c r="AZ72" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA72" t="s">
+        <v>231</v>
+      </c>
+      <c r="BB72" t="s">
+        <v>224</v>
+      </c>
+      <c r="BC72" t="s">
+        <v>231</v>
+      </c>
+      <c r="BD72" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE72" t="s">
+        <v>231</v>
+      </c>
+      <c r="BF72" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG72" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH72" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI72" t="s">
+        <v>231</v>
+      </c>
+      <c r="BJ72" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK72" t="s">
+        <v>231</v>
+      </c>
+      <c r="BL72" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM72" t="s">
+        <v>231</v>
+      </c>
+      <c r="BN72" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO72" t="s">
+        <v>231</v>
+      </c>
+      <c r="BP72" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ72" t="s">
+        <v>231</v>
+      </c>
+      <c r="BR72" t="s">
+        <v>173</v>
+      </c>
+      <c r="BS72" t="s">
+        <v>231</v>
+      </c>
+      <c r="BT72" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="73" spans="1:72" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>231</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C73" t="s">
+        <v>231</v>
+      </c>
+      <c r="D73">
+        <v>110</v>
+      </c>
+      <c r="E73" t="s">
+        <v>171</v>
+      </c>
+      <c r="F73">
+        <v>5</v>
+      </c>
+      <c r="G73">
+        <v>7240</v>
+      </c>
+      <c r="H73" t="s">
+        <v>21</v>
+      </c>
+      <c r="I73">
+        <v>130</v>
+      </c>
+      <c r="J73" t="s">
+        <v>22</v>
+      </c>
+      <c r="K73">
+        <v>15</v>
+      </c>
+      <c r="L73" t="s">
+        <v>135</v>
+      </c>
+      <c r="M73" t="s">
+        <v>231</v>
+      </c>
+      <c r="N73" t="s">
+        <v>171</v>
+      </c>
+      <c r="O73" t="s">
+        <v>231</v>
+      </c>
+      <c r="P73" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>231</v>
+      </c>
+      <c r="R73" t="s">
+        <v>135</v>
+      </c>
+      <c r="S73">
+        <v>46</v>
+      </c>
+      <c r="T73" t="s">
+        <v>135</v>
+      </c>
+      <c r="U73">
+        <v>260</v>
+      </c>
+      <c r="V73" t="s">
+        <v>173</v>
+      </c>
+      <c r="W73" t="s">
+        <v>231</v>
+      </c>
+      <c r="X73" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>231</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA73" t="s">
+        <v>231</v>
+      </c>
+      <c r="AB73" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC73">
+        <v>76.2</v>
+      </c>
+      <c r="AD73" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE73">
+        <v>342</v>
+      </c>
+      <c r="AF73" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG73">
+        <v>420</v>
+      </c>
+      <c r="AH73" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI73">
+        <v>250</v>
+      </c>
+      <c r="AJ73" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK73">
+        <v>17.5</v>
+      </c>
+      <c r="AL73" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM73">
+        <v>2.8</v>
+      </c>
+      <c r="AN73" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO73">
+        <v>2.6</v>
+      </c>
+      <c r="AP73" t="s">
+        <v>174</v>
+      </c>
+      <c r="AQ73">
+        <v>130</v>
+      </c>
+      <c r="AR73" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS73" t="s">
+        <v>231</v>
+      </c>
+      <c r="AT73" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU73" t="s">
+        <v>231</v>
+      </c>
+      <c r="AV73" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW73" t="s">
+        <v>231</v>
+      </c>
+      <c r="AX73" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY73" t="s">
+        <v>231</v>
+      </c>
+      <c r="AZ73" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA73" t="s">
+        <v>231</v>
+      </c>
+      <c r="BB73" t="s">
+        <v>224</v>
+      </c>
+      <c r="BC73" t="s">
+        <v>231</v>
+      </c>
+      <c r="BD73" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE73" t="s">
+        <v>231</v>
+      </c>
+      <c r="BF73" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG73" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH73" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI73" t="s">
+        <v>231</v>
+      </c>
+      <c r="BJ73" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK73" t="s">
+        <v>231</v>
+      </c>
+      <c r="BL73" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM73" t="s">
+        <v>231</v>
+      </c>
+      <c r="BN73" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO73" t="s">
+        <v>231</v>
+      </c>
+      <c r="BP73" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ73" t="s">
+        <v>231</v>
+      </c>
+      <c r="BR73" t="s">
+        <v>173</v>
+      </c>
+      <c r="BS73" t="s">
+        <v>231</v>
+      </c>
+      <c r="BT73" t="s">
+        <v>231</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/Aepms-backend/data/Engine_Performance_Data.xlsx
+++ b/Aepms-backend/data/Engine_Performance_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GOKUL\Desktop\WORKPLACE\Workplace\Aepms-backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1ED77D-5904-4AE2-A294-C4F5C92A510E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC303C7E-297A-4E5B-917F-EBFB5C4D190E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2920" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3331" uniqueCount="255">
   <si>
     <t>hull_no</t>
   </si>
@@ -779,13 +779,37 @@
   </si>
   <si>
     <t>STX Dalian Engine Co.</t>
+  </si>
+  <si>
+    <t>NAMURA S-317</t>
+  </si>
+  <si>
+    <t>NAMURA SHIPBUILDING</t>
+  </si>
+  <si>
+    <t>MITSUI-MAN B&amp;W 6S70MC-C</t>
+  </si>
+  <si>
+    <t>AMNSI MAXIMUS</t>
+  </si>
+  <si>
+    <t>Hebei Ocean Shipping Co.,Ltd</t>
+  </si>
+  <si>
+    <t>Qingdao Beihai Shipbuilding Heavy Industry Co.,Ltd</t>
+  </si>
+  <si>
+    <t>DMD-WÄRTSILÄ (Dalian Marine Diesel Co.,Ltd)</t>
+  </si>
+  <si>
+    <t>DMD-WÄRTSILÄ 5RT-flex58T-D</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -800,6 +824,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -828,7 +865,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -837,7 +874,30 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -958,7 +1018,7 @@
     <tableColumn id="70" xr3:uid="{00000000-0010-0000-0200-000046000000}" name="created_at"/>
     <tableColumn id="71" xr3:uid="{00000000-0010-0000-0200-000047000000}" name="updated_at"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1314,7 +1374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB18"/>
+  <dimension ref="A1:AB17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.77734375" customWidth="1"/>
@@ -1955,7 +2015,7 @@
       <c r="C9">
         <v>9792058</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="13" t="s">
         <v>214</v>
       </c>
       <c r="E9" s="2">
@@ -2018,170 +2078,206 @@
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="C10">
-        <v>9521813</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>220</v>
+        <v>9532082</v>
+      </c>
+      <c r="D10" s="2">
+        <v>5933</v>
+      </c>
+      <c r="E10" t="s">
+        <v>247</v>
       </c>
       <c r="F10" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G10" t="s">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="H10" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="I10" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="J10" t="s">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M10" t="s">
         <v>19</v>
       </c>
-      <c r="N10">
-        <v>168.37</v>
+      <c r="N10" s="6">
+        <v>163.69999999999999</v>
       </c>
       <c r="O10" t="s">
         <v>20</v>
       </c>
       <c r="P10">
-        <v>6570</v>
+        <v>16860</v>
       </c>
       <c r="Q10" t="s">
         <v>21</v>
       </c>
       <c r="R10">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="S10" t="s">
         <v>22</v>
       </c>
       <c r="T10">
-        <v>5585</v>
-      </c>
-      <c r="Y10">
-        <v>100</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>171</v>
+        <v>14330</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="D11" s="3"/>
-      <c r="E11" s="2"/>
+      <c r="B11" t="s">
+        <v>219</v>
+      </c>
+      <c r="C11">
+        <v>9521813</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F11" t="s">
+        <v>221</v>
+      </c>
+      <c r="G11" t="s">
+        <v>222</v>
+      </c>
+      <c r="H11" t="s">
+        <v>246</v>
+      </c>
+      <c r="I11" t="s">
+        <v>245</v>
+      </c>
+      <c r="J11" t="s">
+        <v>218</v>
+      </c>
+      <c r="K11">
+        <v>5</v>
+      </c>
+      <c r="M11" t="s">
+        <v>19</v>
+      </c>
+      <c r="N11" s="10">
+        <v>164.66</v>
+      </c>
+      <c r="O11" t="s">
+        <v>20</v>
+      </c>
+      <c r="P11">
+        <v>6570</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>21</v>
+      </c>
+      <c r="R11">
+        <v>127</v>
+      </c>
+      <c r="S11" t="s">
+        <v>22</v>
+      </c>
+      <c r="T11">
+        <v>5585</v>
+      </c>
+      <c r="Y11">
+        <v>100</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="D12" s="3"/>
-      <c r="E12" s="2"/>
+      <c r="B12" t="s">
+        <v>250</v>
+      </c>
+      <c r="C12">
+        <v>9628893</v>
+      </c>
+      <c r="D12" s="2">
+        <v>774</v>
+      </c>
+      <c r="E12" t="s">
+        <v>237</v>
+      </c>
+      <c r="F12" t="s">
+        <v>251</v>
+      </c>
+      <c r="G12" t="s">
+        <v>252</v>
+      </c>
+      <c r="H12" t="s">
+        <v>253</v>
+      </c>
+      <c r="I12" t="s">
+        <v>240</v>
+      </c>
+      <c r="J12" t="s">
+        <v>254</v>
+      </c>
+      <c r="K12">
+        <v>5</v>
+      </c>
+      <c r="M12" t="s">
+        <v>19</v>
+      </c>
+      <c r="N12">
+        <v>172.2</v>
+      </c>
+      <c r="O12" t="s">
+        <v>20</v>
+      </c>
+      <c r="P12">
+        <v>9760</v>
+      </c>
+      <c r="Q12" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="R12">
+        <v>92.9</v>
+      </c>
+      <c r="S12" s="13" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B13" t="s">
-        <v>236</v>
-      </c>
-      <c r="C13">
-        <v>9628910</v>
-      </c>
-      <c r="D13">
-        <v>774</v>
-      </c>
-      <c r="E13" t="s">
-        <v>237</v>
-      </c>
-      <c r="F13" t="s">
-        <v>239</v>
-      </c>
-      <c r="G13" t="s">
-        <v>238</v>
-      </c>
-      <c r="H13" t="s">
-        <v>241</v>
-      </c>
-      <c r="I13" t="s">
-        <v>240</v>
-      </c>
-      <c r="J13" t="s">
-        <v>240</v>
-      </c>
-      <c r="K13">
-        <v>5</v>
-      </c>
-      <c r="M13" t="s">
-        <v>19</v>
-      </c>
-      <c r="N13" t="s">
-        <v>231</v>
-      </c>
-      <c r="O13" t="s">
-        <v>20</v>
-      </c>
-      <c r="P13">
-        <v>9760</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>21</v>
-      </c>
-      <c r="R13">
-        <v>92.9</v>
-      </c>
-      <c r="S13" t="s">
-        <v>22</v>
-      </c>
-      <c r="T13" t="s">
-        <v>231</v>
-      </c>
-      <c r="U13" t="s">
-        <v>231</v>
-      </c>
-      <c r="V13" t="s">
-        <v>231</v>
-      </c>
-      <c r="W13" t="s">
-        <v>231</v>
-      </c>
-      <c r="X13" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>231</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>171</v>
-      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C14">
-        <v>9486295</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="2" t="s">
-        <v>243</v>
+        <v>9628910</v>
+      </c>
+      <c r="D14" s="2">
+        <v>774</v>
+      </c>
+      <c r="E14" t="s">
+        <v>237</v>
+      </c>
+      <c r="F14" t="s">
+        <v>239</v>
       </c>
       <c r="G14" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="H14" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="I14" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="J14" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="K14">
         <v>5</v>
@@ -2189,32 +2285,32 @@
       <c r="M14" t="s">
         <v>19</v>
       </c>
-      <c r="N14">
-        <v>164.6</v>
+      <c r="N14" t="s">
+        <v>231</v>
       </c>
       <c r="O14" t="s">
         <v>20</v>
       </c>
       <c r="P14">
-        <v>6570</v>
+        <v>9760</v>
       </c>
       <c r="Q14" t="s">
         <v>21</v>
       </c>
       <c r="R14">
-        <v>127</v>
+        <v>92.9</v>
       </c>
       <c r="S14" t="s">
         <v>22</v>
       </c>
-      <c r="T14">
-        <v>5510</v>
-      </c>
-      <c r="U14">
-        <v>56</v>
-      </c>
-      <c r="V14">
-        <v>73</v>
+      <c r="T14" t="s">
+        <v>231</v>
+      </c>
+      <c r="U14" t="s">
+        <v>231</v>
+      </c>
+      <c r="V14" t="s">
+        <v>231</v>
       </c>
       <c r="W14" t="s">
         <v>231</v>
@@ -2230,118 +2326,133 @@
       </c>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="D15" s="3"/>
-      <c r="E15" s="2"/>
+      <c r="B15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C15">
+        <v>9486295</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="G15" t="s">
+        <v>244</v>
+      </c>
+      <c r="H15" t="s">
+        <v>223</v>
+      </c>
+      <c r="I15" t="s">
+        <v>245</v>
+      </c>
+      <c r="J15" t="s">
+        <v>245</v>
+      </c>
+      <c r="K15">
+        <v>5</v>
+      </c>
+      <c r="M15" t="s">
+        <v>19</v>
+      </c>
+      <c r="N15">
+        <v>164.6</v>
+      </c>
+      <c r="O15" t="s">
+        <v>20</v>
+      </c>
+      <c r="P15">
+        <v>6570</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>21</v>
+      </c>
+      <c r="R15">
+        <v>127</v>
+      </c>
+      <c r="S15" t="s">
+        <v>22</v>
+      </c>
+      <c r="T15">
+        <v>5510</v>
+      </c>
+      <c r="U15">
+        <v>56</v>
+      </c>
+      <c r="V15">
+        <v>73</v>
+      </c>
+      <c r="W15" t="s">
+        <v>231</v>
+      </c>
+      <c r="X15" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>231</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="D16" s="3"/>
-      <c r="E16" s="2"/>
+      <c r="B16" t="s">
+        <v>225</v>
+      </c>
+      <c r="C16">
+        <v>9644500</v>
+      </c>
+      <c r="D16" s="2">
+        <v>4078</v>
+      </c>
+      <c r="E16" s="2">
+        <v>10701</v>
+      </c>
+      <c r="F16" t="s">
+        <v>226</v>
+      </c>
+      <c r="G16" t="s">
+        <v>227</v>
+      </c>
+      <c r="H16" t="s">
+        <v>228</v>
+      </c>
+      <c r="I16" t="s">
+        <v>229</v>
+      </c>
+      <c r="J16" t="s">
+        <v>230</v>
+      </c>
+      <c r="K16">
+        <v>6</v>
+      </c>
+      <c r="M16" t="s">
+        <v>19</v>
+      </c>
+      <c r="N16">
+        <v>166.6</v>
+      </c>
+      <c r="O16" t="s">
+        <v>20</v>
+      </c>
+      <c r="P16" s="4">
+        <v>12270</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>21</v>
+      </c>
+      <c r="R16">
+        <v>105</v>
+      </c>
+      <c r="S16" t="s">
+        <v>22</v>
+      </c>
+      <c r="T16" s="4">
+        <v>10436</v>
+      </c>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
-        <v>225</v>
-      </c>
-      <c r="C17">
-        <v>9644500</v>
-      </c>
-      <c r="D17" s="2">
-        <v>4078</v>
-      </c>
-      <c r="E17" s="2">
-        <v>10701</v>
-      </c>
-      <c r="F17" t="s">
-        <v>226</v>
-      </c>
-      <c r="G17" t="s">
-        <v>227</v>
-      </c>
-      <c r="H17" t="s">
-        <v>228</v>
-      </c>
-      <c r="I17" t="s">
-        <v>229</v>
-      </c>
-      <c r="J17" t="s">
-        <v>230</v>
-      </c>
-      <c r="K17">
-        <v>6</v>
-      </c>
-      <c r="M17" t="s">
-        <v>19</v>
-      </c>
-      <c r="N17">
-        <v>166.6</v>
-      </c>
-      <c r="O17" t="s">
-        <v>20</v>
-      </c>
-      <c r="P17" s="4">
-        <v>12270</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>21</v>
-      </c>
-      <c r="R17">
-        <v>105</v>
-      </c>
-      <c r="S17" t="s">
-        <v>22</v>
-      </c>
-      <c r="T17" s="4">
-        <v>10436</v>
-      </c>
-    </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B18" t="s">
-        <v>232</v>
-      </c>
-      <c r="C18">
-        <v>9532082</v>
-      </c>
-      <c r="D18">
-        <v>5933</v>
-      </c>
-      <c r="F18" t="s">
-        <v>235</v>
-      </c>
-      <c r="G18" t="s">
-        <v>234</v>
-      </c>
-      <c r="H18" t="s">
-        <v>210</v>
-      </c>
-      <c r="I18" t="s">
-        <v>233</v>
-      </c>
-      <c r="J18" t="s">
-        <v>233</v>
-      </c>
-      <c r="K18">
-        <v>6</v>
-      </c>
-      <c r="N18">
-        <v>163.69999999999999</v>
-      </c>
-      <c r="O18" t="s">
-        <v>20</v>
-      </c>
-      <c r="P18">
-        <v>16860</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>21</v>
-      </c>
-      <c r="R18">
-        <v>91</v>
-      </c>
-      <c r="S18" t="s">
-        <v>22</v>
-      </c>
-      <c r="T18">
-        <v>14330</v>
-      </c>
+    <row r="17" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2758,7 +2869,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:BT73"/>
+  <dimension ref="A1:CG92"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="26.21875" customWidth="1"/>
@@ -12662,7 +12773,7 @@
       </c>
     </row>
     <row r="49" spans="2:70" x14ac:dyDescent="0.3">
-      <c r="B49" s="3" t="s">
+      <c r="B49" t="s">
         <v>214</v>
       </c>
       <c r="D49">
@@ -12862,7 +12973,7 @@
       </c>
     </row>
     <row r="50" spans="2:70" x14ac:dyDescent="0.3">
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="13" t="s">
         <v>214</v>
       </c>
       <c r="D50">
@@ -13062,7 +13173,7 @@
       </c>
     </row>
     <row r="51" spans="2:70" x14ac:dyDescent="0.3">
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="13" t="s">
         <v>214</v>
       </c>
       <c r="D51">
@@ -13262,7 +13373,7 @@
       </c>
     </row>
     <row r="52" spans="2:70" x14ac:dyDescent="0.3">
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="13" t="s">
         <v>214</v>
       </c>
       <c r="D52">
@@ -13462,7 +13573,7 @@
       </c>
     </row>
     <row r="53" spans="2:70" x14ac:dyDescent="0.3">
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="13" t="s">
         <v>214</v>
       </c>
       <c r="D53">
@@ -13662,7 +13773,7 @@
       </c>
     </row>
     <row r="54" spans="2:70" x14ac:dyDescent="0.3">
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="13" t="s">
         <v>214</v>
       </c>
       <c r="D54">
@@ -13862,8 +13973,8 @@
       </c>
     </row>
     <row r="55" spans="2:70" x14ac:dyDescent="0.3">
-      <c r="B55" s="3" t="s">
-        <v>218</v>
+      <c r="B55" s="2">
+        <v>5933</v>
       </c>
       <c r="D55">
         <v>25</v>
@@ -13875,141 +13986,171 @@
         <v>1</v>
       </c>
       <c r="G55">
-        <v>1643</v>
+        <v>4235</v>
       </c>
       <c r="H55" t="s">
         <v>21</v>
       </c>
       <c r="I55">
-        <v>80</v>
+        <v>57.3</v>
       </c>
       <c r="J55" t="s">
         <v>22</v>
       </c>
       <c r="K55">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="L55" t="s">
         <v>135</v>
       </c>
       <c r="M55">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="N55" t="s">
         <v>171</v>
       </c>
       <c r="O55">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="P55" t="s">
         <v>172</v>
       </c>
       <c r="Q55">
-        <v>17</v>
+        <v>24.1</v>
       </c>
       <c r="R55" t="s">
         <v>135</v>
       </c>
       <c r="S55">
-        <v>35</v>
+        <v>34.299999999999997</v>
       </c>
       <c r="T55" t="s">
         <v>135</v>
       </c>
       <c r="U55">
-        <v>40</v>
+        <v>20.39</v>
       </c>
       <c r="V55" t="s">
         <v>173</v>
       </c>
       <c r="W55">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="X55" t="s">
         <v>174</v>
       </c>
       <c r="Y55">
-        <v>52</v>
+        <v>50.3</v>
       </c>
       <c r="Z55" t="s">
         <v>174</v>
       </c>
-      <c r="AA55">
-        <v>6.28</v>
-      </c>
       <c r="AB55" t="s">
         <v>174</v>
       </c>
       <c r="AC55">
-        <v>34.200000000000003</v>
+        <v>53</v>
       </c>
       <c r="AD55" t="s">
         <v>19</v>
       </c>
       <c r="AE55">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="AF55" t="s">
         <v>135</v>
       </c>
       <c r="AG55">
-        <v>295</v>
+        <v>327</v>
       </c>
       <c r="AH55" t="s">
         <v>135</v>
       </c>
       <c r="AI55">
-        <v>235</v>
+        <v>278</v>
       </c>
       <c r="AJ55" t="s">
         <v>135</v>
       </c>
       <c r="AK55">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="AL55" t="s">
         <v>175</v>
       </c>
       <c r="AM55">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="AN55" t="s">
         <v>174</v>
       </c>
-      <c r="AO55">
-        <v>0.25</v>
+      <c r="AO55" s="7" t="s">
+        <v>231</v>
       </c>
       <c r="AP55" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="AQ55">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="AR55" t="s">
         <v>135</v>
       </c>
-      <c r="AS55">
-        <v>300</v>
+      <c r="AS55" s="7" t="s">
+        <v>231</v>
       </c>
       <c r="AT55" t="s">
         <v>177</v>
       </c>
       <c r="AU55">
-        <v>182.59</v>
+        <v>176.4</v>
       </c>
       <c r="AV55" t="s">
         <v>20</v>
       </c>
-      <c r="BJ55">
-        <v>183.02</v>
-      </c>
-      <c r="BK55" t="s">
+      <c r="AX55" t="s">
+        <v>174</v>
+      </c>
+      <c r="AZ55" t="s">
+        <v>174</v>
+      </c>
+      <c r="BB55" t="s">
+        <v>205</v>
+      </c>
+      <c r="BD55" t="s">
+        <v>135</v>
+      </c>
+      <c r="BF55" t="s">
+        <v>135</v>
+      </c>
+      <c r="BH55" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI55">
+        <v>176.6</v>
+      </c>
+      <c r="BJ55" t="s">
         <v>20</v>
+      </c>
+      <c r="BK55">
+        <v>1000</v>
+      </c>
+      <c r="BL55" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM55">
+        <v>25</v>
+      </c>
+      <c r="BN55" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP55" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="56" spans="2:70" x14ac:dyDescent="0.3">
-      <c r="B56" s="3" t="s">
-        <v>218</v>
+      <c r="B56" s="2">
+        <v>5933</v>
       </c>
       <c r="D56">
         <v>50</v>
@@ -14021,25 +14162,25 @@
         <v>2</v>
       </c>
       <c r="G56">
-        <v>3285</v>
+        <v>8454</v>
       </c>
       <c r="H56" t="s">
         <v>21</v>
       </c>
       <c r="I56">
-        <v>100.8</v>
+        <v>72.2</v>
       </c>
       <c r="J56" t="s">
         <v>22</v>
       </c>
       <c r="K56">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L56" t="s">
         <v>135</v>
       </c>
       <c r="M56">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="N56" t="s">
         <v>171</v>
@@ -14051,67 +14192,64 @@
         <v>172</v>
       </c>
       <c r="Q56">
-        <v>17</v>
+        <v>22.5</v>
       </c>
       <c r="R56" t="s">
         <v>135</v>
       </c>
       <c r="S56">
-        <v>30</v>
+        <v>28.2</v>
       </c>
       <c r="T56" t="s">
         <v>135</v>
       </c>
       <c r="U56">
-        <v>90</v>
+        <v>60.16</v>
       </c>
       <c r="V56" t="s">
         <v>173</v>
       </c>
       <c r="W56">
-        <v>105.2</v>
+        <v>106.8</v>
       </c>
       <c r="X56" t="s">
         <v>174</v>
       </c>
       <c r="Y56">
-        <v>78.400000000000006</v>
+        <v>77.7</v>
       </c>
       <c r="Z56" t="s">
         <v>174</v>
       </c>
-      <c r="AA56">
-        <v>9.9600000000000009</v>
-      </c>
       <c r="AB56" t="s">
         <v>174</v>
       </c>
       <c r="AC56">
-        <v>46.2</v>
+        <v>70.8</v>
       </c>
       <c r="AD56" t="s">
         <v>19</v>
       </c>
       <c r="AE56">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="AF56" t="s">
         <v>135</v>
       </c>
       <c r="AG56">
-        <v>325</v>
+        <v>355</v>
       </c>
       <c r="AH56" t="s">
         <v>135</v>
       </c>
       <c r="AI56">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="AJ56" t="s">
         <v>135</v>
       </c>
       <c r="AK56">
-        <v>12.6</v>
+        <v>8.75</v>
       </c>
       <c r="AL56" t="s">
         <v>175</v>
@@ -14122,40 +14260,73 @@
       <c r="AN56" t="s">
         <v>174</v>
       </c>
-      <c r="AO56">
-        <v>0.9</v>
+      <c r="AO56" s="6">
+        <v>3.7699999999999999E-3</v>
       </c>
       <c r="AP56" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="AQ56">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AR56" t="s">
         <v>135</v>
       </c>
-      <c r="AS56">
-        <v>552</v>
+      <c r="AS56" s="7" t="s">
+        <v>231</v>
       </c>
       <c r="AT56" t="s">
         <v>177</v>
       </c>
       <c r="AU56">
-        <v>168.04</v>
+        <v>167.8</v>
       </c>
       <c r="AV56" t="s">
         <v>20</v>
       </c>
-      <c r="BJ56">
-        <v>168.43</v>
-      </c>
-      <c r="BK56" t="s">
+      <c r="AX56" t="s">
+        <v>174</v>
+      </c>
+      <c r="AZ56" t="s">
+        <v>174</v>
+      </c>
+      <c r="BB56" t="s">
+        <v>205</v>
+      </c>
+      <c r="BD56" t="s">
+        <v>135</v>
+      </c>
+      <c r="BF56" t="s">
+        <v>135</v>
+      </c>
+      <c r="BH56" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI56">
+        <v>168</v>
+      </c>
+      <c r="BJ56" t="s">
         <v>20</v>
+      </c>
+      <c r="BK56">
+        <v>1000</v>
+      </c>
+      <c r="BL56" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM56">
+        <v>25</v>
+      </c>
+      <c r="BN56" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP56" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="57" spans="2:70" x14ac:dyDescent="0.3">
-      <c r="B57" s="3" t="s">
-        <v>218</v>
+      <c r="B57" s="2">
+        <v>5933</v>
       </c>
       <c r="D57">
         <v>75</v>
@@ -14167,141 +14338,171 @@
         <v>3</v>
       </c>
       <c r="G57">
-        <v>4928</v>
+        <v>12658</v>
       </c>
       <c r="H57" t="s">
         <v>21</v>
       </c>
       <c r="I57">
-        <v>115.4</v>
+        <v>82.6</v>
       </c>
       <c r="J57" t="s">
         <v>22</v>
       </c>
       <c r="K57">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L57" t="s">
         <v>135</v>
       </c>
       <c r="M57">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="N57" t="s">
         <v>171</v>
       </c>
       <c r="O57">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="P57" t="s">
         <v>172</v>
       </c>
       <c r="Q57">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="R57" t="s">
         <v>135</v>
       </c>
       <c r="S57">
-        <v>30</v>
+        <v>31.3</v>
       </c>
       <c r="T57" t="s">
         <v>135</v>
       </c>
       <c r="U57">
-        <v>126</v>
+        <v>160.09</v>
       </c>
       <c r="V57" t="s">
         <v>173</v>
       </c>
       <c r="W57">
-        <v>142.80000000000001</v>
+        <v>139.69999999999999</v>
       </c>
       <c r="X57" t="s">
         <v>174</v>
       </c>
       <c r="Y57">
-        <v>113.4</v>
+        <v>108.8</v>
       </c>
       <c r="Z57" t="s">
         <v>174</v>
       </c>
-      <c r="AA57">
-        <v>13.06</v>
-      </c>
       <c r="AB57" t="s">
         <v>174</v>
       </c>
       <c r="AC57">
-        <v>56.4</v>
+        <v>86.5</v>
       </c>
       <c r="AD57" t="s">
         <v>19</v>
       </c>
       <c r="AE57">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="AF57" t="s">
         <v>135</v>
       </c>
       <c r="AG57">
-        <v>330</v>
+        <v>372</v>
       </c>
       <c r="AH57" t="s">
         <v>135</v>
       </c>
       <c r="AI57">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="AJ57" t="s">
         <v>135</v>
       </c>
       <c r="AK57">
-        <v>14.7</v>
+        <v>10.8</v>
       </c>
       <c r="AL57" t="s">
         <v>175</v>
       </c>
       <c r="AM57">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AN57" t="s">
         <v>174</v>
       </c>
       <c r="AO57">
-        <v>1.6</v>
+        <v>7.2399999999999999E-3</v>
       </c>
       <c r="AP57" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="AQ57">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AR57" t="s">
         <v>135</v>
       </c>
-      <c r="AS57">
-        <v>804</v>
+      <c r="AS57" s="7" t="s">
+        <v>231</v>
       </c>
       <c r="AT57" t="s">
         <v>177</v>
       </c>
       <c r="AU57">
-        <v>163.15</v>
+        <v>163.1</v>
       </c>
       <c r="AV57" t="s">
         <v>20</v>
       </c>
-      <c r="BJ57">
-        <v>163.46</v>
-      </c>
-      <c r="BK57" t="s">
+      <c r="AX57" t="s">
+        <v>174</v>
+      </c>
+      <c r="AZ57" t="s">
+        <v>174</v>
+      </c>
+      <c r="BB57" t="s">
+        <v>205</v>
+      </c>
+      <c r="BD57" t="s">
+        <v>135</v>
+      </c>
+      <c r="BF57" t="s">
+        <v>135</v>
+      </c>
+      <c r="BH57" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI57">
+        <v>163.30000000000001</v>
+      </c>
+      <c r="BJ57" t="s">
         <v>20</v>
+      </c>
+      <c r="BK57">
+        <v>1000</v>
+      </c>
+      <c r="BL57" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM57">
+        <v>25</v>
+      </c>
+      <c r="BN57" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP57" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="58" spans="2:70" x14ac:dyDescent="0.3">
-      <c r="B58" s="3" t="s">
-        <v>218</v>
+      <c r="B58" s="2">
+        <v>5933</v>
       </c>
       <c r="D58">
         <v>85</v>
@@ -14313,2981 +14514,5282 @@
         <v>4</v>
       </c>
       <c r="G58">
-        <v>5585</v>
+        <v>14406</v>
       </c>
       <c r="H58" t="s">
         <v>21</v>
       </c>
       <c r="I58">
-        <v>120.3</v>
+        <v>86.2</v>
       </c>
       <c r="J58" t="s">
         <v>22</v>
       </c>
       <c r="K58">
-        <v>17</v>
+        <v>20.5</v>
       </c>
       <c r="L58" t="s">
         <v>135</v>
       </c>
       <c r="M58">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="N58" t="s">
         <v>171</v>
       </c>
       <c r="O58">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="P58" t="s">
         <v>172</v>
       </c>
       <c r="Q58">
-        <v>18</v>
+        <v>23.5</v>
       </c>
       <c r="R58" t="s">
         <v>135</v>
       </c>
       <c r="S58">
-        <v>36</v>
+        <v>33.5</v>
       </c>
       <c r="T58" t="s">
         <v>135</v>
+      </c>
+      <c r="U58">
+        <v>215.16</v>
       </c>
       <c r="V58" t="s">
         <v>173</v>
       </c>
       <c r="W58">
-        <v>152</v>
+        <v>149.69999999999999</v>
       </c>
       <c r="X58" t="s">
         <v>174</v>
       </c>
       <c r="Y58">
-        <v>124</v>
+        <v>120.2</v>
       </c>
       <c r="Z58" t="s">
         <v>174</v>
       </c>
-      <c r="AA58">
-        <v>14.19</v>
-      </c>
       <c r="AB58" t="s">
         <v>174</v>
       </c>
       <c r="AC58">
-        <v>60.4</v>
+        <v>95.3</v>
       </c>
       <c r="AD58" t="s">
         <v>19</v>
       </c>
       <c r="AE58">
-        <v>281</v>
+        <v>309</v>
       </c>
       <c r="AF58" t="s">
         <v>135</v>
       </c>
       <c r="AG58">
-        <v>345</v>
+        <v>384</v>
       </c>
       <c r="AH58" t="s">
         <v>135</v>
       </c>
       <c r="AI58">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="AJ58" t="s">
         <v>135</v>
       </c>
       <c r="AK58">
-        <v>15.6</v>
+        <v>11.45</v>
       </c>
       <c r="AL58" t="s">
         <v>175</v>
       </c>
       <c r="AM58">
-        <v>2.15</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="AN58" t="s">
         <v>174</v>
       </c>
       <c r="AO58">
-        <v>1.95</v>
+        <v>8.4600000000000005E-3</v>
       </c>
       <c r="AP58" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="AQ58">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="AR58" t="s">
         <v>135</v>
       </c>
-      <c r="AS58">
-        <v>919.2</v>
+      <c r="AS58" s="7" t="s">
+        <v>231</v>
       </c>
       <c r="AT58" t="s">
         <v>177</v>
       </c>
       <c r="AU58">
-        <v>164.58</v>
+        <v>163.30000000000001</v>
       </c>
       <c r="AV58" t="s">
         <v>20</v>
       </c>
-      <c r="BJ58">
-        <v>164.66</v>
-      </c>
-      <c r="BK58" t="s">
+      <c r="AX58" t="s">
+        <v>174</v>
+      </c>
+      <c r="AZ58" t="s">
+        <v>174</v>
+      </c>
+      <c r="BB58" t="s">
+        <v>205</v>
+      </c>
+      <c r="BD58" t="s">
+        <v>135</v>
+      </c>
+      <c r="BF58" t="s">
+        <v>135</v>
+      </c>
+      <c r="BH58" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI58">
+        <v>163.5</v>
+      </c>
+      <c r="BJ58" t="s">
         <v>20</v>
+      </c>
+      <c r="BK58">
+        <v>1000</v>
+      </c>
+      <c r="BL58" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM58">
+        <v>25</v>
+      </c>
+      <c r="BN58" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP58" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="59" spans="2:70" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="6" t="s">
-        <v>218</v>
+      <c r="B59" s="2">
+        <v>5933</v>
       </c>
       <c r="D59" s="5">
         <v>100</v>
       </c>
-      <c r="E59" s="5" t="s">
+      <c r="E59" t="s">
         <v>171</v>
       </c>
       <c r="F59" s="5">
         <v>5</v>
       </c>
-      <c r="G59" s="5">
-        <v>6570</v>
-      </c>
-      <c r="H59" s="5" t="s">
+      <c r="G59">
+        <v>16913</v>
+      </c>
+      <c r="H59" t="s">
         <v>21</v>
       </c>
-      <c r="I59" s="5">
-        <v>127</v>
-      </c>
-      <c r="J59" s="5" t="s">
+      <c r="I59">
+        <v>91</v>
+      </c>
+      <c r="J59" t="s">
         <v>22</v>
       </c>
       <c r="K59" s="5">
-        <v>17</v>
-      </c>
-      <c r="L59" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L59" t="s">
         <v>135</v>
       </c>
       <c r="M59" s="5">
-        <v>30</v>
-      </c>
-      <c r="N59" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N59" t="s">
         <v>171</v>
       </c>
       <c r="O59" s="5">
-        <v>1021</v>
-      </c>
-      <c r="P59" s="5" t="s">
+        <v>1023</v>
+      </c>
+      <c r="P59" t="s">
         <v>172</v>
       </c>
       <c r="Q59" s="5">
-        <v>18</v>
-      </c>
-      <c r="R59" s="5" t="s">
+        <v>24.3</v>
+      </c>
+      <c r="R59" t="s">
         <v>135</v>
       </c>
       <c r="S59" s="5">
-        <v>36</v>
-      </c>
-      <c r="T59" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="U59" s="5">
-        <v>220</v>
-      </c>
-      <c r="V59" s="5" t="s">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="T59" t="s">
+        <v>135</v>
+      </c>
+      <c r="U59">
+        <v>289.60000000000002</v>
+      </c>
+      <c r="V59" t="s">
         <v>173</v>
       </c>
       <c r="W59" s="5">
-        <v>151.80000000000001</v>
-      </c>
-      <c r="X59" s="5" t="s">
+        <v>149.30000000000001</v>
+      </c>
+      <c r="X59" t="s">
         <v>174</v>
       </c>
       <c r="Y59" s="5">
-        <v>148.19999999999999</v>
-      </c>
-      <c r="Z59" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA59" s="5">
-        <v>15.82</v>
-      </c>
-      <c r="AB59" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>174</v>
+      </c>
+      <c r="AB59" t="s">
         <v>174</v>
       </c>
       <c r="AC59" s="5">
-        <v>67.400000000000006</v>
+        <v>106.2</v>
       </c>
       <c r="AD59" s="5" t="s">
         <v>19</v>
       </c>
       <c r="AE59" s="5">
-        <v>293</v>
-      </c>
-      <c r="AF59" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="AF59" t="s">
         <v>135</v>
       </c>
       <c r="AG59" s="5">
-        <v>375</v>
-      </c>
-      <c r="AH59" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="AH59" t="s">
         <v>135</v>
       </c>
       <c r="AI59" s="5">
-        <v>220</v>
-      </c>
-      <c r="AJ59" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="AJ59" t="s">
         <v>135</v>
       </c>
       <c r="AK59" s="5">
-        <v>17</v>
-      </c>
-      <c r="AL59" s="5" t="s">
+        <v>12.4</v>
+      </c>
+      <c r="AL59" t="s">
         <v>175</v>
       </c>
       <c r="AM59" s="5">
-        <v>2.7</v>
-      </c>
-      <c r="AN59" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="AO59" s="5">
-        <v>2.5</v>
-      </c>
-      <c r="AP59" s="5" t="s">
-        <v>174</v>
+        <v>2.58</v>
+      </c>
+      <c r="AN59" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO59">
+        <v>1.1010000000000001E-2</v>
+      </c>
+      <c r="AP59" t="s">
+        <v>205</v>
       </c>
       <c r="AQ59" s="5">
-        <v>28</v>
-      </c>
-      <c r="AR59" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="AS59" s="5">
-        <v>1107</v>
-      </c>
-      <c r="AT59" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR59" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS59" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="AT59" t="s">
         <v>177</v>
       </c>
       <c r="AU59" s="5">
-        <v>168.49</v>
-      </c>
-      <c r="AV59" s="5" t="s">
+        <v>167.2</v>
+      </c>
+      <c r="AV59" t="s">
         <v>20</v>
       </c>
-      <c r="BJ59" s="5">
-        <v>168.37</v>
-      </c>
-      <c r="BK59" s="5" t="s">
+      <c r="AW59" s="8"/>
+      <c r="AX59" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY59" s="8"/>
+      <c r="AZ59" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA59" s="8"/>
+      <c r="BB59" t="s">
+        <v>205</v>
+      </c>
+      <c r="BD59" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE59" s="8"/>
+      <c r="BF59" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG59" s="8"/>
+      <c r="BH59" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI59" s="5">
+        <v>167.4</v>
+      </c>
+      <c r="BJ59" t="s">
         <v>20</v>
+      </c>
+      <c r="BK59" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BL59" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM59" s="5">
+        <v>25</v>
+      </c>
+      <c r="BN59" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO59" s="5">
+        <v>25</v>
+      </c>
+      <c r="BP59" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="60" spans="2:70" x14ac:dyDescent="0.3">
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="D60">
-        <v>110</v>
-      </c>
-      <c r="E60" t="s">
+      <c r="C60" s="14"/>
+      <c r="D60" s="10">
+        <v>25</v>
+      </c>
+      <c r="E60" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="F60">
-        <v>6</v>
-      </c>
-      <c r="G60">
-        <v>7227</v>
-      </c>
-      <c r="H60" t="s">
+      <c r="F60" s="10">
+        <v>1</v>
+      </c>
+      <c r="G60" s="10">
+        <v>1643</v>
+      </c>
+      <c r="H60" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I60">
-        <v>131.1</v>
-      </c>
-      <c r="J60" t="s">
+      <c r="I60" s="10">
+        <v>80</v>
+      </c>
+      <c r="J60" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K60">
+      <c r="K60" s="10">
+        <v>14</v>
+      </c>
+      <c r="L60" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="M60" s="10">
+        <v>24</v>
+      </c>
+      <c r="N60" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="O60" s="10">
+        <v>1023</v>
+      </c>
+      <c r="P60" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q60" s="10">
         <v>17</v>
       </c>
-      <c r="L60" t="s">
-        <v>135</v>
-      </c>
-      <c r="M60">
-        <v>26</v>
-      </c>
-      <c r="N60" t="s">
-        <v>171</v>
-      </c>
-      <c r="O60">
-        <v>1021</v>
-      </c>
-      <c r="P60" t="s">
+      <c r="R60" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="S60" s="10">
+        <v>37</v>
+      </c>
+      <c r="T60" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="U60" s="10">
+        <v>40</v>
+      </c>
+      <c r="V60" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="W60" s="10">
+        <v>65.400000000000006</v>
+      </c>
+      <c r="X60" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y60" s="10">
+        <v>57.2</v>
+      </c>
+      <c r="Z60" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA60" s="10">
+        <v>6.28</v>
+      </c>
+      <c r="AB60" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC60" s="10">
+        <v>25.4</v>
+      </c>
+      <c r="AD60" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE60" s="10">
+        <v>233</v>
+      </c>
+      <c r="AF60" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG60" s="10">
+        <v>285</v>
+      </c>
+      <c r="AH60" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI60" s="10">
+        <v>235</v>
+      </c>
+      <c r="AJ60" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK60" s="10">
+        <v>8.0790000000000006</v>
+      </c>
+      <c r="AL60" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM60" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AN60" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO60" s="10">
+        <v>0.40799999999999997</v>
+      </c>
+      <c r="AP60" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="AQ60" s="10">
+        <v>30</v>
+      </c>
+      <c r="AR60" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS60" s="10">
+        <v>300.60000000000002</v>
+      </c>
+      <c r="AT60" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU60" s="10">
+        <v>183.01</v>
+      </c>
+      <c r="AV60" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW60" s="10">
+        <v>75</v>
+      </c>
+      <c r="AX60" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY60" s="10">
+        <v>52</v>
+      </c>
+      <c r="AZ60" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA60" s="10">
+        <v>0.35699999999999998</v>
+      </c>
+      <c r="BB60" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="BC60" s="10">
+        <v>295</v>
+      </c>
+      <c r="BD60" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE60" s="10">
+        <v>235</v>
+      </c>
+      <c r="BF60" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG60" s="10">
+        <v>7</v>
+      </c>
+      <c r="BH60" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI60" s="10">
+        <v>183.02</v>
+      </c>
+      <c r="BJ60" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK60" s="14"/>
+      <c r="BL60" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="Q60">
-        <v>18</v>
-      </c>
-      <c r="R60" t="s">
-        <v>135</v>
-      </c>
-      <c r="S60">
-        <v>38</v>
-      </c>
-      <c r="T60" t="s">
-        <v>135</v>
-      </c>
-      <c r="U60">
-        <v>240</v>
-      </c>
-      <c r="V60" t="s">
+      <c r="BM60" s="14"/>
+      <c r="BN60" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO60" s="14"/>
+      <c r="BP60" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ60" s="14"/>
+      <c r="BR60" s="13" t="s">
         <v>173</v>
-      </c>
-      <c r="W60">
-        <v>153.80000000000001</v>
-      </c>
-      <c r="X60" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y60">
-        <v>155.80000000000001</v>
-      </c>
-      <c r="Z60" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA60">
-        <v>16.850000000000001</v>
-      </c>
-      <c r="AB60" t="s">
-        <v>174</v>
-      </c>
-      <c r="AC60">
-        <v>69.8</v>
-      </c>
-      <c r="AD60" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE60">
-        <v>304</v>
-      </c>
-      <c r="AF60" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG60">
-        <v>390</v>
-      </c>
-      <c r="AH60" t="s">
-        <v>135</v>
-      </c>
-      <c r="AI60">
-        <v>220</v>
-      </c>
-      <c r="AJ60" t="s">
-        <v>135</v>
-      </c>
-      <c r="AK60">
-        <v>17.600000000000001</v>
-      </c>
-      <c r="AL60" t="s">
-        <v>175</v>
-      </c>
-      <c r="AM60">
-        <v>2.85</v>
-      </c>
-      <c r="AN60" t="s">
-        <v>174</v>
-      </c>
-      <c r="AO60">
-        <v>2.65</v>
-      </c>
-      <c r="AP60" t="s">
-        <v>174</v>
-      </c>
-      <c r="AQ60">
-        <v>29</v>
-      </c>
-      <c r="AR60" t="s">
-        <v>135</v>
-      </c>
-      <c r="AS60">
-        <v>1236</v>
-      </c>
-      <c r="AT60" t="s">
-        <v>177</v>
-      </c>
-      <c r="AU60">
-        <v>171.03</v>
-      </c>
-      <c r="AV60" t="s">
-        <v>20</v>
-      </c>
-      <c r="BJ60">
-        <v>170.8</v>
-      </c>
-      <c r="BK60" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="61" spans="2:70" x14ac:dyDescent="0.3">
-      <c r="B61" s="3"/>
+      <c r="B61" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="C61" s="14"/>
+      <c r="D61" s="10">
+        <v>50</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="F61" s="10">
+        <v>2</v>
+      </c>
+      <c r="G61" s="10">
+        <v>3285</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I61" s="10">
+        <v>100.8</v>
+      </c>
+      <c r="J61" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K61" s="10">
+        <v>14</v>
+      </c>
+      <c r="L61" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="M61" s="10">
+        <v>28</v>
+      </c>
+      <c r="N61" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="O61" s="10">
+        <v>1023</v>
+      </c>
+      <c r="P61" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q61" s="10">
+        <v>17</v>
+      </c>
+      <c r="R61" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="S61" s="10">
+        <v>35</v>
+      </c>
+      <c r="T61" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="U61" s="10">
+        <v>90</v>
+      </c>
+      <c r="V61" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="W61" s="10">
+        <v>99.2</v>
+      </c>
+      <c r="X61" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y61" s="10">
+        <v>81.599999999999994</v>
+      </c>
+      <c r="Z61" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA61" s="10">
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="AB61" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC61" s="10">
+        <v>39.6</v>
+      </c>
+      <c r="AD61" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE61" s="10">
+        <v>256</v>
+      </c>
+      <c r="AF61" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG61" s="10">
+        <v>320</v>
+      </c>
+      <c r="AH61" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI61" s="10">
+        <v>225</v>
+      </c>
+      <c r="AJ61" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK61" s="10">
+        <v>12.077999999999999</v>
+      </c>
+      <c r="AL61" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM61" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AN61" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO61" s="10">
+        <v>0.96899999999999997</v>
+      </c>
+      <c r="AP61" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="AQ61" s="10">
+        <v>30</v>
+      </c>
+      <c r="AR61" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS61" s="10">
+        <v>561</v>
+      </c>
+      <c r="AT61" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU61" s="10">
+        <v>170.78</v>
+      </c>
+      <c r="AV61" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW61" s="10">
+        <v>105.2</v>
+      </c>
+      <c r="AX61" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY61" s="10">
+        <v>78.400000000000006</v>
+      </c>
+      <c r="AZ61" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA61" s="10">
+        <v>1.02</v>
+      </c>
+      <c r="BB61" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="BC61" s="10">
+        <v>325</v>
+      </c>
+      <c r="BD61" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE61" s="10">
+        <v>235</v>
+      </c>
+      <c r="BF61" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG61" s="10">
+        <v>12.6</v>
+      </c>
+      <c r="BH61" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI61" s="10">
+        <v>168.43</v>
+      </c>
+      <c r="BJ61" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK61" s="14"/>
+      <c r="BL61" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM61" s="14"/>
+      <c r="BN61" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO61" s="14"/>
+      <c r="BP61" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ61" s="14"/>
+      <c r="BR61" s="13" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="62" spans="2:70" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="5">
-        <v>774</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="D62" s="5">
-        <v>25</v>
-      </c>
-      <c r="E62" s="5" t="s">
+      <c r="B62" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="C62" s="14"/>
+      <c r="D62" s="10">
+        <v>75</v>
+      </c>
+      <c r="E62" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="F62" s="5">
-        <v>1</v>
-      </c>
-      <c r="G62" s="5">
-        <v>2440</v>
-      </c>
-      <c r="H62" s="5" t="s">
+      <c r="F62" s="10">
+        <v>3</v>
+      </c>
+      <c r="G62" s="10">
+        <v>4928</v>
+      </c>
+      <c r="H62" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I62" s="5">
-        <v>58</v>
-      </c>
-      <c r="J62" s="5" t="s">
+      <c r="I62" s="10">
+        <v>115.4</v>
+      </c>
+      <c r="J62" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K62" s="5">
-        <v>13</v>
-      </c>
-      <c r="L62" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="M62" s="5">
-        <v>64</v>
-      </c>
-      <c r="N62" s="5" t="s">
+      <c r="K62" s="10">
+        <v>16</v>
+      </c>
+      <c r="L62" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="M62" s="10">
+        <v>34</v>
+      </c>
+      <c r="N62" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="O62" s="5">
-        <v>1028</v>
-      </c>
-      <c r="P62" s="5" t="s">
+      <c r="O62" s="10">
+        <v>1022</v>
+      </c>
+      <c r="P62" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="Q62" s="5">
-        <v>14.2</v>
-      </c>
-      <c r="R62" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="S62" s="5">
-        <v>21</v>
+      <c r="Q62" s="10">
+        <v>18</v>
+      </c>
+      <c r="R62" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="S62" s="10">
+        <v>36</v>
       </c>
       <c r="T62" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="U62" s="5">
-        <v>17</v>
+      <c r="U62" s="10">
+        <v>126</v>
       </c>
       <c r="V62" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="W62" s="5">
-        <v>80.2</v>
+      <c r="W62" s="10">
+        <v>140.19999999999999</v>
       </c>
       <c r="X62" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="Y62" s="5">
-        <v>50.6</v>
+      <c r="Y62" s="10">
+        <v>115</v>
       </c>
       <c r="Z62" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="AA62" s="5">
-        <v>7.91</v>
+      <c r="AA62" s="10">
+        <v>13.06</v>
       </c>
       <c r="AB62" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="AC62" s="5">
-        <v>29.5</v>
+      <c r="AC62" s="10">
+        <v>53.8</v>
       </c>
       <c r="AD62" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="AE62" s="5">
-        <v>257</v>
+        <v>19</v>
+      </c>
+      <c r="AE62" s="10">
+        <v>268</v>
       </c>
       <c r="AF62" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="AG62" s="5">
-        <v>300</v>
-      </c>
-      <c r="AH62" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="AI62" s="5">
-        <v>240</v>
-      </c>
-      <c r="AJ62" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="AK62" s="5">
-        <v>6.35</v>
-      </c>
-      <c r="AL62" s="5" t="s">
+      <c r="AG62" s="10">
+        <v>340</v>
+      </c>
+      <c r="AH62" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI62" s="10">
+        <v>210</v>
+      </c>
+      <c r="AJ62" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK62" s="10">
+        <v>14.95</v>
+      </c>
+      <c r="AL62" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="AM62" s="5">
-        <v>0.33</v>
-      </c>
-      <c r="AN62" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="AO62" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="AP62" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="AQ62" s="5">
-        <v>18</v>
-      </c>
-      <c r="AR62" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="AS62" s="5">
-        <v>434.78</v>
-      </c>
-      <c r="AT62" s="5" t="s">
+      <c r="AM62" s="10">
+        <v>1.9</v>
+      </c>
+      <c r="AN62" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO62" s="10">
+        <v>1.7849999999999999</v>
+      </c>
+      <c r="AP62" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="AQ62" s="10">
+        <v>30</v>
+      </c>
+      <c r="AR62" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS62" s="10">
+        <v>816</v>
+      </c>
+      <c r="AT62" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="AU62" s="5">
-        <v>178.19</v>
-      </c>
-      <c r="AV62" s="5" t="s">
+      <c r="AU62" s="10">
+        <v>165.6</v>
+      </c>
+      <c r="AV62" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="AW62" s="5">
-        <v>77.5</v>
-      </c>
-      <c r="AX62" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="AY62" s="5">
-        <v>46.8</v>
-      </c>
-      <c r="AZ62" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="BA62" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="BB62" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="BC62" s="5">
-        <v>321.5</v>
-      </c>
-      <c r="BD62" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="BE62" s="5">
-        <v>259.2</v>
-      </c>
-      <c r="BF62" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="BG62" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="BH62" s="5" t="s">
+      <c r="AW62" s="10">
+        <v>142.80000000000001</v>
+      </c>
+      <c r="AX62" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY62" s="10">
+        <v>113.4</v>
+      </c>
+      <c r="AZ62" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA62" s="10">
+        <v>1.7849999999999999</v>
+      </c>
+      <c r="BB62" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="BC62" s="10">
+        <v>330</v>
+      </c>
+      <c r="BD62" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE62" s="10">
+        <v>210</v>
+      </c>
+      <c r="BF62" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG62" s="10">
+        <v>14.7</v>
+      </c>
+      <c r="BH62" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="BI62" s="5">
-        <v>179.62</v>
-      </c>
-      <c r="BJ62" s="5" t="s">
+      <c r="BI62" s="10">
+        <v>163.46</v>
+      </c>
+      <c r="BJ62" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="BK62" s="5">
-        <v>1000</v>
-      </c>
-      <c r="BL62" s="5" t="s">
+      <c r="BK62" s="14"/>
+      <c r="BL62" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="BM62" s="5">
-        <v>25</v>
-      </c>
-      <c r="BN62" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="BO62" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="BP62" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="BQ62" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="BR62" s="5" t="s">
+      <c r="BM62" s="14"/>
+      <c r="BN62" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO62" s="14"/>
+      <c r="BP62" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ62" s="14"/>
+      <c r="BR62" s="13" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="63" spans="2:70" x14ac:dyDescent="0.3">
-      <c r="B63">
-        <v>774</v>
-      </c>
-      <c r="C63" t="s">
-        <v>231</v>
-      </c>
-      <c r="D63">
-        <v>50</v>
-      </c>
-      <c r="E63" t="s">
+      <c r="B63" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="C63" s="14"/>
+      <c r="D63" s="10">
+        <v>85</v>
+      </c>
+      <c r="E63" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="F63">
-        <v>2</v>
-      </c>
-      <c r="G63">
-        <v>4880</v>
-      </c>
-      <c r="H63" t="s">
+      <c r="F63" s="10">
+        <v>4</v>
+      </c>
+      <c r="G63" s="10">
+        <v>5585</v>
+      </c>
+      <c r="H63" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I63">
-        <v>74</v>
-      </c>
-      <c r="J63" t="s">
+      <c r="I63" s="10">
+        <v>120.3</v>
+      </c>
+      <c r="J63" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K63">
-        <v>14</v>
-      </c>
-      <c r="L63" t="s">
-        <v>135</v>
-      </c>
-      <c r="M63">
-        <v>65</v>
-      </c>
-      <c r="N63" t="s">
+      <c r="K63" s="10">
+        <v>17</v>
+      </c>
+      <c r="L63" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="M63" s="10">
+        <v>32</v>
+      </c>
+      <c r="N63" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="O63">
-        <v>1027</v>
-      </c>
-      <c r="P63" t="s">
+      <c r="O63" s="10">
+        <v>1021</v>
+      </c>
+      <c r="P63" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="Q63">
-        <v>15</v>
-      </c>
-      <c r="R63" t="s">
-        <v>135</v>
-      </c>
-      <c r="S63">
+      <c r="Q63" s="10"/>
+      <c r="R63" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="S63" s="10">
+        <v>36</v>
+      </c>
+      <c r="T63" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="U63" s="10"/>
+      <c r="V63" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="W63" s="10">
+        <v>152</v>
+      </c>
+      <c r="X63" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y63" s="10">
+        <v>124</v>
+      </c>
+      <c r="Z63" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA63" s="10">
+        <v>14.19</v>
+      </c>
+      <c r="AB63" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC63" s="10">
+        <v>60.4</v>
+      </c>
+      <c r="AD63" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="T63" t="s">
-        <v>135</v>
-      </c>
-      <c r="U63">
-        <v>75</v>
-      </c>
-      <c r="V63" t="s">
-        <v>173</v>
-      </c>
-      <c r="W63">
-        <v>117.8</v>
-      </c>
-      <c r="X63" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y63">
-        <v>77.400000000000006</v>
-      </c>
-      <c r="Z63" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA63">
-        <v>12.4</v>
-      </c>
-      <c r="AB63" t="s">
-        <v>174</v>
-      </c>
-      <c r="AC63">
-        <v>44.4</v>
-      </c>
-      <c r="AD63" t="s">
-        <v>171</v>
-      </c>
-      <c r="AE63">
-        <v>270</v>
-      </c>
-      <c r="AF63" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG63">
-        <v>320</v>
-      </c>
-      <c r="AH63" t="s">
-        <v>135</v>
-      </c>
-      <c r="AI63">
-        <v>220</v>
-      </c>
-      <c r="AJ63" t="s">
-        <v>135</v>
-      </c>
-      <c r="AK63">
-        <v>11.35</v>
-      </c>
-      <c r="AL63" t="s">
+      <c r="AE63" s="10">
+        <v>281</v>
+      </c>
+      <c r="AF63" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG63" s="10">
+        <v>345</v>
+      </c>
+      <c r="AH63" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI63" s="10">
+        <v>210</v>
+      </c>
+      <c r="AJ63" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK63" s="10">
+        <v>15.6</v>
+      </c>
+      <c r="AL63" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="AM63">
-        <v>1.18</v>
-      </c>
-      <c r="AN63" t="s">
-        <v>174</v>
-      </c>
-      <c r="AO63" t="s">
-        <v>231</v>
-      </c>
-      <c r="AP63" t="s">
-        <v>224</v>
-      </c>
-      <c r="AQ63">
+      <c r="AM63" s="10">
+        <v>2.15</v>
+      </c>
+      <c r="AN63" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO63" s="10">
+        <v>1.988</v>
+      </c>
+      <c r="AP63" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="AQ63" s="10">
+        <v>28</v>
+      </c>
+      <c r="AR63" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS63" s="10">
+        <v>919.2</v>
+      </c>
+      <c r="AT63" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU63" s="10">
+        <v>164.58</v>
+      </c>
+      <c r="AV63" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="AR63" t="s">
-        <v>135</v>
-      </c>
-      <c r="AS63">
-        <v>861.24</v>
-      </c>
-      <c r="AT63" t="s">
-        <v>177</v>
-      </c>
-      <c r="AU63">
-        <v>176.48</v>
-      </c>
-      <c r="AV63" t="s">
+      <c r="AW63" s="10">
+        <v>152</v>
+      </c>
+      <c r="AX63" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY63" s="10">
+        <v>124</v>
+      </c>
+      <c r="AZ63" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA63" s="10">
+        <v>2.1920000000000002</v>
+      </c>
+      <c r="BB63" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="BC63" s="10">
+        <v>345</v>
+      </c>
+      <c r="BD63" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE63" s="10">
+        <v>210</v>
+      </c>
+      <c r="BF63" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG63" s="10">
+        <v>15.6</v>
+      </c>
+      <c r="BH63" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI63" s="10">
+        <v>164.66</v>
+      </c>
+      <c r="BJ63" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="AW63">
-        <v>116.5</v>
-      </c>
-      <c r="AX63" t="s">
-        <v>174</v>
-      </c>
-      <c r="AY63">
-        <v>75.8</v>
-      </c>
-      <c r="AZ63" t="s">
-        <v>174</v>
-      </c>
-      <c r="BA63" t="s">
-        <v>231</v>
-      </c>
-      <c r="BB63" t="s">
-        <v>224</v>
-      </c>
-      <c r="BC63">
-        <v>347.7</v>
-      </c>
-      <c r="BD63" t="s">
-        <v>135</v>
-      </c>
-      <c r="BE63">
-        <v>241.7</v>
-      </c>
-      <c r="BF63" t="s">
-        <v>135</v>
-      </c>
-      <c r="BG63" t="s">
-        <v>231</v>
-      </c>
-      <c r="BH63" t="s">
-        <v>175</v>
-      </c>
-      <c r="BI63">
-        <v>178.08</v>
-      </c>
-      <c r="BJ63" t="s">
-        <v>20</v>
-      </c>
-      <c r="BK63">
-        <v>1000</v>
-      </c>
-      <c r="BL63" t="s">
+      <c r="BK63" s="14"/>
+      <c r="BL63" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="BM63">
-        <v>25</v>
-      </c>
-      <c r="BN63" t="s">
-        <v>135</v>
-      </c>
-      <c r="BO63" t="s">
-        <v>231</v>
-      </c>
-      <c r="BP63" t="s">
-        <v>135</v>
-      </c>
-      <c r="BQ63" t="s">
-        <v>231</v>
-      </c>
-      <c r="BR63" t="s">
+      <c r="BM63" s="14"/>
+      <c r="BN63" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO63" s="14"/>
+      <c r="BP63" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ63" s="14"/>
+      <c r="BR63" s="13" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="64" spans="2:70" x14ac:dyDescent="0.3">
-      <c r="B64">
-        <v>774</v>
-      </c>
-      <c r="C64" t="s">
-        <v>231</v>
-      </c>
-      <c r="D64">
-        <v>75</v>
-      </c>
-      <c r="E64" t="s">
+      <c r="B64" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="C64" s="14"/>
+      <c r="D64" s="10">
+        <v>100</v>
+      </c>
+      <c r="E64" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="F64">
-        <v>3</v>
-      </c>
-      <c r="G64">
-        <v>7320</v>
-      </c>
-      <c r="H64" t="s">
+      <c r="F64" s="10">
+        <v>5</v>
+      </c>
+      <c r="G64" s="10">
+        <v>6570</v>
+      </c>
+      <c r="H64" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I64">
-        <v>84</v>
-      </c>
-      <c r="J64" t="s">
+      <c r="I64" s="10">
+        <v>127</v>
+      </c>
+      <c r="J64" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K64">
-        <v>12</v>
-      </c>
-      <c r="L64" t="s">
-        <v>135</v>
-      </c>
-      <c r="M64">
-        <v>62</v>
-      </c>
-      <c r="N64" t="s">
+      <c r="K64" s="10">
+        <v>17</v>
+      </c>
+      <c r="L64" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="M64" s="10">
+        <v>30</v>
+      </c>
+      <c r="N64" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="O64">
-        <v>1027</v>
-      </c>
-      <c r="P64" t="s">
+      <c r="O64" s="10">
+        <v>1021</v>
+      </c>
+      <c r="P64" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="Q64">
-        <v>15.7</v>
-      </c>
-      <c r="R64" t="s">
-        <v>135</v>
-      </c>
-      <c r="S64">
-        <v>22</v>
-      </c>
-      <c r="T64" t="s">
-        <v>135</v>
-      </c>
-      <c r="U64">
-        <v>140</v>
-      </c>
-      <c r="V64" t="s">
+      <c r="Q64" s="10">
+        <v>18</v>
+      </c>
+      <c r="R64" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="S64" s="10">
+        <v>36</v>
+      </c>
+      <c r="T64" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="U64" s="10">
+        <v>220</v>
+      </c>
+      <c r="V64" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="W64">
-        <v>140.6</v>
-      </c>
-      <c r="X64" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y64">
-        <v>102.6</v>
-      </c>
-      <c r="Z64" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA64">
-        <v>16.39</v>
-      </c>
-      <c r="AB64" t="s">
-        <v>174</v>
-      </c>
-      <c r="AC64">
-        <v>57.4</v>
-      </c>
-      <c r="AD64" t="s">
-        <v>171</v>
-      </c>
-      <c r="AE64">
-        <v>295</v>
-      </c>
-      <c r="AF64" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG64">
-        <v>355</v>
-      </c>
-      <c r="AH64" t="s">
-        <v>135</v>
-      </c>
-      <c r="AI64">
-        <v>200</v>
-      </c>
-      <c r="AJ64" t="s">
-        <v>135</v>
-      </c>
-      <c r="AK64">
-        <v>14.372</v>
-      </c>
-      <c r="AL64" t="s">
+      <c r="W64" s="10">
+        <v>151.80000000000001</v>
+      </c>
+      <c r="X64" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y64" s="10">
+        <v>148.19999999999999</v>
+      </c>
+      <c r="Z64" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA64" s="10">
+        <v>15.82</v>
+      </c>
+      <c r="AB64" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC64" s="10">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="AD64" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE64" s="10">
+        <v>293</v>
+      </c>
+      <c r="AF64" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG64" s="10">
+        <v>375</v>
+      </c>
+      <c r="AH64" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI64" s="10">
+        <v>220</v>
+      </c>
+      <c r="AJ64" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK64" s="10">
+        <v>17.03</v>
+      </c>
+      <c r="AL64" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="AM64">
-        <v>2.23</v>
-      </c>
-      <c r="AN64" t="s">
-        <v>174</v>
-      </c>
-      <c r="AO64" t="s">
-        <v>231</v>
-      </c>
-      <c r="AP64" t="s">
-        <v>224</v>
-      </c>
-      <c r="AQ64">
-        <v>21</v>
-      </c>
-      <c r="AR64" t="s">
-        <v>135</v>
-      </c>
-      <c r="AS64">
-        <v>1228.67</v>
-      </c>
-      <c r="AT64" t="s">
+      <c r="AM64" s="10">
+        <v>2.7</v>
+      </c>
+      <c r="AN64" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO64" s="10">
+        <v>2.5489999999999999</v>
+      </c>
+      <c r="AP64" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="AQ64" s="10">
+        <v>28</v>
+      </c>
+      <c r="AR64" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS64" s="10">
+        <v>1107</v>
+      </c>
+      <c r="AT64" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="AU64">
-        <v>172.76</v>
-      </c>
-      <c r="AV64" t="s">
+      <c r="AU64" s="10">
+        <v>168.49</v>
+      </c>
+      <c r="AV64" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="AW64">
-        <v>139.5</v>
-      </c>
-      <c r="AX64" t="s">
-        <v>174</v>
-      </c>
-      <c r="AY64">
-        <v>101.2</v>
-      </c>
-      <c r="AZ64" t="s">
-        <v>174</v>
-      </c>
-      <c r="BA64" t="s">
-        <v>231</v>
-      </c>
-      <c r="BB64" t="s">
-        <v>224</v>
-      </c>
-      <c r="BC64">
-        <v>381.8</v>
-      </c>
-      <c r="BD64" t="s">
-        <v>135</v>
-      </c>
-      <c r="BE64">
-        <v>220.7</v>
-      </c>
-      <c r="BF64" t="s">
-        <v>135</v>
-      </c>
-      <c r="BG64" t="s">
-        <v>231</v>
-      </c>
-      <c r="BH64" t="s">
+      <c r="AW64" s="10">
+        <v>151.80000000000001</v>
+      </c>
+      <c r="AX64" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY64" s="10">
+        <v>148.19999999999999</v>
+      </c>
+      <c r="AZ64" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA64" s="10">
+        <v>2.7530000000000001</v>
+      </c>
+      <c r="BB64" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="BC64" s="10">
+        <v>375</v>
+      </c>
+      <c r="BD64" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE64" s="10">
+        <v>220</v>
+      </c>
+      <c r="BF64" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG64" s="10">
+        <v>17</v>
+      </c>
+      <c r="BH64" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="BI64">
-        <v>169.05</v>
-      </c>
-      <c r="BJ64" t="s">
+      <c r="BI64" s="10">
+        <v>168.37</v>
+      </c>
+      <c r="BJ64" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="BK64">
-        <v>1000</v>
-      </c>
-      <c r="BL64" t="s">
+      <c r="BK64" s="14"/>
+      <c r="BL64" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="BM64">
-        <v>25</v>
-      </c>
-      <c r="BN64" t="s">
-        <v>135</v>
-      </c>
-      <c r="BO64" t="s">
-        <v>231</v>
-      </c>
-      <c r="BP64" t="s">
-        <v>135</v>
-      </c>
-      <c r="BQ64" t="s">
-        <v>231</v>
-      </c>
-      <c r="BR64" t="s">
+      <c r="BM64" s="14"/>
+      <c r="BN64" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO64" s="14"/>
+      <c r="BP64" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ64" s="14"/>
+      <c r="BR64" s="13" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="65" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="B65">
-        <v>774</v>
-      </c>
-      <c r="C65" t="s">
-        <v>231</v>
-      </c>
-      <c r="D65">
-        <v>85</v>
-      </c>
-      <c r="E65" t="s">
+      <c r="B65" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="C65" s="14"/>
+      <c r="D65" s="10">
+        <v>100</v>
+      </c>
+      <c r="E65" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="F65">
-        <v>4</v>
-      </c>
-      <c r="G65">
-        <v>8296</v>
-      </c>
-      <c r="H65" t="s">
+      <c r="F65" s="10">
+        <v>6</v>
+      </c>
+      <c r="G65" s="10">
+        <v>6570</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I65">
-        <v>88</v>
-      </c>
-      <c r="J65" t="s">
+      <c r="I65" s="10">
+        <v>127</v>
+      </c>
+      <c r="J65" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K65">
-        <v>12</v>
-      </c>
-      <c r="L65" t="s">
-        <v>135</v>
-      </c>
-      <c r="M65">
-        <v>62</v>
-      </c>
-      <c r="N65" t="s">
+      <c r="K65" s="10">
+        <v>17</v>
+      </c>
+      <c r="L65" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="M65" s="10">
+        <v>30</v>
+      </c>
+      <c r="N65" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="O65">
-        <v>1027</v>
-      </c>
-      <c r="P65" t="s">
+      <c r="O65" s="10">
+        <v>1021</v>
+      </c>
+      <c r="P65" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="Q65">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="R65" t="s">
-        <v>135</v>
-      </c>
-      <c r="S65">
-        <v>27</v>
-      </c>
-      <c r="T65" t="s">
-        <v>135</v>
-      </c>
-      <c r="U65">
-        <v>190</v>
-      </c>
-      <c r="V65" t="s">
+      <c r="Q65" s="10">
+        <v>18</v>
+      </c>
+      <c r="R65" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="S65" s="10">
+        <v>37</v>
+      </c>
+      <c r="T65" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="U65" s="10">
+        <v>220</v>
+      </c>
+      <c r="V65" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="W65">
-        <v>152.19999999999999</v>
-      </c>
-      <c r="X65" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y65">
-        <v>114.6</v>
-      </c>
-      <c r="Z65" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA65">
-        <v>17.73</v>
-      </c>
-      <c r="AB65" t="s">
-        <v>174</v>
-      </c>
-      <c r="AC65">
-        <v>61</v>
-      </c>
-      <c r="AD65" t="s">
-        <v>171</v>
-      </c>
-      <c r="AE65">
-        <v>310</v>
-      </c>
-      <c r="AF65" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG65">
+      <c r="W65" s="10">
+        <v>151.6</v>
+      </c>
+      <c r="X65" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y65" s="10">
+        <v>147.4</v>
+      </c>
+      <c r="Z65" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA65" s="10">
+        <v>15.82</v>
+      </c>
+      <c r="AB65" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC65" s="10">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="AD65" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE65" s="10">
+        <v>293</v>
+      </c>
+      <c r="AF65" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG65" s="10">
         <v>375</v>
       </c>
-      <c r="AH65" t="s">
-        <v>135</v>
-      </c>
-      <c r="AI65">
+      <c r="AH65" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI65" s="10">
+        <v>215</v>
+      </c>
+      <c r="AJ65" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK65" s="10">
+        <v>16.97</v>
+      </c>
+      <c r="AL65" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM65" s="10">
+        <v>2.65</v>
+      </c>
+      <c r="AN65" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO65" s="10">
+        <v>2.4980000000000002</v>
+      </c>
+      <c r="AP65" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="AJ65" t="s">
-        <v>135</v>
-      </c>
-      <c r="AK65">
-        <v>15.108000000000001</v>
-      </c>
-      <c r="AL65" t="s">
+      <c r="AQ65" s="10">
+        <v>28</v>
+      </c>
+      <c r="AR65" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS65" s="10">
+        <v>1107</v>
+      </c>
+      <c r="AT65" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU65" s="10">
+        <v>168.49</v>
+      </c>
+      <c r="AV65" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW65" s="10">
+        <v>151.6</v>
+      </c>
+      <c r="AX65" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY65" s="10">
+        <v>147.4</v>
+      </c>
+      <c r="AZ65" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA65" s="10">
+        <v>2.702</v>
+      </c>
+      <c r="BB65" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="BC65" s="10">
+        <v>375</v>
+      </c>
+      <c r="BD65" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE65" s="10">
+        <v>215</v>
+      </c>
+      <c r="BF65" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG65" s="10">
+        <v>17</v>
+      </c>
+      <c r="BH65" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="AM65">
-        <v>2.56</v>
-      </c>
-      <c r="AN65" t="s">
-        <v>174</v>
-      </c>
-      <c r="AO65" t="s">
-        <v>231</v>
-      </c>
-      <c r="AP65" t="s">
-        <v>224</v>
-      </c>
-      <c r="AQ65">
-        <v>22</v>
-      </c>
-      <c r="AR65" t="s">
-        <v>135</v>
-      </c>
-      <c r="AS65">
-        <v>1422.92</v>
-      </c>
-      <c r="AT65" t="s">
-        <v>177</v>
-      </c>
-      <c r="AU65">
-        <v>171.52</v>
-      </c>
-      <c r="AV65" t="s">
+      <c r="BI65" s="10">
+        <v>168.58</v>
+      </c>
+      <c r="BJ65" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="AW65">
-        <v>152.19999999999999</v>
-      </c>
-      <c r="AX65" t="s">
-        <v>174</v>
-      </c>
-      <c r="AY65">
-        <v>111</v>
-      </c>
-      <c r="AZ65" t="s">
-        <v>174</v>
-      </c>
-      <c r="BA65" t="s">
-        <v>231</v>
-      </c>
-      <c r="BB65" t="s">
-        <v>224</v>
-      </c>
-      <c r="BC65">
-        <v>397.1</v>
-      </c>
-      <c r="BD65" t="s">
-        <v>135</v>
-      </c>
-      <c r="BE65">
-        <v>220.9</v>
-      </c>
-      <c r="BF65" t="s">
-        <v>135</v>
-      </c>
-      <c r="BG65" t="s">
-        <v>231</v>
-      </c>
-      <c r="BH65" t="s">
-        <v>175</v>
-      </c>
-      <c r="BI65">
-        <v>172.2</v>
-      </c>
-      <c r="BJ65" t="s">
-        <v>20</v>
-      </c>
-      <c r="BK65">
-        <v>1000</v>
-      </c>
-      <c r="BL65" t="s">
+      <c r="BK65" s="14"/>
+      <c r="BL65" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="BM65">
-        <v>25</v>
-      </c>
-      <c r="BN65" t="s">
-        <v>135</v>
-      </c>
-      <c r="BO65" t="s">
-        <v>231</v>
-      </c>
-      <c r="BP65" t="s">
-        <v>135</v>
-      </c>
-      <c r="BQ65" t="s">
-        <v>231</v>
-      </c>
-      <c r="BR65" t="s">
+      <c r="BM65" s="14"/>
+      <c r="BN65" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO65" s="14"/>
+      <c r="BP65" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ65" s="14"/>
+      <c r="BR65" s="13" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="66" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="B66">
-        <v>774</v>
-      </c>
-      <c r="C66" t="s">
-        <v>231</v>
-      </c>
-      <c r="D66">
-        <v>100</v>
-      </c>
-      <c r="E66" t="s">
+      <c r="B66" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="C66" s="14"/>
+      <c r="D66" s="10">
+        <v>110</v>
+      </c>
+      <c r="E66" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="F66">
-        <v>5</v>
-      </c>
-      <c r="G66">
-        <v>9760</v>
-      </c>
-      <c r="H66" t="s">
+      <c r="F66" s="10">
+        <v>7</v>
+      </c>
+      <c r="G66" s="10">
+        <v>7227</v>
+      </c>
+      <c r="H66" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I66">
-        <v>93</v>
-      </c>
-      <c r="J66" t="s">
+      <c r="I66" s="10">
+        <v>131.1</v>
+      </c>
+      <c r="J66" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K66">
-        <v>12</v>
-      </c>
-      <c r="L66" t="s">
-        <v>135</v>
-      </c>
-      <c r="M66">
-        <v>62</v>
-      </c>
-      <c r="N66" t="s">
+      <c r="K66" s="10">
+        <v>17</v>
+      </c>
+      <c r="L66" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="M66" s="10">
+        <v>26</v>
+      </c>
+      <c r="N66" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="O66">
-        <v>1028</v>
-      </c>
-      <c r="P66" t="s">
+      <c r="O66" s="10">
+        <v>1021</v>
+      </c>
+      <c r="P66" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="Q66">
-        <v>17</v>
-      </c>
-      <c r="R66" t="s">
-        <v>135</v>
-      </c>
-      <c r="S66">
-        <v>30</v>
-      </c>
-      <c r="T66" t="s">
-        <v>135</v>
-      </c>
-      <c r="U66">
-        <v>250</v>
-      </c>
-      <c r="V66" t="s">
+      <c r="Q66" s="10">
+        <v>18</v>
+      </c>
+      <c r="R66" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="S66" s="10">
+        <v>38</v>
+      </c>
+      <c r="T66" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="U66" s="10">
+        <v>240</v>
+      </c>
+      <c r="V66" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="W66">
-        <v>147.6</v>
-      </c>
-      <c r="X66" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y66">
-        <v>129.6</v>
-      </c>
-      <c r="Z66" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA66">
-        <v>19.739999999999998</v>
-      </c>
-      <c r="AB66" t="s">
-        <v>174</v>
-      </c>
-      <c r="AC66">
-        <v>70.5</v>
-      </c>
-      <c r="AD66" t="s">
-        <v>171</v>
-      </c>
-      <c r="AE66">
-        <v>362</v>
-      </c>
-      <c r="AF66" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG66">
-        <v>425</v>
-      </c>
-      <c r="AH66" t="s">
-        <v>135</v>
-      </c>
-      <c r="AI66">
-        <v>230</v>
-      </c>
-      <c r="AJ66" t="s">
-        <v>135</v>
-      </c>
-      <c r="AK66">
-        <v>16.654</v>
-      </c>
-      <c r="AL66" t="s">
+      <c r="W66" s="10">
+        <v>153.80000000000001</v>
+      </c>
+      <c r="X66" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y66" s="10">
+        <v>155.80000000000001</v>
+      </c>
+      <c r="Z66" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA66" s="10">
+        <v>16.850000000000001</v>
+      </c>
+      <c r="AB66" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC66" s="10">
+        <v>69.8</v>
+      </c>
+      <c r="AD66" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE66" s="10">
+        <v>304</v>
+      </c>
+      <c r="AF66" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG66" s="10">
+        <v>390</v>
+      </c>
+      <c r="AH66" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI66" s="10">
+        <v>220</v>
+      </c>
+      <c r="AJ66" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK66" s="10">
+        <v>17.608000000000001</v>
+      </c>
+      <c r="AL66" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="AM66">
-        <v>3.28</v>
-      </c>
-      <c r="AN66" t="s">
-        <v>174</v>
-      </c>
-      <c r="AO66" t="s">
-        <v>231</v>
-      </c>
-      <c r="AP66" t="s">
-        <v>224</v>
-      </c>
-      <c r="AQ66">
-        <v>24</v>
-      </c>
-      <c r="AR66" t="s">
-        <v>135</v>
-      </c>
-      <c r="AS66">
-        <v>1690.14</v>
-      </c>
-      <c r="AT66" t="s">
+      <c r="AM66" s="10">
+        <v>2.85</v>
+      </c>
+      <c r="AN66" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO66" s="10">
+        <v>2.702</v>
+      </c>
+      <c r="AP66" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="AQ66" s="10">
+        <v>29</v>
+      </c>
+      <c r="AR66" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS66" s="10">
+        <v>1236</v>
+      </c>
+      <c r="AT66" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="AU66">
-        <v>173.17</v>
-      </c>
-      <c r="AV66" t="s">
+      <c r="AU66" s="10">
+        <v>171.03</v>
+      </c>
+      <c r="AV66" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="AW66">
-        <v>147.6</v>
-      </c>
-      <c r="AX66" t="s">
-        <v>174</v>
-      </c>
-      <c r="AY66">
-        <v>126.2</v>
-      </c>
-      <c r="AZ66" t="s">
-        <v>174</v>
-      </c>
-      <c r="BA66" t="s">
-        <v>231</v>
-      </c>
-      <c r="BB66" t="s">
-        <v>224</v>
-      </c>
-      <c r="BC66">
-        <v>446.8</v>
-      </c>
-      <c r="BD66" t="s">
-        <v>135</v>
-      </c>
-      <c r="BE66">
-        <v>245.6</v>
-      </c>
-      <c r="BF66" t="s">
-        <v>135</v>
-      </c>
-      <c r="BG66" t="s">
-        <v>231</v>
-      </c>
-      <c r="BH66" t="s">
+      <c r="AW66" s="10">
+        <v>153.80000000000001</v>
+      </c>
+      <c r="AX66" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY66" s="10">
+        <v>155.80000000000001</v>
+      </c>
+      <c r="AZ66" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA66" s="10">
+        <v>2.9060000000000001</v>
+      </c>
+      <c r="BB66" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="BC66" s="10">
+        <v>390</v>
+      </c>
+      <c r="BD66" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE66" s="10">
+        <v>220</v>
+      </c>
+      <c r="BF66" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG66" s="10">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="BH66" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="BI66">
-        <v>173.54</v>
-      </c>
-      <c r="BJ66" t="s">
+      <c r="BI66" s="10">
+        <v>170.8</v>
+      </c>
+      <c r="BJ66" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="BK66">
-        <v>1000</v>
-      </c>
-      <c r="BL66" t="s">
+      <c r="BK66" s="14"/>
+      <c r="BL66" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="BM66">
-        <v>25</v>
-      </c>
-      <c r="BN66" t="s">
-        <v>135</v>
-      </c>
-      <c r="BO66" t="s">
-        <v>231</v>
-      </c>
-      <c r="BP66" t="s">
-        <v>135</v>
-      </c>
-      <c r="BQ66" t="s">
-        <v>231</v>
-      </c>
-      <c r="BR66" t="s">
+      <c r="BM66" s="14"/>
+      <c r="BN66" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO66" s="14"/>
+      <c r="BP66" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ66" s="14"/>
+      <c r="BR66" s="13" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="67" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="B67">
+      <c r="B67" s="15">
         <v>774</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="5"/>
+      <c r="D67" s="5">
+        <v>25</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="F67" s="5">
+        <v>1</v>
+      </c>
+      <c r="G67" s="5">
+        <v>2440</v>
+      </c>
+      <c r="H67" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I67" s="5">
+        <v>58</v>
+      </c>
+      <c r="J67" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K67" s="5">
+        <v>13</v>
+      </c>
+      <c r="L67" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="M67" s="5">
+        <v>64</v>
+      </c>
+      <c r="N67" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="O67" s="5">
+        <v>1028</v>
+      </c>
+      <c r="P67" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q67" s="5">
+        <v>14.2</v>
+      </c>
+      <c r="R67" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="S67" s="5">
+        <v>21</v>
+      </c>
+      <c r="T67" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="U67" s="5">
+        <v>17</v>
+      </c>
+      <c r="V67" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="W67" s="5">
+        <v>80.2</v>
+      </c>
+      <c r="X67" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y67" s="5">
+        <v>50.6</v>
+      </c>
+      <c r="Z67" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA67" s="5">
+        <v>7.91</v>
+      </c>
+      <c r="AB67" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC67" s="5">
+        <v>29.5</v>
+      </c>
+      <c r="AD67" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE67" s="5">
+        <v>257</v>
+      </c>
+      <c r="AF67" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG67" s="5">
+        <v>300</v>
+      </c>
+      <c r="AH67" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI67" s="5">
+        <v>240</v>
+      </c>
+      <c r="AJ67" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK67" s="5">
+        <v>6.35</v>
+      </c>
+      <c r="AL67" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM67" s="5">
+        <v>0.33</v>
+      </c>
+      <c r="AN67" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO67" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="D67">
-        <v>110</v>
-      </c>
-      <c r="E67" t="s">
-        <v>171</v>
-      </c>
-      <c r="F67">
-        <v>6</v>
-      </c>
-      <c r="G67">
-        <v>10736</v>
-      </c>
-      <c r="H67" t="s">
-        <v>21</v>
-      </c>
-      <c r="I67">
-        <v>96</v>
-      </c>
-      <c r="J67" t="s">
-        <v>22</v>
-      </c>
-      <c r="K67">
-        <v>13</v>
-      </c>
-      <c r="L67" t="s">
-        <v>135</v>
-      </c>
-      <c r="M67">
-        <v>62</v>
-      </c>
-      <c r="N67" t="s">
-        <v>171</v>
-      </c>
-      <c r="O67">
-        <v>1027</v>
-      </c>
-      <c r="P67" t="s">
+      <c r="AP67" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="AQ67" s="5">
+        <v>18</v>
+      </c>
+      <c r="AR67" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS67" s="5">
+        <v>434.78</v>
+      </c>
+      <c r="AT67" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU67" s="5">
+        <v>178.19</v>
+      </c>
+      <c r="AV67" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW67" s="5">
+        <v>77.5</v>
+      </c>
+      <c r="AX67" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY67" s="5">
+        <v>46.8</v>
+      </c>
+      <c r="AZ67" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA67" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="BB67" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="BC67" s="5">
+        <v>321.5</v>
+      </c>
+      <c r="BD67" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE67" s="5">
+        <v>259.2</v>
+      </c>
+      <c r="BF67" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG67" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH67" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI67" s="5">
+        <v>179.62</v>
+      </c>
+      <c r="BJ67" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK67" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BL67" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="Q67">
-        <v>18</v>
-      </c>
-      <c r="R67" t="s">
-        <v>135</v>
-      </c>
-      <c r="S67">
-        <v>28</v>
-      </c>
-      <c r="T67" t="s">
-        <v>135</v>
-      </c>
-      <c r="U67">
-        <v>285</v>
-      </c>
-      <c r="V67" t="s">
+      <c r="BM67" s="5">
+        <v>25</v>
+      </c>
+      <c r="BN67" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO67" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="BP67" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ67" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="BR67" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="W67">
-        <v>153.6</v>
-      </c>
-      <c r="X67" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y67">
-        <v>142.80000000000001</v>
-      </c>
-      <c r="Z67" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA67">
-        <v>21.03</v>
-      </c>
-      <c r="AB67" t="s">
-        <v>174</v>
-      </c>
-      <c r="AC67">
-        <v>75.3</v>
-      </c>
-      <c r="AD67" t="s">
-        <v>171</v>
-      </c>
-      <c r="AE67">
-        <v>389</v>
-      </c>
-      <c r="AF67" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG67">
-        <v>450</v>
-      </c>
-      <c r="AH67" t="s">
-        <v>135</v>
-      </c>
-      <c r="AI67">
-        <v>245</v>
-      </c>
-      <c r="AJ67" t="s">
-        <v>135</v>
-      </c>
-      <c r="AK67">
-        <v>17.189</v>
-      </c>
-      <c r="AL67" t="s">
-        <v>175</v>
-      </c>
-      <c r="AM67">
-        <v>3.45</v>
-      </c>
-      <c r="AN67" t="s">
-        <v>174</v>
-      </c>
-      <c r="AO67" t="s">
-        <v>231</v>
-      </c>
-      <c r="AP67" t="s">
-        <v>224</v>
-      </c>
-      <c r="AQ67">
-        <v>24</v>
-      </c>
-      <c r="AR67" t="s">
-        <v>135</v>
-      </c>
-      <c r="AS67">
-        <v>1935.48</v>
-      </c>
-      <c r="AT67" t="s">
-        <v>177</v>
-      </c>
-      <c r="AU67">
-        <v>180.28</v>
-      </c>
-      <c r="AV67" t="s">
-        <v>20</v>
-      </c>
-      <c r="AW67">
-        <v>153.6</v>
-      </c>
-      <c r="AX67" t="s">
-        <v>174</v>
-      </c>
-      <c r="AY67">
-        <v>140.80000000000001</v>
-      </c>
-      <c r="AZ67" t="s">
-        <v>174</v>
-      </c>
-      <c r="BA67" t="s">
-        <v>231</v>
-      </c>
-      <c r="BB67" t="s">
-        <v>224</v>
-      </c>
-      <c r="BC67">
-        <v>473.9</v>
-      </c>
-      <c r="BD67" t="s">
-        <v>135</v>
-      </c>
-      <c r="BE67">
-        <v>261</v>
-      </c>
-      <c r="BF67" t="s">
-        <v>135</v>
-      </c>
-      <c r="BG67" t="s">
-        <v>231</v>
-      </c>
-      <c r="BH67" t="s">
-        <v>175</v>
-      </c>
-      <c r="BI67">
-        <v>180.84</v>
-      </c>
-      <c r="BJ67" t="s">
-        <v>20</v>
-      </c>
-      <c r="BK67">
-        <v>1000</v>
-      </c>
-      <c r="BL67" t="s">
-        <v>172</v>
-      </c>
-      <c r="BM67">
-        <v>25</v>
-      </c>
-      <c r="BN67" t="s">
-        <v>135</v>
-      </c>
-      <c r="BO67" t="s">
-        <v>231</v>
-      </c>
-      <c r="BP67" t="s">
-        <v>135</v>
-      </c>
-      <c r="BQ67" t="s">
-        <v>231</v>
-      </c>
-      <c r="BR67" t="s">
-        <v>173</v>
-      </c>
+      <c r="BS67" s="5"/>
+      <c r="BT67" s="5"/>
     </row>
     <row r="68" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="B68">
+      <c r="B68" s="2">
         <v>774</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="13"/>
+      <c r="D68" s="13">
+        <v>50</v>
+      </c>
+      <c r="E68" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="F68" s="13">
+        <v>2</v>
+      </c>
+      <c r="G68" s="13">
+        <v>4880</v>
+      </c>
+      <c r="H68" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I68" s="13">
+        <v>74</v>
+      </c>
+      <c r="J68" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K68" s="13">
+        <v>14</v>
+      </c>
+      <c r="L68" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="M68" s="13">
+        <v>65</v>
+      </c>
+      <c r="N68" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="O68" s="13">
+        <v>1027</v>
+      </c>
+      <c r="P68" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q68" s="13">
+        <v>15</v>
+      </c>
+      <c r="R68" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="S68" s="13">
+        <v>19</v>
+      </c>
+      <c r="T68" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="U68" s="13">
+        <v>75</v>
+      </c>
+      <c r="V68" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="W68" s="13">
+        <v>117.8</v>
+      </c>
+      <c r="X68" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y68" s="13">
+        <v>77.400000000000006</v>
+      </c>
+      <c r="Z68" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA68" s="13">
+        <v>12.4</v>
+      </c>
+      <c r="AB68" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC68" s="13">
+        <v>44.4</v>
+      </c>
+      <c r="AD68" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE68" s="13">
+        <v>270</v>
+      </c>
+      <c r="AF68" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG68" s="13">
+        <v>320</v>
+      </c>
+      <c r="AH68" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI68" s="13">
+        <v>220</v>
+      </c>
+      <c r="AJ68" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK68" s="13">
+        <v>11.35</v>
+      </c>
+      <c r="AL68" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM68" s="13">
+        <v>1.18</v>
+      </c>
+      <c r="AN68" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO68" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="D68">
-        <v>100</v>
-      </c>
-      <c r="E68" t="s">
-        <v>171</v>
-      </c>
-      <c r="F68">
-        <v>7</v>
-      </c>
-      <c r="G68">
-        <v>9760</v>
-      </c>
-      <c r="H68" t="s">
-        <v>21</v>
-      </c>
-      <c r="I68">
-        <v>93</v>
-      </c>
-      <c r="J68" t="s">
-        <v>22</v>
-      </c>
-      <c r="K68">
-        <v>12</v>
-      </c>
-      <c r="L68" t="s">
-        <v>135</v>
-      </c>
-      <c r="M68">
-        <v>62</v>
-      </c>
-      <c r="N68" t="s">
-        <v>171</v>
-      </c>
-      <c r="O68">
-        <v>1028</v>
-      </c>
-      <c r="P68" t="s">
+      <c r="AP68" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="AQ68" s="13">
+        <v>20</v>
+      </c>
+      <c r="AR68" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS68" s="13">
+        <v>861.24</v>
+      </c>
+      <c r="AT68" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU68" s="13">
+        <v>176.48</v>
+      </c>
+      <c r="AV68" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW68" s="13">
+        <v>116.5</v>
+      </c>
+      <c r="AX68" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY68" s="13">
+        <v>75.8</v>
+      </c>
+      <c r="AZ68" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA68" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="BB68" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="BC68" s="13">
+        <v>347.7</v>
+      </c>
+      <c r="BD68" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE68" s="13">
+        <v>241.7</v>
+      </c>
+      <c r="BF68" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG68" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH68" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI68" s="13">
+        <v>178.08</v>
+      </c>
+      <c r="BJ68" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK68" s="13">
+        <v>1000</v>
+      </c>
+      <c r="BL68" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="Q68">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="R68" t="s">
-        <v>135</v>
-      </c>
-      <c r="S68">
-        <v>30</v>
-      </c>
-      <c r="T68" t="s">
-        <v>135</v>
-      </c>
-      <c r="U68">
-        <v>250</v>
-      </c>
-      <c r="V68" t="s">
+      <c r="BM68" s="13">
+        <v>25</v>
+      </c>
+      <c r="BN68" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO68" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="BP68" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ68" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="BR68" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="W68">
-        <v>147.80000000000001</v>
-      </c>
-      <c r="X68" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y68">
-        <v>134</v>
-      </c>
-      <c r="Z68" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA68">
-        <v>19.739999999999998</v>
-      </c>
-      <c r="AB68" t="s">
-        <v>174</v>
-      </c>
-      <c r="AC68">
-        <v>71</v>
-      </c>
-      <c r="AD68" t="s">
-        <v>171</v>
-      </c>
-      <c r="AE68">
-        <v>364</v>
-      </c>
-      <c r="AF68" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG68">
-        <v>425</v>
-      </c>
-      <c r="AH68" t="s">
-        <v>135</v>
-      </c>
-      <c r="AI68">
-        <v>230</v>
-      </c>
-      <c r="AJ68" t="s">
-        <v>135</v>
-      </c>
-      <c r="AK68">
-        <v>16.622</v>
-      </c>
-      <c r="AL68" t="s">
-        <v>175</v>
-      </c>
-      <c r="AM68">
-        <v>3.26</v>
-      </c>
-      <c r="AN68" t="s">
-        <v>174</v>
-      </c>
-      <c r="AO68" t="s">
-        <v>231</v>
-      </c>
-      <c r="AP68" t="s">
-        <v>224</v>
-      </c>
-      <c r="AQ68">
-        <v>23</v>
-      </c>
-      <c r="AR68" t="s">
-        <v>135</v>
-      </c>
-      <c r="AS68">
-        <v>1698.11</v>
-      </c>
-      <c r="AT68" t="s">
-        <v>177</v>
-      </c>
-      <c r="AU68">
-        <v>173.99</v>
-      </c>
-      <c r="AV68" t="s">
-        <v>20</v>
-      </c>
-      <c r="AW68">
-        <v>147.80000000000001</v>
-      </c>
-      <c r="AX68" t="s">
-        <v>174</v>
-      </c>
-      <c r="AY68">
-        <v>130.80000000000001</v>
-      </c>
-      <c r="AZ68" t="s">
-        <v>174</v>
-      </c>
-      <c r="BA68" t="s">
-        <v>231</v>
-      </c>
-      <c r="BB68" t="s">
-        <v>224</v>
-      </c>
-      <c r="BC68">
-        <v>446.3</v>
-      </c>
-      <c r="BD68" t="s">
-        <v>135</v>
-      </c>
-      <c r="BE68">
-        <v>245.1</v>
-      </c>
-      <c r="BF68" t="s">
-        <v>135</v>
-      </c>
-      <c r="BG68" t="s">
-        <v>231</v>
-      </c>
-      <c r="BH68" t="s">
-        <v>175</v>
-      </c>
-      <c r="BI68">
-        <v>174.34</v>
-      </c>
-      <c r="BJ68" t="s">
-        <v>20</v>
-      </c>
-      <c r="BK68">
-        <v>1000</v>
-      </c>
-      <c r="BL68" t="s">
-        <v>172</v>
-      </c>
-      <c r="BM68">
-        <v>25</v>
-      </c>
-      <c r="BN68" t="s">
-        <v>135</v>
-      </c>
-      <c r="BO68" t="s">
-        <v>231</v>
-      </c>
-      <c r="BP68" t="s">
-        <v>135</v>
-      </c>
-      <c r="BQ68" t="s">
-        <v>231</v>
-      </c>
-      <c r="BR68" t="s">
-        <v>173</v>
-      </c>
+      <c r="BS68" s="13"/>
+      <c r="BT68" s="13"/>
     </row>
     <row r="69" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+      <c r="B69" s="2">
+        <v>774</v>
+      </c>
+      <c r="C69" s="13"/>
+      <c r="D69" s="13">
+        <v>75</v>
+      </c>
+      <c r="E69" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="F69" s="13">
+        <v>3</v>
+      </c>
+      <c r="G69" s="13">
+        <v>7320</v>
+      </c>
+      <c r="H69" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I69" s="13">
+        <v>84</v>
+      </c>
+      <c r="J69" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K69" s="13">
+        <v>12</v>
+      </c>
+      <c r="L69" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="M69" s="13">
+        <v>62</v>
+      </c>
+      <c r="N69" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="O69" s="13">
+        <v>1027</v>
+      </c>
+      <c r="P69" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q69" s="13">
+        <v>15.7</v>
+      </c>
+      <c r="R69" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="S69" s="13">
+        <v>22</v>
+      </c>
+      <c r="T69" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="U69" s="13">
+        <v>140</v>
+      </c>
+      <c r="V69" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="W69" s="13">
+        <v>140.6</v>
+      </c>
+      <c r="X69" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y69" s="13">
+        <v>102.6</v>
+      </c>
+      <c r="Z69" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA69" s="13">
+        <v>16.39</v>
+      </c>
+      <c r="AB69" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC69" s="13">
+        <v>57.4</v>
+      </c>
+      <c r="AD69" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE69" s="13">
+        <v>295</v>
+      </c>
+      <c r="AF69" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG69" s="13">
+        <v>355</v>
+      </c>
+      <c r="AH69" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI69" s="13">
+        <v>200</v>
+      </c>
+      <c r="AJ69" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK69" s="13">
+        <v>14.372</v>
+      </c>
+      <c r="AL69" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM69" s="13">
+        <v>2.23</v>
+      </c>
+      <c r="AN69" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO69" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="AP69" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="AQ69" s="13">
+        <v>21</v>
+      </c>
+      <c r="AR69" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS69" s="13">
+        <v>1228.67</v>
+      </c>
+      <c r="AT69" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU69" s="13">
+        <v>172.76</v>
+      </c>
+      <c r="AV69" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW69" s="13">
+        <v>139.5</v>
+      </c>
+      <c r="AX69" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY69" s="13">
+        <v>101.2</v>
+      </c>
+      <c r="AZ69" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA69" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="C69" t="s">
+      <c r="BB69" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="BC69" s="13">
+        <v>381.8</v>
+      </c>
+      <c r="BD69" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE69" s="13">
+        <v>220.7</v>
+      </c>
+      <c r="BF69" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG69" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="D69">
-        <v>50</v>
-      </c>
-      <c r="E69" t="s">
-        <v>171</v>
-      </c>
-      <c r="F69">
-        <v>1</v>
-      </c>
-      <c r="G69" s="4">
-        <v>3135</v>
-      </c>
-      <c r="H69" t="s">
-        <v>21</v>
-      </c>
-      <c r="I69">
-        <v>114</v>
-      </c>
-      <c r="J69" t="s">
-        <v>22</v>
-      </c>
-      <c r="K69">
-        <v>15</v>
-      </c>
-      <c r="L69" t="s">
-        <v>135</v>
-      </c>
-      <c r="M69" t="s">
+      <c r="BH69" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI69" s="13">
+        <v>169.05</v>
+      </c>
+      <c r="BJ69" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK69" s="13">
+        <v>1000</v>
+      </c>
+      <c r="BL69" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM69" s="13">
+        <v>25</v>
+      </c>
+      <c r="BN69" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO69" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="N69" t="s">
-        <v>171</v>
-      </c>
-      <c r="O69" t="s">
+      <c r="BP69" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ69" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="P69" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q69" t="s">
-        <v>231</v>
-      </c>
-      <c r="R69" t="s">
-        <v>135</v>
-      </c>
-      <c r="S69">
-        <v>34</v>
-      </c>
-      <c r="T69" t="s">
-        <v>135</v>
-      </c>
-      <c r="U69">
-        <v>80</v>
-      </c>
-      <c r="V69" t="s">
+      <c r="BR69" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="W69" t="s">
-        <v>231</v>
-      </c>
-      <c r="X69" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y69" t="s">
-        <v>231</v>
-      </c>
-      <c r="Z69" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA69" t="s">
-        <v>231</v>
-      </c>
-      <c r="AB69" t="s">
-        <v>174</v>
-      </c>
-      <c r="AC69">
-        <v>43</v>
-      </c>
-      <c r="AD69" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE69">
-        <v>286</v>
-      </c>
-      <c r="AF69" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG69">
-        <v>340</v>
-      </c>
-      <c r="AH69" t="s">
-        <v>135</v>
-      </c>
-      <c r="AI69">
-        <v>250</v>
-      </c>
-      <c r="AJ69" t="s">
-        <v>135</v>
-      </c>
-      <c r="AK69">
-        <v>11.6</v>
-      </c>
-      <c r="AL69" t="s">
-        <v>175</v>
-      </c>
-      <c r="AM69">
-        <v>1</v>
-      </c>
-      <c r="AN69" t="s">
-        <v>174</v>
-      </c>
-      <c r="AO69">
-        <v>0.9</v>
-      </c>
-      <c r="AP69" t="s">
-        <v>174</v>
-      </c>
-      <c r="AQ69">
-        <v>130</v>
-      </c>
-      <c r="AR69" t="s">
-        <v>135</v>
-      </c>
-      <c r="AS69" t="s">
-        <v>231</v>
-      </c>
-      <c r="AT69" t="s">
-        <v>177</v>
-      </c>
-      <c r="AU69" t="s">
-        <v>231</v>
-      </c>
-      <c r="AV69" t="s">
-        <v>20</v>
-      </c>
-      <c r="AW69" t="s">
-        <v>231</v>
-      </c>
-      <c r="AX69" t="s">
-        <v>174</v>
-      </c>
-      <c r="AY69" t="s">
-        <v>231</v>
-      </c>
-      <c r="AZ69" t="s">
-        <v>174</v>
-      </c>
-      <c r="BA69" t="s">
-        <v>231</v>
-      </c>
-      <c r="BB69" t="s">
-        <v>224</v>
-      </c>
-      <c r="BC69" t="s">
-        <v>231</v>
-      </c>
-      <c r="BD69" t="s">
-        <v>135</v>
-      </c>
-      <c r="BE69" t="s">
-        <v>231</v>
-      </c>
-      <c r="BF69" t="s">
-        <v>135</v>
-      </c>
-      <c r="BG69" t="s">
-        <v>231</v>
-      </c>
-      <c r="BH69" t="s">
-        <v>175</v>
-      </c>
-      <c r="BI69" t="s">
-        <v>231</v>
-      </c>
-      <c r="BJ69" t="s">
-        <v>20</v>
-      </c>
-      <c r="BK69" t="s">
-        <v>231</v>
-      </c>
-      <c r="BL69" t="s">
-        <v>172</v>
-      </c>
-      <c r="BM69" t="s">
-        <v>231</v>
-      </c>
-      <c r="BN69" t="s">
-        <v>135</v>
-      </c>
-      <c r="BO69" t="s">
-        <v>231</v>
-      </c>
-      <c r="BP69" t="s">
-        <v>135</v>
-      </c>
-      <c r="BQ69" t="s">
-        <v>231</v>
-      </c>
-      <c r="BR69" t="s">
-        <v>173</v>
-      </c>
-      <c r="BS69" t="s">
-        <v>231</v>
-      </c>
-      <c r="BT69" t="s">
-        <v>231</v>
-      </c>
+      <c r="BS69" s="13"/>
+      <c r="BT69" s="13"/>
     </row>
     <row r="70" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+      <c r="B70" s="2">
+        <v>774</v>
+      </c>
+      <c r="C70" s="13"/>
+      <c r="D70" s="13">
+        <v>85</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="F70" s="13">
+        <v>4</v>
+      </c>
+      <c r="G70" s="13">
+        <v>8296</v>
+      </c>
+      <c r="H70" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I70" s="13">
+        <v>88</v>
+      </c>
+      <c r="J70" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K70" s="13">
+        <v>12</v>
+      </c>
+      <c r="L70" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="M70" s="13">
+        <v>62</v>
+      </c>
+      <c r="N70" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="O70" s="13">
+        <v>1027</v>
+      </c>
+      <c r="P70" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q70" s="13">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="R70" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="S70" s="13">
+        <v>27</v>
+      </c>
+      <c r="T70" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="U70" s="13">
+        <v>190</v>
+      </c>
+      <c r="V70" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="W70" s="13">
+        <v>152.19999999999999</v>
+      </c>
+      <c r="X70" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y70" s="13">
+        <v>114.6</v>
+      </c>
+      <c r="Z70" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA70" s="13">
+        <v>17.73</v>
+      </c>
+      <c r="AB70" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC70" s="13">
+        <v>61</v>
+      </c>
+      <c r="AD70" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE70" s="13">
+        <v>310</v>
+      </c>
+      <c r="AF70" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG70" s="13">
+        <v>375</v>
+      </c>
+      <c r="AH70" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI70" s="13">
+        <v>205</v>
+      </c>
+      <c r="AJ70" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK70" s="13">
+        <v>15.108000000000001</v>
+      </c>
+      <c r="AL70" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM70" s="13">
+        <v>2.56</v>
+      </c>
+      <c r="AN70" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO70" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="B70" t="s">
+      <c r="AP70" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="AQ70" s="13">
+        <v>22</v>
+      </c>
+      <c r="AR70" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS70" s="13">
+        <v>1422.92</v>
+      </c>
+      <c r="AT70" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU70" s="13">
+        <v>171.52</v>
+      </c>
+      <c r="AV70" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW70" s="13">
+        <v>152.19999999999999</v>
+      </c>
+      <c r="AX70" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY70" s="13">
+        <v>111</v>
+      </c>
+      <c r="AZ70" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA70" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="BB70" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="BC70" s="13">
+        <v>397.1</v>
+      </c>
+      <c r="BD70" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE70" s="13">
+        <v>220.9</v>
+      </c>
+      <c r="BF70" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG70" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="D70">
-        <v>75</v>
-      </c>
-      <c r="E70" t="s">
-        <v>171</v>
-      </c>
-      <c r="F70">
-        <v>2</v>
-      </c>
-      <c r="G70">
-        <v>4927.5</v>
-      </c>
-      <c r="H70" t="s">
-        <v>21</v>
-      </c>
-      <c r="I70" s="4">
-        <v>120</v>
-      </c>
-      <c r="J70" t="s">
-        <v>22</v>
-      </c>
-      <c r="K70">
-        <v>15</v>
-      </c>
-      <c r="L70" t="s">
-        <v>135</v>
-      </c>
-      <c r="M70" t="s">
+      <c r="BH70" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI70" s="13">
+        <v>172.2</v>
+      </c>
+      <c r="BJ70" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK70" s="13">
+        <v>1000</v>
+      </c>
+      <c r="BL70" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM70" s="13">
+        <v>25</v>
+      </c>
+      <c r="BN70" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO70" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="N70" t="s">
-        <v>171</v>
-      </c>
-      <c r="O70" t="s">
+      <c r="BP70" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ70" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="P70" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q70" t="s">
-        <v>231</v>
-      </c>
-      <c r="R70" t="s">
-        <v>135</v>
-      </c>
-      <c r="S70">
-        <v>39</v>
-      </c>
-      <c r="T70" t="s">
-        <v>135</v>
-      </c>
-      <c r="U70">
-        <v>180</v>
-      </c>
-      <c r="V70" t="s">
+      <c r="BR70" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="W70" t="s">
-        <v>231</v>
-      </c>
-      <c r="X70" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y70" t="s">
-        <v>231</v>
-      </c>
-      <c r="Z70" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA70" t="s">
-        <v>231</v>
-      </c>
-      <c r="AB70" t="s">
-        <v>174</v>
-      </c>
-      <c r="AC70">
-        <v>54.8</v>
-      </c>
-      <c r="AD70" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE70">
-        <v>300</v>
-      </c>
-      <c r="AF70" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG70">
-        <v>360</v>
-      </c>
-      <c r="AH70" t="s">
-        <v>135</v>
-      </c>
-      <c r="AI70">
-        <v>238</v>
-      </c>
-      <c r="AJ70" t="s">
-        <v>135</v>
-      </c>
-      <c r="AK70">
-        <v>14.8</v>
-      </c>
-      <c r="AL70" t="s">
-        <v>175</v>
-      </c>
-      <c r="AM70">
-        <v>1.8</v>
-      </c>
-      <c r="AN70" t="s">
-        <v>174</v>
-      </c>
-      <c r="AO70">
-        <v>1.6</v>
-      </c>
-      <c r="AP70" t="s">
-        <v>174</v>
-      </c>
-      <c r="AQ70">
-        <v>130</v>
-      </c>
-      <c r="AR70" t="s">
-        <v>135</v>
-      </c>
-      <c r="AS70" t="s">
-        <v>231</v>
-      </c>
-      <c r="AT70" t="s">
-        <v>177</v>
-      </c>
-      <c r="AU70" t="s">
-        <v>231</v>
-      </c>
-      <c r="AV70" t="s">
-        <v>20</v>
-      </c>
-      <c r="AW70" t="s">
-        <v>231</v>
-      </c>
-      <c r="AX70" t="s">
-        <v>174</v>
-      </c>
-      <c r="AY70" t="s">
-        <v>231</v>
-      </c>
-      <c r="AZ70" t="s">
-        <v>174</v>
-      </c>
-      <c r="BA70" t="s">
-        <v>231</v>
-      </c>
-      <c r="BB70" t="s">
-        <v>224</v>
-      </c>
-      <c r="BC70" t="s">
-        <v>231</v>
-      </c>
-      <c r="BD70" t="s">
-        <v>135</v>
-      </c>
-      <c r="BE70" t="s">
-        <v>231</v>
-      </c>
-      <c r="BF70" t="s">
-        <v>135</v>
-      </c>
-      <c r="BG70" t="s">
-        <v>231</v>
-      </c>
-      <c r="BH70" t="s">
-        <v>175</v>
-      </c>
-      <c r="BI70" t="s">
-        <v>231</v>
-      </c>
-      <c r="BJ70" t="s">
-        <v>20</v>
-      </c>
-      <c r="BK70" t="s">
-        <v>231</v>
-      </c>
-      <c r="BL70" t="s">
-        <v>172</v>
-      </c>
-      <c r="BM70" t="s">
-        <v>231</v>
-      </c>
-      <c r="BN70" t="s">
-        <v>135</v>
-      </c>
-      <c r="BO70" t="s">
-        <v>231</v>
-      </c>
-      <c r="BP70" t="s">
-        <v>135</v>
-      </c>
-      <c r="BQ70" t="s">
-        <v>231</v>
-      </c>
-      <c r="BR70" t="s">
-        <v>173</v>
-      </c>
-      <c r="BS70" t="s">
-        <v>231</v>
-      </c>
-      <c r="BT70" t="s">
-        <v>231</v>
-      </c>
+      <c r="BS70" s="13"/>
+      <c r="BT70" s="13"/>
     </row>
     <row r="71" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+      <c r="B71" s="2">
+        <v>774</v>
+      </c>
+      <c r="C71" s="13"/>
+      <c r="D71" s="13">
+        <v>100</v>
+      </c>
+      <c r="E71" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="F71" s="13">
+        <v>5</v>
+      </c>
+      <c r="G71" s="13">
+        <v>9760</v>
+      </c>
+      <c r="H71" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I71" s="13">
+        <v>93</v>
+      </c>
+      <c r="J71" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K71" s="13">
+        <v>12</v>
+      </c>
+      <c r="L71" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="M71" s="13">
+        <v>62</v>
+      </c>
+      <c r="N71" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="O71" s="13">
+        <v>1028</v>
+      </c>
+      <c r="P71" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q71" s="13">
+        <v>17</v>
+      </c>
+      <c r="R71" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="S71" s="13">
+        <v>30</v>
+      </c>
+      <c r="T71" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="U71" s="13">
+        <v>250</v>
+      </c>
+      <c r="V71" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="W71" s="13">
+        <v>147.6</v>
+      </c>
+      <c r="X71" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y71" s="13">
+        <v>129.6</v>
+      </c>
+      <c r="Z71" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA71" s="13">
+        <v>19.739999999999998</v>
+      </c>
+      <c r="AB71" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC71" s="13">
+        <v>70.5</v>
+      </c>
+      <c r="AD71" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE71" s="13">
+        <v>362</v>
+      </c>
+      <c r="AF71" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG71" s="13">
+        <v>425</v>
+      </c>
+      <c r="AH71" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI71" s="13">
+        <v>230</v>
+      </c>
+      <c r="AJ71" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK71" s="13">
+        <v>16.654</v>
+      </c>
+      <c r="AL71" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM71" s="13">
+        <v>3.28</v>
+      </c>
+      <c r="AN71" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO71" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="AP71" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="AQ71" s="13">
+        <v>24</v>
+      </c>
+      <c r="AR71" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS71" s="13">
+        <v>1690.14</v>
+      </c>
+      <c r="AT71" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU71" s="13">
+        <v>173.17</v>
+      </c>
+      <c r="AV71" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW71" s="13">
+        <v>147.6</v>
+      </c>
+      <c r="AX71" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY71" s="13">
+        <v>126.2</v>
+      </c>
+      <c r="AZ71" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA71" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="C71" t="s">
+      <c r="BB71" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="BC71" s="13">
+        <v>446.8</v>
+      </c>
+      <c r="BD71" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE71" s="13">
+        <v>245.6</v>
+      </c>
+      <c r="BF71" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG71" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="D71">
-        <v>85</v>
-      </c>
-      <c r="E71" t="s">
-        <v>171</v>
-      </c>
-      <c r="F71">
-        <v>3</v>
-      </c>
-      <c r="G71" s="4">
-        <v>5548.3</v>
-      </c>
-      <c r="H71" t="s">
-        <v>21</v>
-      </c>
-      <c r="I71">
-        <v>122</v>
-      </c>
-      <c r="J71" t="s">
-        <v>22</v>
-      </c>
-      <c r="K71">
-        <v>15</v>
-      </c>
-      <c r="L71" t="s">
-        <v>135</v>
-      </c>
-      <c r="M71" t="s">
+      <c r="BH71" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI71" s="13">
+        <v>173.54</v>
+      </c>
+      <c r="BJ71" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK71" s="13">
+        <v>1000</v>
+      </c>
+      <c r="BL71" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM71" s="13">
+        <v>25</v>
+      </c>
+      <c r="BN71" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO71" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="N71" t="s">
-        <v>171</v>
-      </c>
-      <c r="O71" t="s">
+      <c r="BP71" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ71" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="P71" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q71" t="s">
-        <v>231</v>
-      </c>
-      <c r="R71" t="s">
-        <v>135</v>
-      </c>
-      <c r="S71">
-        <v>40</v>
-      </c>
-      <c r="T71" t="s">
-        <v>135</v>
-      </c>
-      <c r="U71">
-        <v>210</v>
-      </c>
-      <c r="V71" t="s">
+      <c r="BR71" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="W71" t="s">
-        <v>231</v>
-      </c>
-      <c r="X71" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y71" t="s">
-        <v>231</v>
-      </c>
-      <c r="Z71" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA71" t="s">
-        <v>231</v>
-      </c>
-      <c r="AB71" t="s">
-        <v>174</v>
-      </c>
-      <c r="AC71">
-        <v>60.6</v>
-      </c>
-      <c r="AD71" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE71">
-        <v>301</v>
-      </c>
-      <c r="AF71" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG71">
-        <v>365</v>
-      </c>
-      <c r="AH71" t="s">
-        <v>135</v>
-      </c>
-      <c r="AI71">
-        <v>238</v>
-      </c>
-      <c r="AJ71" t="s">
-        <v>135</v>
-      </c>
-      <c r="AK71">
-        <v>15.4</v>
-      </c>
-      <c r="AL71" t="s">
-        <v>175</v>
-      </c>
-      <c r="AM71">
-        <v>2</v>
-      </c>
-      <c r="AN71" t="s">
-        <v>174</v>
-      </c>
-      <c r="AO71">
-        <v>1.8</v>
-      </c>
-      <c r="AP71" t="s">
-        <v>174</v>
-      </c>
-      <c r="AQ71">
-        <v>130</v>
-      </c>
-      <c r="AR71" t="s">
-        <v>135</v>
-      </c>
-      <c r="AS71" t="s">
-        <v>231</v>
-      </c>
-      <c r="AT71" t="s">
-        <v>177</v>
-      </c>
-      <c r="AU71" t="s">
-        <v>231</v>
-      </c>
-      <c r="AV71" t="s">
-        <v>20</v>
-      </c>
-      <c r="AW71" t="s">
-        <v>231</v>
-      </c>
-      <c r="AX71" t="s">
-        <v>174</v>
-      </c>
-      <c r="AY71" t="s">
-        <v>231</v>
-      </c>
-      <c r="AZ71" t="s">
-        <v>174</v>
-      </c>
-      <c r="BA71" t="s">
-        <v>231</v>
-      </c>
-      <c r="BB71" t="s">
-        <v>224</v>
-      </c>
-      <c r="BC71" t="s">
-        <v>231</v>
-      </c>
-      <c r="BD71" t="s">
-        <v>135</v>
-      </c>
-      <c r="BE71" t="s">
-        <v>231</v>
-      </c>
-      <c r="BF71" t="s">
-        <v>135</v>
-      </c>
-      <c r="BG71" t="s">
-        <v>231</v>
-      </c>
-      <c r="BH71" t="s">
-        <v>175</v>
-      </c>
-      <c r="BI71" t="s">
-        <v>231</v>
-      </c>
-      <c r="BJ71" t="s">
-        <v>20</v>
-      </c>
-      <c r="BK71" t="s">
-        <v>231</v>
-      </c>
-      <c r="BL71" t="s">
-        <v>172</v>
-      </c>
-      <c r="BM71" t="s">
-        <v>231</v>
-      </c>
-      <c r="BN71" t="s">
-        <v>135</v>
-      </c>
-      <c r="BO71" t="s">
-        <v>231</v>
-      </c>
-      <c r="BP71" t="s">
-        <v>135</v>
-      </c>
-      <c r="BQ71" t="s">
-        <v>231</v>
-      </c>
-      <c r="BR71" t="s">
-        <v>173</v>
-      </c>
-      <c r="BS71" t="s">
-        <v>231</v>
-      </c>
-      <c r="BT71" t="s">
-        <v>231</v>
-      </c>
+      <c r="BS71" s="13"/>
+      <c r="BT71" s="13"/>
     </row>
     <row r="72" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+      <c r="B72" s="2">
+        <v>774</v>
+      </c>
+      <c r="C72" s="13"/>
+      <c r="D72" s="13">
+        <v>110</v>
+      </c>
+      <c r="E72" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="F72" s="13">
+        <v>6</v>
+      </c>
+      <c r="G72" s="13">
+        <v>10736</v>
+      </c>
+      <c r="H72" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I72" s="13">
+        <v>96</v>
+      </c>
+      <c r="J72" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K72" s="13">
+        <v>13</v>
+      </c>
+      <c r="L72" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="M72" s="13">
+        <v>62</v>
+      </c>
+      <c r="N72" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="O72" s="13">
+        <v>1027</v>
+      </c>
+      <c r="P72" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q72" s="13">
+        <v>18</v>
+      </c>
+      <c r="R72" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="S72" s="13">
+        <v>28</v>
+      </c>
+      <c r="T72" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="U72" s="13">
+        <v>285</v>
+      </c>
+      <c r="V72" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="W72" s="13">
+        <v>153.6</v>
+      </c>
+      <c r="X72" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y72" s="13">
+        <v>142.80000000000001</v>
+      </c>
+      <c r="Z72" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA72" s="13">
+        <v>21.03</v>
+      </c>
+      <c r="AB72" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC72" s="13">
+        <v>75.3</v>
+      </c>
+      <c r="AD72" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE72" s="13">
+        <v>389</v>
+      </c>
+      <c r="AF72" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG72" s="13">
+        <v>450</v>
+      </c>
+      <c r="AH72" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI72" s="13">
+        <v>245</v>
+      </c>
+      <c r="AJ72" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK72" s="13">
+        <v>17.189</v>
+      </c>
+      <c r="AL72" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM72" s="13">
+        <v>3.45</v>
+      </c>
+      <c r="AN72" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO72" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="AP72" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="AQ72" s="13">
+        <v>24</v>
+      </c>
+      <c r="AR72" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS72" s="13">
+        <v>1935.48</v>
+      </c>
+      <c r="AT72" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU72" s="13">
+        <v>180.28</v>
+      </c>
+      <c r="AV72" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW72" s="13">
+        <v>153.6</v>
+      </c>
+      <c r="AX72" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY72" s="13">
+        <v>140.80000000000001</v>
+      </c>
+      <c r="AZ72" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA72" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="C72" t="s">
+      <c r="BB72" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="BC72" s="13">
+        <v>473.9</v>
+      </c>
+      <c r="BD72" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE72" s="13">
+        <v>261</v>
+      </c>
+      <c r="BF72" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG72" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="D72">
-        <v>100</v>
-      </c>
-      <c r="E72" t="s">
-        <v>171</v>
-      </c>
-      <c r="F72">
-        <v>4</v>
-      </c>
-      <c r="G72" s="4">
-        <v>6580</v>
-      </c>
-      <c r="H72" t="s">
-        <v>21</v>
-      </c>
-      <c r="I72">
-        <v>127</v>
-      </c>
-      <c r="J72" t="s">
-        <v>22</v>
-      </c>
-      <c r="K72">
-        <v>15</v>
-      </c>
-      <c r="L72" t="s">
-        <v>135</v>
-      </c>
-      <c r="M72" t="s">
+      <c r="BH72" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI72" s="13">
+        <v>180.84</v>
+      </c>
+      <c r="BJ72" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK72" s="13">
+        <v>1000</v>
+      </c>
+      <c r="BL72" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM72" s="13">
+        <v>25</v>
+      </c>
+      <c r="BN72" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO72" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="N72" t="s">
-        <v>171</v>
-      </c>
-      <c r="O72" t="s">
+      <c r="BP72" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ72" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="P72" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q72" t="s">
-        <v>231</v>
-      </c>
-      <c r="R72" t="s">
-        <v>135</v>
-      </c>
-      <c r="S72">
-        <v>43</v>
-      </c>
-      <c r="T72" t="s">
-        <v>135</v>
-      </c>
-      <c r="U72">
-        <v>265</v>
-      </c>
-      <c r="V72" t="s">
+      <c r="BR72" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="W72" t="s">
-        <v>231</v>
-      </c>
-      <c r="X72" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y72" t="s">
-        <v>231</v>
-      </c>
-      <c r="Z72" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA72" t="s">
-        <v>231</v>
-      </c>
-      <c r="AB72" t="s">
-        <v>174</v>
-      </c>
-      <c r="AC72">
-        <v>69.400000000000006</v>
-      </c>
-      <c r="AD72" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE72">
-        <v>335.6</v>
-      </c>
-      <c r="AF72" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG72">
-        <v>400</v>
-      </c>
-      <c r="AH72" t="s">
-        <v>135</v>
-      </c>
-      <c r="AI72">
-        <v>245</v>
-      </c>
-      <c r="AJ72" t="s">
-        <v>135</v>
-      </c>
-      <c r="AK72">
-        <v>17.010000000000002</v>
-      </c>
-      <c r="AL72" t="s">
-        <v>175</v>
-      </c>
-      <c r="AM72">
-        <v>2.5</v>
-      </c>
-      <c r="AN72" t="s">
-        <v>174</v>
-      </c>
-      <c r="AO72">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="AP72" t="s">
-        <v>174</v>
-      </c>
-      <c r="AQ72">
-        <v>129</v>
-      </c>
-      <c r="AR72" t="s">
-        <v>135</v>
-      </c>
-      <c r="AS72" t="s">
-        <v>231</v>
-      </c>
-      <c r="AT72" t="s">
-        <v>177</v>
-      </c>
-      <c r="AU72" t="s">
-        <v>231</v>
-      </c>
-      <c r="AV72" t="s">
-        <v>20</v>
-      </c>
-      <c r="AW72" t="s">
-        <v>231</v>
-      </c>
-      <c r="AX72" t="s">
-        <v>174</v>
-      </c>
-      <c r="AY72" t="s">
-        <v>231</v>
-      </c>
-      <c r="AZ72" t="s">
-        <v>174</v>
-      </c>
-      <c r="BA72" t="s">
-        <v>231</v>
-      </c>
-      <c r="BB72" t="s">
-        <v>224</v>
-      </c>
-      <c r="BC72" t="s">
-        <v>231</v>
-      </c>
-      <c r="BD72" t="s">
-        <v>135</v>
-      </c>
-      <c r="BE72" t="s">
-        <v>231</v>
-      </c>
-      <c r="BF72" t="s">
-        <v>135</v>
-      </c>
-      <c r="BG72" t="s">
-        <v>231</v>
-      </c>
-      <c r="BH72" t="s">
-        <v>175</v>
-      </c>
-      <c r="BI72" t="s">
-        <v>231</v>
-      </c>
-      <c r="BJ72" t="s">
-        <v>20</v>
-      </c>
-      <c r="BK72" t="s">
-        <v>231</v>
-      </c>
-      <c r="BL72" t="s">
-        <v>172</v>
-      </c>
-      <c r="BM72" t="s">
-        <v>231</v>
-      </c>
-      <c r="BN72" t="s">
-        <v>135</v>
-      </c>
-      <c r="BO72" t="s">
-        <v>231</v>
-      </c>
-      <c r="BP72" t="s">
-        <v>135</v>
-      </c>
-      <c r="BQ72" t="s">
-        <v>231</v>
-      </c>
-      <c r="BR72" t="s">
-        <v>173</v>
-      </c>
-      <c r="BS72" t="s">
-        <v>231</v>
-      </c>
-      <c r="BT72" t="s">
-        <v>231</v>
-      </c>
+      <c r="BS72" s="13"/>
+      <c r="BT72" s="13"/>
     </row>
     <row r="73" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+      <c r="B73" s="2">
+        <v>774</v>
+      </c>
+      <c r="C73" s="13"/>
+      <c r="D73" s="13">
+        <v>100</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="F73" s="13">
+        <v>7</v>
+      </c>
+      <c r="G73" s="13">
+        <v>9760</v>
+      </c>
+      <c r="H73" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I73" s="13">
+        <v>93</v>
+      </c>
+      <c r="J73" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K73" s="13">
+        <v>12</v>
+      </c>
+      <c r="L73" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="M73" s="13">
+        <v>62</v>
+      </c>
+      <c r="N73" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="O73" s="13">
+        <v>1028</v>
+      </c>
+      <c r="P73" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q73" s="13">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="R73" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="S73" s="13">
+        <v>30</v>
+      </c>
+      <c r="T73" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="U73" s="13">
+        <v>250</v>
+      </c>
+      <c r="V73" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="W73" s="13">
+        <v>147.80000000000001</v>
+      </c>
+      <c r="X73" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y73" s="13">
+        <v>134</v>
+      </c>
+      <c r="Z73" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA73" s="13">
+        <v>19.739999999999998</v>
+      </c>
+      <c r="AB73" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC73" s="13">
+        <v>71</v>
+      </c>
+      <c r="AD73" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE73" s="13">
+        <v>364</v>
+      </c>
+      <c r="AF73" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG73" s="13">
+        <v>425</v>
+      </c>
+      <c r="AH73" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI73" s="13">
+        <v>230</v>
+      </c>
+      <c r="AJ73" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK73" s="13">
+        <v>16.622</v>
+      </c>
+      <c r="AL73" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM73" s="13">
+        <v>3.26</v>
+      </c>
+      <c r="AN73" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO73" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="AP73" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="AQ73" s="13">
+        <v>23</v>
+      </c>
+      <c r="AR73" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS73" s="13">
+        <v>1698.11</v>
+      </c>
+      <c r="AT73" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU73" s="13">
+        <v>173.99</v>
+      </c>
+      <c r="AV73" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW73" s="13">
+        <v>147.80000000000001</v>
+      </c>
+      <c r="AX73" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY73" s="13">
+        <v>130.80000000000001</v>
+      </c>
+      <c r="AZ73" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA73" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="C73" t="s">
+      <c r="BB73" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="BC73" s="13">
+        <v>446.3</v>
+      </c>
+      <c r="BD73" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE73" s="13">
+        <v>245.1</v>
+      </c>
+      <c r="BF73" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG73" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="D73">
+      <c r="BH73" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI73" s="13">
+        <v>174.34</v>
+      </c>
+      <c r="BJ73" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK73" s="13">
+        <v>1000</v>
+      </c>
+      <c r="BL73" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM73" s="13">
+        <v>25</v>
+      </c>
+      <c r="BN73" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO73" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="BP73" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ73" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="BR73" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="BS73" s="13"/>
+      <c r="BT73" s="13"/>
+    </row>
+    <row r="74" spans="1:72" x14ac:dyDescent="0.3">
+      <c r="A74" s="5"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="5"/>
+      <c r="L74" s="5"/>
+      <c r="M74" s="5"/>
+      <c r="N74" s="5"/>
+      <c r="O74" s="5"/>
+      <c r="P74" s="5"/>
+      <c r="Q74" s="5"/>
+      <c r="R74" s="5"/>
+      <c r="S74" s="5"/>
+      <c r="T74" s="5"/>
+      <c r="U74" s="5"/>
+      <c r="V74" s="5"/>
+      <c r="W74" s="5"/>
+      <c r="X74" s="5"/>
+      <c r="Y74" s="5"/>
+      <c r="Z74" s="5"/>
+      <c r="AA74" s="5"/>
+      <c r="AB74" s="5"/>
+      <c r="AC74" s="5"/>
+      <c r="AD74" s="5"/>
+      <c r="AE74" s="5"/>
+      <c r="AF74" s="5"/>
+      <c r="AG74" s="5"/>
+      <c r="AH74" s="5"/>
+      <c r="AI74" s="5"/>
+      <c r="AJ74" s="5"/>
+      <c r="AK74" s="5"/>
+      <c r="AL74" s="5"/>
+      <c r="AM74" s="5"/>
+      <c r="AN74" s="5"/>
+      <c r="AO74" s="5"/>
+      <c r="AP74" s="5"/>
+      <c r="AQ74" s="5"/>
+      <c r="AR74" s="5"/>
+      <c r="AS74" s="5"/>
+      <c r="AT74" s="5"/>
+      <c r="AU74" s="5"/>
+      <c r="AV74" s="5"/>
+      <c r="AW74" s="5"/>
+      <c r="AX74" s="5"/>
+      <c r="AY74" s="5"/>
+      <c r="AZ74" s="5"/>
+      <c r="BA74" s="5"/>
+      <c r="BB74" s="5"/>
+      <c r="BC74" s="5"/>
+      <c r="BD74" s="5"/>
+      <c r="BE74" s="5"/>
+      <c r="BF74" s="5"/>
+      <c r="BG74" s="5"/>
+      <c r="BH74" s="5"/>
+      <c r="BI74" s="5"/>
+      <c r="BJ74" s="5"/>
+      <c r="BK74" s="5"/>
+      <c r="BL74" s="5"/>
+      <c r="BM74" s="5"/>
+      <c r="BN74" s="5"/>
+      <c r="BO74" s="5"/>
+      <c r="BP74" s="5"/>
+      <c r="BQ74" s="5"/>
+      <c r="BR74" s="5"/>
+      <c r="BS74" s="5"/>
+      <c r="BT74" s="5"/>
+    </row>
+    <row r="81" spans="1:85" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>231</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C81" t="s">
+        <v>231</v>
+      </c>
+      <c r="D81">
+        <v>50</v>
+      </c>
+      <c r="E81" t="s">
+        <v>171</v>
+      </c>
+      <c r="F81">
+        <v>1</v>
+      </c>
+      <c r="G81" s="4">
+        <v>3135</v>
+      </c>
+      <c r="H81" t="s">
+        <v>21</v>
+      </c>
+      <c r="I81">
+        <v>114</v>
+      </c>
+      <c r="J81" t="s">
+        <v>22</v>
+      </c>
+      <c r="K81">
+        <v>15</v>
+      </c>
+      <c r="L81" t="s">
+        <v>135</v>
+      </c>
+      <c r="M81" t="s">
+        <v>231</v>
+      </c>
+      <c r="N81" t="s">
+        <v>171</v>
+      </c>
+      <c r="O81" t="s">
+        <v>231</v>
+      </c>
+      <c r="P81" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>231</v>
+      </c>
+      <c r="R81" t="s">
+        <v>135</v>
+      </c>
+      <c r="S81">
+        <v>34</v>
+      </c>
+      <c r="T81" t="s">
+        <v>135</v>
+      </c>
+      <c r="U81">
+        <v>80</v>
+      </c>
+      <c r="V81" t="s">
+        <v>173</v>
+      </c>
+      <c r="W81" t="s">
+        <v>231</v>
+      </c>
+      <c r="X81" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>231</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA81" t="s">
+        <v>231</v>
+      </c>
+      <c r="AB81" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC81">
+        <v>43</v>
+      </c>
+      <c r="AD81" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE81">
+        <v>286</v>
+      </c>
+      <c r="AF81" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG81">
+        <v>340</v>
+      </c>
+      <c r="AH81" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI81">
+        <v>250</v>
+      </c>
+      <c r="AJ81" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK81">
+        <v>11.6</v>
+      </c>
+      <c r="AL81" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM81">
+        <v>1</v>
+      </c>
+      <c r="AN81" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO81">
+        <v>0.9</v>
+      </c>
+      <c r="AP81" t="s">
+        <v>174</v>
+      </c>
+      <c r="AQ81">
+        <v>130</v>
+      </c>
+      <c r="AR81" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS81" t="s">
+        <v>231</v>
+      </c>
+      <c r="AT81" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU81" t="s">
+        <v>231</v>
+      </c>
+      <c r="AV81" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW81" t="s">
+        <v>231</v>
+      </c>
+      <c r="AX81" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY81" t="s">
+        <v>231</v>
+      </c>
+      <c r="AZ81" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA81" t="s">
+        <v>231</v>
+      </c>
+      <c r="BB81" t="s">
+        <v>224</v>
+      </c>
+      <c r="BC81" t="s">
+        <v>231</v>
+      </c>
+      <c r="BD81" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE81" t="s">
+        <v>231</v>
+      </c>
+      <c r="BF81" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG81" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH81" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI81" t="s">
+        <v>231</v>
+      </c>
+      <c r="BJ81" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK81" t="s">
+        <v>231</v>
+      </c>
+      <c r="BL81" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM81" t="s">
+        <v>231</v>
+      </c>
+      <c r="BN81" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO81" t="s">
+        <v>231</v>
+      </c>
+      <c r="BP81" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ81" t="s">
+        <v>231</v>
+      </c>
+      <c r="BR81" t="s">
+        <v>173</v>
+      </c>
+      <c r="BS81" t="s">
+        <v>231</v>
+      </c>
+      <c r="BT81" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="82" spans="1:85" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>231</v>
+      </c>
+      <c r="B82" t="s">
+        <v>231</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D82">
+        <v>75</v>
+      </c>
+      <c r="E82" t="s">
+        <v>171</v>
+      </c>
+      <c r="F82">
+        <v>2</v>
+      </c>
+      <c r="G82">
+        <v>4927.5</v>
+      </c>
+      <c r="H82" t="s">
+        <v>21</v>
+      </c>
+      <c r="I82" s="4">
+        <v>120</v>
+      </c>
+      <c r="J82" t="s">
+        <v>22</v>
+      </c>
+      <c r="K82">
+        <v>15</v>
+      </c>
+      <c r="L82" t="s">
+        <v>135</v>
+      </c>
+      <c r="M82" t="s">
+        <v>231</v>
+      </c>
+      <c r="N82" t="s">
+        <v>171</v>
+      </c>
+      <c r="O82" t="s">
+        <v>231</v>
+      </c>
+      <c r="P82" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>231</v>
+      </c>
+      <c r="R82" t="s">
+        <v>135</v>
+      </c>
+      <c r="S82">
+        <v>39</v>
+      </c>
+      <c r="T82" t="s">
+        <v>135</v>
+      </c>
+      <c r="U82">
+        <v>180</v>
+      </c>
+      <c r="V82" t="s">
+        <v>173</v>
+      </c>
+      <c r="W82" t="s">
+        <v>231</v>
+      </c>
+      <c r="X82" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>231</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA82" t="s">
+        <v>231</v>
+      </c>
+      <c r="AB82" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC82">
+        <v>54.8</v>
+      </c>
+      <c r="AD82" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE82">
+        <v>300</v>
+      </c>
+      <c r="AF82" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG82">
+        <v>360</v>
+      </c>
+      <c r="AH82" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI82">
+        <v>238</v>
+      </c>
+      <c r="AJ82" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK82">
+        <v>14.8</v>
+      </c>
+      <c r="AL82" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM82">
+        <v>1.8</v>
+      </c>
+      <c r="AN82" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO82">
+        <v>1.6</v>
+      </c>
+      <c r="AP82" t="s">
+        <v>174</v>
+      </c>
+      <c r="AQ82">
+        <v>130</v>
+      </c>
+      <c r="AR82" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS82" t="s">
+        <v>231</v>
+      </c>
+      <c r="AT82" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU82" t="s">
+        <v>231</v>
+      </c>
+      <c r="AV82" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW82" t="s">
+        <v>231</v>
+      </c>
+      <c r="AX82" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY82" t="s">
+        <v>231</v>
+      </c>
+      <c r="AZ82" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA82" t="s">
+        <v>231</v>
+      </c>
+      <c r="BB82" t="s">
+        <v>224</v>
+      </c>
+      <c r="BC82" t="s">
+        <v>231</v>
+      </c>
+      <c r="BD82" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE82" t="s">
+        <v>231</v>
+      </c>
+      <c r="BF82" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG82" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH82" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI82" t="s">
+        <v>231</v>
+      </c>
+      <c r="BJ82" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK82" t="s">
+        <v>231</v>
+      </c>
+      <c r="BL82" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM82" t="s">
+        <v>231</v>
+      </c>
+      <c r="BN82" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO82" t="s">
+        <v>231</v>
+      </c>
+      <c r="BP82" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ82" t="s">
+        <v>231</v>
+      </c>
+      <c r="BR82" t="s">
+        <v>173</v>
+      </c>
+      <c r="BS82" t="s">
+        <v>231</v>
+      </c>
+      <c r="BT82" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="83" spans="1:85" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>231</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C83" t="s">
+        <v>231</v>
+      </c>
+      <c r="D83">
+        <v>85</v>
+      </c>
+      <c r="E83" t="s">
+        <v>171</v>
+      </c>
+      <c r="F83">
+        <v>3</v>
+      </c>
+      <c r="G83" s="4">
+        <v>5548.3</v>
+      </c>
+      <c r="H83" t="s">
+        <v>21</v>
+      </c>
+      <c r="I83">
+        <v>122</v>
+      </c>
+      <c r="J83" t="s">
+        <v>22</v>
+      </c>
+      <c r="K83">
+        <v>15</v>
+      </c>
+      <c r="L83" t="s">
+        <v>135</v>
+      </c>
+      <c r="M83" t="s">
+        <v>231</v>
+      </c>
+      <c r="N83" t="s">
+        <v>171</v>
+      </c>
+      <c r="O83" t="s">
+        <v>231</v>
+      </c>
+      <c r="P83" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>231</v>
+      </c>
+      <c r="R83" t="s">
+        <v>135</v>
+      </c>
+      <c r="S83">
+        <v>40</v>
+      </c>
+      <c r="T83" t="s">
+        <v>135</v>
+      </c>
+      <c r="U83">
+        <v>210</v>
+      </c>
+      <c r="V83" t="s">
+        <v>173</v>
+      </c>
+      <c r="W83" t="s">
+        <v>231</v>
+      </c>
+      <c r="X83" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>231</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA83" t="s">
+        <v>231</v>
+      </c>
+      <c r="AB83" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC83">
+        <v>60.6</v>
+      </c>
+      <c r="AD83" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE83">
+        <v>301</v>
+      </c>
+      <c r="AF83" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG83">
+        <v>365</v>
+      </c>
+      <c r="AH83" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI83">
+        <v>238</v>
+      </c>
+      <c r="AJ83" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK83">
+        <v>15.4</v>
+      </c>
+      <c r="AL83" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM83">
+        <v>2</v>
+      </c>
+      <c r="AN83" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO83">
+        <v>1.8</v>
+      </c>
+      <c r="AP83" t="s">
+        <v>174</v>
+      </c>
+      <c r="AQ83">
+        <v>130</v>
+      </c>
+      <c r="AR83" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS83" t="s">
+        <v>231</v>
+      </c>
+      <c r="AT83" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU83" t="s">
+        <v>231</v>
+      </c>
+      <c r="AV83" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW83" t="s">
+        <v>231</v>
+      </c>
+      <c r="AX83" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY83" t="s">
+        <v>231</v>
+      </c>
+      <c r="AZ83" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA83" t="s">
+        <v>231</v>
+      </c>
+      <c r="BB83" t="s">
+        <v>224</v>
+      </c>
+      <c r="BC83" t="s">
+        <v>231</v>
+      </c>
+      <c r="BD83" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE83" t="s">
+        <v>231</v>
+      </c>
+      <c r="BF83" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG83" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH83" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI83" t="s">
+        <v>231</v>
+      </c>
+      <c r="BJ83" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK83" t="s">
+        <v>231</v>
+      </c>
+      <c r="BL83" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM83" t="s">
+        <v>231</v>
+      </c>
+      <c r="BN83" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO83" t="s">
+        <v>231</v>
+      </c>
+      <c r="BP83" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ83" t="s">
+        <v>231</v>
+      </c>
+      <c r="BR83" t="s">
+        <v>173</v>
+      </c>
+      <c r="BS83" t="s">
+        <v>231</v>
+      </c>
+      <c r="BT83" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="84" spans="1:85" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>231</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C84" t="s">
+        <v>231</v>
+      </c>
+      <c r="D84">
+        <v>100</v>
+      </c>
+      <c r="E84" t="s">
+        <v>171</v>
+      </c>
+      <c r="F84">
+        <v>4</v>
+      </c>
+      <c r="G84" s="4">
+        <v>6580</v>
+      </c>
+      <c r="H84" t="s">
+        <v>21</v>
+      </c>
+      <c r="I84">
+        <v>127</v>
+      </c>
+      <c r="J84" t="s">
+        <v>22</v>
+      </c>
+      <c r="K84">
+        <v>15</v>
+      </c>
+      <c r="L84" t="s">
+        <v>135</v>
+      </c>
+      <c r="M84" t="s">
+        <v>231</v>
+      </c>
+      <c r="N84" t="s">
+        <v>171</v>
+      </c>
+      <c r="O84" t="s">
+        <v>231</v>
+      </c>
+      <c r="P84" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>231</v>
+      </c>
+      <c r="R84" t="s">
+        <v>135</v>
+      </c>
+      <c r="S84">
+        <v>43</v>
+      </c>
+      <c r="T84" t="s">
+        <v>135</v>
+      </c>
+      <c r="U84">
+        <v>265</v>
+      </c>
+      <c r="V84" t="s">
+        <v>173</v>
+      </c>
+      <c r="W84" t="s">
+        <v>231</v>
+      </c>
+      <c r="X84" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>231</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA84" t="s">
+        <v>231</v>
+      </c>
+      <c r="AB84" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC84">
+        <v>69.400000000000006</v>
+      </c>
+      <c r="AD84" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE84">
+        <v>335.6</v>
+      </c>
+      <c r="AF84" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG84">
+        <v>400</v>
+      </c>
+      <c r="AH84" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI84">
+        <v>245</v>
+      </c>
+      <c r="AJ84" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK84">
+        <v>17.010000000000002</v>
+      </c>
+      <c r="AL84" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM84">
+        <v>2.5</v>
+      </c>
+      <c r="AN84" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO84">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AP84" t="s">
+        <v>174</v>
+      </c>
+      <c r="AQ84">
+        <v>129</v>
+      </c>
+      <c r="AR84" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS84" t="s">
+        <v>231</v>
+      </c>
+      <c r="AT84" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU84" t="s">
+        <v>231</v>
+      </c>
+      <c r="AV84" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW84" t="s">
+        <v>231</v>
+      </c>
+      <c r="AX84" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY84" t="s">
+        <v>231</v>
+      </c>
+      <c r="AZ84" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA84" t="s">
+        <v>231</v>
+      </c>
+      <c r="BB84" t="s">
+        <v>224</v>
+      </c>
+      <c r="BC84" t="s">
+        <v>231</v>
+      </c>
+      <c r="BD84" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE84" t="s">
+        <v>231</v>
+      </c>
+      <c r="BF84" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG84" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH84" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI84" t="s">
+        <v>231</v>
+      </c>
+      <c r="BJ84" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK84" t="s">
+        <v>231</v>
+      </c>
+      <c r="BL84" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM84" t="s">
+        <v>231</v>
+      </c>
+      <c r="BN84" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO84" t="s">
+        <v>231</v>
+      </c>
+      <c r="BP84" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ84" t="s">
+        <v>231</v>
+      </c>
+      <c r="BR84" t="s">
+        <v>173</v>
+      </c>
+      <c r="BS84" t="s">
+        <v>231</v>
+      </c>
+      <c r="BT84" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="85" spans="1:85" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>231</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C85" t="s">
+        <v>231</v>
+      </c>
+      <c r="D85">
         <v>110</v>
       </c>
-      <c r="E73" t="s">
+      <c r="E85" t="s">
         <v>171</v>
       </c>
-      <c r="F73">
+      <c r="F85">
         <v>5</v>
       </c>
-      <c r="G73">
+      <c r="G85">
         <v>7240</v>
       </c>
-      <c r="H73" t="s">
+      <c r="H85" t="s">
         <v>21</v>
       </c>
-      <c r="I73">
+      <c r="I85">
         <v>130</v>
       </c>
-      <c r="J73" t="s">
+      <c r="J85" t="s">
         <v>22</v>
       </c>
-      <c r="K73">
+      <c r="K85">
         <v>15</v>
       </c>
-      <c r="L73" t="s">
-        <v>135</v>
-      </c>
-      <c r="M73" t="s">
+      <c r="L85" t="s">
+        <v>135</v>
+      </c>
+      <c r="M85" t="s">
         <v>231</v>
       </c>
-      <c r="N73" t="s">
+      <c r="N85" t="s">
         <v>171</v>
       </c>
-      <c r="O73" t="s">
+      <c r="O85" t="s">
         <v>231</v>
       </c>
-      <c r="P73" t="s">
+      <c r="P85" t="s">
         <v>172</v>
       </c>
-      <c r="Q73" t="s">
+      <c r="Q85" t="s">
         <v>231</v>
       </c>
-      <c r="R73" t="s">
-        <v>135</v>
-      </c>
-      <c r="S73">
+      <c r="R85" t="s">
+        <v>135</v>
+      </c>
+      <c r="S85">
         <v>46</v>
       </c>
-      <c r="T73" t="s">
-        <v>135</v>
-      </c>
-      <c r="U73">
+      <c r="T85" t="s">
+        <v>135</v>
+      </c>
+      <c r="U85">
         <v>260</v>
       </c>
-      <c r="V73" t="s">
+      <c r="V85" t="s">
         <v>173</v>
       </c>
-      <c r="W73" t="s">
+      <c r="W85" t="s">
         <v>231</v>
       </c>
-      <c r="X73" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y73" t="s">
+      <c r="X85" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y85" t="s">
         <v>231</v>
       </c>
-      <c r="Z73" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA73" t="s">
+      <c r="Z85" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA85" t="s">
         <v>231</v>
       </c>
-      <c r="AB73" t="s">
-        <v>174</v>
-      </c>
-      <c r="AC73">
+      <c r="AB85" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC85">
         <v>76.2</v>
       </c>
-      <c r="AD73" t="s">
+      <c r="AD85" t="s">
         <v>19</v>
       </c>
-      <c r="AE73">
+      <c r="AE85">
         <v>342</v>
       </c>
-      <c r="AF73" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG73">
+      <c r="AF85" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG85">
         <v>420</v>
       </c>
-      <c r="AH73" t="s">
-        <v>135</v>
-      </c>
-      <c r="AI73">
+      <c r="AH85" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI85">
         <v>250</v>
       </c>
-      <c r="AJ73" t="s">
-        <v>135</v>
-      </c>
-      <c r="AK73">
+      <c r="AJ85" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK85">
         <v>17.5</v>
       </c>
-      <c r="AL73" t="s">
+      <c r="AL85" t="s">
         <v>175</v>
       </c>
-      <c r="AM73">
+      <c r="AM85">
         <v>2.8</v>
       </c>
-      <c r="AN73" t="s">
-        <v>174</v>
-      </c>
-      <c r="AO73">
+      <c r="AN85" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO85">
         <v>2.6</v>
       </c>
-      <c r="AP73" t="s">
-        <v>174</v>
-      </c>
-      <c r="AQ73">
+      <c r="AP85" t="s">
+        <v>174</v>
+      </c>
+      <c r="AQ85">
         <v>130</v>
       </c>
-      <c r="AR73" t="s">
-        <v>135</v>
-      </c>
-      <c r="AS73" t="s">
+      <c r="AR85" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS85" t="s">
         <v>231</v>
       </c>
-      <c r="AT73" t="s">
+      <c r="AT85" t="s">
         <v>177</v>
       </c>
-      <c r="AU73" t="s">
+      <c r="AU85" t="s">
         <v>231</v>
       </c>
-      <c r="AV73" t="s">
+      <c r="AV85" t="s">
         <v>20</v>
       </c>
-      <c r="AW73" t="s">
+      <c r="AW85" t="s">
         <v>231</v>
       </c>
-      <c r="AX73" t="s">
-        <v>174</v>
-      </c>
-      <c r="AY73" t="s">
+      <c r="AX85" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY85" t="s">
         <v>231</v>
       </c>
-      <c r="AZ73" t="s">
-        <v>174</v>
-      </c>
-      <c r="BA73" t="s">
+      <c r="AZ85" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA85" t="s">
         <v>231</v>
       </c>
-      <c r="BB73" t="s">
+      <c r="BB85" t="s">
         <v>224</v>
       </c>
-      <c r="BC73" t="s">
+      <c r="BC85" t="s">
         <v>231</v>
       </c>
-      <c r="BD73" t="s">
-        <v>135</v>
-      </c>
-      <c r="BE73" t="s">
+      <c r="BD85" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE85" t="s">
         <v>231</v>
       </c>
-      <c r="BF73" t="s">
-        <v>135</v>
-      </c>
-      <c r="BG73" t="s">
+      <c r="BF85" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG85" t="s">
         <v>231</v>
       </c>
-      <c r="BH73" t="s">
+      <c r="BH85" t="s">
         <v>175</v>
       </c>
-      <c r="BI73" t="s">
+      <c r="BI85" t="s">
         <v>231</v>
       </c>
-      <c r="BJ73" t="s">
+      <c r="BJ85" t="s">
         <v>20</v>
       </c>
-      <c r="BK73" t="s">
+      <c r="BK85" t="s">
         <v>231</v>
       </c>
-      <c r="BL73" t="s">
+      <c r="BL85" t="s">
         <v>172</v>
       </c>
-      <c r="BM73" t="s">
+      <c r="BM85" t="s">
         <v>231</v>
       </c>
-      <c r="BN73" t="s">
-        <v>135</v>
-      </c>
-      <c r="BO73" t="s">
+      <c r="BN85" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO85" t="s">
         <v>231</v>
       </c>
-      <c r="BP73" t="s">
-        <v>135</v>
-      </c>
-      <c r="BQ73" t="s">
+      <c r="BP85" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ85" t="s">
         <v>231</v>
       </c>
-      <c r="BR73" t="s">
+      <c r="BR85" t="s">
         <v>173</v>
       </c>
-      <c r="BS73" t="s">
+      <c r="BS85" t="s">
         <v>231</v>
       </c>
-      <c r="BT73" t="s">
+      <c r="BT85" t="s">
         <v>231</v>
+      </c>
+    </row>
+    <row r="86" spans="1:85" x14ac:dyDescent="0.3">
+      <c r="A86" s="5"/>
+      <c r="B86" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="87" spans="1:85" x14ac:dyDescent="0.3">
+      <c r="A87" s="5"/>
+      <c r="B87" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="D87">
+        <v>25</v>
+      </c>
+      <c r="E87" t="s">
+        <v>171</v>
+      </c>
+      <c r="F87">
+        <v>1</v>
+      </c>
+      <c r="G87">
+        <v>1643</v>
+      </c>
+      <c r="H87" t="s">
+        <v>21</v>
+      </c>
+      <c r="I87">
+        <v>80</v>
+      </c>
+      <c r="J87" t="s">
+        <v>22</v>
+      </c>
+      <c r="K87">
+        <v>14</v>
+      </c>
+      <c r="L87" t="s">
+        <v>135</v>
+      </c>
+      <c r="M87">
+        <v>24</v>
+      </c>
+      <c r="N87" t="s">
+        <v>171</v>
+      </c>
+      <c r="O87">
+        <v>1023</v>
+      </c>
+      <c r="P87" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q87">
+        <v>17</v>
+      </c>
+      <c r="R87" t="s">
+        <v>135</v>
+      </c>
+      <c r="S87">
+        <v>35</v>
+      </c>
+      <c r="T87" t="s">
+        <v>135</v>
+      </c>
+      <c r="U87">
+        <v>40</v>
+      </c>
+      <c r="V87" t="s">
+        <v>173</v>
+      </c>
+      <c r="W87">
+        <v>75</v>
+      </c>
+      <c r="X87" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y87">
+        <v>52</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA87">
+        <v>6.28</v>
+      </c>
+      <c r="AB87" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC87">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="AD87" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE87">
+        <v>251</v>
+      </c>
+      <c r="AF87" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG87">
+        <v>295</v>
+      </c>
+      <c r="AH87" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI87">
+        <v>235</v>
+      </c>
+      <c r="AJ87" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK87">
+        <v>7</v>
+      </c>
+      <c r="AL87" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM87">
+        <v>0.35</v>
+      </c>
+      <c r="AN87" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO87">
+        <v>0.25</v>
+      </c>
+      <c r="AP87" t="s">
+        <v>174</v>
+      </c>
+      <c r="AQ87">
+        <v>26</v>
+      </c>
+      <c r="AR87" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS87">
+        <v>300</v>
+      </c>
+      <c r="AT87" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU87">
+        <v>182.59</v>
+      </c>
+      <c r="AV87" t="s">
+        <v>20</v>
+      </c>
+      <c r="BI87">
+        <v>183.02</v>
+      </c>
+      <c r="BJ87" t="s">
+        <v>20</v>
+      </c>
+      <c r="BT87" s="5"/>
+      <c r="BU87" s="5"/>
+      <c r="BV87" s="5"/>
+      <c r="BW87" s="5"/>
+      <c r="BX87" s="5"/>
+      <c r="BY87" s="5"/>
+      <c r="BZ87" s="5"/>
+      <c r="CA87" s="5"/>
+      <c r="CB87" s="5"/>
+      <c r="CC87" s="5"/>
+      <c r="CD87" s="5"/>
+      <c r="CE87" s="5"/>
+      <c r="CF87" s="5"/>
+      <c r="CG87" s="5"/>
+    </row>
+    <row r="88" spans="1:85" x14ac:dyDescent="0.3">
+      <c r="B88" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="D88">
+        <v>50</v>
+      </c>
+      <c r="E88" t="s">
+        <v>171</v>
+      </c>
+      <c r="F88">
+        <v>2</v>
+      </c>
+      <c r="G88">
+        <v>3285</v>
+      </c>
+      <c r="H88" t="s">
+        <v>21</v>
+      </c>
+      <c r="I88">
+        <v>100.8</v>
+      </c>
+      <c r="J88" t="s">
+        <v>22</v>
+      </c>
+      <c r="K88">
+        <v>14</v>
+      </c>
+      <c r="L88" t="s">
+        <v>135</v>
+      </c>
+      <c r="M88">
+        <v>28</v>
+      </c>
+      <c r="N88" t="s">
+        <v>171</v>
+      </c>
+      <c r="O88">
+        <v>1023</v>
+      </c>
+      <c r="P88" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q88">
+        <v>17</v>
+      </c>
+      <c r="R88" t="s">
+        <v>135</v>
+      </c>
+      <c r="S88">
+        <v>30</v>
+      </c>
+      <c r="T88" t="s">
+        <v>135</v>
+      </c>
+      <c r="U88">
+        <v>90</v>
+      </c>
+      <c r="V88" t="s">
+        <v>173</v>
+      </c>
+      <c r="W88">
+        <v>105.2</v>
+      </c>
+      <c r="X88" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y88">
+        <v>78.400000000000006</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA88">
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="AB88" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC88">
+        <v>46.2</v>
+      </c>
+      <c r="AD88" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE88">
+        <v>271</v>
+      </c>
+      <c r="AF88" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG88">
+        <v>325</v>
+      </c>
+      <c r="AH88" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI88">
+        <v>235</v>
+      </c>
+      <c r="AJ88" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK88">
+        <v>12.6</v>
+      </c>
+      <c r="AL88" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM88">
+        <v>1</v>
+      </c>
+      <c r="AN88" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO88">
+        <v>0.9</v>
+      </c>
+      <c r="AP88" t="s">
+        <v>174</v>
+      </c>
+      <c r="AQ88">
+        <v>26</v>
+      </c>
+      <c r="AR88" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS88">
+        <v>552</v>
+      </c>
+      <c r="AT88" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU88">
+        <v>168.04</v>
+      </c>
+      <c r="AV88" t="s">
+        <v>20</v>
+      </c>
+      <c r="BI88">
+        <v>168.43</v>
+      </c>
+      <c r="BJ88" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="89" spans="1:85" x14ac:dyDescent="0.3">
+      <c r="B89" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="D89">
+        <v>75</v>
+      </c>
+      <c r="E89" t="s">
+        <v>171</v>
+      </c>
+      <c r="F89">
+        <v>3</v>
+      </c>
+      <c r="G89">
+        <v>4928</v>
+      </c>
+      <c r="H89" t="s">
+        <v>21</v>
+      </c>
+      <c r="I89">
+        <v>115.4</v>
+      </c>
+      <c r="J89" t="s">
+        <v>22</v>
+      </c>
+      <c r="K89">
+        <v>16</v>
+      </c>
+      <c r="L89" t="s">
+        <v>135</v>
+      </c>
+      <c r="M89">
+        <v>34</v>
+      </c>
+      <c r="N89" t="s">
+        <v>171</v>
+      </c>
+      <c r="O89">
+        <v>1022</v>
+      </c>
+      <c r="P89" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q89">
+        <v>18</v>
+      </c>
+      <c r="R89" t="s">
+        <v>135</v>
+      </c>
+      <c r="S89">
+        <v>30</v>
+      </c>
+      <c r="T89" t="s">
+        <v>135</v>
+      </c>
+      <c r="U89">
+        <v>126</v>
+      </c>
+      <c r="V89" t="s">
+        <v>173</v>
+      </c>
+      <c r="W89">
+        <v>142.80000000000001</v>
+      </c>
+      <c r="X89" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y89">
+        <v>113.4</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA89">
+        <v>13.06</v>
+      </c>
+      <c r="AB89" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC89">
+        <v>56.4</v>
+      </c>
+      <c r="AD89" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE89">
+        <v>272</v>
+      </c>
+      <c r="AF89" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG89">
+        <v>330</v>
+      </c>
+      <c r="AH89" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI89">
+        <v>210</v>
+      </c>
+      <c r="AJ89" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK89">
+        <v>14.7</v>
+      </c>
+      <c r="AL89" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM89">
+        <v>1.75</v>
+      </c>
+      <c r="AN89" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO89">
+        <v>1.6</v>
+      </c>
+      <c r="AP89" t="s">
+        <v>174</v>
+      </c>
+      <c r="AQ89">
+        <v>26</v>
+      </c>
+      <c r="AR89" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS89">
+        <v>804</v>
+      </c>
+      <c r="AT89" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU89">
+        <v>163.15</v>
+      </c>
+      <c r="AV89" t="s">
+        <v>20</v>
+      </c>
+      <c r="BI89">
+        <v>163.46</v>
+      </c>
+      <c r="BJ89" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="90" spans="1:85" x14ac:dyDescent="0.3">
+      <c r="B90" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="D90">
+        <v>85</v>
+      </c>
+      <c r="E90" t="s">
+        <v>171</v>
+      </c>
+      <c r="F90">
+        <v>4</v>
+      </c>
+      <c r="G90">
+        <v>5585</v>
+      </c>
+      <c r="H90" t="s">
+        <v>21</v>
+      </c>
+      <c r="I90">
+        <v>120.3</v>
+      </c>
+      <c r="J90" t="s">
+        <v>22</v>
+      </c>
+      <c r="K90">
+        <v>17</v>
+      </c>
+      <c r="L90" t="s">
+        <v>135</v>
+      </c>
+      <c r="M90">
+        <v>32</v>
+      </c>
+      <c r="N90" t="s">
+        <v>171</v>
+      </c>
+      <c r="O90">
+        <v>1021</v>
+      </c>
+      <c r="P90" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q90">
+        <v>18</v>
+      </c>
+      <c r="R90" t="s">
+        <v>135</v>
+      </c>
+      <c r="S90">
+        <v>36</v>
+      </c>
+      <c r="T90" t="s">
+        <v>135</v>
+      </c>
+      <c r="V90" t="s">
+        <v>173</v>
+      </c>
+      <c r="W90">
+        <v>152</v>
+      </c>
+      <c r="X90" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y90">
+        <v>124</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA90">
+        <v>14.19</v>
+      </c>
+      <c r="AB90" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC90">
+        <v>60.4</v>
+      </c>
+      <c r="AD90" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE90">
+        <v>281</v>
+      </c>
+      <c r="AF90" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG90">
+        <v>345</v>
+      </c>
+      <c r="AH90" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI90">
+        <v>210</v>
+      </c>
+      <c r="AJ90" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK90">
+        <v>15.6</v>
+      </c>
+      <c r="AL90" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM90">
+        <v>2.15</v>
+      </c>
+      <c r="AN90" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO90">
+        <v>1.95</v>
+      </c>
+      <c r="AP90" t="s">
+        <v>174</v>
+      </c>
+      <c r="AQ90">
+        <v>28</v>
+      </c>
+      <c r="AR90" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS90">
+        <v>919.2</v>
+      </c>
+      <c r="AT90" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU90">
+        <v>164.58</v>
+      </c>
+      <c r="AV90" t="s">
+        <v>20</v>
+      </c>
+      <c r="BI90">
+        <v>164.66</v>
+      </c>
+      <c r="BJ90" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="91" spans="1:85" x14ac:dyDescent="0.3">
+      <c r="B91" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="C91" s="5"/>
+      <c r="D91" s="5">
+        <v>100</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="F91" s="5">
+        <v>5</v>
+      </c>
+      <c r="G91" s="5">
+        <v>6570</v>
+      </c>
+      <c r="H91" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I91" s="5">
+        <v>127</v>
+      </c>
+      <c r="J91" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K91" s="5">
+        <v>17</v>
+      </c>
+      <c r="L91" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="M91" s="5">
+        <v>30</v>
+      </c>
+      <c r="N91" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="O91" s="5">
+        <v>1021</v>
+      </c>
+      <c r="P91" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q91" s="5">
+        <v>18</v>
+      </c>
+      <c r="R91" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="S91" s="5">
+        <v>36</v>
+      </c>
+      <c r="T91" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="U91" s="5">
+        <v>220</v>
+      </c>
+      <c r="V91" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="W91" s="5">
+        <v>151.80000000000001</v>
+      </c>
+      <c r="X91" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y91" s="5">
+        <v>148.19999999999999</v>
+      </c>
+      <c r="Z91" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA91" s="5">
+        <v>15.82</v>
+      </c>
+      <c r="AB91" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC91" s="5">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="AD91" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE91" s="5">
+        <v>293</v>
+      </c>
+      <c r="AF91" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG91" s="5">
+        <v>375</v>
+      </c>
+      <c r="AH91" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI91" s="5">
+        <v>220</v>
+      </c>
+      <c r="AJ91" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK91" s="5">
+        <v>17</v>
+      </c>
+      <c r="AL91" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM91" s="5">
+        <v>2.7</v>
+      </c>
+      <c r="AN91" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO91" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="AP91" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AQ91" s="5">
+        <v>28</v>
+      </c>
+      <c r="AR91" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS91" s="5">
+        <v>1107</v>
+      </c>
+      <c r="AT91" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU91" s="5">
+        <v>168.49</v>
+      </c>
+      <c r="AV91" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW91" s="5"/>
+      <c r="AX91" s="5"/>
+      <c r="AY91" s="5"/>
+      <c r="AZ91" s="5"/>
+      <c r="BA91" s="5"/>
+      <c r="BB91" s="5"/>
+      <c r="BC91" s="5"/>
+      <c r="BD91" s="5"/>
+      <c r="BE91" s="5"/>
+      <c r="BF91" s="5"/>
+      <c r="BG91" s="5"/>
+      <c r="BH91" s="5"/>
+      <c r="BI91" s="5">
+        <v>168.37</v>
+      </c>
+      <c r="BJ91" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK91" s="5"/>
+      <c r="BL91" s="5"/>
+      <c r="BM91" s="5"/>
+      <c r="BN91" s="5"/>
+      <c r="BO91" s="5"/>
+      <c r="BP91" s="5"/>
+      <c r="BQ91" s="5"/>
+      <c r="BR91" s="5"/>
+      <c r="BS91" s="5"/>
+    </row>
+    <row r="92" spans="1:85" x14ac:dyDescent="0.3">
+      <c r="B92" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="D92">
+        <v>110</v>
+      </c>
+      <c r="E92" t="s">
+        <v>171</v>
+      </c>
+      <c r="F92">
+        <v>6</v>
+      </c>
+      <c r="G92">
+        <v>7227</v>
+      </c>
+      <c r="H92" t="s">
+        <v>21</v>
+      </c>
+      <c r="I92">
+        <v>131.1</v>
+      </c>
+      <c r="J92" t="s">
+        <v>22</v>
+      </c>
+      <c r="K92">
+        <v>17</v>
+      </c>
+      <c r="L92" t="s">
+        <v>135</v>
+      </c>
+      <c r="M92">
+        <v>26</v>
+      </c>
+      <c r="N92" t="s">
+        <v>171</v>
+      </c>
+      <c r="O92">
+        <v>1021</v>
+      </c>
+      <c r="P92" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q92">
+        <v>18</v>
+      </c>
+      <c r="R92" t="s">
+        <v>135</v>
+      </c>
+      <c r="S92">
+        <v>38</v>
+      </c>
+      <c r="T92" t="s">
+        <v>135</v>
+      </c>
+      <c r="U92">
+        <v>240</v>
+      </c>
+      <c r="V92" t="s">
+        <v>173</v>
+      </c>
+      <c r="W92">
+        <v>153.80000000000001</v>
+      </c>
+      <c r="X92" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y92">
+        <v>155.80000000000001</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA92">
+        <v>16.850000000000001</v>
+      </c>
+      <c r="AB92" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC92">
+        <v>69.8</v>
+      </c>
+      <c r="AD92" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE92">
+        <v>304</v>
+      </c>
+      <c r="AF92" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG92">
+        <v>390</v>
+      </c>
+      <c r="AH92" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI92">
+        <v>220</v>
+      </c>
+      <c r="AJ92" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK92">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="AL92" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM92">
+        <v>2.85</v>
+      </c>
+      <c r="AN92" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO92">
+        <v>2.65</v>
+      </c>
+      <c r="AP92" t="s">
+        <v>174</v>
+      </c>
+      <c r="AQ92">
+        <v>29</v>
+      </c>
+      <c r="AR92" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS92">
+        <v>1236</v>
+      </c>
+      <c r="AT92" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU92">
+        <v>171.03</v>
+      </c>
+      <c r="AV92" t="s">
+        <v>20</v>
+      </c>
+      <c r="BI92">
+        <v>170.8</v>
+      </c>
+      <c r="BJ92" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Aepms-backend/data/Engine_Performance_Data.xlsx
+++ b/Aepms-backend/data/Engine_Performance_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GOKUL\Desktop\WORKPLACE\Workplace\Aepms-backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC303C7E-297A-4E5B-917F-EBFB5C4D190E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656CD45D-1287-449F-BEAF-3CE83B132A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="vessel_info" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3331" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3790" uniqueCount="259">
   <si>
     <t>hull_no</t>
   </si>
@@ -709,9 +709,6 @@
     <t>SANFU</t>
   </si>
   <si>
-    <t>MAN B&amp;W</t>
-  </si>
-  <si>
     <t>kg/cm2</t>
   </si>
   <si>
@@ -772,9 +769,6 @@
     <t>SF080103</t>
   </si>
   <si>
-    <t>Taizhou Sanfu Ship Engineering</t>
-  </si>
-  <si>
     <t>5S50MC-C</t>
   </si>
   <si>
@@ -803,13 +797,31 @@
   </si>
   <si>
     <t>DMD-WÄRTSILÄ 5RT-flex58T-D</t>
+  </si>
+  <si>
+    <t>0774-STALLION</t>
+  </si>
+  <si>
+    <t>DK828Z0309</t>
+  </si>
+  <si>
+    <t>MESSRS. NINGBO DONGHAI SHIPPING CO.,LTD</t>
+  </si>
+  <si>
+    <t>MESSRS. NINGBO XINLE SHIPBUILDING CO.,LTD</t>
+  </si>
+  <si>
+    <t>8DKM-28</t>
+  </si>
+  <si>
+    <t>DAIHATSU DIESEL MFG. CO., LTD.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -838,8 +850,23 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF888888"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -852,8 +879,28 @@
         <bgColor theme="0" tint="-0.14999847407452621"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F7FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8E8E8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -861,11 +908,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -887,16 +949,35 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2015,7 +2096,7 @@
       <c r="C9">
         <v>9792058</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" t="s">
         <v>214</v>
       </c>
       <c r="E9" s="2">
@@ -2078,7 +2159,7 @@
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C10">
         <v>9532082</v>
@@ -2087,22 +2168,22 @@
         <v>5933</v>
       </c>
       <c r="E10" t="s">
+        <v>245</v>
+      </c>
+      <c r="F10" t="s">
+        <v>234</v>
+      </c>
+      <c r="G10" t="s">
+        <v>246</v>
+      </c>
+      <c r="H10" t="s">
+        <v>233</v>
+      </c>
+      <c r="I10" t="s">
+        <v>232</v>
+      </c>
+      <c r="J10" t="s">
         <v>247</v>
-      </c>
-      <c r="F10" t="s">
-        <v>235</v>
-      </c>
-      <c r="G10" t="s">
-        <v>248</v>
-      </c>
-      <c r="H10" t="s">
-        <v>234</v>
-      </c>
-      <c r="I10" t="s">
-        <v>233</v>
-      </c>
-      <c r="J10" t="s">
-        <v>249</v>
       </c>
       <c r="K10">
         <v>6</v>
@@ -2111,7 +2192,7 @@
         <v>19</v>
       </c>
       <c r="N10" s="6">
-        <v>163.69999999999999</v>
+        <v>163.5</v>
       </c>
       <c r="O10" t="s">
         <v>20</v>
@@ -2130,6 +2211,12 @@
       </c>
       <c r="T10">
         <v>14330</v>
+      </c>
+      <c r="X10" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.3">
@@ -2152,10 +2239,10 @@
         <v>222</v>
       </c>
       <c r="H11" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="I11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="J11" t="s">
         <v>218</v>
@@ -2186,6 +2273,9 @@
       </c>
       <c r="T11">
         <v>5585</v>
+      </c>
+      <c r="X11" t="s">
+        <v>21</v>
       </c>
       <c r="Y11">
         <v>100</v>
@@ -2196,7 +2286,7 @@
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C12">
         <v>9628893</v>
@@ -2205,22 +2295,22 @@
         <v>774</v>
       </c>
       <c r="E12" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F12" t="s">
+        <v>249</v>
+      </c>
+      <c r="G12" t="s">
+        <v>250</v>
+      </c>
+      <c r="H12" t="s">
         <v>251</v>
       </c>
-      <c r="G12" t="s">
+      <c r="I12" t="s">
+        <v>239</v>
+      </c>
+      <c r="J12" t="s">
         <v>252</v>
-      </c>
-      <c r="H12" t="s">
-        <v>253</v>
-      </c>
-      <c r="I12" t="s">
-        <v>240</v>
-      </c>
-      <c r="J12" t="s">
-        <v>254</v>
       </c>
       <c r="K12">
         <v>5</v>
@@ -2237,47 +2327,114 @@
       <c r="P12">
         <v>9760</v>
       </c>
-      <c r="Q12" s="13" t="s">
+      <c r="Q12" t="s">
         <v>21</v>
       </c>
       <c r="R12">
         <v>92.9</v>
       </c>
-      <c r="S12" s="13" t="s">
+      <c r="S12" t="s">
         <v>22</v>
+      </c>
+      <c r="T12" s="4">
+        <v>8296</v>
+      </c>
+      <c r="X12" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="B13" t="s">
+        <v>224</v>
+      </c>
+      <c r="C13">
+        <v>9644500</v>
+      </c>
+      <c r="D13" s="2">
+        <v>4078</v>
+      </c>
+      <c r="E13" s="2">
+        <v>10701</v>
+      </c>
+      <c r="F13" t="s">
+        <v>225</v>
+      </c>
+      <c r="G13" t="s">
+        <v>226</v>
+      </c>
+      <c r="H13" t="s">
+        <v>227</v>
+      </c>
+      <c r="I13" t="s">
+        <v>228</v>
+      </c>
+      <c r="J13" t="s">
+        <v>229</v>
+      </c>
+      <c r="K13">
+        <v>6</v>
+      </c>
+      <c r="M13" t="s">
+        <v>19</v>
+      </c>
+      <c r="N13">
+        <v>166.6</v>
+      </c>
+      <c r="O13" t="s">
+        <v>20</v>
+      </c>
+      <c r="P13" s="4">
+        <v>12270</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>21</v>
+      </c>
+      <c r="R13">
+        <v>105</v>
+      </c>
+      <c r="S13" t="s">
+        <v>22</v>
+      </c>
+      <c r="T13" s="4">
+        <v>10436</v>
+      </c>
+      <c r="X13" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C14">
         <v>9628910</v>
       </c>
-      <c r="D14" s="2">
-        <v>774</v>
+      <c r="D14" s="2" t="s">
+        <v>253</v>
       </c>
       <c r="E14" t="s">
+        <v>236</v>
+      </c>
+      <c r="F14" t="s">
+        <v>238</v>
+      </c>
+      <c r="G14" t="s">
         <v>237</v>
       </c>
-      <c r="F14" t="s">
+      <c r="H14" t="s">
+        <v>240</v>
+      </c>
+      <c r="I14" t="s">
         <v>239</v>
       </c>
-      <c r="G14" t="s">
-        <v>238</v>
-      </c>
-      <c r="H14" t="s">
-        <v>241</v>
-      </c>
-      <c r="I14" t="s">
-        <v>240</v>
-      </c>
       <c r="J14" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K14">
         <v>5</v>
@@ -2285,8 +2442,8 @@
       <c r="M14" t="s">
         <v>19</v>
       </c>
-      <c r="N14" t="s">
-        <v>231</v>
+      <c r="N14">
+        <v>172.2</v>
       </c>
       <c r="O14" t="s">
         <v>20</v>
@@ -2304,52 +2461,57 @@
         <v>22</v>
       </c>
       <c r="T14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="U14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="V14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="W14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="X14" t="s">
         <v>21</v>
       </c>
       <c r="Y14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Z14" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C15">
         <v>9486295</v>
       </c>
-      <c r="D15" s="2"/>
+      <c r="D15" s="2" t="s">
+        <v>254</v>
+      </c>
       <c r="E15" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
+      </c>
+      <c r="F15" t="s">
+        <v>255</v>
       </c>
       <c r="G15" t="s">
-        <v>244</v>
-      </c>
-      <c r="H15" t="s">
-        <v>223</v>
+        <v>256</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>258</v>
       </c>
       <c r="I15" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="J15" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="K15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M15" t="s">
         <v>19</v>
@@ -2382,72 +2544,16 @@
         <v>73</v>
       </c>
       <c r="W15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="X15" t="s">
         <v>21</v>
       </c>
       <c r="Y15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Z15" t="s">
         <v>171</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
-        <v>225</v>
-      </c>
-      <c r="C16">
-        <v>9644500</v>
-      </c>
-      <c r="D16" s="2">
-        <v>4078</v>
-      </c>
-      <c r="E16" s="2">
-        <v>10701</v>
-      </c>
-      <c r="F16" t="s">
-        <v>226</v>
-      </c>
-      <c r="G16" t="s">
-        <v>227</v>
-      </c>
-      <c r="H16" t="s">
-        <v>228</v>
-      </c>
-      <c r="I16" t="s">
-        <v>229</v>
-      </c>
-      <c r="J16" t="s">
-        <v>230</v>
-      </c>
-      <c r="K16">
-        <v>6</v>
-      </c>
-      <c r="M16" t="s">
-        <v>19</v>
-      </c>
-      <c r="N16">
-        <v>166.6</v>
-      </c>
-      <c r="O16" t="s">
-        <v>20</v>
-      </c>
-      <c r="P16" s="4">
-        <v>12270</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>21</v>
-      </c>
-      <c r="R16">
-        <v>105</v>
-      </c>
-      <c r="S16" t="s">
-        <v>22</v>
-      </c>
-      <c r="T16" s="4">
-        <v>10436</v>
       </c>
     </row>
     <row r="17" spans="4:5" x14ac:dyDescent="0.3">
@@ -2462,7 +2568,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.21875" customWidth="1"/>
@@ -2851,10 +2957,175 @@
       <c r="H9">
         <v>5</v>
       </c>
+      <c r="I9" t="s">
+        <v>135</v>
+      </c>
       <c r="J9">
         <v>45</v>
       </c>
+      <c r="K9" t="s">
+        <v>135</v>
+      </c>
+      <c r="M9" t="s">
+        <v>135</v>
+      </c>
       <c r="O9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B10" s="2">
+        <v>5933</v>
+      </c>
+      <c r="C10" s="1">
+        <v>42788</v>
+      </c>
+      <c r="D10" t="s">
+        <v>131</v>
+      </c>
+      <c r="H10">
+        <v>8</v>
+      </c>
+      <c r="I10" t="s">
+        <v>135</v>
+      </c>
+      <c r="J10">
+        <v>42</v>
+      </c>
+      <c r="K10" t="s">
+        <v>135</v>
+      </c>
+      <c r="O10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B11" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="C11" s="1">
+        <v>42788</v>
+      </c>
+      <c r="D11" t="s">
+        <v>131</v>
+      </c>
+      <c r="H11">
+        <v>7</v>
+      </c>
+      <c r="I11" t="s">
+        <v>135</v>
+      </c>
+      <c r="J11">
+        <v>44</v>
+      </c>
+      <c r="K11" t="s">
+        <v>135</v>
+      </c>
+      <c r="O11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B12" s="2">
+        <v>774</v>
+      </c>
+      <c r="C12" s="1">
+        <v>42788</v>
+      </c>
+      <c r="D12" t="s">
+        <v>131</v>
+      </c>
+      <c r="H12">
+        <v>4</v>
+      </c>
+      <c r="I12" t="s">
+        <v>135</v>
+      </c>
+      <c r="J12">
+        <v>45</v>
+      </c>
+      <c r="K12" t="s">
+        <v>135</v>
+      </c>
+      <c r="O12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B13" s="2">
+        <v>4078</v>
+      </c>
+      <c r="C13" s="1">
+        <v>42788</v>
+      </c>
+      <c r="D13" t="s">
+        <v>131</v>
+      </c>
+      <c r="H13">
+        <v>3</v>
+      </c>
+      <c r="I13" t="s">
+        <v>135</v>
+      </c>
+      <c r="J13">
+        <v>41</v>
+      </c>
+      <c r="K13" t="s">
+        <v>135</v>
+      </c>
+      <c r="O13" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C14" s="1">
+        <v>42788</v>
+      </c>
+      <c r="D14" t="s">
+        <v>131</v>
+      </c>
+      <c r="H14">
+        <v>2</v>
+      </c>
+      <c r="I14" t="s">
+        <v>135</v>
+      </c>
+      <c r="J14">
+        <v>43</v>
+      </c>
+      <c r="K14" t="s">
+        <v>135</v>
+      </c>
+      <c r="O14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C15" s="1">
+        <v>42788</v>
+      </c>
+      <c r="D15" t="s">
+        <v>131</v>
+      </c>
+      <c r="H15">
+        <v>3</v>
+      </c>
+      <c r="I15" t="s">
+        <v>135</v>
+      </c>
+      <c r="J15">
+        <v>40</v>
+      </c>
+      <c r="K15" t="s">
+        <v>135</v>
+      </c>
+      <c r="O15" t="s">
         <v>137</v>
       </c>
     </row>
@@ -2869,7 +3140,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:CG92"/>
+  <dimension ref="A1:CG93"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="26.21875" customWidth="1"/>
@@ -12973,7 +13244,7 @@
       </c>
     </row>
     <row r="50" spans="2:70" x14ac:dyDescent="0.3">
-      <c r="B50" s="13" t="s">
+      <c r="B50" t="s">
         <v>214</v>
       </c>
       <c r="D50">
@@ -13173,7 +13444,7 @@
       </c>
     </row>
     <row r="51" spans="2:70" x14ac:dyDescent="0.3">
-      <c r="B51" s="13" t="s">
+      <c r="B51" t="s">
         <v>214</v>
       </c>
       <c r="D51">
@@ -13373,7 +13644,7 @@
       </c>
     </row>
     <row r="52" spans="2:70" x14ac:dyDescent="0.3">
-      <c r="B52" s="13" t="s">
+      <c r="B52" t="s">
         <v>214</v>
       </c>
       <c r="D52">
@@ -13573,7 +13844,7 @@
       </c>
     </row>
     <row r="53" spans="2:70" x14ac:dyDescent="0.3">
-      <c r="B53" s="13" t="s">
+      <c r="B53" t="s">
         <v>214</v>
       </c>
       <c r="D53">
@@ -13773,7 +14044,7 @@
       </c>
     </row>
     <row r="54" spans="2:70" x14ac:dyDescent="0.3">
-      <c r="B54" s="13" t="s">
+      <c r="B54" t="s">
         <v>214</v>
       </c>
       <c r="D54">
@@ -14085,7 +14356,7 @@
         <v>174</v>
       </c>
       <c r="AO55" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AP55" t="s">
         <v>205</v>
@@ -14097,7 +14368,7 @@
         <v>135</v>
       </c>
       <c r="AS55" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AT55" t="s">
         <v>177</v>
@@ -14146,6 +14417,9 @@
       </c>
       <c r="BP55" t="s">
         <v>135</v>
+      </c>
+      <c r="BR55" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="56" spans="2:70" x14ac:dyDescent="0.3">
@@ -14273,7 +14547,7 @@
         <v>135</v>
       </c>
       <c r="AS56" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AT56" t="s">
         <v>177</v>
@@ -14322,6 +14596,9 @@
       </c>
       <c r="BP56" t="s">
         <v>135</v>
+      </c>
+      <c r="BR56" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="57" spans="2:70" x14ac:dyDescent="0.3">
@@ -14449,7 +14726,7 @@
         <v>135</v>
       </c>
       <c r="AS57" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AT57" t="s">
         <v>177</v>
@@ -14498,6 +14775,9 @@
       </c>
       <c r="BP57" t="s">
         <v>135</v>
+      </c>
+      <c r="BR57" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="58" spans="2:70" x14ac:dyDescent="0.3">
@@ -14625,7 +14905,7 @@
         <v>135</v>
       </c>
       <c r="AS58" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AT58" t="s">
         <v>177</v>
@@ -14674,6 +14954,9 @@
       </c>
       <c r="BP58" t="s">
         <v>135</v>
+      </c>
+      <c r="BR58" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="59" spans="2:70" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -14801,7 +15084,7 @@
         <v>135</v>
       </c>
       <c r="AS59" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AT59" t="s">
         <v>177</v>
@@ -14858,13 +15141,16 @@
       </c>
       <c r="BP59" t="s">
         <v>135</v>
+      </c>
+      <c r="BR59" s="5" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="60" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B60" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="C60" s="14"/>
+      <c r="C60" s="12"/>
       <c r="D60" s="10">
         <v>25</v>
       </c>
@@ -14889,7 +15175,7 @@
       <c r="K60" s="10">
         <v>14</v>
       </c>
-      <c r="L60" s="12" t="s">
+      <c r="L60" s="11" t="s">
         <v>135</v>
       </c>
       <c r="M60" s="10">
@@ -14973,13 +15259,13 @@
       <c r="AM60" s="10">
         <v>0.5</v>
       </c>
-      <c r="AN60" s="13" t="s">
+      <c r="AN60" t="s">
         <v>174</v>
       </c>
       <c r="AO60" s="10">
         <v>0.40799999999999997</v>
       </c>
-      <c r="AP60" s="13" t="s">
+      <c r="AP60" t="s">
         <v>205</v>
       </c>
       <c r="AQ60" s="10">
@@ -14991,71 +15277,71 @@
       <c r="AS60" s="10">
         <v>300.60000000000002</v>
       </c>
-      <c r="AT60" s="13" t="s">
+      <c r="AT60" t="s">
         <v>177</v>
       </c>
       <c r="AU60" s="10">
         <v>183.01</v>
       </c>
-      <c r="AV60" s="13" t="s">
+      <c r="AV60" t="s">
         <v>20</v>
       </c>
       <c r="AW60" s="10">
         <v>75</v>
       </c>
-      <c r="AX60" s="13" t="s">
+      <c r="AX60" t="s">
         <v>174</v>
       </c>
       <c r="AY60" s="10">
         <v>52</v>
       </c>
-      <c r="AZ60" s="13" t="s">
+      <c r="AZ60" t="s">
         <v>174</v>
       </c>
       <c r="BA60" s="10">
         <v>0.35699999999999998</v>
       </c>
-      <c r="BB60" s="13" t="s">
+      <c r="BB60" t="s">
         <v>205</v>
       </c>
       <c r="BC60" s="10">
         <v>295</v>
       </c>
-      <c r="BD60" s="13" t="s">
+      <c r="BD60" t="s">
         <v>135</v>
       </c>
       <c r="BE60" s="10">
         <v>235</v>
       </c>
-      <c r="BF60" s="13" t="s">
+      <c r="BF60" t="s">
         <v>135</v>
       </c>
       <c r="BG60" s="10">
         <v>7</v>
       </c>
-      <c r="BH60" s="13" t="s">
+      <c r="BH60" t="s">
         <v>175</v>
       </c>
       <c r="BI60" s="10">
         <v>183.02</v>
       </c>
-      <c r="BJ60" s="13" t="s">
+      <c r="BJ60" t="s">
         <v>20</v>
       </c>
-      <c r="BK60" s="14"/>
-      <c r="BL60" s="13" t="s">
+      <c r="BK60" s="12"/>
+      <c r="BL60" t="s">
         <v>172</v>
       </c>
-      <c r="BM60" s="14"/>
-      <c r="BN60" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BO60" s="14"/>
-      <c r="BP60" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BQ60" s="14"/>
-      <c r="BR60" s="13" t="s">
+      <c r="BM60" s="12"/>
+      <c r="BN60" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO60" s="12"/>
+      <c r="BP60" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ60" s="12"/>
+      <c r="BR60" t="s">
         <v>173</v>
       </c>
     </row>
@@ -15063,7 +15349,7 @@
       <c r="B61" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="C61" s="14"/>
+      <c r="C61" s="12"/>
       <c r="D61" s="10">
         <v>50</v>
       </c>
@@ -15088,7 +15374,7 @@
       <c r="K61" s="10">
         <v>14</v>
       </c>
-      <c r="L61" s="12" t="s">
+      <c r="L61" s="11" t="s">
         <v>135</v>
       </c>
       <c r="M61" s="10">
@@ -15172,13 +15458,13 @@
       <c r="AM61" s="10">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AN61" s="13" t="s">
+      <c r="AN61" t="s">
         <v>174</v>
       </c>
       <c r="AO61" s="10">
         <v>0.96899999999999997</v>
       </c>
-      <c r="AP61" s="13" t="s">
+      <c r="AP61" t="s">
         <v>205</v>
       </c>
       <c r="AQ61" s="10">
@@ -15190,71 +15476,71 @@
       <c r="AS61" s="10">
         <v>561</v>
       </c>
-      <c r="AT61" s="13" t="s">
+      <c r="AT61" t="s">
         <v>177</v>
       </c>
       <c r="AU61" s="10">
         <v>170.78</v>
       </c>
-      <c r="AV61" s="13" t="s">
+      <c r="AV61" t="s">
         <v>20</v>
       </c>
       <c r="AW61" s="10">
         <v>105.2</v>
       </c>
-      <c r="AX61" s="13" t="s">
+      <c r="AX61" t="s">
         <v>174</v>
       </c>
       <c r="AY61" s="10">
         <v>78.400000000000006</v>
       </c>
-      <c r="AZ61" s="13" t="s">
+      <c r="AZ61" t="s">
         <v>174</v>
       </c>
       <c r="BA61" s="10">
         <v>1.02</v>
       </c>
-      <c r="BB61" s="13" t="s">
+      <c r="BB61" t="s">
         <v>205</v>
       </c>
       <c r="BC61" s="10">
         <v>325</v>
       </c>
-      <c r="BD61" s="13" t="s">
+      <c r="BD61" t="s">
         <v>135</v>
       </c>
       <c r="BE61" s="10">
         <v>235</v>
       </c>
-      <c r="BF61" s="13" t="s">
+      <c r="BF61" t="s">
         <v>135</v>
       </c>
       <c r="BG61" s="10">
         <v>12.6</v>
       </c>
-      <c r="BH61" s="13" t="s">
+      <c r="BH61" t="s">
         <v>175</v>
       </c>
       <c r="BI61" s="10">
         <v>168.43</v>
       </c>
-      <c r="BJ61" s="13" t="s">
+      <c r="BJ61" t="s">
         <v>20</v>
       </c>
-      <c r="BK61" s="14"/>
-      <c r="BL61" s="13" t="s">
+      <c r="BK61" s="12"/>
+      <c r="BL61" t="s">
         <v>172</v>
       </c>
-      <c r="BM61" s="14"/>
-      <c r="BN61" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BO61" s="14"/>
-      <c r="BP61" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BQ61" s="14"/>
-      <c r="BR61" s="13" t="s">
+      <c r="BM61" s="12"/>
+      <c r="BN61" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO61" s="12"/>
+      <c r="BP61" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ61" s="12"/>
+      <c r="BR61" t="s">
         <v>173</v>
       </c>
     </row>
@@ -15262,7 +15548,7 @@
       <c r="B62" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="C62" s="14"/>
+      <c r="C62" s="12"/>
       <c r="D62" s="10">
         <v>75</v>
       </c>
@@ -15287,7 +15573,7 @@
       <c r="K62" s="10">
         <v>16</v>
       </c>
-      <c r="L62" s="12" t="s">
+      <c r="L62" s="11" t="s">
         <v>135</v>
       </c>
       <c r="M62" s="10">
@@ -15371,13 +15657,13 @@
       <c r="AM62" s="10">
         <v>1.9</v>
       </c>
-      <c r="AN62" s="13" t="s">
+      <c r="AN62" t="s">
         <v>174</v>
       </c>
       <c r="AO62" s="10">
         <v>1.7849999999999999</v>
       </c>
-      <c r="AP62" s="13" t="s">
+      <c r="AP62" t="s">
         <v>205</v>
       </c>
       <c r="AQ62" s="10">
@@ -15389,71 +15675,71 @@
       <c r="AS62" s="10">
         <v>816</v>
       </c>
-      <c r="AT62" s="13" t="s">
+      <c r="AT62" t="s">
         <v>177</v>
       </c>
       <c r="AU62" s="10">
         <v>165.6</v>
       </c>
-      <c r="AV62" s="13" t="s">
+      <c r="AV62" t="s">
         <v>20</v>
       </c>
       <c r="AW62" s="10">
         <v>142.80000000000001</v>
       </c>
-      <c r="AX62" s="13" t="s">
+      <c r="AX62" t="s">
         <v>174</v>
       </c>
       <c r="AY62" s="10">
         <v>113.4</v>
       </c>
-      <c r="AZ62" s="13" t="s">
+      <c r="AZ62" t="s">
         <v>174</v>
       </c>
       <c r="BA62" s="10">
         <v>1.7849999999999999</v>
       </c>
-      <c r="BB62" s="13" t="s">
+      <c r="BB62" t="s">
         <v>205</v>
       </c>
       <c r="BC62" s="10">
         <v>330</v>
       </c>
-      <c r="BD62" s="13" t="s">
+      <c r="BD62" t="s">
         <v>135</v>
       </c>
       <c r="BE62" s="10">
         <v>210</v>
       </c>
-      <c r="BF62" s="13" t="s">
+      <c r="BF62" t="s">
         <v>135</v>
       </c>
       <c r="BG62" s="10">
         <v>14.7</v>
       </c>
-      <c r="BH62" s="13" t="s">
+      <c r="BH62" t="s">
         <v>175</v>
       </c>
       <c r="BI62" s="10">
         <v>163.46</v>
       </c>
-      <c r="BJ62" s="13" t="s">
+      <c r="BJ62" t="s">
         <v>20</v>
       </c>
-      <c r="BK62" s="14"/>
-      <c r="BL62" s="13" t="s">
+      <c r="BK62" s="12"/>
+      <c r="BL62" t="s">
         <v>172</v>
       </c>
-      <c r="BM62" s="14"/>
-      <c r="BN62" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BO62" s="14"/>
-      <c r="BP62" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BQ62" s="14"/>
-      <c r="BR62" s="13" t="s">
+      <c r="BM62" s="12"/>
+      <c r="BN62" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO62" s="12"/>
+      <c r="BP62" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ62" s="12"/>
+      <c r="BR62" t="s">
         <v>173</v>
       </c>
     </row>
@@ -15461,7 +15747,7 @@
       <c r="B63" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="C63" s="14"/>
+      <c r="C63" s="12"/>
       <c r="D63" s="10">
         <v>85</v>
       </c>
@@ -15486,7 +15772,7 @@
       <c r="K63" s="10">
         <v>17</v>
       </c>
-      <c r="L63" s="12" t="s">
+      <c r="L63" s="11" t="s">
         <v>135</v>
       </c>
       <c r="M63" s="10">
@@ -15566,13 +15852,13 @@
       <c r="AM63" s="10">
         <v>2.15</v>
       </c>
-      <c r="AN63" s="13" t="s">
+      <c r="AN63" t="s">
         <v>174</v>
       </c>
       <c r="AO63" s="10">
         <v>1.988</v>
       </c>
-      <c r="AP63" s="13" t="s">
+      <c r="AP63" t="s">
         <v>205</v>
       </c>
       <c r="AQ63" s="10">
@@ -15584,71 +15870,71 @@
       <c r="AS63" s="10">
         <v>919.2</v>
       </c>
-      <c r="AT63" s="13" t="s">
+      <c r="AT63" t="s">
         <v>177</v>
       </c>
       <c r="AU63" s="10">
         <v>164.58</v>
       </c>
-      <c r="AV63" s="13" t="s">
+      <c r="AV63" t="s">
         <v>20</v>
       </c>
       <c r="AW63" s="10">
         <v>152</v>
       </c>
-      <c r="AX63" s="13" t="s">
+      <c r="AX63" t="s">
         <v>174</v>
       </c>
       <c r="AY63" s="10">
         <v>124</v>
       </c>
-      <c r="AZ63" s="13" t="s">
+      <c r="AZ63" t="s">
         <v>174</v>
       </c>
       <c r="BA63" s="10">
         <v>2.1920000000000002</v>
       </c>
-      <c r="BB63" s="13" t="s">
+      <c r="BB63" t="s">
         <v>205</v>
       </c>
       <c r="BC63" s="10">
         <v>345</v>
       </c>
-      <c r="BD63" s="13" t="s">
+      <c r="BD63" t="s">
         <v>135</v>
       </c>
       <c r="BE63" s="10">
         <v>210</v>
       </c>
-      <c r="BF63" s="13" t="s">
+      <c r="BF63" t="s">
         <v>135</v>
       </c>
       <c r="BG63" s="10">
         <v>15.6</v>
       </c>
-      <c r="BH63" s="13" t="s">
+      <c r="BH63" t="s">
         <v>175</v>
       </c>
       <c r="BI63" s="10">
         <v>164.66</v>
       </c>
-      <c r="BJ63" s="13" t="s">
+      <c r="BJ63" t="s">
         <v>20</v>
       </c>
-      <c r="BK63" s="14"/>
-      <c r="BL63" s="13" t="s">
+      <c r="BK63" s="12"/>
+      <c r="BL63" t="s">
         <v>172</v>
       </c>
-      <c r="BM63" s="14"/>
-      <c r="BN63" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BO63" s="14"/>
-      <c r="BP63" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BQ63" s="14"/>
-      <c r="BR63" s="13" t="s">
+      <c r="BM63" s="12"/>
+      <c r="BN63" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO63" s="12"/>
+      <c r="BP63" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ63" s="12"/>
+      <c r="BR63" t="s">
         <v>173</v>
       </c>
     </row>
@@ -15656,7 +15942,7 @@
       <c r="B64" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="C64" s="14"/>
+      <c r="C64" s="12"/>
       <c r="D64" s="10">
         <v>100</v>
       </c>
@@ -15681,7 +15967,7 @@
       <c r="K64" s="10">
         <v>17</v>
       </c>
-      <c r="L64" s="12" t="s">
+      <c r="L64" s="11" t="s">
         <v>135</v>
       </c>
       <c r="M64" s="10">
@@ -15765,13 +16051,13 @@
       <c r="AM64" s="10">
         <v>2.7</v>
       </c>
-      <c r="AN64" s="13" t="s">
+      <c r="AN64" t="s">
         <v>174</v>
       </c>
       <c r="AO64" s="10">
         <v>2.5489999999999999</v>
       </c>
-      <c r="AP64" s="13" t="s">
+      <c r="AP64" t="s">
         <v>205</v>
       </c>
       <c r="AQ64" s="10">
@@ -15783,71 +16069,71 @@
       <c r="AS64" s="10">
         <v>1107</v>
       </c>
-      <c r="AT64" s="13" t="s">
+      <c r="AT64" t="s">
         <v>177</v>
       </c>
       <c r="AU64" s="10">
         <v>168.49</v>
       </c>
-      <c r="AV64" s="13" t="s">
+      <c r="AV64" t="s">
         <v>20</v>
       </c>
       <c r="AW64" s="10">
         <v>151.80000000000001</v>
       </c>
-      <c r="AX64" s="13" t="s">
+      <c r="AX64" t="s">
         <v>174</v>
       </c>
       <c r="AY64" s="10">
         <v>148.19999999999999</v>
       </c>
-      <c r="AZ64" s="13" t="s">
+      <c r="AZ64" t="s">
         <v>174</v>
       </c>
       <c r="BA64" s="10">
         <v>2.7530000000000001</v>
       </c>
-      <c r="BB64" s="13" t="s">
+      <c r="BB64" t="s">
         <v>205</v>
       </c>
       <c r="BC64" s="10">
         <v>375</v>
       </c>
-      <c r="BD64" s="13" t="s">
+      <c r="BD64" t="s">
         <v>135</v>
       </c>
       <c r="BE64" s="10">
         <v>220</v>
       </c>
-      <c r="BF64" s="13" t="s">
+      <c r="BF64" t="s">
         <v>135</v>
       </c>
       <c r="BG64" s="10">
         <v>17</v>
       </c>
-      <c r="BH64" s="13" t="s">
+      <c r="BH64" t="s">
         <v>175</v>
       </c>
       <c r="BI64" s="10">
         <v>168.37</v>
       </c>
-      <c r="BJ64" s="13" t="s">
+      <c r="BJ64" t="s">
         <v>20</v>
       </c>
-      <c r="BK64" s="14"/>
-      <c r="BL64" s="13" t="s">
+      <c r="BK64" s="12"/>
+      <c r="BL64" t="s">
         <v>172</v>
       </c>
-      <c r="BM64" s="14"/>
-      <c r="BN64" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BO64" s="14"/>
-      <c r="BP64" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BQ64" s="14"/>
-      <c r="BR64" s="13" t="s">
+      <c r="BM64" s="12"/>
+      <c r="BN64" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO64" s="12"/>
+      <c r="BP64" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ64" s="12"/>
+      <c r="BR64" t="s">
         <v>173</v>
       </c>
     </row>
@@ -15855,7 +16141,7 @@
       <c r="B65" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="C65" s="14"/>
+      <c r="C65" s="12"/>
       <c r="D65" s="10">
         <v>100</v>
       </c>
@@ -15880,7 +16166,7 @@
       <c r="K65" s="10">
         <v>17</v>
       </c>
-      <c r="L65" s="12" t="s">
+      <c r="L65" s="11" t="s">
         <v>135</v>
       </c>
       <c r="M65" s="10">
@@ -15964,13 +16250,13 @@
       <c r="AM65" s="10">
         <v>2.65</v>
       </c>
-      <c r="AN65" s="13" t="s">
+      <c r="AN65" t="s">
         <v>174</v>
       </c>
       <c r="AO65" s="10">
         <v>2.4980000000000002</v>
       </c>
-      <c r="AP65" s="13" t="s">
+      <c r="AP65" t="s">
         <v>205</v>
       </c>
       <c r="AQ65" s="10">
@@ -15982,71 +16268,71 @@
       <c r="AS65" s="10">
         <v>1107</v>
       </c>
-      <c r="AT65" s="13" t="s">
+      <c r="AT65" t="s">
         <v>177</v>
       </c>
       <c r="AU65" s="10">
         <v>168.49</v>
       </c>
-      <c r="AV65" s="13" t="s">
+      <c r="AV65" t="s">
         <v>20</v>
       </c>
       <c r="AW65" s="10">
         <v>151.6</v>
       </c>
-      <c r="AX65" s="13" t="s">
+      <c r="AX65" t="s">
         <v>174</v>
       </c>
       <c r="AY65" s="10">
         <v>147.4</v>
       </c>
-      <c r="AZ65" s="13" t="s">
+      <c r="AZ65" t="s">
         <v>174</v>
       </c>
       <c r="BA65" s="10">
         <v>2.702</v>
       </c>
-      <c r="BB65" s="13" t="s">
+      <c r="BB65" t="s">
         <v>205</v>
       </c>
       <c r="BC65" s="10">
         <v>375</v>
       </c>
-      <c r="BD65" s="13" t="s">
+      <c r="BD65" t="s">
         <v>135</v>
       </c>
       <c r="BE65" s="10">
         <v>215</v>
       </c>
-      <c r="BF65" s="13" t="s">
+      <c r="BF65" t="s">
         <v>135</v>
       </c>
       <c r="BG65" s="10">
         <v>17</v>
       </c>
-      <c r="BH65" s="13" t="s">
+      <c r="BH65" t="s">
         <v>175</v>
       </c>
       <c r="BI65" s="10">
         <v>168.58</v>
       </c>
-      <c r="BJ65" s="13" t="s">
+      <c r="BJ65" t="s">
         <v>20</v>
       </c>
-      <c r="BK65" s="14"/>
-      <c r="BL65" s="13" t="s">
+      <c r="BK65" s="12"/>
+      <c r="BL65" t="s">
         <v>172</v>
       </c>
-      <c r="BM65" s="14"/>
-      <c r="BN65" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BO65" s="14"/>
-      <c r="BP65" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BQ65" s="14"/>
-      <c r="BR65" s="13" t="s">
+      <c r="BM65" s="12"/>
+      <c r="BN65" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO65" s="12"/>
+      <c r="BP65" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ65" s="12"/>
+      <c r="BR65" t="s">
         <v>173</v>
       </c>
     </row>
@@ -16054,7 +16340,7 @@
       <c r="B66" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="C66" s="14"/>
+      <c r="C66" s="12"/>
       <c r="D66" s="10">
         <v>110</v>
       </c>
@@ -16079,7 +16365,7 @@
       <c r="K66" s="10">
         <v>17</v>
       </c>
-      <c r="L66" s="12" t="s">
+      <c r="L66" s="11" t="s">
         <v>135</v>
       </c>
       <c r="M66" s="10">
@@ -16163,13 +16449,13 @@
       <c r="AM66" s="10">
         <v>2.85</v>
       </c>
-      <c r="AN66" s="13" t="s">
+      <c r="AN66" t="s">
         <v>174</v>
       </c>
       <c r="AO66" s="10">
         <v>2.702</v>
       </c>
-      <c r="AP66" s="13" t="s">
+      <c r="AP66" t="s">
         <v>205</v>
       </c>
       <c r="AQ66" s="10">
@@ -16181,76 +16467,76 @@
       <c r="AS66" s="10">
         <v>1236</v>
       </c>
-      <c r="AT66" s="13" t="s">
+      <c r="AT66" t="s">
         <v>177</v>
       </c>
       <c r="AU66" s="10">
         <v>171.03</v>
       </c>
-      <c r="AV66" s="13" t="s">
+      <c r="AV66" t="s">
         <v>20</v>
       </c>
       <c r="AW66" s="10">
         <v>153.80000000000001</v>
       </c>
-      <c r="AX66" s="13" t="s">
+      <c r="AX66" t="s">
         <v>174</v>
       </c>
       <c r="AY66" s="10">
         <v>155.80000000000001</v>
       </c>
-      <c r="AZ66" s="13" t="s">
+      <c r="AZ66" t="s">
         <v>174</v>
       </c>
       <c r="BA66" s="10">
         <v>2.9060000000000001</v>
       </c>
-      <c r="BB66" s="13" t="s">
+      <c r="BB66" t="s">
         <v>205</v>
       </c>
       <c r="BC66" s="10">
         <v>390</v>
       </c>
-      <c r="BD66" s="13" t="s">
+      <c r="BD66" t="s">
         <v>135</v>
       </c>
       <c r="BE66" s="10">
         <v>220</v>
       </c>
-      <c r="BF66" s="13" t="s">
+      <c r="BF66" t="s">
         <v>135</v>
       </c>
       <c r="BG66" s="10">
         <v>17.600000000000001</v>
       </c>
-      <c r="BH66" s="13" t="s">
+      <c r="BH66" t="s">
         <v>175</v>
       </c>
       <c r="BI66" s="10">
         <v>170.8</v>
       </c>
-      <c r="BJ66" s="13" t="s">
+      <c r="BJ66" t="s">
         <v>20</v>
       </c>
-      <c r="BK66" s="14"/>
-      <c r="BL66" s="13" t="s">
+      <c r="BK66" s="12"/>
+      <c r="BL66" t="s">
         <v>172</v>
       </c>
-      <c r="BM66" s="14"/>
-      <c r="BN66" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BO66" s="14"/>
-      <c r="BP66" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BQ66" s="14"/>
-      <c r="BR66" s="13" t="s">
+      <c r="BM66" s="12"/>
+      <c r="BN66" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO66" s="12"/>
+      <c r="BP66" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ66" s="12"/>
+      <c r="BR66" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="67" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="B67" s="15">
+      <c r="B67" s="13">
         <v>774</v>
       </c>
       <c r="C67" s="5"/>
@@ -16366,10 +16652,10 @@
         <v>174</v>
       </c>
       <c r="AO67" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AP67" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AQ67" s="5">
         <v>18</v>
@@ -16402,10 +16688,10 @@
         <v>174</v>
       </c>
       <c r="BA67" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BB67" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="BC67" s="5">
         <v>321.5</v>
@@ -16420,7 +16706,7 @@
         <v>135</v>
       </c>
       <c r="BG67" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BH67" s="5" t="s">
         <v>175</v>
@@ -16444,13 +16730,13 @@
         <v>135</v>
       </c>
       <c r="BO67" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BP67" s="5" t="s">
         <v>135</v>
       </c>
       <c r="BQ67" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BR67" s="5" t="s">
         <v>173</v>
@@ -16462,1993 +16748,3179 @@
       <c r="B68" s="2">
         <v>774</v>
       </c>
-      <c r="C68" s="13"/>
-      <c r="D68" s="13">
+      <c r="D68">
         <v>50</v>
       </c>
-      <c r="E68" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="F68" s="13">
+      <c r="E68" t="s">
+        <v>171</v>
+      </c>
+      <c r="F68">
         <v>2</v>
       </c>
-      <c r="G68" s="13">
+      <c r="G68">
         <v>4880</v>
       </c>
-      <c r="H68" s="13" t="s">
+      <c r="H68" t="s">
         <v>21</v>
       </c>
-      <c r="I68" s="13">
+      <c r="I68">
         <v>74</v>
       </c>
-      <c r="J68" s="13" t="s">
+      <c r="J68" t="s">
         <v>22</v>
       </c>
-      <c r="K68" s="13">
+      <c r="K68">
         <v>14</v>
       </c>
-      <c r="L68" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="M68" s="13">
+      <c r="L68" t="s">
+        <v>135</v>
+      </c>
+      <c r="M68">
         <v>65</v>
       </c>
-      <c r="N68" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="O68" s="13">
+      <c r="N68" t="s">
+        <v>171</v>
+      </c>
+      <c r="O68">
         <v>1027</v>
       </c>
-      <c r="P68" s="13" t="s">
+      <c r="P68" t="s">
         <v>172</v>
       </c>
-      <c r="Q68" s="13">
+      <c r="Q68">
         <v>15</v>
       </c>
-      <c r="R68" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="S68" s="13">
+      <c r="R68" t="s">
+        <v>135</v>
+      </c>
+      <c r="S68">
         <v>19</v>
       </c>
-      <c r="T68" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="U68" s="13">
+      <c r="T68" t="s">
+        <v>135</v>
+      </c>
+      <c r="U68">
         <v>75</v>
       </c>
-      <c r="V68" s="13" t="s">
+      <c r="V68" t="s">
         <v>173</v>
       </c>
-      <c r="W68" s="13">
+      <c r="W68">
         <v>117.8</v>
       </c>
-      <c r="X68" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y68" s="13">
+      <c r="X68" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y68">
         <v>77.400000000000006</v>
       </c>
-      <c r="Z68" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA68" s="13">
+      <c r="Z68" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA68">
         <v>12.4</v>
       </c>
-      <c r="AB68" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="AC68" s="13">
+      <c r="AB68" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC68">
         <v>44.4</v>
       </c>
-      <c r="AD68" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="AE68" s="13">
+      <c r="AD68" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE68">
         <v>270</v>
       </c>
-      <c r="AF68" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG68" s="13">
+      <c r="AF68" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG68">
         <v>320</v>
       </c>
-      <c r="AH68" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="AI68" s="13">
+      <c r="AH68" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI68">
         <v>220</v>
       </c>
-      <c r="AJ68" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="AK68" s="13">
+      <c r="AJ68" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK68">
         <v>11.35</v>
       </c>
-      <c r="AL68" s="13" t="s">
+      <c r="AL68" t="s">
         <v>175</v>
       </c>
-      <c r="AM68" s="13">
+      <c r="AM68">
         <v>1.18</v>
       </c>
-      <c r="AN68" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="AO68" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="AP68" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="AQ68" s="13">
+      <c r="AN68" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO68" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP68" t="s">
+        <v>223</v>
+      </c>
+      <c r="AQ68">
         <v>20</v>
       </c>
-      <c r="AR68" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="AS68" s="13">
+      <c r="AR68" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS68">
         <v>861.24</v>
       </c>
-      <c r="AT68" s="13" t="s">
+      <c r="AT68" t="s">
         <v>177</v>
       </c>
-      <c r="AU68" s="13">
+      <c r="AU68">
         <v>176.48</v>
       </c>
-      <c r="AV68" s="13" t="s">
+      <c r="AV68" t="s">
         <v>20</v>
       </c>
-      <c r="AW68" s="13">
+      <c r="AW68">
         <v>116.5</v>
       </c>
-      <c r="AX68" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="AY68" s="13">
+      <c r="AX68" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY68">
         <v>75.8</v>
       </c>
-      <c r="AZ68" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="BA68" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="BB68" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="BC68" s="13">
+      <c r="AZ68" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA68" t="s">
+        <v>230</v>
+      </c>
+      <c r="BB68" t="s">
+        <v>223</v>
+      </c>
+      <c r="BC68">
         <v>347.7</v>
       </c>
-      <c r="BD68" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BE68" s="13">
+      <c r="BD68" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE68">
         <v>241.7</v>
       </c>
-      <c r="BF68" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BG68" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="BH68" s="13" t="s">
+      <c r="BF68" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG68" t="s">
+        <v>230</v>
+      </c>
+      <c r="BH68" t="s">
         <v>175</v>
       </c>
-      <c r="BI68" s="13">
+      <c r="BI68">
         <v>178.08</v>
       </c>
-      <c r="BJ68" s="13" t="s">
+      <c r="BJ68" t="s">
         <v>20</v>
       </c>
-      <c r="BK68" s="13">
+      <c r="BK68">
         <v>1000</v>
       </c>
-      <c r="BL68" s="13" t="s">
+      <c r="BL68" t="s">
         <v>172</v>
       </c>
-      <c r="BM68" s="13">
+      <c r="BM68">
         <v>25</v>
       </c>
-      <c r="BN68" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BO68" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="BP68" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BQ68" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="BR68" s="13" t="s">
+      <c r="BN68" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO68" t="s">
+        <v>230</v>
+      </c>
+      <c r="BP68" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ68" t="s">
+        <v>230</v>
+      </c>
+      <c r="BR68" t="s">
         <v>173</v>
       </c>
-      <c r="BS68" s="13"/>
-      <c r="BT68" s="13"/>
     </row>
     <row r="69" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B69" s="2">
         <v>774</v>
       </c>
-      <c r="C69" s="13"/>
-      <c r="D69" s="13">
+      <c r="D69">
         <v>75</v>
       </c>
-      <c r="E69" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="F69" s="13">
+      <c r="E69" t="s">
+        <v>171</v>
+      </c>
+      <c r="F69">
         <v>3</v>
       </c>
-      <c r="G69" s="13">
+      <c r="G69">
         <v>7320</v>
       </c>
-      <c r="H69" s="13" t="s">
+      <c r="H69" t="s">
         <v>21</v>
       </c>
-      <c r="I69" s="13">
+      <c r="I69">
         <v>84</v>
       </c>
-      <c r="J69" s="13" t="s">
+      <c r="J69" t="s">
         <v>22</v>
       </c>
-      <c r="K69" s="13">
+      <c r="K69">
         <v>12</v>
       </c>
-      <c r="L69" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="M69" s="13">
+      <c r="L69" t="s">
+        <v>135</v>
+      </c>
+      <c r="M69">
         <v>62</v>
       </c>
-      <c r="N69" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="O69" s="13">
+      <c r="N69" t="s">
+        <v>171</v>
+      </c>
+      <c r="O69">
         <v>1027</v>
       </c>
-      <c r="P69" s="13" t="s">
+      <c r="P69" t="s">
         <v>172</v>
       </c>
-      <c r="Q69" s="13">
+      <c r="Q69">
         <v>15.7</v>
       </c>
-      <c r="R69" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="S69" s="13">
+      <c r="R69" t="s">
+        <v>135</v>
+      </c>
+      <c r="S69">
         <v>22</v>
       </c>
-      <c r="T69" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="U69" s="13">
+      <c r="T69" t="s">
+        <v>135</v>
+      </c>
+      <c r="U69">
         <v>140</v>
       </c>
-      <c r="V69" s="13" t="s">
+      <c r="V69" t="s">
         <v>173</v>
       </c>
-      <c r="W69" s="13">
+      <c r="W69">
         <v>140.6</v>
       </c>
-      <c r="X69" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y69" s="13">
+      <c r="X69" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y69">
         <v>102.6</v>
       </c>
-      <c r="Z69" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA69" s="13">
+      <c r="Z69" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA69">
         <v>16.39</v>
       </c>
-      <c r="AB69" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="AC69" s="13">
+      <c r="AB69" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC69">
         <v>57.4</v>
       </c>
-      <c r="AD69" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="AE69" s="13">
+      <c r="AD69" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE69">
         <v>295</v>
       </c>
-      <c r="AF69" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG69" s="13">
+      <c r="AF69" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG69">
         <v>355</v>
       </c>
-      <c r="AH69" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="AI69" s="13">
+      <c r="AH69" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI69">
         <v>200</v>
       </c>
-      <c r="AJ69" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="AK69" s="13">
+      <c r="AJ69" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK69">
         <v>14.372</v>
       </c>
-      <c r="AL69" s="13" t="s">
+      <c r="AL69" t="s">
         <v>175</v>
       </c>
-      <c r="AM69" s="13">
+      <c r="AM69">
         <v>2.23</v>
       </c>
-      <c r="AN69" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="AO69" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="AP69" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="AQ69" s="13">
+      <c r="AN69" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO69" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP69" t="s">
+        <v>223</v>
+      </c>
+      <c r="AQ69">
         <v>21</v>
       </c>
-      <c r="AR69" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="AS69" s="13">
+      <c r="AR69" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS69">
         <v>1228.67</v>
       </c>
-      <c r="AT69" s="13" t="s">
+      <c r="AT69" t="s">
         <v>177</v>
       </c>
-      <c r="AU69" s="13">
+      <c r="AU69">
         <v>172.76</v>
       </c>
-      <c r="AV69" s="13" t="s">
+      <c r="AV69" t="s">
         <v>20</v>
       </c>
-      <c r="AW69" s="13">
+      <c r="AW69">
         <v>139.5</v>
       </c>
-      <c r="AX69" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="AY69" s="13">
+      <c r="AX69" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY69">
         <v>101.2</v>
       </c>
-      <c r="AZ69" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="BA69" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="BB69" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="BC69" s="13">
+      <c r="AZ69" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA69" t="s">
+        <v>230</v>
+      </c>
+      <c r="BB69" t="s">
+        <v>223</v>
+      </c>
+      <c r="BC69">
         <v>381.8</v>
       </c>
-      <c r="BD69" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BE69" s="13">
+      <c r="BD69" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE69">
         <v>220.7</v>
       </c>
-      <c r="BF69" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BG69" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="BH69" s="13" t="s">
+      <c r="BF69" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG69" t="s">
+        <v>230</v>
+      </c>
+      <c r="BH69" t="s">
         <v>175</v>
       </c>
-      <c r="BI69" s="13">
+      <c r="BI69">
         <v>169.05</v>
       </c>
-      <c r="BJ69" s="13" t="s">
+      <c r="BJ69" t="s">
         <v>20</v>
       </c>
-      <c r="BK69" s="13">
+      <c r="BK69">
         <v>1000</v>
       </c>
-      <c r="BL69" s="13" t="s">
+      <c r="BL69" t="s">
         <v>172</v>
       </c>
-      <c r="BM69" s="13">
+      <c r="BM69">
         <v>25</v>
       </c>
-      <c r="BN69" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BO69" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="BP69" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BQ69" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="BR69" s="13" t="s">
+      <c r="BN69" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO69" t="s">
+        <v>230</v>
+      </c>
+      <c r="BP69" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ69" t="s">
+        <v>230</v>
+      </c>
+      <c r="BR69" t="s">
         <v>173</v>
       </c>
-      <c r="BS69" s="13"/>
-      <c r="BT69" s="13"/>
     </row>
     <row r="70" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B70" s="2">
         <v>774</v>
       </c>
-      <c r="C70" s="13"/>
-      <c r="D70" s="13">
+      <c r="D70">
         <v>85</v>
       </c>
-      <c r="E70" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="F70" s="13">
+      <c r="E70" t="s">
+        <v>171</v>
+      </c>
+      <c r="F70">
         <v>4</v>
       </c>
-      <c r="G70" s="13">
+      <c r="G70">
         <v>8296</v>
       </c>
-      <c r="H70" s="13" t="s">
+      <c r="H70" t="s">
         <v>21</v>
       </c>
-      <c r="I70" s="13">
+      <c r="I70">
         <v>88</v>
       </c>
-      <c r="J70" s="13" t="s">
+      <c r="J70" t="s">
         <v>22</v>
       </c>
-      <c r="K70" s="13">
+      <c r="K70">
         <v>12</v>
       </c>
-      <c r="L70" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="M70" s="13">
+      <c r="L70" t="s">
+        <v>135</v>
+      </c>
+      <c r="M70">
         <v>62</v>
       </c>
-      <c r="N70" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="O70" s="13">
+      <c r="N70" t="s">
+        <v>171</v>
+      </c>
+      <c r="O70">
         <v>1027</v>
       </c>
-      <c r="P70" s="13" t="s">
+      <c r="P70" t="s">
         <v>172</v>
       </c>
-      <c r="Q70" s="13">
+      <c r="Q70">
         <v>16.600000000000001</v>
       </c>
-      <c r="R70" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="S70" s="13">
+      <c r="R70" t="s">
+        <v>135</v>
+      </c>
+      <c r="S70">
         <v>27</v>
       </c>
-      <c r="T70" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="U70" s="13">
+      <c r="T70" t="s">
+        <v>135</v>
+      </c>
+      <c r="U70">
         <v>190</v>
       </c>
-      <c r="V70" s="13" t="s">
+      <c r="V70" t="s">
         <v>173</v>
       </c>
-      <c r="W70" s="13">
+      <c r="W70">
         <v>152.19999999999999</v>
       </c>
-      <c r="X70" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y70" s="13">
+      <c r="X70" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y70">
         <v>114.6</v>
       </c>
-      <c r="Z70" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA70" s="13">
+      <c r="Z70" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA70">
         <v>17.73</v>
       </c>
-      <c r="AB70" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="AC70" s="13">
+      <c r="AB70" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC70">
         <v>61</v>
       </c>
-      <c r="AD70" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="AE70" s="13">
+      <c r="AD70" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE70">
         <v>310</v>
       </c>
-      <c r="AF70" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG70" s="13">
+      <c r="AF70" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG70">
         <v>375</v>
       </c>
-      <c r="AH70" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="AI70" s="13">
+      <c r="AH70" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI70">
         <v>205</v>
       </c>
-      <c r="AJ70" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="AK70" s="13">
+      <c r="AJ70" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK70">
         <v>15.108000000000001</v>
       </c>
-      <c r="AL70" s="13" t="s">
+      <c r="AL70" t="s">
         <v>175</v>
       </c>
-      <c r="AM70" s="13">
+      <c r="AM70">
         <v>2.56</v>
       </c>
-      <c r="AN70" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="AO70" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="AP70" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="AQ70" s="13">
+      <c r="AN70" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO70" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP70" t="s">
+        <v>223</v>
+      </c>
+      <c r="AQ70">
         <v>22</v>
       </c>
-      <c r="AR70" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="AS70" s="13">
+      <c r="AR70" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS70">
         <v>1422.92</v>
       </c>
-      <c r="AT70" s="13" t="s">
+      <c r="AT70" t="s">
         <v>177</v>
       </c>
-      <c r="AU70" s="13">
+      <c r="AU70">
         <v>171.52</v>
       </c>
-      <c r="AV70" s="13" t="s">
+      <c r="AV70" t="s">
         <v>20</v>
       </c>
-      <c r="AW70" s="13">
+      <c r="AW70">
         <v>152.19999999999999</v>
       </c>
-      <c r="AX70" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="AY70" s="13">
+      <c r="AX70" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY70">
         <v>111</v>
       </c>
-      <c r="AZ70" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="BA70" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="BB70" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="BC70" s="13">
+      <c r="AZ70" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA70" t="s">
+        <v>230</v>
+      </c>
+      <c r="BB70" t="s">
+        <v>223</v>
+      </c>
+      <c r="BC70">
         <v>397.1</v>
       </c>
-      <c r="BD70" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BE70" s="13">
+      <c r="BD70" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE70">
         <v>220.9</v>
       </c>
-      <c r="BF70" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BG70" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="BH70" s="13" t="s">
+      <c r="BF70" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG70" t="s">
+        <v>230</v>
+      </c>
+      <c r="BH70" t="s">
         <v>175</v>
       </c>
-      <c r="BI70" s="13">
+      <c r="BI70">
         <v>172.2</v>
       </c>
-      <c r="BJ70" s="13" t="s">
+      <c r="BJ70" t="s">
         <v>20</v>
       </c>
-      <c r="BK70" s="13">
+      <c r="BK70">
         <v>1000</v>
       </c>
-      <c r="BL70" s="13" t="s">
+      <c r="BL70" t="s">
         <v>172</v>
       </c>
-      <c r="BM70" s="13">
+      <c r="BM70">
         <v>25</v>
       </c>
-      <c r="BN70" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BO70" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="BP70" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BQ70" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="BR70" s="13" t="s">
+      <c r="BN70" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO70" t="s">
+        <v>230</v>
+      </c>
+      <c r="BP70" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ70" t="s">
+        <v>230</v>
+      </c>
+      <c r="BR70" t="s">
         <v>173</v>
       </c>
-      <c r="BS70" s="13"/>
-      <c r="BT70" s="13"/>
     </row>
     <row r="71" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B71" s="2">
         <v>774</v>
       </c>
-      <c r="C71" s="13"/>
-      <c r="D71" s="13">
+      <c r="D71">
         <v>100</v>
       </c>
-      <c r="E71" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="F71" s="13">
+      <c r="E71" t="s">
+        <v>171</v>
+      </c>
+      <c r="F71">
         <v>5</v>
       </c>
-      <c r="G71" s="13">
+      <c r="G71">
         <v>9760</v>
       </c>
-      <c r="H71" s="13" t="s">
+      <c r="H71" t="s">
         <v>21</v>
       </c>
-      <c r="I71" s="13">
+      <c r="I71">
         <v>93</v>
       </c>
-      <c r="J71" s="13" t="s">
+      <c r="J71" t="s">
         <v>22</v>
       </c>
-      <c r="K71" s="13">
+      <c r="K71">
         <v>12</v>
       </c>
-      <c r="L71" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="M71" s="13">
+      <c r="L71" t="s">
+        <v>135</v>
+      </c>
+      <c r="M71">
         <v>62</v>
       </c>
-      <c r="N71" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="O71" s="13">
+      <c r="N71" t="s">
+        <v>171</v>
+      </c>
+      <c r="O71">
         <v>1028</v>
       </c>
-      <c r="P71" s="13" t="s">
+      <c r="P71" t="s">
         <v>172</v>
       </c>
-      <c r="Q71" s="13">
+      <c r="Q71">
         <v>17</v>
       </c>
-      <c r="R71" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="S71" s="13">
+      <c r="R71" t="s">
+        <v>135</v>
+      </c>
+      <c r="S71">
         <v>30</v>
       </c>
-      <c r="T71" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="U71" s="13">
+      <c r="T71" t="s">
+        <v>135</v>
+      </c>
+      <c r="U71">
         <v>250</v>
       </c>
-      <c r="V71" s="13" t="s">
+      <c r="V71" t="s">
         <v>173</v>
       </c>
-      <c r="W71" s="13">
+      <c r="W71">
         <v>147.6</v>
       </c>
-      <c r="X71" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y71" s="13">
+      <c r="X71" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y71">
         <v>129.6</v>
       </c>
-      <c r="Z71" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA71" s="13">
+      <c r="Z71" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA71">
         <v>19.739999999999998</v>
       </c>
-      <c r="AB71" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="AC71" s="13">
+      <c r="AB71" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC71">
         <v>70.5</v>
       </c>
-      <c r="AD71" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="AE71" s="13">
+      <c r="AD71" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE71">
         <v>362</v>
       </c>
-      <c r="AF71" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG71" s="13">
+      <c r="AF71" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG71">
         <v>425</v>
       </c>
-      <c r="AH71" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="AI71" s="13">
-        <v>230</v>
-      </c>
-      <c r="AJ71" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="AK71" s="13">
+      <c r="AH71" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI71">
+        <v>230</v>
+      </c>
+      <c r="AJ71" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK71">
         <v>16.654</v>
       </c>
-      <c r="AL71" s="13" t="s">
+      <c r="AL71" t="s">
         <v>175</v>
       </c>
-      <c r="AM71" s="13">
+      <c r="AM71">
         <v>3.28</v>
       </c>
-      <c r="AN71" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="AO71" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="AP71" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="AQ71" s="13">
+      <c r="AN71" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO71" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP71" t="s">
+        <v>223</v>
+      </c>
+      <c r="AQ71">
         <v>24</v>
       </c>
-      <c r="AR71" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="AS71" s="13">
+      <c r="AR71" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS71">
         <v>1690.14</v>
       </c>
-      <c r="AT71" s="13" t="s">
+      <c r="AT71" t="s">
         <v>177</v>
       </c>
-      <c r="AU71" s="13">
+      <c r="AU71">
         <v>173.17</v>
       </c>
-      <c r="AV71" s="13" t="s">
+      <c r="AV71" t="s">
         <v>20</v>
       </c>
-      <c r="AW71" s="13">
+      <c r="AW71">
         <v>147.6</v>
       </c>
-      <c r="AX71" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="AY71" s="13">
+      <c r="AX71" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY71">
         <v>126.2</v>
       </c>
-      <c r="AZ71" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="BA71" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="BB71" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="BC71" s="13">
+      <c r="AZ71" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA71" t="s">
+        <v>230</v>
+      </c>
+      <c r="BB71" t="s">
+        <v>223</v>
+      </c>
+      <c r="BC71">
         <v>446.8</v>
       </c>
-      <c r="BD71" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BE71" s="13">
+      <c r="BD71" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE71">
         <v>245.6</v>
       </c>
-      <c r="BF71" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BG71" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="BH71" s="13" t="s">
+      <c r="BF71" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG71" t="s">
+        <v>230</v>
+      </c>
+      <c r="BH71" t="s">
         <v>175</v>
       </c>
-      <c r="BI71" s="13">
+      <c r="BI71">
         <v>173.54</v>
       </c>
-      <c r="BJ71" s="13" t="s">
+      <c r="BJ71" t="s">
         <v>20</v>
       </c>
-      <c r="BK71" s="13">
+      <c r="BK71">
         <v>1000</v>
       </c>
-      <c r="BL71" s="13" t="s">
+      <c r="BL71" t="s">
         <v>172</v>
       </c>
-      <c r="BM71" s="13">
+      <c r="BM71">
         <v>25</v>
       </c>
-      <c r="BN71" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BO71" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="BP71" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BQ71" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="BR71" s="13" t="s">
+      <c r="BN71" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO71" t="s">
+        <v>230</v>
+      </c>
+      <c r="BP71" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ71" t="s">
+        <v>230</v>
+      </c>
+      <c r="BR71" t="s">
         <v>173</v>
       </c>
-      <c r="BS71" s="13"/>
-      <c r="BT71" s="13"/>
     </row>
     <row r="72" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B72" s="2">
         <v>774</v>
       </c>
-      <c r="C72" s="13"/>
-      <c r="D72" s="13">
+      <c r="D72">
         <v>110</v>
       </c>
-      <c r="E72" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="F72" s="13">
+      <c r="E72" t="s">
+        <v>171</v>
+      </c>
+      <c r="F72">
         <v>6</v>
       </c>
-      <c r="G72" s="13">
+      <c r="G72">
         <v>10736</v>
       </c>
-      <c r="H72" s="13" t="s">
+      <c r="H72" t="s">
         <v>21</v>
       </c>
-      <c r="I72" s="13">
+      <c r="I72">
         <v>96</v>
       </c>
-      <c r="J72" s="13" t="s">
+      <c r="J72" t="s">
         <v>22</v>
       </c>
-      <c r="K72" s="13">
+      <c r="K72">
         <v>13</v>
       </c>
-      <c r="L72" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="M72" s="13">
+      <c r="L72" t="s">
+        <v>135</v>
+      </c>
+      <c r="M72">
         <v>62</v>
       </c>
-      <c r="N72" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="O72" s="13">
+      <c r="N72" t="s">
+        <v>171</v>
+      </c>
+      <c r="O72">
         <v>1027</v>
       </c>
-      <c r="P72" s="13" t="s">
+      <c r="P72" t="s">
         <v>172</v>
       </c>
-      <c r="Q72" s="13">
+      <c r="Q72">
         <v>18</v>
       </c>
-      <c r="R72" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="S72" s="13">
+      <c r="R72" t="s">
+        <v>135</v>
+      </c>
+      <c r="S72">
         <v>28</v>
       </c>
-      <c r="T72" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="U72" s="13">
+      <c r="T72" t="s">
+        <v>135</v>
+      </c>
+      <c r="U72">
         <v>285</v>
       </c>
-      <c r="V72" s="13" t="s">
+      <c r="V72" t="s">
         <v>173</v>
       </c>
-      <c r="W72" s="13">
+      <c r="W72">
         <v>153.6</v>
       </c>
-      <c r="X72" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y72" s="13">
+      <c r="X72" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y72">
         <v>142.80000000000001</v>
       </c>
-      <c r="Z72" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA72" s="13">
+      <c r="Z72" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA72">
         <v>21.03</v>
       </c>
-      <c r="AB72" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="AC72" s="13">
+      <c r="AB72" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC72">
         <v>75.3</v>
       </c>
-      <c r="AD72" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="AE72" s="13">
+      <c r="AD72" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE72">
         <v>389</v>
       </c>
-      <c r="AF72" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG72" s="13">
+      <c r="AF72" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG72">
         <v>450</v>
       </c>
-      <c r="AH72" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="AI72" s="13">
+      <c r="AH72" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI72">
         <v>245</v>
       </c>
-      <c r="AJ72" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="AK72" s="13">
+      <c r="AJ72" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK72">
         <v>17.189</v>
       </c>
-      <c r="AL72" s="13" t="s">
+      <c r="AL72" t="s">
         <v>175</v>
       </c>
-      <c r="AM72" s="13">
+      <c r="AM72">
         <v>3.45</v>
       </c>
-      <c r="AN72" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="AO72" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="AP72" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="AQ72" s="13">
+      <c r="AN72" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO72" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP72" t="s">
+        <v>223</v>
+      </c>
+      <c r="AQ72">
         <v>24</v>
       </c>
-      <c r="AR72" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="AS72" s="13">
+      <c r="AR72" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS72">
         <v>1935.48</v>
       </c>
-      <c r="AT72" s="13" t="s">
+      <c r="AT72" t="s">
         <v>177</v>
       </c>
-      <c r="AU72" s="13">
+      <c r="AU72">
         <v>180.28</v>
       </c>
-      <c r="AV72" s="13" t="s">
+      <c r="AV72" t="s">
         <v>20</v>
       </c>
-      <c r="AW72" s="13">
+      <c r="AW72">
         <v>153.6</v>
       </c>
-      <c r="AX72" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="AY72" s="13">
+      <c r="AX72" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY72">
         <v>140.80000000000001</v>
       </c>
-      <c r="AZ72" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="BA72" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="BB72" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="BC72" s="13">
+      <c r="AZ72" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA72" t="s">
+        <v>230</v>
+      </c>
+      <c r="BB72" t="s">
+        <v>223</v>
+      </c>
+      <c r="BC72">
         <v>473.9</v>
       </c>
-      <c r="BD72" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BE72" s="13">
+      <c r="BD72" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE72">
         <v>261</v>
       </c>
-      <c r="BF72" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BG72" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="BH72" s="13" t="s">
+      <c r="BF72" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG72" t="s">
+        <v>230</v>
+      </c>
+      <c r="BH72" t="s">
         <v>175</v>
       </c>
-      <c r="BI72" s="13">
+      <c r="BI72">
         <v>180.84</v>
       </c>
-      <c r="BJ72" s="13" t="s">
+      <c r="BJ72" t="s">
         <v>20</v>
       </c>
-      <c r="BK72" s="13">
+      <c r="BK72">
         <v>1000</v>
       </c>
-      <c r="BL72" s="13" t="s">
+      <c r="BL72" t="s">
         <v>172</v>
       </c>
-      <c r="BM72" s="13">
+      <c r="BM72">
         <v>25</v>
       </c>
-      <c r="BN72" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BO72" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="BP72" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BQ72" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="BR72" s="13" t="s">
+      <c r="BN72" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO72" t="s">
+        <v>230</v>
+      </c>
+      <c r="BP72" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ72" t="s">
+        <v>230</v>
+      </c>
+      <c r="BR72" t="s">
         <v>173</v>
       </c>
-      <c r="BS72" s="13"/>
-      <c r="BT72" s="13"/>
     </row>
     <row r="73" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B73" s="2">
         <v>774</v>
       </c>
-      <c r="C73" s="13"/>
-      <c r="D73" s="13">
+      <c r="D73">
         <v>100</v>
       </c>
-      <c r="E73" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="F73" s="13">
+      <c r="E73" t="s">
+        <v>171</v>
+      </c>
+      <c r="F73">
         <v>7</v>
       </c>
-      <c r="G73" s="13">
+      <c r="G73">
         <v>9760</v>
       </c>
-      <c r="H73" s="13" t="s">
+      <c r="H73" t="s">
         <v>21</v>
       </c>
-      <c r="I73" s="13">
+      <c r="I73">
         <v>93</v>
       </c>
-      <c r="J73" s="13" t="s">
+      <c r="J73" t="s">
         <v>22</v>
       </c>
-      <c r="K73" s="13">
+      <c r="K73">
         <v>12</v>
       </c>
-      <c r="L73" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="M73" s="13">
+      <c r="L73" t="s">
+        <v>135</v>
+      </c>
+      <c r="M73">
         <v>62</v>
       </c>
-      <c r="N73" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="O73" s="13">
+      <c r="N73" t="s">
+        <v>171</v>
+      </c>
+      <c r="O73">
         <v>1028</v>
       </c>
-      <c r="P73" s="13" t="s">
+      <c r="P73" t="s">
         <v>172</v>
       </c>
-      <c r="Q73" s="13">
+      <c r="Q73">
         <v>17.399999999999999</v>
       </c>
-      <c r="R73" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="S73" s="13">
+      <c r="R73" t="s">
+        <v>135</v>
+      </c>
+      <c r="S73">
         <v>30</v>
       </c>
-      <c r="T73" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="U73" s="13">
+      <c r="T73" t="s">
+        <v>135</v>
+      </c>
+      <c r="U73">
         <v>250</v>
       </c>
-      <c r="V73" s="13" t="s">
+      <c r="V73" t="s">
         <v>173</v>
       </c>
-      <c r="W73" s="13">
+      <c r="W73">
         <v>147.80000000000001</v>
       </c>
-      <c r="X73" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y73" s="13">
+      <c r="X73" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y73">
         <v>134</v>
       </c>
-      <c r="Z73" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA73" s="13">
+      <c r="Z73" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA73">
         <v>19.739999999999998</v>
       </c>
-      <c r="AB73" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="AC73" s="13">
+      <c r="AB73" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC73">
         <v>71</v>
       </c>
-      <c r="AD73" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="AE73" s="13">
+      <c r="AD73" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE73">
         <v>364</v>
       </c>
-      <c r="AF73" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG73" s="13">
+      <c r="AF73" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG73">
         <v>425</v>
       </c>
-      <c r="AH73" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="AI73" s="13">
-        <v>230</v>
-      </c>
-      <c r="AJ73" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="AK73" s="13">
+      <c r="AH73" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI73">
+        <v>230</v>
+      </c>
+      <c r="AJ73" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK73">
         <v>16.622</v>
       </c>
-      <c r="AL73" s="13" t="s">
+      <c r="AL73" t="s">
         <v>175</v>
       </c>
-      <c r="AM73" s="13">
+      <c r="AM73">
         <v>3.26</v>
       </c>
-      <c r="AN73" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="AO73" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="AP73" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="AQ73" s="13">
+      <c r="AN73" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO73" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP73" t="s">
+        <v>223</v>
+      </c>
+      <c r="AQ73">
         <v>23</v>
       </c>
-      <c r="AR73" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="AS73" s="13">
+      <c r="AR73" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS73">
         <v>1698.11</v>
       </c>
-      <c r="AT73" s="13" t="s">
+      <c r="AT73" t="s">
         <v>177</v>
       </c>
-      <c r="AU73" s="13">
+      <c r="AU73">
         <v>173.99</v>
       </c>
-      <c r="AV73" s="13" t="s">
+      <c r="AV73" t="s">
         <v>20</v>
       </c>
-      <c r="AW73" s="13">
+      <c r="AW73">
         <v>147.80000000000001</v>
       </c>
-      <c r="AX73" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="AY73" s="13">
+      <c r="AX73" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY73">
         <v>130.80000000000001</v>
       </c>
-      <c r="AZ73" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="BA73" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="BB73" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="BC73" s="13">
+      <c r="AZ73" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA73" t="s">
+        <v>230</v>
+      </c>
+      <c r="BB73" t="s">
+        <v>223</v>
+      </c>
+      <c r="BC73">
         <v>446.3</v>
       </c>
-      <c r="BD73" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BE73" s="13">
+      <c r="BD73" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE73">
         <v>245.1</v>
       </c>
-      <c r="BF73" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BG73" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="BH73" s="13" t="s">
+      <c r="BF73" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG73" t="s">
+        <v>230</v>
+      </c>
+      <c r="BH73" t="s">
         <v>175</v>
       </c>
-      <c r="BI73" s="13">
+      <c r="BI73">
         <v>174.34</v>
       </c>
-      <c r="BJ73" s="13" t="s">
+      <c r="BJ73" t="s">
         <v>20</v>
       </c>
-      <c r="BK73" s="13">
+      <c r="BK73">
         <v>1000</v>
       </c>
-      <c r="BL73" s="13" t="s">
+      <c r="BL73" t="s">
         <v>172</v>
       </c>
-      <c r="BM73" s="13">
+      <c r="BM73">
         <v>25</v>
       </c>
-      <c r="BN73" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BO73" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="BP73" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="BQ73" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="BR73" s="13" t="s">
+      <c r="BN73" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO73" t="s">
+        <v>230</v>
+      </c>
+      <c r="BP73" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ73" t="s">
+        <v>230</v>
+      </c>
+      <c r="BR73" t="s">
         <v>173</v>
       </c>
-      <c r="BS73" s="13"/>
-      <c r="BT73" s="13"/>
     </row>
     <row r="74" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A74" s="5"/>
-      <c r="B74" s="5"/>
+      <c r="B74" s="13">
+        <v>4078</v>
+      </c>
       <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
-      <c r="I74" s="5"/>
-      <c r="J74" s="5"/>
-      <c r="K74" s="5"/>
-      <c r="L74" s="5"/>
-      <c r="M74" s="5"/>
-      <c r="N74" s="5"/>
-      <c r="O74" s="5"/>
-      <c r="P74" s="5"/>
+      <c r="D74" s="5">
+        <v>50</v>
+      </c>
+      <c r="E74" t="s">
+        <v>171</v>
+      </c>
+      <c r="F74" s="5">
+        <v>1</v>
+      </c>
+      <c r="G74" s="5">
+        <v>6139</v>
+      </c>
+      <c r="H74" t="s">
+        <v>21</v>
+      </c>
+      <c r="I74" s="5">
+        <v>83.3</v>
+      </c>
+      <c r="J74" t="s">
+        <v>22</v>
+      </c>
+      <c r="K74" s="5">
+        <v>25.5</v>
+      </c>
+      <c r="L74" t="s">
+        <v>135</v>
+      </c>
+      <c r="M74" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="N74" t="s">
+        <v>171</v>
+      </c>
+      <c r="O74" s="5">
+        <v>1009.5</v>
+      </c>
+      <c r="P74" t="s">
+        <v>172</v>
+      </c>
       <c r="Q74" s="5"/>
-      <c r="R74" s="5"/>
-      <c r="S74" s="5"/>
-      <c r="T74" s="5"/>
-      <c r="U74" s="5"/>
-      <c r="V74" s="5"/>
-      <c r="W74" s="5"/>
-      <c r="X74" s="5"/>
-      <c r="Y74" s="5"/>
-      <c r="Z74" s="5"/>
-      <c r="AA74" s="5"/>
-      <c r="AB74" s="5"/>
-      <c r="AC74" s="5"/>
-      <c r="AD74" s="5"/>
-      <c r="AE74" s="5"/>
-      <c r="AF74" s="5"/>
-      <c r="AG74" s="5"/>
-      <c r="AH74" s="5"/>
-      <c r="AI74" s="5"/>
-      <c r="AJ74" s="5"/>
-      <c r="AK74" s="5"/>
-      <c r="AL74" s="5"/>
-      <c r="AM74" s="5"/>
-      <c r="AN74" s="5"/>
-      <c r="AO74" s="5"/>
-      <c r="AP74" s="5"/>
-      <c r="AQ74" s="5"/>
-      <c r="AR74" s="5"/>
-      <c r="AS74" s="5"/>
-      <c r="AT74" s="5"/>
-      <c r="AU74" s="5"/>
-      <c r="AV74" s="5"/>
+      <c r="R74" t="s">
+        <v>135</v>
+      </c>
+      <c r="S74" s="5">
+        <v>31</v>
+      </c>
+      <c r="T74" t="s">
+        <v>135</v>
+      </c>
+      <c r="U74" s="5">
+        <v>61</v>
+      </c>
+      <c r="V74" t="s">
+        <v>173</v>
+      </c>
+      <c r="W74" s="5">
+        <v>118.7</v>
+      </c>
+      <c r="X74" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y74" s="5">
+        <v>72.8</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA74" s="5">
+        <v>11.33</v>
+      </c>
+      <c r="AB74" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC74" s="5">
+        <v>53.25</v>
+      </c>
+      <c r="AD74" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE74" s="5">
+        <v>313</v>
+      </c>
+      <c r="AF74" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG74" s="5">
+        <v>356</v>
+      </c>
+      <c r="AH74" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI74" s="5">
+        <v>256</v>
+      </c>
+      <c r="AJ74" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK74" s="5">
+        <v>7.819</v>
+      </c>
+      <c r="AL74" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM74" s="5">
+        <v>1.05</v>
+      </c>
+      <c r="AN74" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO74" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP74" t="s">
+        <v>223</v>
+      </c>
+      <c r="AQ74" s="5">
+        <v>37</v>
+      </c>
+      <c r="AR74" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS74" s="5">
+        <v>1035.8800000000001</v>
+      </c>
+      <c r="AT74" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU74" s="5">
+        <v>167.2</v>
+      </c>
+      <c r="AV74" t="s">
+        <v>20</v>
+      </c>
       <c r="AW74" s="5"/>
-      <c r="AX74" s="5"/>
+      <c r="AX74" t="s">
+        <v>174</v>
+      </c>
       <c r="AY74" s="5"/>
-      <c r="AZ74" s="5"/>
+      <c r="AZ74" t="s">
+        <v>174</v>
+      </c>
       <c r="BA74" s="5"/>
-      <c r="BB74" s="5"/>
+      <c r="BB74" t="s">
+        <v>223</v>
+      </c>
       <c r="BC74" s="5"/>
-      <c r="BD74" s="5"/>
+      <c r="BD74" t="s">
+        <v>135</v>
+      </c>
       <c r="BE74" s="5"/>
-      <c r="BF74" s="5"/>
+      <c r="BF74" t="s">
+        <v>135</v>
+      </c>
       <c r="BG74" s="5"/>
-      <c r="BH74" s="5"/>
+      <c r="BH74" t="s">
+        <v>175</v>
+      </c>
       <c r="BI74" s="5"/>
-      <c r="BJ74" s="5"/>
+      <c r="BJ74" t="s">
+        <v>20</v>
+      </c>
       <c r="BK74" s="5"/>
-      <c r="BL74" s="5"/>
+      <c r="BL74" t="s">
+        <v>172</v>
+      </c>
       <c r="BM74" s="5"/>
-      <c r="BN74" s="5"/>
+      <c r="BN74" t="s">
+        <v>135</v>
+      </c>
       <c r="BO74" s="5"/>
-      <c r="BP74" s="5"/>
+      <c r="BP74" t="s">
+        <v>135</v>
+      </c>
       <c r="BQ74" s="5"/>
-      <c r="BR74" s="5"/>
+      <c r="BR74" t="s">
+        <v>173</v>
+      </c>
       <c r="BS74" s="5"/>
       <c r="BT74" s="5"/>
     </row>
+    <row r="75" spans="1:72" x14ac:dyDescent="0.3">
+      <c r="B75" s="13">
+        <v>4078</v>
+      </c>
+      <c r="D75">
+        <v>75</v>
+      </c>
+      <c r="E75" t="s">
+        <v>171</v>
+      </c>
+      <c r="F75">
+        <v>2</v>
+      </c>
+      <c r="G75">
+        <v>9213</v>
+      </c>
+      <c r="H75" t="s">
+        <v>21</v>
+      </c>
+      <c r="I75">
+        <v>95.4</v>
+      </c>
+      <c r="J75" t="s">
+        <v>22</v>
+      </c>
+      <c r="K75">
+        <v>26</v>
+      </c>
+      <c r="L75" t="s">
+        <v>135</v>
+      </c>
+      <c r="M75" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="N75" t="s">
+        <v>171</v>
+      </c>
+      <c r="O75" s="5">
+        <v>1009.5</v>
+      </c>
+      <c r="P75" t="s">
+        <v>172</v>
+      </c>
+      <c r="R75" t="s">
+        <v>135</v>
+      </c>
+      <c r="S75">
+        <v>40</v>
+      </c>
+      <c r="T75" t="s">
+        <v>135</v>
+      </c>
+      <c r="U75">
+        <v>152</v>
+      </c>
+      <c r="V75" t="s">
+        <v>173</v>
+      </c>
+      <c r="W75">
+        <v>136.30000000000001</v>
+      </c>
+      <c r="X75" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y75">
+        <v>94.8</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA75">
+        <v>14.84</v>
+      </c>
+      <c r="AB75" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC75">
+        <v>65.25</v>
+      </c>
+      <c r="AD75" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE75">
+        <v>328</v>
+      </c>
+      <c r="AF75" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG75">
+        <v>377</v>
+      </c>
+      <c r="AH75" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI75">
+        <v>246</v>
+      </c>
+      <c r="AJ75" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK75">
+        <v>9.5359999999999996</v>
+      </c>
+      <c r="AL75" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM75">
+        <v>1.65</v>
+      </c>
+      <c r="AN75" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO75" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP75" t="s">
+        <v>223</v>
+      </c>
+      <c r="AQ75">
+        <v>37</v>
+      </c>
+      <c r="AR75" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS75">
+        <v>1539.64</v>
+      </c>
+      <c r="AT75" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU75">
+        <v>165.6</v>
+      </c>
+      <c r="AV75" t="s">
+        <v>20</v>
+      </c>
+      <c r="AX75" t="s">
+        <v>174</v>
+      </c>
+      <c r="AZ75" t="s">
+        <v>174</v>
+      </c>
+      <c r="BB75" t="s">
+        <v>223</v>
+      </c>
+      <c r="BD75" t="s">
+        <v>135</v>
+      </c>
+      <c r="BF75" t="s">
+        <v>135</v>
+      </c>
+      <c r="BH75" t="s">
+        <v>175</v>
+      </c>
+      <c r="BJ75" t="s">
+        <v>20</v>
+      </c>
+      <c r="BL75" t="s">
+        <v>172</v>
+      </c>
+      <c r="BN75" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP75" t="s">
+        <v>135</v>
+      </c>
+      <c r="BR75" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="76" spans="1:72" x14ac:dyDescent="0.3">
+      <c r="B76" s="13">
+        <v>4078</v>
+      </c>
+      <c r="D76">
+        <v>85</v>
+      </c>
+      <c r="E76" t="s">
+        <v>171</v>
+      </c>
+      <c r="F76">
+        <v>3</v>
+      </c>
+      <c r="G76">
+        <v>10436</v>
+      </c>
+      <c r="H76" t="s">
+        <v>21</v>
+      </c>
+      <c r="I76">
+        <v>99.5</v>
+      </c>
+      <c r="J76" t="s">
+        <v>22</v>
+      </c>
+      <c r="K76">
+        <v>26</v>
+      </c>
+      <c r="L76" t="s">
+        <v>135</v>
+      </c>
+      <c r="M76" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="N76" t="s">
+        <v>171</v>
+      </c>
+      <c r="O76" s="5">
+        <v>1009.5</v>
+      </c>
+      <c r="P76" t="s">
+        <v>172</v>
+      </c>
+      <c r="R76" t="s">
+        <v>135</v>
+      </c>
+      <c r="S76">
+        <v>47</v>
+      </c>
+      <c r="T76" t="s">
+        <v>135</v>
+      </c>
+      <c r="U76">
+        <v>192</v>
+      </c>
+      <c r="V76" t="s">
+        <v>173</v>
+      </c>
+      <c r="W76">
+        <v>139.80000000000001</v>
+      </c>
+      <c r="X76" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y76">
+        <v>107.9</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA76">
+        <v>16.12</v>
+      </c>
+      <c r="AB76" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC76">
+        <v>70.25</v>
+      </c>
+      <c r="AD76" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE76">
+        <v>344</v>
+      </c>
+      <c r="AF76" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG76">
+        <v>395</v>
+      </c>
+      <c r="AH76" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI76">
+        <v>250</v>
+      </c>
+      <c r="AJ76" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK76">
+        <v>10.218</v>
+      </c>
+      <c r="AL76" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM76">
+        <v>2</v>
+      </c>
+      <c r="AN76" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO76" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP76" t="s">
+        <v>223</v>
+      </c>
+      <c r="AQ76">
+        <v>37</v>
+      </c>
+      <c r="AR76" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS76">
+        <v>1749.04</v>
+      </c>
+      <c r="AT76" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU76">
+        <v>166</v>
+      </c>
+      <c r="AV76" t="s">
+        <v>20</v>
+      </c>
+      <c r="AX76" t="s">
+        <v>174</v>
+      </c>
+      <c r="AZ76" t="s">
+        <v>174</v>
+      </c>
+      <c r="BB76" t="s">
+        <v>223</v>
+      </c>
+      <c r="BD76" t="s">
+        <v>135</v>
+      </c>
+      <c r="BF76" t="s">
+        <v>135</v>
+      </c>
+      <c r="BH76" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI76">
+        <v>165.6</v>
+      </c>
+      <c r="BJ76" t="s">
+        <v>20</v>
+      </c>
+      <c r="BL76" t="s">
+        <v>172</v>
+      </c>
+      <c r="BN76" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP76" t="s">
+        <v>135</v>
+      </c>
+      <c r="BR76" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="77" spans="1:72" x14ac:dyDescent="0.3">
+      <c r="B77" s="13">
+        <v>4078</v>
+      </c>
+      <c r="D77">
+        <v>100</v>
+      </c>
+      <c r="E77" t="s">
+        <v>171</v>
+      </c>
+      <c r="F77">
+        <v>4</v>
+      </c>
+      <c r="G77">
+        <v>12279</v>
+      </c>
+      <c r="H77" t="s">
+        <v>21</v>
+      </c>
+      <c r="I77">
+        <v>105</v>
+      </c>
+      <c r="J77" t="s">
+        <v>22</v>
+      </c>
+      <c r="K77">
+        <v>27</v>
+      </c>
+      <c r="L77" t="s">
+        <v>135</v>
+      </c>
+      <c r="M77" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="N77" t="s">
+        <v>171</v>
+      </c>
+      <c r="O77" s="5">
+        <v>1009.5</v>
+      </c>
+      <c r="P77" t="s">
+        <v>172</v>
+      </c>
+      <c r="R77" t="s">
+        <v>135</v>
+      </c>
+      <c r="S77">
+        <v>54</v>
+      </c>
+      <c r="T77" t="s">
+        <v>135</v>
+      </c>
+      <c r="U77">
+        <v>258</v>
+      </c>
+      <c r="V77" t="s">
+        <v>173</v>
+      </c>
+      <c r="W77">
+        <v>124.7</v>
+      </c>
+      <c r="X77" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y77">
+        <v>124.5</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA77">
+        <v>17.97</v>
+      </c>
+      <c r="AB77" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC77">
+        <v>79.25</v>
+      </c>
+      <c r="AD77" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE77">
+        <v>374</v>
+      </c>
+      <c r="AF77" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG77">
+        <v>438</v>
+      </c>
+      <c r="AH77" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI77">
+        <v>268</v>
+      </c>
+      <c r="AJ77" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK77">
+        <v>11.081</v>
+      </c>
+      <c r="AL77" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM77">
+        <v>2.5</v>
+      </c>
+      <c r="AN77" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO77" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP77" t="s">
+        <v>223</v>
+      </c>
+      <c r="AQ77">
+        <v>37</v>
+      </c>
+      <c r="AR77" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS77">
+        <v>2105.84</v>
+      </c>
+      <c r="AT77" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU77">
+        <v>169.9</v>
+      </c>
+      <c r="AV77" t="s">
+        <v>20</v>
+      </c>
+      <c r="AX77" t="s">
+        <v>174</v>
+      </c>
+      <c r="AZ77" t="s">
+        <v>174</v>
+      </c>
+      <c r="BB77" t="s">
+        <v>223</v>
+      </c>
+      <c r="BD77" t="s">
+        <v>135</v>
+      </c>
+      <c r="BF77" t="s">
+        <v>135</v>
+      </c>
+      <c r="BH77" t="s">
+        <v>175</v>
+      </c>
+      <c r="BJ77" t="s">
+        <v>20</v>
+      </c>
+      <c r="BL77" t="s">
+        <v>172</v>
+      </c>
+      <c r="BN77" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP77" t="s">
+        <v>135</v>
+      </c>
+      <c r="BR77" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="78" spans="1:72" x14ac:dyDescent="0.3">
+      <c r="B78" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C78" s="5"/>
+      <c r="D78" s="5">
+        <v>25</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="F78" s="5">
+        <v>1</v>
+      </c>
+      <c r="G78" s="5">
+        <v>2440</v>
+      </c>
+      <c r="H78" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I78" s="5">
+        <v>58</v>
+      </c>
+      <c r="J78" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K78" s="5">
+        <v>13</v>
+      </c>
+      <c r="L78" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="M78" s="5">
+        <v>64</v>
+      </c>
+      <c r="N78" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="O78" s="5">
+        <v>1028</v>
+      </c>
+      <c r="P78" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q78" s="5">
+        <v>14.2</v>
+      </c>
+      <c r="R78" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="S78" s="5">
+        <v>21</v>
+      </c>
+      <c r="T78" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="U78" s="5">
+        <v>17</v>
+      </c>
+      <c r="V78" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="W78" s="5">
+        <v>80.2</v>
+      </c>
+      <c r="X78" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y78" s="5">
+        <v>50.6</v>
+      </c>
+      <c r="Z78" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA78" s="5">
+        <v>7.91</v>
+      </c>
+      <c r="AB78" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC78" s="5">
+        <v>29.5</v>
+      </c>
+      <c r="AD78" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE78" s="5">
+        <v>257</v>
+      </c>
+      <c r="AF78" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG78" s="5">
+        <v>300</v>
+      </c>
+      <c r="AH78" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI78" s="5">
+        <v>240</v>
+      </c>
+      <c r="AJ78" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK78" s="5">
+        <v>6.35</v>
+      </c>
+      <c r="AL78" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM78" s="5">
+        <v>0.33</v>
+      </c>
+      <c r="AN78" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO78" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP78" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="AQ78" s="5">
+        <v>18</v>
+      </c>
+      <c r="AR78" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS78" s="5">
+        <v>434.78</v>
+      </c>
+      <c r="AT78" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU78" s="5">
+        <v>178.19</v>
+      </c>
+      <c r="AV78" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW78" s="5">
+        <v>77.5</v>
+      </c>
+      <c r="AX78" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY78" s="5">
+        <v>46.8</v>
+      </c>
+      <c r="AZ78" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA78" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="BB78" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="BC78" s="5">
+        <v>321.5</v>
+      </c>
+      <c r="BD78" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE78" s="5">
+        <v>259.2</v>
+      </c>
+      <c r="BF78" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG78" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="BH78" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI78" s="5">
+        <v>179.62</v>
+      </c>
+      <c r="BJ78" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK78" s="5">
+        <v>1000</v>
+      </c>
+      <c r="BL78" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM78" s="5">
+        <v>25</v>
+      </c>
+      <c r="BN78" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO78" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="BP78" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ78" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="BR78" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="BS78" s="5"/>
+      <c r="BT78" s="5"/>
+    </row>
+    <row r="79" spans="1:72" x14ac:dyDescent="0.3">
+      <c r="B79" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D79">
+        <v>50</v>
+      </c>
+      <c r="E79" t="s">
+        <v>171</v>
+      </c>
+      <c r="F79">
+        <v>2</v>
+      </c>
+      <c r="G79">
+        <v>4880</v>
+      </c>
+      <c r="H79" t="s">
+        <v>21</v>
+      </c>
+      <c r="I79">
+        <v>74</v>
+      </c>
+      <c r="J79" t="s">
+        <v>22</v>
+      </c>
+      <c r="K79">
+        <v>14</v>
+      </c>
+      <c r="L79" t="s">
+        <v>135</v>
+      </c>
+      <c r="M79">
+        <v>65</v>
+      </c>
+      <c r="N79" t="s">
+        <v>171</v>
+      </c>
+      <c r="O79">
+        <v>1027</v>
+      </c>
+      <c r="P79" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q79">
+        <v>15</v>
+      </c>
+      <c r="R79" t="s">
+        <v>135</v>
+      </c>
+      <c r="S79">
+        <v>19</v>
+      </c>
+      <c r="T79" t="s">
+        <v>135</v>
+      </c>
+      <c r="U79">
+        <v>75</v>
+      </c>
+      <c r="V79" t="s">
+        <v>173</v>
+      </c>
+      <c r="W79">
+        <v>117.8</v>
+      </c>
+      <c r="X79" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y79">
+        <v>77.400000000000006</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA79">
+        <v>12.4</v>
+      </c>
+      <c r="AB79" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC79">
+        <v>44.4</v>
+      </c>
+      <c r="AD79" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE79">
+        <v>270</v>
+      </c>
+      <c r="AF79" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG79">
+        <v>320</v>
+      </c>
+      <c r="AH79" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI79">
+        <v>220</v>
+      </c>
+      <c r="AJ79" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK79">
+        <v>11.35</v>
+      </c>
+      <c r="AL79" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM79">
+        <v>1.18</v>
+      </c>
+      <c r="AN79" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO79" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP79" t="s">
+        <v>223</v>
+      </c>
+      <c r="AQ79">
+        <v>20</v>
+      </c>
+      <c r="AR79" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS79">
+        <v>861.24</v>
+      </c>
+      <c r="AT79" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU79">
+        <v>176.48</v>
+      </c>
+      <c r="AV79" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW79">
+        <v>116.5</v>
+      </c>
+      <c r="AX79" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY79">
+        <v>75.8</v>
+      </c>
+      <c r="AZ79" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA79" t="s">
+        <v>230</v>
+      </c>
+      <c r="BB79" t="s">
+        <v>223</v>
+      </c>
+      <c r="BC79">
+        <v>347.7</v>
+      </c>
+      <c r="BD79" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE79">
+        <v>241.7</v>
+      </c>
+      <c r="BF79" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG79" t="s">
+        <v>230</v>
+      </c>
+      <c r="BH79" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI79">
+        <v>178.08</v>
+      </c>
+      <c r="BJ79" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK79">
+        <v>1000</v>
+      </c>
+      <c r="BL79" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM79">
+        <v>25</v>
+      </c>
+      <c r="BN79" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO79" t="s">
+        <v>230</v>
+      </c>
+      <c r="BP79" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ79" t="s">
+        <v>230</v>
+      </c>
+      <c r="BR79" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="80" spans="1:72" x14ac:dyDescent="0.3">
+      <c r="B80" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D80">
+        <v>75</v>
+      </c>
+      <c r="E80" t="s">
+        <v>171</v>
+      </c>
+      <c r="F80">
+        <v>3</v>
+      </c>
+      <c r="G80">
+        <v>7320</v>
+      </c>
+      <c r="H80" t="s">
+        <v>21</v>
+      </c>
+      <c r="I80">
+        <v>84</v>
+      </c>
+      <c r="J80" t="s">
+        <v>22</v>
+      </c>
+      <c r="K80">
+        <v>12</v>
+      </c>
+      <c r="L80" t="s">
+        <v>135</v>
+      </c>
+      <c r="M80">
+        <v>62</v>
+      </c>
+      <c r="N80" t="s">
+        <v>171</v>
+      </c>
+      <c r="O80">
+        <v>1027</v>
+      </c>
+      <c r="P80" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q80">
+        <v>15.7</v>
+      </c>
+      <c r="R80" t="s">
+        <v>135</v>
+      </c>
+      <c r="S80">
+        <v>22</v>
+      </c>
+      <c r="T80" t="s">
+        <v>135</v>
+      </c>
+      <c r="U80">
+        <v>140</v>
+      </c>
+      <c r="V80" t="s">
+        <v>173</v>
+      </c>
+      <c r="W80">
+        <v>140.6</v>
+      </c>
+      <c r="X80" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y80">
+        <v>102.6</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA80">
+        <v>16.39</v>
+      </c>
+      <c r="AB80" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC80">
+        <v>57.4</v>
+      </c>
+      <c r="AD80" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE80">
+        <v>295</v>
+      </c>
+      <c r="AF80" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG80">
+        <v>355</v>
+      </c>
+      <c r="AH80" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI80">
+        <v>200</v>
+      </c>
+      <c r="AJ80" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK80">
+        <v>14.372</v>
+      </c>
+      <c r="AL80" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM80">
+        <v>2.23</v>
+      </c>
+      <c r="AN80" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO80" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP80" t="s">
+        <v>223</v>
+      </c>
+      <c r="AQ80">
+        <v>21</v>
+      </c>
+      <c r="AR80" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS80">
+        <v>1228.67</v>
+      </c>
+      <c r="AT80" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU80">
+        <v>172.76</v>
+      </c>
+      <c r="AV80" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW80">
+        <v>139.5</v>
+      </c>
+      <c r="AX80" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY80">
+        <v>101.2</v>
+      </c>
+      <c r="AZ80" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA80" t="s">
+        <v>230</v>
+      </c>
+      <c r="BB80" t="s">
+        <v>223</v>
+      </c>
+      <c r="BC80">
+        <v>381.8</v>
+      </c>
+      <c r="BD80" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE80">
+        <v>220.7</v>
+      </c>
+      <c r="BF80" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG80" t="s">
+        <v>230</v>
+      </c>
+      <c r="BH80" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI80">
+        <v>169.05</v>
+      </c>
+      <c r="BJ80" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK80">
+        <v>1000</v>
+      </c>
+      <c r="BL80" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM80">
+        <v>25</v>
+      </c>
+      <c r="BN80" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO80" t="s">
+        <v>230</v>
+      </c>
+      <c r="BP80" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ80" t="s">
+        <v>230</v>
+      </c>
+      <c r="BR80" t="s">
+        <v>173</v>
+      </c>
+    </row>
     <row r="81" spans="1:85" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>231</v>
-      </c>
       <c r="B81" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C81" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="D81">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="E81" t="s">
         <v>171</v>
       </c>
       <c r="F81">
-        <v>1</v>
-      </c>
-      <c r="G81" s="4">
-        <v>3135</v>
+        <v>4</v>
+      </c>
+      <c r="G81">
+        <v>8296</v>
       </c>
       <c r="H81" t="s">
         <v>21</v>
       </c>
       <c r="I81">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="J81" t="s">
         <v>22</v>
       </c>
       <c r="K81">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L81" t="s">
         <v>135</v>
       </c>
-      <c r="M81" t="s">
-        <v>231</v>
+      <c r="M81">
+        <v>62</v>
       </c>
       <c r="N81" t="s">
         <v>171</v>
       </c>
-      <c r="O81" t="s">
-        <v>231</v>
+      <c r="O81">
+        <v>1027</v>
       </c>
       <c r="P81" t="s">
         <v>172</v>
       </c>
-      <c r="Q81" t="s">
-        <v>231</v>
+      <c r="Q81">
+        <v>16.600000000000001</v>
       </c>
       <c r="R81" t="s">
         <v>135</v>
       </c>
       <c r="S81">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="T81" t="s">
         <v>135</v>
       </c>
       <c r="U81">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="V81" t="s">
         <v>173</v>
       </c>
-      <c r="W81" t="s">
-        <v>231</v>
+      <c r="W81">
+        <v>152.19999999999999</v>
       </c>
       <c r="X81" t="s">
         <v>174</v>
       </c>
-      <c r="Y81" t="s">
-        <v>231</v>
+      <c r="Y81">
+        <v>114.6</v>
       </c>
       <c r="Z81" t="s">
         <v>174</v>
       </c>
-      <c r="AA81" t="s">
-        <v>231</v>
+      <c r="AA81">
+        <v>17.73</v>
       </c>
       <c r="AB81" t="s">
         <v>174</v>
       </c>
       <c r="AC81">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AD81" t="s">
-        <v>19</v>
+        <v>171</v>
       </c>
       <c r="AE81">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="AF81" t="s">
         <v>135</v>
       </c>
       <c r="AG81">
-        <v>340</v>
+        <v>375</v>
       </c>
       <c r="AH81" t="s">
         <v>135</v>
       </c>
       <c r="AI81">
-        <v>250</v>
+        <v>205</v>
       </c>
       <c r="AJ81" t="s">
         <v>135</v>
       </c>
       <c r="AK81">
-        <v>11.6</v>
+        <v>15.108000000000001</v>
       </c>
       <c r="AL81" t="s">
         <v>175</v>
       </c>
       <c r="AM81">
-        <v>1</v>
+        <v>2.56</v>
       </c>
       <c r="AN81" t="s">
         <v>174</v>
       </c>
-      <c r="AO81">
-        <v>0.9</v>
+      <c r="AO81" t="s">
+        <v>230</v>
       </c>
       <c r="AP81" t="s">
-        <v>174</v>
+        <v>223</v>
       </c>
       <c r="AQ81">
-        <v>130</v>
+        <v>22</v>
       </c>
       <c r="AR81" t="s">
         <v>135</v>
       </c>
-      <c r="AS81" t="s">
-        <v>231</v>
+      <c r="AS81">
+        <v>1422.92</v>
       </c>
       <c r="AT81" t="s">
         <v>177</v>
       </c>
-      <c r="AU81" t="s">
-        <v>231</v>
+      <c r="AU81">
+        <v>171.52</v>
       </c>
       <c r="AV81" t="s">
         <v>20</v>
       </c>
-      <c r="AW81" t="s">
-        <v>231</v>
+      <c r="AW81">
+        <v>152.19999999999999</v>
       </c>
       <c r="AX81" t="s">
         <v>174</v>
       </c>
-      <c r="AY81" t="s">
-        <v>231</v>
+      <c r="AY81">
+        <v>111</v>
       </c>
       <c r="AZ81" t="s">
         <v>174</v>
       </c>
       <c r="BA81" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BB81" t="s">
-        <v>224</v>
-      </c>
-      <c r="BC81" t="s">
-        <v>231</v>
+        <v>223</v>
+      </c>
+      <c r="BC81">
+        <v>397.1</v>
       </c>
       <c r="BD81" t="s">
         <v>135</v>
       </c>
-      <c r="BE81" t="s">
-        <v>231</v>
+      <c r="BE81">
+        <v>220.9</v>
       </c>
       <c r="BF81" t="s">
         <v>135</v>
       </c>
       <c r="BG81" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BH81" t="s">
         <v>175</v>
       </c>
-      <c r="BI81" t="s">
-        <v>231</v>
+      <c r="BI81">
+        <v>172.2</v>
       </c>
       <c r="BJ81" t="s">
         <v>20</v>
       </c>
-      <c r="BK81" t="s">
-        <v>231</v>
+      <c r="BK81">
+        <v>1000</v>
       </c>
       <c r="BL81" t="s">
         <v>172</v>
       </c>
-      <c r="BM81" t="s">
-        <v>231</v>
+      <c r="BM81">
+        <v>25</v>
       </c>
       <c r="BN81" t="s">
         <v>135</v>
       </c>
       <c r="BO81" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BP81" t="s">
         <v>135</v>
       </c>
       <c r="BQ81" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BR81" t="s">
         <v>173</v>
       </c>
-      <c r="BS81" t="s">
-        <v>231</v>
-      </c>
-      <c r="BT81" t="s">
-        <v>231</v>
-      </c>
     </row>
     <row r="82" spans="1:85" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>231</v>
-      </c>
-      <c r="B82" t="s">
-        <v>231</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>231</v>
+      <c r="B82" s="2" t="s">
+        <v>253</v>
       </c>
       <c r="D82">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E82" t="s">
         <v>171</v>
       </c>
       <c r="F82">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G82">
-        <v>4927.5</v>
+        <v>9760</v>
       </c>
       <c r="H82" t="s">
         <v>21</v>
       </c>
-      <c r="I82" s="4">
-        <v>120</v>
+      <c r="I82">
+        <v>93</v>
       </c>
       <c r="J82" t="s">
         <v>22</v>
       </c>
       <c r="K82">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L82" t="s">
         <v>135</v>
       </c>
-      <c r="M82" t="s">
-        <v>231</v>
+      <c r="M82">
+        <v>62</v>
       </c>
       <c r="N82" t="s">
         <v>171</v>
       </c>
-      <c r="O82" t="s">
-        <v>231</v>
+      <c r="O82">
+        <v>1028</v>
       </c>
       <c r="P82" t="s">
         <v>172</v>
       </c>
-      <c r="Q82" t="s">
-        <v>231</v>
+      <c r="Q82">
+        <v>17</v>
       </c>
       <c r="R82" t="s">
         <v>135</v>
       </c>
       <c r="S82">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="T82" t="s">
         <v>135</v>
       </c>
       <c r="U82">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="V82" t="s">
         <v>173</v>
       </c>
-      <c r="W82" t="s">
-        <v>231</v>
+      <c r="W82">
+        <v>147.6</v>
       </c>
       <c r="X82" t="s">
         <v>174</v>
       </c>
-      <c r="Y82" t="s">
-        <v>231</v>
+      <c r="Y82">
+        <v>129.6</v>
       </c>
       <c r="Z82" t="s">
         <v>174</v>
       </c>
-      <c r="AA82" t="s">
-        <v>231</v>
+      <c r="AA82">
+        <v>19.739999999999998</v>
       </c>
       <c r="AB82" t="s">
         <v>174</v>
       </c>
       <c r="AC82">
-        <v>54.8</v>
+        <v>70.5</v>
       </c>
       <c r="AD82" t="s">
-        <v>19</v>
+        <v>171</v>
       </c>
       <c r="AE82">
-        <v>300</v>
+        <v>362</v>
       </c>
       <c r="AF82" t="s">
         <v>135</v>
       </c>
       <c r="AG82">
-        <v>360</v>
+        <v>425</v>
       </c>
       <c r="AH82" t="s">
         <v>135</v>
       </c>
       <c r="AI82">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="AJ82" t="s">
         <v>135</v>
       </c>
       <c r="AK82">
-        <v>14.8</v>
+        <v>16.654</v>
       </c>
       <c r="AL82" t="s">
         <v>175</v>
       </c>
       <c r="AM82">
-        <v>1.8</v>
+        <v>3.28</v>
       </c>
       <c r="AN82" t="s">
         <v>174</v>
       </c>
-      <c r="AO82">
-        <v>1.6</v>
+      <c r="AO82" t="s">
+        <v>230</v>
       </c>
       <c r="AP82" t="s">
-        <v>174</v>
+        <v>223</v>
       </c>
       <c r="AQ82">
-        <v>130</v>
+        <v>24</v>
       </c>
       <c r="AR82" t="s">
         <v>135</v>
       </c>
-      <c r="AS82" t="s">
-        <v>231</v>
+      <c r="AS82">
+        <v>1690.14</v>
       </c>
       <c r="AT82" t="s">
         <v>177</v>
       </c>
-      <c r="AU82" t="s">
-        <v>231</v>
+      <c r="AU82">
+        <v>173.17</v>
       </c>
       <c r="AV82" t="s">
         <v>20</v>
       </c>
-      <c r="AW82" t="s">
-        <v>231</v>
+      <c r="AW82">
+        <v>147.6</v>
       </c>
       <c r="AX82" t="s">
         <v>174</v>
       </c>
-      <c r="AY82" t="s">
-        <v>231</v>
+      <c r="AY82">
+        <v>126.2</v>
       </c>
       <c r="AZ82" t="s">
         <v>174</v>
       </c>
       <c r="BA82" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BB82" t="s">
-        <v>224</v>
-      </c>
-      <c r="BC82" t="s">
-        <v>231</v>
+        <v>223</v>
+      </c>
+      <c r="BC82">
+        <v>446.8</v>
       </c>
       <c r="BD82" t="s">
         <v>135</v>
       </c>
-      <c r="BE82" t="s">
-        <v>231</v>
+      <c r="BE82">
+        <v>245.6</v>
       </c>
       <c r="BF82" t="s">
         <v>135</v>
       </c>
       <c r="BG82" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BH82" t="s">
         <v>175</v>
       </c>
-      <c r="BI82" t="s">
-        <v>231</v>
+      <c r="BI82">
+        <v>173.54</v>
       </c>
       <c r="BJ82" t="s">
         <v>20</v>
       </c>
-      <c r="BK82" t="s">
-        <v>231</v>
+      <c r="BK82">
+        <v>1000</v>
       </c>
       <c r="BL82" t="s">
         <v>172</v>
       </c>
-      <c r="BM82" t="s">
-        <v>231</v>
+      <c r="BM82">
+        <v>25</v>
       </c>
       <c r="BN82" t="s">
         <v>135</v>
       </c>
       <c r="BO82" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BP82" t="s">
         <v>135</v>
       </c>
       <c r="BQ82" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BR82" t="s">
         <v>173</v>
       </c>
-      <c r="BS82" t="s">
-        <v>231</v>
-      </c>
-      <c r="BT82" t="s">
-        <v>231</v>
-      </c>
     </row>
     <row r="83" spans="1:85" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>231</v>
-      </c>
       <c r="B83" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C83" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="D83">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="E83" t="s">
         <v>171</v>
       </c>
       <c r="F83">
-        <v>3</v>
-      </c>
-      <c r="G83" s="4">
-        <v>5548.3</v>
+        <v>6</v>
+      </c>
+      <c r="G83">
+        <v>10736</v>
       </c>
       <c r="H83" t="s">
         <v>21</v>
       </c>
       <c r="I83">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="J83" t="s">
         <v>22</v>
       </c>
       <c r="K83">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L83" t="s">
         <v>135</v>
       </c>
-      <c r="M83" t="s">
-        <v>231</v>
+      <c r="M83">
+        <v>62</v>
       </c>
       <c r="N83" t="s">
         <v>171</v>
       </c>
-      <c r="O83" t="s">
-        <v>231</v>
+      <c r="O83">
+        <v>1027</v>
       </c>
       <c r="P83" t="s">
         <v>172</v>
       </c>
-      <c r="Q83" t="s">
-        <v>231</v>
+      <c r="Q83">
+        <v>18</v>
       </c>
       <c r="R83" t="s">
         <v>135</v>
       </c>
       <c r="S83">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="T83" t="s">
         <v>135</v>
       </c>
       <c r="U83">
-        <v>210</v>
+        <v>285</v>
       </c>
       <c r="V83" t="s">
         <v>173</v>
       </c>
-      <c r="W83" t="s">
-        <v>231</v>
+      <c r="W83">
+        <v>153.6</v>
       </c>
       <c r="X83" t="s">
         <v>174</v>
       </c>
-      <c r="Y83" t="s">
-        <v>231</v>
+      <c r="Y83">
+        <v>142.80000000000001</v>
       </c>
       <c r="Z83" t="s">
         <v>174</v>
       </c>
-      <c r="AA83" t="s">
-        <v>231</v>
+      <c r="AA83">
+        <v>21.03</v>
       </c>
       <c r="AB83" t="s">
         <v>174</v>
       </c>
       <c r="AC83">
-        <v>60.6</v>
+        <v>75.3</v>
       </c>
       <c r="AD83" t="s">
-        <v>19</v>
+        <v>171</v>
       </c>
       <c r="AE83">
-        <v>301</v>
+        <v>389</v>
       </c>
       <c r="AF83" t="s">
         <v>135</v>
       </c>
       <c r="AG83">
-        <v>365</v>
+        <v>450</v>
       </c>
       <c r="AH83" t="s">
         <v>135</v>
       </c>
       <c r="AI83">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="AJ83" t="s">
         <v>135</v>
       </c>
       <c r="AK83">
-        <v>15.4</v>
+        <v>17.189</v>
       </c>
       <c r="AL83" t="s">
         <v>175</v>
       </c>
       <c r="AM83">
-        <v>2</v>
+        <v>3.45</v>
       </c>
       <c r="AN83" t="s">
         <v>174</v>
       </c>
-      <c r="AO83">
-        <v>1.8</v>
+      <c r="AO83" t="s">
+        <v>230</v>
       </c>
       <c r="AP83" t="s">
-        <v>174</v>
+        <v>223</v>
       </c>
       <c r="AQ83">
-        <v>130</v>
+        <v>24</v>
       </c>
       <c r="AR83" t="s">
         <v>135</v>
       </c>
-      <c r="AS83" t="s">
-        <v>231</v>
+      <c r="AS83">
+        <v>1935.48</v>
       </c>
       <c r="AT83" t="s">
         <v>177</v>
       </c>
-      <c r="AU83" t="s">
-        <v>231</v>
+      <c r="AU83">
+        <v>180.28</v>
       </c>
       <c r="AV83" t="s">
         <v>20</v>
       </c>
-      <c r="AW83" t="s">
-        <v>231</v>
+      <c r="AW83">
+        <v>153.6</v>
       </c>
       <c r="AX83" t="s">
         <v>174</v>
       </c>
-      <c r="AY83" t="s">
-        <v>231</v>
+      <c r="AY83">
+        <v>140.80000000000001</v>
       </c>
       <c r="AZ83" t="s">
         <v>174</v>
       </c>
       <c r="BA83" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BB83" t="s">
-        <v>224</v>
-      </c>
-      <c r="BC83" t="s">
-        <v>231</v>
+        <v>223</v>
+      </c>
+      <c r="BC83">
+        <v>473.9</v>
       </c>
       <c r="BD83" t="s">
         <v>135</v>
       </c>
-      <c r="BE83" t="s">
-        <v>231</v>
+      <c r="BE83">
+        <v>261</v>
       </c>
       <c r="BF83" t="s">
         <v>135</v>
       </c>
       <c r="BG83" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BH83" t="s">
         <v>175</v>
       </c>
-      <c r="BI83" t="s">
-        <v>231</v>
+      <c r="BI83">
+        <v>180.84</v>
       </c>
       <c r="BJ83" t="s">
         <v>20</v>
       </c>
-      <c r="BK83" t="s">
-        <v>231</v>
+      <c r="BK83">
+        <v>1000</v>
       </c>
       <c r="BL83" t="s">
         <v>172</v>
       </c>
-      <c r="BM83" t="s">
-        <v>231</v>
+      <c r="BM83">
+        <v>25</v>
       </c>
       <c r="BN83" t="s">
         <v>135</v>
       </c>
       <c r="BO83" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BP83" t="s">
         <v>135</v>
       </c>
       <c r="BQ83" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BR83" t="s">
         <v>173</v>
       </c>
-      <c r="BS83" t="s">
-        <v>231</v>
-      </c>
-      <c r="BT83" t="s">
-        <v>231</v>
-      </c>
     </row>
     <row r="84" spans="1:85" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>231</v>
-      </c>
       <c r="B84" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C84" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="D84">
         <v>100</v>
@@ -18457,576 +19929,819 @@
         <v>171</v>
       </c>
       <c r="F84">
-        <v>4</v>
-      </c>
-      <c r="G84" s="4">
-        <v>6580</v>
+        <v>7</v>
+      </c>
+      <c r="G84">
+        <v>9760</v>
       </c>
       <c r="H84" t="s">
         <v>21</v>
       </c>
-      <c r="I84">
-        <v>127</v>
+      <c r="I84" s="7">
+        <v>93</v>
       </c>
       <c r="J84" t="s">
         <v>22</v>
       </c>
       <c r="K84">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L84" t="s">
         <v>135</v>
       </c>
-      <c r="M84" t="s">
-        <v>231</v>
+      <c r="M84">
+        <v>62</v>
       </c>
       <c r="N84" t="s">
         <v>171</v>
       </c>
-      <c r="O84" t="s">
-        <v>231</v>
+      <c r="O84">
+        <v>1028</v>
       </c>
       <c r="P84" t="s">
         <v>172</v>
       </c>
-      <c r="Q84" t="s">
-        <v>231</v>
+      <c r="Q84">
+        <v>17.399999999999999</v>
       </c>
       <c r="R84" t="s">
         <v>135</v>
       </c>
       <c r="S84">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="T84" t="s">
         <v>135</v>
       </c>
       <c r="U84">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="V84" t="s">
         <v>173</v>
       </c>
-      <c r="W84" t="s">
-        <v>231</v>
+      <c r="W84">
+        <v>147.80000000000001</v>
       </c>
       <c r="X84" t="s">
         <v>174</v>
       </c>
-      <c r="Y84" t="s">
-        <v>231</v>
+      <c r="Y84">
+        <v>134</v>
       </c>
       <c r="Z84" t="s">
         <v>174</v>
       </c>
-      <c r="AA84" t="s">
-        <v>231</v>
+      <c r="AA84">
+        <v>19.739999999999998</v>
       </c>
       <c r="AB84" t="s">
         <v>174</v>
       </c>
       <c r="AC84">
-        <v>69.400000000000006</v>
+        <v>71</v>
       </c>
       <c r="AD84" t="s">
-        <v>19</v>
+        <v>171</v>
       </c>
       <c r="AE84">
-        <v>335.6</v>
+        <v>364</v>
       </c>
       <c r="AF84" t="s">
         <v>135</v>
       </c>
       <c r="AG84">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="AH84" t="s">
         <v>135</v>
       </c>
       <c r="AI84">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="AJ84" t="s">
         <v>135</v>
       </c>
       <c r="AK84">
-        <v>17.010000000000002</v>
+        <v>16.622</v>
       </c>
       <c r="AL84" t="s">
         <v>175</v>
       </c>
       <c r="AM84">
-        <v>2.5</v>
+        <v>3.26</v>
       </c>
       <c r="AN84" t="s">
         <v>174</v>
       </c>
-      <c r="AO84">
-        <v>2.2999999999999998</v>
+      <c r="AO84" t="s">
+        <v>230</v>
       </c>
       <c r="AP84" t="s">
-        <v>174</v>
+        <v>223</v>
       </c>
       <c r="AQ84">
-        <v>129</v>
+        <v>23</v>
       </c>
       <c r="AR84" t="s">
         <v>135</v>
       </c>
-      <c r="AS84" t="s">
-        <v>231</v>
+      <c r="AS84">
+        <v>1698.11</v>
       </c>
       <c r="AT84" t="s">
         <v>177</v>
       </c>
-      <c r="AU84" t="s">
-        <v>231</v>
+      <c r="AU84">
+        <v>173.99</v>
       </c>
       <c r="AV84" t="s">
         <v>20</v>
       </c>
-      <c r="AW84" t="s">
-        <v>231</v>
+      <c r="AW84">
+        <v>147.80000000000001</v>
       </c>
       <c r="AX84" t="s">
         <v>174</v>
       </c>
-      <c r="AY84" t="s">
-        <v>231</v>
+      <c r="AY84">
+        <v>130.80000000000001</v>
       </c>
       <c r="AZ84" t="s">
         <v>174</v>
       </c>
       <c r="BA84" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BB84" t="s">
-        <v>224</v>
-      </c>
-      <c r="BC84" t="s">
-        <v>231</v>
+        <v>223</v>
+      </c>
+      <c r="BC84">
+        <v>446.3</v>
       </c>
       <c r="BD84" t="s">
         <v>135</v>
       </c>
-      <c r="BE84" t="s">
-        <v>231</v>
+      <c r="BE84">
+        <v>245.1</v>
       </c>
       <c r="BF84" t="s">
         <v>135</v>
       </c>
       <c r="BG84" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BH84" t="s">
         <v>175</v>
       </c>
-      <c r="BI84" t="s">
-        <v>231</v>
+      <c r="BI84">
+        <v>174.34</v>
       </c>
       <c r="BJ84" t="s">
         <v>20</v>
       </c>
-      <c r="BK84" t="s">
-        <v>231</v>
+      <c r="BK84">
+        <v>1000</v>
       </c>
       <c r="BL84" t="s">
         <v>172</v>
       </c>
-      <c r="BM84" t="s">
-        <v>231</v>
+      <c r="BM84">
+        <v>25</v>
       </c>
       <c r="BN84" t="s">
         <v>135</v>
       </c>
       <c r="BO84" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BP84" t="s">
         <v>135</v>
       </c>
       <c r="BQ84" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BR84" t="s">
         <v>173</v>
       </c>
-      <c r="BS84" t="s">
-        <v>231</v>
-      </c>
-      <c r="BT84" t="s">
-        <v>231</v>
-      </c>
     </row>
     <row r="85" spans="1:85" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>231</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C85" t="s">
-        <v>231</v>
-      </c>
-      <c r="D85">
-        <v>110</v>
+      <c r="B85" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D85" s="14">
+        <v>15</v>
       </c>
       <c r="E85" t="s">
         <v>171</v>
       </c>
       <c r="F85">
-        <v>5</v>
-      </c>
-      <c r="G85">
-        <v>7240</v>
+        <v>1</v>
+      </c>
+      <c r="G85" s="14">
+        <v>379</v>
       </c>
       <c r="H85" t="s">
         <v>21</v>
       </c>
-      <c r="I85">
-        <v>130</v>
+      <c r="I85" s="14">
+        <v>400</v>
       </c>
       <c r="J85" t="s">
         <v>22</v>
       </c>
-      <c r="K85">
-        <v>15</v>
+      <c r="K85" s="18">
+        <v>31</v>
       </c>
       <c r="L85" t="s">
         <v>135</v>
       </c>
-      <c r="M85" t="s">
-        <v>231</v>
+      <c r="M85" s="18">
+        <v>65</v>
       </c>
       <c r="N85" t="s">
         <v>171</v>
       </c>
-      <c r="O85" t="s">
-        <v>231</v>
+      <c r="O85" s="18">
+        <v>994</v>
       </c>
       <c r="P85" t="s">
         <v>172</v>
       </c>
-      <c r="Q85" t="s">
-        <v>231</v>
+      <c r="Q85" s="18">
+        <v>31</v>
       </c>
       <c r="R85" t="s">
         <v>135</v>
       </c>
-      <c r="S85">
-        <v>46</v>
+      <c r="S85" s="18">
+        <v>27</v>
       </c>
       <c r="T85" t="s">
         <v>135</v>
       </c>
-      <c r="U85">
-        <v>260</v>
+      <c r="U85" t="s">
+        <v>230</v>
       </c>
       <c r="V85" t="s">
         <v>173</v>
       </c>
-      <c r="W85" t="s">
-        <v>231</v>
+      <c r="W85" s="18">
+        <v>75.25</v>
       </c>
       <c r="X85" t="s">
         <v>174</v>
       </c>
       <c r="Y85" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Z85" t="s">
         <v>174</v>
       </c>
       <c r="AA85" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AB85" t="s">
         <v>174</v>
       </c>
-      <c r="AC85">
-        <v>76.2</v>
+      <c r="AC85" s="18">
+        <v>2.6</v>
       </c>
       <c r="AD85" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE85">
-        <v>342</v>
+        <v>171</v>
+      </c>
+      <c r="AE85" s="18">
+        <v>293.8</v>
       </c>
       <c r="AF85" t="s">
         <v>135</v>
       </c>
-      <c r="AG85">
-        <v>420</v>
+      <c r="AG85" s="18">
+        <v>350</v>
       </c>
       <c r="AH85" t="s">
         <v>135</v>
       </c>
-      <c r="AI85">
-        <v>250</v>
+      <c r="AI85" s="18">
+        <v>315</v>
       </c>
       <c r="AJ85" t="s">
         <v>135</v>
       </c>
-      <c r="AK85">
-        <v>17.5</v>
+      <c r="AK85" s="18">
+        <v>6.7</v>
       </c>
       <c r="AL85" t="s">
         <v>175</v>
       </c>
-      <c r="AM85">
-        <v>2.8</v>
+      <c r="AM85" s="18">
+        <v>0.08</v>
       </c>
       <c r="AN85" t="s">
         <v>174</v>
       </c>
-      <c r="AO85">
-        <v>2.6</v>
+      <c r="AO85" t="s">
+        <v>230</v>
       </c>
       <c r="AP85" t="s">
-        <v>174</v>
-      </c>
-      <c r="AQ85">
-        <v>130</v>
+        <v>223</v>
+      </c>
+      <c r="AQ85" s="18">
+        <v>30.5</v>
       </c>
       <c r="AR85" t="s">
         <v>135</v>
       </c>
-      <c r="AS85" t="s">
-        <v>231</v>
+      <c r="AS85" s="18">
+        <v>88.4</v>
       </c>
       <c r="AT85" t="s">
         <v>177</v>
       </c>
-      <c r="AU85" t="s">
-        <v>231</v>
+      <c r="AU85" s="18">
+        <v>235.7</v>
       </c>
       <c r="AV85" t="s">
         <v>20</v>
       </c>
       <c r="AW85" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AX85" t="s">
         <v>174</v>
       </c>
       <c r="AY85" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AZ85" t="s">
         <v>174</v>
       </c>
       <c r="BA85" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BB85" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="BC85" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BD85" t="s">
         <v>135</v>
       </c>
       <c r="BE85" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BF85" t="s">
         <v>135</v>
       </c>
       <c r="BG85" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BH85" t="s">
         <v>175</v>
       </c>
-      <c r="BI85" t="s">
-        <v>231</v>
+      <c r="BI85" s="18">
+        <v>235.7</v>
       </c>
       <c r="BJ85" t="s">
         <v>20</v>
       </c>
-      <c r="BK85" t="s">
-        <v>231</v>
+      <c r="BK85" s="20" t="s">
+        <v>230</v>
       </c>
       <c r="BL85" t="s">
         <v>172</v>
       </c>
-      <c r="BM85" t="s">
-        <v>231</v>
+      <c r="BM85" s="20" t="s">
+        <v>230</v>
       </c>
       <c r="BN85" t="s">
         <v>135</v>
       </c>
-      <c r="BO85" t="s">
-        <v>231</v>
+      <c r="BO85" s="20" t="s">
+        <v>230</v>
       </c>
       <c r="BP85" t="s">
         <v>135</v>
       </c>
-      <c r="BQ85" t="s">
-        <v>231</v>
+      <c r="BQ85" s="20" t="s">
+        <v>230</v>
       </c>
       <c r="BR85" t="s">
         <v>173</v>
-      </c>
-      <c r="BS85" t="s">
-        <v>231</v>
-      </c>
-      <c r="BT85" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="86" spans="1:85" x14ac:dyDescent="0.3">
       <c r="A86" s="5"/>
-      <c r="B86" t="s">
-        <v>218</v>
+      <c r="B86" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D86" s="17">
+        <v>25</v>
+      </c>
+      <c r="E86" t="s">
+        <v>171</v>
+      </c>
+      <c r="F86">
+        <v>2</v>
+      </c>
+      <c r="G86" s="17">
+        <v>625</v>
+      </c>
+      <c r="H86" t="s">
+        <v>21</v>
+      </c>
+      <c r="I86" s="17">
+        <v>472</v>
+      </c>
+      <c r="J86" t="s">
+        <v>22</v>
+      </c>
+      <c r="K86" s="19">
+        <v>33</v>
+      </c>
+      <c r="L86" t="s">
+        <v>135</v>
+      </c>
+      <c r="M86" s="19">
+        <v>64</v>
+      </c>
+      <c r="N86" t="s">
+        <v>171</v>
+      </c>
+      <c r="O86" s="19">
+        <v>994</v>
+      </c>
+      <c r="P86" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q86" s="19">
+        <v>33</v>
+      </c>
+      <c r="R86" t="s">
+        <v>135</v>
+      </c>
+      <c r="S86" s="19">
+        <v>33</v>
+      </c>
+      <c r="T86" t="s">
+        <v>135</v>
+      </c>
+      <c r="U86" t="s">
+        <v>230</v>
+      </c>
+      <c r="V86" t="s">
+        <v>173</v>
+      </c>
+      <c r="W86" s="19">
+        <v>81.75</v>
+      </c>
+      <c r="X86" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>230</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA86" t="s">
+        <v>230</v>
+      </c>
+      <c r="AB86" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC86" s="19">
+        <v>3</v>
+      </c>
+      <c r="AD86" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE86" s="19">
+        <v>330.6</v>
+      </c>
+      <c r="AF86" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG86" s="19">
+        <v>455</v>
+      </c>
+      <c r="AH86" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI86" s="19">
+        <v>420</v>
+      </c>
+      <c r="AJ86" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK86" s="19">
+        <v>10.1</v>
+      </c>
+      <c r="AL86" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM86" s="19">
+        <v>0.26</v>
+      </c>
+      <c r="AN86" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO86" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP86" t="s">
+        <v>223</v>
+      </c>
+      <c r="AQ86" s="19">
+        <v>31</v>
+      </c>
+      <c r="AR86" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS86" s="19">
+        <v>134.1</v>
+      </c>
+      <c r="AT86" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU86" s="19">
+        <v>214.6</v>
+      </c>
+      <c r="AV86" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW86" t="s">
+        <v>230</v>
+      </c>
+      <c r="AX86" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY86" t="s">
+        <v>230</v>
+      </c>
+      <c r="AZ86" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA86" t="s">
+        <v>230</v>
+      </c>
+      <c r="BB86" t="s">
+        <v>223</v>
+      </c>
+      <c r="BC86" t="s">
+        <v>230</v>
+      </c>
+      <c r="BD86" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE86" t="s">
+        <v>230</v>
+      </c>
+      <c r="BF86" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG86" t="s">
+        <v>230</v>
+      </c>
+      <c r="BH86" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI86" s="19">
+        <v>214.6</v>
+      </c>
+      <c r="BJ86" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK86" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BL86" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM86" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BN86" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO86" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BP86" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ86" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BR86" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="87" spans="1:85" x14ac:dyDescent="0.3">
       <c r="A87" s="5"/>
-      <c r="B87" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="D87">
-        <v>25</v>
+      <c r="B87" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D87" s="14">
+        <v>50</v>
       </c>
       <c r="E87" t="s">
         <v>171</v>
       </c>
       <c r="F87">
-        <v>1</v>
-      </c>
-      <c r="G87">
-        <v>1643</v>
+        <v>3</v>
+      </c>
+      <c r="G87" s="14">
+        <v>1250</v>
       </c>
       <c r="H87" t="s">
         <v>21</v>
       </c>
-      <c r="I87">
-        <v>80</v>
+      <c r="I87" s="14">
+        <v>595</v>
       </c>
       <c r="J87" t="s">
         <v>22</v>
       </c>
-      <c r="K87">
-        <v>14</v>
+      <c r="K87" s="18">
+        <v>34</v>
       </c>
       <c r="L87" t="s">
         <v>135</v>
       </c>
-      <c r="M87">
-        <v>24</v>
+      <c r="M87" s="18">
+        <v>63</v>
       </c>
       <c r="N87" t="s">
         <v>171</v>
       </c>
-      <c r="O87">
-        <v>1023</v>
+      <c r="O87" s="18">
+        <v>994</v>
       </c>
       <c r="P87" t="s">
         <v>172</v>
       </c>
-      <c r="Q87">
-        <v>17</v>
+      <c r="Q87" s="18">
+        <v>34</v>
       </c>
       <c r="R87" t="s">
         <v>135</v>
       </c>
-      <c r="S87">
-        <v>35</v>
+      <c r="S87" s="18">
+        <v>47</v>
       </c>
       <c r="T87" t="s">
         <v>135</v>
       </c>
-      <c r="U87">
-        <v>40</v>
+      <c r="U87" t="s">
+        <v>230</v>
       </c>
       <c r="V87" t="s">
         <v>173</v>
       </c>
-      <c r="W87">
-        <v>75</v>
+      <c r="W87" s="18">
+        <v>111.38</v>
       </c>
       <c r="X87" t="s">
         <v>174</v>
       </c>
-      <c r="Y87">
-        <v>52</v>
+      <c r="Y87" t="s">
+        <v>230</v>
       </c>
       <c r="Z87" t="s">
         <v>174</v>
       </c>
-      <c r="AA87">
-        <v>6.28</v>
+      <c r="AA87" t="s">
+        <v>230</v>
       </c>
       <c r="AB87" t="s">
         <v>174</v>
       </c>
-      <c r="AC87">
-        <v>34.200000000000003</v>
+      <c r="AC87" s="18">
+        <v>4</v>
       </c>
       <c r="AD87" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE87">
-        <v>251</v>
+        <v>171</v>
+      </c>
+      <c r="AE87" s="18">
+        <v>339.4</v>
       </c>
       <c r="AF87" t="s">
         <v>135</v>
       </c>
-      <c r="AG87">
-        <v>295</v>
+      <c r="AG87" s="18">
+        <v>470</v>
       </c>
       <c r="AH87" t="s">
         <v>135</v>
       </c>
-      <c r="AI87">
-        <v>235</v>
+      <c r="AI87" s="18">
+        <v>400</v>
       </c>
       <c r="AJ87" t="s">
         <v>135</v>
       </c>
-      <c r="AK87">
-        <v>7</v>
+      <c r="AK87" s="18">
+        <v>18.2</v>
       </c>
       <c r="AL87" t="s">
         <v>175</v>
       </c>
-      <c r="AM87">
-        <v>0.35</v>
+      <c r="AM87" s="18">
+        <v>0.92</v>
       </c>
       <c r="AN87" t="s">
         <v>174</v>
       </c>
-      <c r="AO87">
-        <v>0.25</v>
+      <c r="AO87" t="s">
+        <v>230</v>
       </c>
       <c r="AP87" t="s">
-        <v>174</v>
-      </c>
-      <c r="AQ87">
-        <v>26</v>
+        <v>223</v>
+      </c>
+      <c r="AQ87" s="18">
+        <v>31</v>
       </c>
       <c r="AR87" t="s">
         <v>135</v>
       </c>
-      <c r="AS87">
-        <v>300</v>
+      <c r="AS87" s="18">
+        <v>257.2</v>
       </c>
       <c r="AT87" t="s">
         <v>177</v>
       </c>
-      <c r="AU87">
-        <v>182.59</v>
+      <c r="AU87" s="18">
+        <v>205.8</v>
       </c>
       <c r="AV87" t="s">
         <v>20</v>
       </c>
-      <c r="BI87">
-        <v>183.02</v>
+      <c r="AW87" t="s">
+        <v>230</v>
+      </c>
+      <c r="AX87" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY87" t="s">
+        <v>230</v>
+      </c>
+      <c r="AZ87" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA87" t="s">
+        <v>230</v>
+      </c>
+      <c r="BB87" t="s">
+        <v>223</v>
+      </c>
+      <c r="BC87" t="s">
+        <v>230</v>
+      </c>
+      <c r="BD87" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE87" t="s">
+        <v>230</v>
+      </c>
+      <c r="BF87" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG87" t="s">
+        <v>230</v>
+      </c>
+      <c r="BH87" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI87" s="18">
+        <v>205.8</v>
       </c>
       <c r="BJ87" t="s">
         <v>20</v>
+      </c>
+      <c r="BK87" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BL87" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM87" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BN87" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO87" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BP87" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ87" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BR87" t="s">
+        <v>173</v>
       </c>
       <c r="BT87" s="5"/>
       <c r="BU87" s="5"/>
@@ -19044,752 +20759,1241 @@
       <c r="CG87" s="5"/>
     </row>
     <row r="88" spans="1:85" x14ac:dyDescent="0.3">
-      <c r="B88" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="D88">
-        <v>50</v>
+      <c r="B88" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D88" s="17">
+        <v>75</v>
       </c>
       <c r="E88" t="s">
         <v>171</v>
       </c>
       <c r="F88">
-        <v>2</v>
-      </c>
-      <c r="G88">
-        <v>3285</v>
+        <v>4</v>
+      </c>
+      <c r="G88" s="17">
+        <v>1875</v>
       </c>
       <c r="H88" t="s">
         <v>21</v>
       </c>
-      <c r="I88">
-        <v>100.8</v>
+      <c r="I88" s="17">
+        <v>681</v>
       </c>
       <c r="J88" t="s">
         <v>22</v>
       </c>
-      <c r="K88">
-        <v>14</v>
+      <c r="K88" s="19">
+        <v>35</v>
       </c>
       <c r="L88" t="s">
         <v>135</v>
       </c>
-      <c r="M88">
-        <v>28</v>
+      <c r="M88" s="19">
+        <v>61</v>
       </c>
       <c r="N88" t="s">
         <v>171</v>
       </c>
-      <c r="O88">
-        <v>1023</v>
+      <c r="O88" s="19">
+        <v>994</v>
       </c>
       <c r="P88" t="s">
         <v>172</v>
       </c>
-      <c r="Q88">
-        <v>17</v>
+      <c r="Q88" s="19">
+        <v>35</v>
       </c>
       <c r="R88" t="s">
         <v>135</v>
       </c>
-      <c r="S88">
-        <v>30</v>
+      <c r="S88" s="19">
+        <v>53</v>
       </c>
       <c r="T88" t="s">
         <v>135</v>
       </c>
-      <c r="U88">
-        <v>90</v>
+      <c r="U88" t="s">
+        <v>230</v>
       </c>
       <c r="V88" t="s">
         <v>173</v>
       </c>
-      <c r="W88">
-        <v>105.2</v>
+      <c r="W88" s="19">
+        <v>141</v>
       </c>
       <c r="X88" t="s">
         <v>174</v>
       </c>
-      <c r="Y88">
-        <v>78.400000000000006</v>
+      <c r="Y88" t="s">
+        <v>230</v>
       </c>
       <c r="Z88" t="s">
         <v>174</v>
       </c>
-      <c r="AA88">
-        <v>9.9600000000000009</v>
+      <c r="AA88" t="s">
+        <v>230</v>
       </c>
       <c r="AB88" t="s">
         <v>174</v>
       </c>
-      <c r="AC88">
-        <v>46.2</v>
+      <c r="AC88" s="19">
+        <v>5</v>
       </c>
       <c r="AD88" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE88">
-        <v>271</v>
+        <v>171</v>
+      </c>
+      <c r="AE88" s="19">
+        <v>351.9</v>
       </c>
       <c r="AF88" t="s">
         <v>135</v>
       </c>
-      <c r="AG88">
-        <v>325</v>
+      <c r="AG88" s="19">
+        <v>472</v>
       </c>
       <c r="AH88" t="s">
         <v>135</v>
       </c>
-      <c r="AI88">
-        <v>235</v>
+      <c r="AI88" s="19">
+        <v>355</v>
       </c>
       <c r="AJ88" t="s">
         <v>135</v>
       </c>
-      <c r="AK88">
-        <v>12.6</v>
+      <c r="AK88" s="19">
+        <v>23.4</v>
       </c>
       <c r="AL88" t="s">
         <v>175</v>
       </c>
-      <c r="AM88">
-        <v>1</v>
+      <c r="AM88" s="19">
+        <v>1.72</v>
       </c>
       <c r="AN88" t="s">
         <v>174</v>
       </c>
-      <c r="AO88">
-        <v>0.9</v>
+      <c r="AO88" t="s">
+        <v>230</v>
       </c>
       <c r="AP88" t="s">
-        <v>174</v>
-      </c>
-      <c r="AQ88">
-        <v>26</v>
+        <v>223</v>
+      </c>
+      <c r="AQ88" s="19">
+        <v>32</v>
       </c>
       <c r="AR88" t="s">
         <v>135</v>
       </c>
-      <c r="AS88">
-        <v>552</v>
+      <c r="AS88" s="19">
+        <v>377.8</v>
       </c>
       <c r="AT88" t="s">
         <v>177</v>
       </c>
-      <c r="AU88">
-        <v>168.04</v>
+      <c r="AU88" s="19">
+        <v>201.5</v>
       </c>
       <c r="AV88" t="s">
         <v>20</v>
       </c>
-      <c r="BI88">
-        <v>168.43</v>
+      <c r="AW88" t="s">
+        <v>230</v>
+      </c>
+      <c r="AX88" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY88" t="s">
+        <v>230</v>
+      </c>
+      <c r="AZ88" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA88" t="s">
+        <v>230</v>
+      </c>
+      <c r="BB88" t="s">
+        <v>223</v>
+      </c>
+      <c r="BC88" t="s">
+        <v>230</v>
+      </c>
+      <c r="BD88" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE88" t="s">
+        <v>230</v>
+      </c>
+      <c r="BF88" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG88" t="s">
+        <v>230</v>
+      </c>
+      <c r="BH88" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI88" s="19">
+        <v>201.5</v>
       </c>
       <c r="BJ88" t="s">
         <v>20</v>
       </c>
+      <c r="BK88" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BL88" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM88" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BN88" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO88" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BP88" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ88" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BR88" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="89" spans="1:85" x14ac:dyDescent="0.3">
-      <c r="B89" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="D89">
-        <v>75</v>
+      <c r="B89" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D89" s="14">
+        <v>85</v>
       </c>
       <c r="E89" t="s">
         <v>171</v>
       </c>
       <c r="F89">
-        <v>3</v>
-      </c>
-      <c r="G89">
-        <v>4928</v>
+        <v>5</v>
+      </c>
+      <c r="G89" s="14">
+        <v>2125</v>
       </c>
       <c r="H89" t="s">
         <v>21</v>
       </c>
-      <c r="I89">
-        <v>115.4</v>
+      <c r="I89" s="14">
+        <v>710</v>
       </c>
       <c r="J89" t="s">
         <v>22</v>
       </c>
-      <c r="K89">
-        <v>16</v>
+      <c r="K89" s="18">
+        <v>35</v>
       </c>
       <c r="L89" t="s">
         <v>135</v>
       </c>
-      <c r="M89">
-        <v>34</v>
+      <c r="M89" s="18">
+        <v>60.5</v>
       </c>
       <c r="N89" t="s">
         <v>171</v>
       </c>
-      <c r="O89">
-        <v>1022</v>
+      <c r="O89" s="18">
+        <v>993.5</v>
       </c>
       <c r="P89" t="s">
         <v>172</v>
       </c>
-      <c r="Q89">
-        <v>18</v>
+      <c r="Q89" s="18">
+        <v>35</v>
       </c>
       <c r="R89" t="s">
         <v>135</v>
       </c>
-      <c r="S89">
-        <v>30</v>
+      <c r="S89" s="18">
+        <v>57</v>
       </c>
       <c r="T89" t="s">
         <v>135</v>
       </c>
-      <c r="U89">
-        <v>126</v>
+      <c r="U89" t="s">
+        <v>230</v>
       </c>
       <c r="V89" t="s">
         <v>173</v>
       </c>
-      <c r="W89">
-        <v>142.80000000000001</v>
+      <c r="W89" s="18">
+        <v>149.88</v>
       </c>
       <c r="X89" t="s">
         <v>174</v>
       </c>
-      <c r="Y89">
-        <v>113.4</v>
+      <c r="Y89" t="s">
+        <v>230</v>
       </c>
       <c r="Z89" t="s">
         <v>174</v>
       </c>
-      <c r="AA89">
-        <v>13.06</v>
+      <c r="AA89" t="s">
+        <v>230</v>
       </c>
       <c r="AB89" t="s">
         <v>174</v>
       </c>
-      <c r="AC89">
-        <v>56.4</v>
+      <c r="AC89" s="18">
+        <v>5.5</v>
       </c>
       <c r="AD89" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE89">
-        <v>272</v>
+        <v>171</v>
+      </c>
+      <c r="AE89" s="18">
+        <v>363.1</v>
       </c>
       <c r="AF89" t="s">
         <v>135</v>
       </c>
-      <c r="AG89">
-        <v>330</v>
+      <c r="AG89" s="18">
+        <v>485</v>
       </c>
       <c r="AH89" t="s">
         <v>135</v>
       </c>
-      <c r="AI89">
-        <v>210</v>
+      <c r="AI89" s="18">
+        <v>350</v>
       </c>
       <c r="AJ89" t="s">
         <v>135</v>
       </c>
-      <c r="AK89">
-        <v>14.7</v>
+      <c r="AK89" s="18">
+        <v>24.8</v>
       </c>
       <c r="AL89" t="s">
         <v>175</v>
       </c>
-      <c r="AM89">
-        <v>1.75</v>
+      <c r="AM89" s="18">
+        <v>1.95</v>
       </c>
       <c r="AN89" t="s">
         <v>174</v>
       </c>
-      <c r="AO89">
-        <v>1.6</v>
+      <c r="AO89" t="s">
+        <v>230</v>
       </c>
       <c r="AP89" t="s">
-        <v>174</v>
-      </c>
-      <c r="AQ89">
-        <v>26</v>
+        <v>223</v>
+      </c>
+      <c r="AQ89" s="18">
+        <v>32.5</v>
       </c>
       <c r="AR89" t="s">
         <v>135</v>
       </c>
-      <c r="AS89">
-        <v>804</v>
+      <c r="AS89" s="18">
+        <v>418.3</v>
       </c>
       <c r="AT89" t="s">
         <v>177</v>
       </c>
-      <c r="AU89">
-        <v>163.15</v>
+      <c r="AU89" s="18">
+        <v>196.8</v>
       </c>
       <c r="AV89" t="s">
         <v>20</v>
       </c>
-      <c r="BI89">
-        <v>163.46</v>
+      <c r="AW89" t="s">
+        <v>230</v>
+      </c>
+      <c r="AX89" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY89" t="s">
+        <v>230</v>
+      </c>
+      <c r="AZ89" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA89" t="s">
+        <v>230</v>
+      </c>
+      <c r="BB89" t="s">
+        <v>223</v>
+      </c>
+      <c r="BC89" t="s">
+        <v>230</v>
+      </c>
+      <c r="BD89" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE89" t="s">
+        <v>230</v>
+      </c>
+      <c r="BF89" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG89" t="s">
+        <v>230</v>
+      </c>
+      <c r="BH89" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI89" s="18">
+        <v>196.8</v>
       </c>
       <c r="BJ89" t="s">
         <v>20</v>
       </c>
+      <c r="BK89" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BL89" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM89" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BN89" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO89" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BP89" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ89" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BR89" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="90" spans="1:85" x14ac:dyDescent="0.3">
-      <c r="B90" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="D90">
-        <v>85</v>
+      <c r="B90" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D90" s="17">
+        <v>90</v>
       </c>
       <c r="E90" t="s">
         <v>171</v>
       </c>
       <c r="F90">
-        <v>4</v>
-      </c>
-      <c r="G90">
-        <v>5585</v>
+        <v>6</v>
+      </c>
+      <c r="G90" s="17">
+        <v>2250</v>
       </c>
       <c r="H90" t="s">
         <v>21</v>
       </c>
-      <c r="I90">
-        <v>120.3</v>
+      <c r="I90" s="17">
+        <v>724</v>
       </c>
       <c r="J90" t="s">
         <v>22</v>
       </c>
-      <c r="K90">
-        <v>17</v>
+      <c r="K90" s="19">
+        <v>36</v>
       </c>
       <c r="L90" t="s">
         <v>135</v>
       </c>
-      <c r="M90">
-        <v>32</v>
+      <c r="M90" s="19">
+        <v>59</v>
       </c>
       <c r="N90" t="s">
         <v>171</v>
       </c>
-      <c r="O90">
-        <v>1021</v>
+      <c r="O90" s="19">
+        <v>993.5</v>
       </c>
       <c r="P90" t="s">
         <v>172</v>
       </c>
-      <c r="Q90">
-        <v>18</v>
+      <c r="Q90" s="19">
+        <v>36</v>
       </c>
       <c r="R90" t="s">
         <v>135</v>
       </c>
-      <c r="S90">
-        <v>36</v>
+      <c r="S90" s="19">
+        <v>58</v>
       </c>
       <c r="T90" t="s">
         <v>135</v>
+      </c>
+      <c r="U90" t="s">
+        <v>230</v>
       </c>
       <c r="V90" t="s">
         <v>173</v>
       </c>
-      <c r="W90">
-        <v>152</v>
+      <c r="W90" s="19">
+        <v>154.12</v>
       </c>
       <c r="X90" t="s">
         <v>174</v>
       </c>
-      <c r="Y90">
-        <v>124</v>
+      <c r="Y90" t="s">
+        <v>230</v>
       </c>
       <c r="Z90" t="s">
         <v>174</v>
       </c>
-      <c r="AA90">
-        <v>14.19</v>
+      <c r="AA90" t="s">
+        <v>230</v>
       </c>
       <c r="AB90" t="s">
         <v>174</v>
       </c>
-      <c r="AC90">
-        <v>60.4</v>
+      <c r="AC90" s="19">
+        <v>5.9</v>
       </c>
       <c r="AD90" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE90">
-        <v>281</v>
+        <v>171</v>
+      </c>
+      <c r="AE90" s="19">
+        <v>375</v>
       </c>
       <c r="AF90" t="s">
         <v>135</v>
       </c>
-      <c r="AG90">
-        <v>345</v>
+      <c r="AG90" s="19">
+        <v>495</v>
       </c>
       <c r="AH90" t="s">
         <v>135</v>
       </c>
-      <c r="AI90">
-        <v>210</v>
+      <c r="AI90" s="19">
+        <v>350</v>
       </c>
       <c r="AJ90" t="s">
         <v>135</v>
       </c>
-      <c r="AK90">
-        <v>15.6</v>
+      <c r="AK90" s="19">
+        <v>26</v>
       </c>
       <c r="AL90" t="s">
         <v>175</v>
       </c>
-      <c r="AM90">
-        <v>2.15</v>
+      <c r="AM90" s="19">
+        <v>2.2400000000000002</v>
       </c>
       <c r="AN90" t="s">
         <v>174</v>
       </c>
-      <c r="AO90">
-        <v>1.95</v>
+      <c r="AO90" t="s">
+        <v>230</v>
       </c>
       <c r="AP90" t="s">
-        <v>174</v>
-      </c>
-      <c r="AQ90">
-        <v>28</v>
+        <v>223</v>
+      </c>
+      <c r="AQ90" s="19">
+        <v>32.5</v>
       </c>
       <c r="AR90" t="s">
         <v>135</v>
       </c>
-      <c r="AS90">
-        <v>919.2</v>
+      <c r="AS90" s="19">
+        <v>458.5</v>
       </c>
       <c r="AT90" t="s">
         <v>177</v>
       </c>
-      <c r="AU90">
-        <v>164.58</v>
+      <c r="AU90" s="19">
+        <v>203.8</v>
       </c>
       <c r="AV90" t="s">
         <v>20</v>
       </c>
-      <c r="BI90">
-        <v>164.66</v>
+      <c r="AW90" t="s">
+        <v>230</v>
+      </c>
+      <c r="AX90" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY90" t="s">
+        <v>230</v>
+      </c>
+      <c r="AZ90" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA90" t="s">
+        <v>230</v>
+      </c>
+      <c r="BB90" t="s">
+        <v>223</v>
+      </c>
+      <c r="BC90" t="s">
+        <v>230</v>
+      </c>
+      <c r="BD90" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE90" t="s">
+        <v>230</v>
+      </c>
+      <c r="BF90" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG90" t="s">
+        <v>230</v>
+      </c>
+      <c r="BH90" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI90" s="19">
+        <v>203.8</v>
       </c>
       <c r="BJ90" t="s">
         <v>20</v>
       </c>
+      <c r="BK90" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BL90" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM90" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BN90" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO90" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BP90" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ90" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BR90" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="91" spans="1:85" x14ac:dyDescent="0.3">
-      <c r="B91" s="11" t="s">
-        <v>218</v>
+      <c r="B91" s="15" t="s">
+        <v>254</v>
       </c>
       <c r="C91" s="5"/>
-      <c r="D91" s="5">
+      <c r="D91" s="14">
         <v>100</v>
       </c>
-      <c r="E91" s="5" t="s">
+      <c r="E91" t="s">
         <v>171</v>
       </c>
       <c r="F91" s="5">
-        <v>5</v>
-      </c>
-      <c r="G91" s="5">
-        <v>6570</v>
-      </c>
-      <c r="H91" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G91" s="14">
+        <v>2500</v>
+      </c>
+      <c r="H91" t="s">
         <v>21</v>
       </c>
-      <c r="I91" s="5">
-        <v>127</v>
-      </c>
-      <c r="J91" s="5" t="s">
+      <c r="I91" s="14">
+        <v>750</v>
+      </c>
+      <c r="J91" t="s">
         <v>22</v>
       </c>
-      <c r="K91" s="5">
-        <v>17</v>
-      </c>
-      <c r="L91" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="M91" s="5">
-        <v>30</v>
-      </c>
-      <c r="N91" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="O91" s="5">
-        <v>1021</v>
-      </c>
-      <c r="P91" s="5" t="s">
+      <c r="K91" s="18">
+        <v>36</v>
+      </c>
+      <c r="L91" t="s">
+        <v>135</v>
+      </c>
+      <c r="M91" s="18">
+        <v>58</v>
+      </c>
+      <c r="N91" t="s">
+        <v>171</v>
+      </c>
+      <c r="O91" s="18">
+        <v>993.5</v>
+      </c>
+      <c r="P91" t="s">
         <v>172</v>
       </c>
-      <c r="Q91" s="5">
-        <v>18</v>
-      </c>
-      <c r="R91" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="S91" s="5">
+      <c r="Q91" s="18">
         <v>36</v>
       </c>
-      <c r="T91" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="U91" s="5">
-        <v>220</v>
-      </c>
-      <c r="V91" s="5" t="s">
+      <c r="R91" t="s">
+        <v>135</v>
+      </c>
+      <c r="S91" s="18">
+        <v>59</v>
+      </c>
+      <c r="T91" t="s">
+        <v>135</v>
+      </c>
+      <c r="U91" t="s">
+        <v>230</v>
+      </c>
+      <c r="V91" t="s">
         <v>173</v>
       </c>
-      <c r="W91" s="5">
-        <v>151.80000000000001</v>
-      </c>
-      <c r="X91" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y91" s="5">
-        <v>148.19999999999999</v>
-      </c>
-      <c r="Z91" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA91" s="5">
-        <v>15.82</v>
-      </c>
-      <c r="AB91" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="AC91" s="5">
-        <v>67.400000000000006</v>
-      </c>
-      <c r="AD91" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE91" s="5">
-        <v>293</v>
-      </c>
-      <c r="AF91" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG91" s="5">
-        <v>375</v>
-      </c>
-      <c r="AH91" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="AI91" s="5">
-        <v>220</v>
-      </c>
-      <c r="AJ91" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="AK91" s="5">
-        <v>17</v>
-      </c>
-      <c r="AL91" s="5" t="s">
+      <c r="W91" s="18">
+        <v>161</v>
+      </c>
+      <c r="X91" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>230</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA91" t="s">
+        <v>230</v>
+      </c>
+      <c r="AB91" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC91" s="18">
+        <v>6.2</v>
+      </c>
+      <c r="AD91" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE91" s="18">
+        <v>393.8</v>
+      </c>
+      <c r="AF91" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG91" s="18">
+        <v>515</v>
+      </c>
+      <c r="AH91" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI91" s="18">
+        <v>355</v>
+      </c>
+      <c r="AJ91" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK91" s="18">
+        <v>27.4</v>
+      </c>
+      <c r="AL91" t="s">
         <v>175</v>
       </c>
-      <c r="AM91" s="5">
-        <v>2.7</v>
-      </c>
-      <c r="AN91" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="AO91" s="5">
-        <v>2.5</v>
-      </c>
-      <c r="AP91" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="AQ91" s="5">
-        <v>28</v>
-      </c>
-      <c r="AR91" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="AS91" s="5">
-        <v>1107</v>
-      </c>
-      <c r="AT91" s="5" t="s">
+      <c r="AM91" s="18">
+        <v>2.48</v>
+      </c>
+      <c r="AN91" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO91" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP91" t="s">
+        <v>223</v>
+      </c>
+      <c r="AQ91" s="18">
+        <v>33</v>
+      </c>
+      <c r="AR91" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS91" s="18">
+        <v>511.2</v>
+      </c>
+      <c r="AT91" t="s">
         <v>177</v>
       </c>
-      <c r="AU91" s="5">
-        <v>168.49</v>
-      </c>
-      <c r="AV91" s="5" t="s">
+      <c r="AU91" s="18">
+        <v>204.5</v>
+      </c>
+      <c r="AV91" t="s">
         <v>20</v>
       </c>
-      <c r="AW91" s="5"/>
-      <c r="AX91" s="5"/>
-      <c r="AY91" s="5"/>
-      <c r="AZ91" s="5"/>
-      <c r="BA91" s="5"/>
-      <c r="BB91" s="5"/>
-      <c r="BC91" s="5"/>
-      <c r="BD91" s="5"/>
-      <c r="BE91" s="5"/>
-      <c r="BF91" s="5"/>
-      <c r="BG91" s="5"/>
-      <c r="BH91" s="5"/>
-      <c r="BI91" s="5">
-        <v>168.37</v>
-      </c>
-      <c r="BJ91" s="5" t="s">
+      <c r="AW91" t="s">
+        <v>230</v>
+      </c>
+      <c r="AX91" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY91" t="s">
+        <v>230</v>
+      </c>
+      <c r="AZ91" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA91" t="s">
+        <v>230</v>
+      </c>
+      <c r="BB91" t="s">
+        <v>223</v>
+      </c>
+      <c r="BC91" t="s">
+        <v>230</v>
+      </c>
+      <c r="BD91" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE91" t="s">
+        <v>230</v>
+      </c>
+      <c r="BF91" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG91" t="s">
+        <v>230</v>
+      </c>
+      <c r="BH91" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI91" s="18">
+        <v>204.5</v>
+      </c>
+      <c r="BJ91" t="s">
         <v>20</v>
       </c>
-      <c r="BK91" s="5"/>
-      <c r="BL91" s="5"/>
-      <c r="BM91" s="5"/>
-      <c r="BN91" s="5"/>
-      <c r="BO91" s="5"/>
-      <c r="BP91" s="5"/>
-      <c r="BQ91" s="5"/>
-      <c r="BR91" s="5"/>
+      <c r="BK91" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BL91" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM91" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BN91" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO91" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BP91" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ91" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BR91" t="s">
+        <v>173</v>
+      </c>
       <c r="BS91" s="5"/>
     </row>
     <row r="92" spans="1:85" x14ac:dyDescent="0.3">
-      <c r="B92" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="D92">
-        <v>110</v>
+      <c r="B92" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D92" s="17">
+        <v>100</v>
       </c>
       <c r="E92" t="s">
         <v>171</v>
       </c>
       <c r="F92">
-        <v>6</v>
-      </c>
-      <c r="G92">
-        <v>7227</v>
+        <v>8</v>
+      </c>
+      <c r="G92" s="17">
+        <v>2500</v>
       </c>
       <c r="H92" t="s">
         <v>21</v>
       </c>
-      <c r="I92">
-        <v>131.1</v>
+      <c r="I92" s="17">
+        <v>750</v>
       </c>
       <c r="J92" t="s">
         <v>22</v>
       </c>
-      <c r="K92">
-        <v>17</v>
+      <c r="K92" s="19">
+        <v>36</v>
       </c>
       <c r="L92" t="s">
         <v>135</v>
       </c>
-      <c r="M92">
-        <v>26</v>
+      <c r="M92" s="19">
+        <v>58</v>
       </c>
       <c r="N92" t="s">
         <v>171</v>
       </c>
-      <c r="O92">
-        <v>1021</v>
+      <c r="O92" s="19">
+        <v>993.5</v>
       </c>
       <c r="P92" t="s">
         <v>172</v>
       </c>
-      <c r="Q92">
-        <v>18</v>
+      <c r="Q92" s="19">
+        <v>36</v>
       </c>
       <c r="R92" t="s">
         <v>135</v>
       </c>
-      <c r="S92">
-        <v>38</v>
+      <c r="S92" s="19">
+        <v>59</v>
       </c>
       <c r="T92" t="s">
         <v>135</v>
       </c>
-      <c r="U92">
-        <v>240</v>
+      <c r="U92" t="s">
+        <v>230</v>
       </c>
       <c r="V92" t="s">
         <v>173</v>
       </c>
-      <c r="W92">
-        <v>153.80000000000001</v>
+      <c r="W92" s="19">
+        <v>161</v>
       </c>
       <c r="X92" t="s">
         <v>174</v>
       </c>
-      <c r="Y92">
-        <v>155.80000000000001</v>
+      <c r="Y92" t="s">
+        <v>230</v>
       </c>
       <c r="Z92" t="s">
         <v>174</v>
       </c>
-      <c r="AA92">
-        <v>16.850000000000001</v>
+      <c r="AA92" t="s">
+        <v>230</v>
       </c>
       <c r="AB92" t="s">
         <v>174</v>
       </c>
-      <c r="AC92">
-        <v>69.8</v>
+      <c r="AC92" s="19">
+        <v>6.2</v>
       </c>
       <c r="AD92" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE92">
-        <v>304</v>
+        <v>171</v>
+      </c>
+      <c r="AE92" s="19">
+        <v>395</v>
       </c>
       <c r="AF92" t="s">
         <v>135</v>
       </c>
-      <c r="AG92">
-        <v>390</v>
+      <c r="AG92" s="19">
+        <v>518</v>
       </c>
       <c r="AH92" t="s">
         <v>135</v>
       </c>
-      <c r="AI92">
-        <v>220</v>
+      <c r="AI92" s="19">
+        <v>355</v>
       </c>
       <c r="AJ92" t="s">
         <v>135</v>
       </c>
-      <c r="AK92">
-        <v>17.600000000000001</v>
+      <c r="AK92" s="19">
+        <v>27.4</v>
       </c>
       <c r="AL92" t="s">
         <v>175</v>
       </c>
-      <c r="AM92">
-        <v>2.85</v>
+      <c r="AM92" s="19">
+        <v>2.48</v>
       </c>
       <c r="AN92" t="s">
         <v>174</v>
       </c>
-      <c r="AO92">
-        <v>2.65</v>
+      <c r="AO92" t="s">
+        <v>230</v>
       </c>
       <c r="AP92" t="s">
-        <v>174</v>
-      </c>
-      <c r="AQ92">
-        <v>29</v>
+        <v>223</v>
+      </c>
+      <c r="AQ92" s="19">
+        <v>33</v>
       </c>
       <c r="AR92" t="s">
         <v>135</v>
       </c>
-      <c r="AS92">
-        <v>1236</v>
+      <c r="AS92" s="19">
+        <v>511.2</v>
       </c>
       <c r="AT92" t="s">
         <v>177</v>
       </c>
-      <c r="AU92">
-        <v>171.03</v>
+      <c r="AU92" s="19">
+        <v>204.5</v>
       </c>
       <c r="AV92" t="s">
         <v>20</v>
       </c>
-      <c r="BI92">
-        <v>170.8</v>
+      <c r="AW92" t="s">
+        <v>230</v>
+      </c>
+      <c r="AX92" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY92" t="s">
+        <v>230</v>
+      </c>
+      <c r="AZ92" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA92" t="s">
+        <v>230</v>
+      </c>
+      <c r="BB92" t="s">
+        <v>223</v>
+      </c>
+      <c r="BC92" t="s">
+        <v>230</v>
+      </c>
+      <c r="BD92" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE92" t="s">
+        <v>230</v>
+      </c>
+      <c r="BF92" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG92" t="s">
+        <v>230</v>
+      </c>
+      <c r="BH92" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI92" s="19">
+        <v>204.5</v>
       </c>
       <c r="BJ92" t="s">
         <v>20</v>
+      </c>
+      <c r="BK92" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BL92" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM92" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BN92" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO92" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BP92" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ92" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BR92" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="93" spans="1:85" x14ac:dyDescent="0.3">
+      <c r="B93" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D93" s="14">
+        <v>110</v>
+      </c>
+      <c r="E93" t="s">
+        <v>171</v>
+      </c>
+      <c r="F93">
+        <v>9</v>
+      </c>
+      <c r="G93" s="14">
+        <v>2750</v>
+      </c>
+      <c r="H93" t="s">
+        <v>21</v>
+      </c>
+      <c r="I93" s="14">
+        <v>774</v>
+      </c>
+      <c r="J93" t="s">
+        <v>22</v>
+      </c>
+      <c r="K93" s="18">
+        <v>36</v>
+      </c>
+      <c r="L93" t="s">
+        <v>135</v>
+      </c>
+      <c r="M93" s="18">
+        <v>62</v>
+      </c>
+      <c r="N93" t="s">
+        <v>171</v>
+      </c>
+      <c r="O93" s="18">
+        <v>993.5</v>
+      </c>
+      <c r="P93" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q93" s="18">
+        <v>36</v>
+      </c>
+      <c r="R93" t="s">
+        <v>135</v>
+      </c>
+      <c r="S93" s="18">
+        <v>61</v>
+      </c>
+      <c r="T93" t="s">
+        <v>135</v>
+      </c>
+      <c r="U93" t="s">
+        <v>230</v>
+      </c>
+      <c r="V93" t="s">
+        <v>173</v>
+      </c>
+      <c r="W93" s="18">
+        <v>166.12</v>
+      </c>
+      <c r="X93" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y93" t="s">
+        <v>230</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA93" t="s">
+        <v>230</v>
+      </c>
+      <c r="AB93" t="s">
+        <v>174</v>
+      </c>
+      <c r="AC93" s="18">
+        <v>6.8</v>
+      </c>
+      <c r="AD93" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE93" s="18">
+        <v>426.9</v>
+      </c>
+      <c r="AF93" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG93" s="18">
+        <v>552</v>
+      </c>
+      <c r="AH93" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI93" s="18">
+        <v>375</v>
+      </c>
+      <c r="AJ93" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK93" s="18">
+        <v>28.7</v>
+      </c>
+      <c r="AL93" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM93" s="18">
+        <v>2.68</v>
+      </c>
+      <c r="AN93" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO93" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP93" t="s">
+        <v>223</v>
+      </c>
+      <c r="AQ93" s="18">
+        <v>32.5</v>
+      </c>
+      <c r="AR93" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS93" s="18">
+        <v>569.4</v>
+      </c>
+      <c r="AT93" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU93" s="18">
+        <v>207.1</v>
+      </c>
+      <c r="AV93" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW93" t="s">
+        <v>230</v>
+      </c>
+      <c r="AX93" t="s">
+        <v>174</v>
+      </c>
+      <c r="AY93" t="s">
+        <v>230</v>
+      </c>
+      <c r="AZ93" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA93" t="s">
+        <v>230</v>
+      </c>
+      <c r="BB93" t="s">
+        <v>223</v>
+      </c>
+      <c r="BC93" t="s">
+        <v>230</v>
+      </c>
+      <c r="BD93" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE93" t="s">
+        <v>230</v>
+      </c>
+      <c r="BF93" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG93" t="s">
+        <v>230</v>
+      </c>
+      <c r="BH93" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI93" s="18">
+        <v>207.1</v>
+      </c>
+      <c r="BJ93" t="s">
+        <v>20</v>
+      </c>
+      <c r="BK93" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BL93" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM93" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BN93" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO93" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BP93" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ93" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="BR93" t="s">
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/Aepms-backend/data/Engine_Performance_Data.xlsx
+++ b/Aepms-backend/data/Engine_Performance_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GOKUL\Desktop\WORKPLACE\Workplace\Aepms-backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656CD45D-1287-449F-BEAF-3CE83B132A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CACAD501-58C8-4E4D-ABA2-BDBB79A7EC48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="vessel_info" sheetId="1" r:id="rId1"/>
@@ -574,9 +574,6 @@
     <t>kg/h</t>
   </si>
   <si>
-    <t>GCL Narmadha</t>
-  </si>
-  <si>
     <t>Summary Data of Shop Trial</t>
   </si>
   <si>
@@ -815,6 +812,9 @@
   </si>
   <si>
     <t>DAIHATSU DIESEL MFG. CO., LTD.</t>
+  </si>
+  <si>
+    <t>GCL Narmada</t>
   </si>
 </sst>
 </file>
@@ -1544,25 +1544,25 @@
         <v>127</v>
       </c>
       <c r="T1" t="s">
+        <v>201</v>
+      </c>
+      <c r="U1" t="s">
         <v>202</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>203</v>
       </c>
-      <c r="V1" t="s">
-        <v>204</v>
-      </c>
       <c r="W1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="X1" t="s">
+        <v>214</v>
+      </c>
+      <c r="Y1" t="s">
         <v>215</v>
       </c>
-      <c r="Y1" t="s">
-        <v>216</v>
-      </c>
       <c r="Z1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AA1" t="s">
         <v>11</v>
@@ -1647,13 +1647,13 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>178</v>
+        <v>258</v>
       </c>
       <c r="C3">
         <v>9481685</v>
       </c>
       <c r="D3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E3" t="s">
         <v>15</v>
@@ -1721,16 +1721,16 @@
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C4">
         <v>9481661</v>
       </c>
       <c r="D4" t="s">
+        <v>181</v>
+      </c>
+      <c r="E4" t="s">
         <v>182</v>
-      </c>
-      <c r="E4" t="s">
-        <v>183</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
@@ -1739,7 +1739,7 @@
         <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I4" t="s">
         <v>123</v>
@@ -1795,16 +1795,16 @@
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C5">
         <v>9481659</v>
       </c>
       <c r="D5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
@@ -1813,7 +1813,7 @@
         <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I5" t="s">
         <v>123</v>
@@ -1869,16 +1869,16 @@
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C6">
         <v>9481219</v>
       </c>
       <c r="D6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
@@ -1887,7 +1887,7 @@
         <v>17</v>
       </c>
       <c r="H6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I6" t="s">
         <v>123</v>
@@ -1943,31 +1943,31 @@
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C7">
         <v>9832913</v>
       </c>
       <c r="D7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E7" t="s">
+        <v>189</v>
+      </c>
+      <c r="F7" t="s">
         <v>190</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>191</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>192</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>193</v>
       </c>
-      <c r="I7" t="s">
-        <v>194</v>
-      </c>
       <c r="J7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K7">
         <v>6</v>
@@ -2017,31 +2017,31 @@
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C8">
         <v>9832925</v>
       </c>
       <c r="D8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E8" t="s">
+        <v>189</v>
+      </c>
+      <c r="F8" t="s">
         <v>190</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>191</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>192</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>193</v>
       </c>
-      <c r="I8" t="s">
-        <v>194</v>
-      </c>
       <c r="J8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K8">
         <v>6</v>
@@ -2091,31 +2091,31 @@
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C9">
         <v>9792058</v>
       </c>
       <c r="D9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E9" s="2">
         <v>1576</v>
       </c>
       <c r="F9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G9" t="s">
+        <v>208</v>
+      </c>
+      <c r="H9" t="s">
         <v>209</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>210</v>
       </c>
-      <c r="I9" t="s">
-        <v>211</v>
-      </c>
       <c r="J9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K9">
         <v>6</v>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C10">
         <v>9532082</v>
@@ -2168,22 +2168,22 @@
         <v>5933</v>
       </c>
       <c r="E10" t="s">
+        <v>244</v>
+      </c>
+      <c r="F10" t="s">
+        <v>233</v>
+      </c>
+      <c r="G10" t="s">
         <v>245</v>
       </c>
-      <c r="F10" t="s">
-        <v>234</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
+        <v>232</v>
+      </c>
+      <c r="I10" t="s">
+        <v>231</v>
+      </c>
+      <c r="J10" t="s">
         <v>246</v>
-      </c>
-      <c r="H10" t="s">
-        <v>233</v>
-      </c>
-      <c r="I10" t="s">
-        <v>232</v>
-      </c>
-      <c r="J10" t="s">
-        <v>247</v>
       </c>
       <c r="K10">
         <v>6</v>
@@ -2221,31 +2221,31 @@
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C11">
         <v>9521813</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F11" t="s">
         <v>220</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>221</v>
       </c>
-      <c r="G11" t="s">
-        <v>222</v>
-      </c>
       <c r="H11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K11">
         <v>5</v>
@@ -2286,7 +2286,7 @@
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C12">
         <v>9628893</v>
@@ -2295,22 +2295,22 @@
         <v>774</v>
       </c>
       <c r="E12" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F12" t="s">
+        <v>248</v>
+      </c>
+      <c r="G12" t="s">
         <v>249</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>250</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
+        <v>238</v>
+      </c>
+      <c r="J12" t="s">
         <v>251</v>
-      </c>
-      <c r="I12" t="s">
-        <v>239</v>
-      </c>
-      <c r="J12" t="s">
-        <v>252</v>
       </c>
       <c r="K12">
         <v>5</v>
@@ -2348,7 +2348,7 @@
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C13">
         <v>9644500</v>
@@ -2360,19 +2360,19 @@
         <v>10701</v>
       </c>
       <c r="F13" t="s">
+        <v>224</v>
+      </c>
+      <c r="G13" t="s">
         <v>225</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>226</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>227</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>228</v>
-      </c>
-      <c r="J13" t="s">
-        <v>229</v>
       </c>
       <c r="K13">
         <v>6</v>
@@ -2410,31 +2410,31 @@
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C14">
         <v>9628910</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E14" t="s">
+        <v>235</v>
+      </c>
+      <c r="F14" t="s">
+        <v>237</v>
+      </c>
+      <c r="G14" t="s">
         <v>236</v>
       </c>
-      <c r="F14" t="s">
+      <c r="H14" t="s">
+        <v>239</v>
+      </c>
+      <c r="I14" t="s">
         <v>238</v>
       </c>
-      <c r="G14" t="s">
-        <v>237</v>
-      </c>
-      <c r="H14" t="s">
-        <v>240</v>
-      </c>
-      <c r="I14" t="s">
-        <v>239</v>
-      </c>
       <c r="J14" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K14">
         <v>5</v>
@@ -2461,22 +2461,22 @@
         <v>22</v>
       </c>
       <c r="T14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="U14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="V14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="W14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="X14" t="s">
         <v>21</v>
       </c>
       <c r="Y14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Z14" t="s">
         <v>171</v>
@@ -2484,31 +2484,31 @@
     </row>
     <row r="15" spans="1:28" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C15">
         <v>9486295</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F15" t="s">
         <v>254</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>255</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="I15" t="s">
         <v>256</v>
       </c>
-      <c r="H15" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="I15" t="s">
-        <v>257</v>
-      </c>
       <c r="J15" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K15">
         <v>8</v>
@@ -2544,13 +2544,13 @@
         <v>73</v>
       </c>
       <c r="W15" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="X15" t="s">
         <v>21</v>
       </c>
       <c r="Y15" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Z15" t="s">
         <v>171</v>
@@ -2685,7 +2685,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C3" s="1">
         <v>40518</v>
@@ -2697,7 +2697,7 @@
         <v>132</v>
       </c>
       <c r="F3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G3" t="s">
         <v>134</v>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C4" s="1">
         <v>40518</v>
@@ -2738,7 +2738,7 @@
         <v>132</v>
       </c>
       <c r="F4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G4" t="s">
         <v>134</v>
@@ -2767,7 +2767,7 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C5" s="1">
         <v>40518</v>
@@ -2779,7 +2779,7 @@
         <v>132</v>
       </c>
       <c r="F5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G5" t="s">
         <v>134</v>
@@ -2808,7 +2808,7 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C6" s="1">
         <v>40518</v>
@@ -2820,7 +2820,7 @@
         <v>132</v>
       </c>
       <c r="F6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G6" t="s">
         <v>134</v>
@@ -2849,7 +2849,7 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C7" s="1">
         <v>43461</v>
@@ -2858,13 +2858,13 @@
         <v>131</v>
       </c>
       <c r="E7" t="s">
+        <v>194</v>
+      </c>
+      <c r="F7" t="s">
         <v>195</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>196</v>
-      </c>
-      <c r="G7" t="s">
-        <v>197</v>
       </c>
       <c r="H7">
         <v>6</v>
@@ -2893,7 +2893,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C8" s="1">
         <v>43461</v>
@@ -2902,13 +2902,13 @@
         <v>131</v>
       </c>
       <c r="E8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H8">
         <v>6</v>
@@ -2937,7 +2937,7 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C9" s="1">
         <v>42788</v>
@@ -2946,13 +2946,13 @@
         <v>131</v>
       </c>
       <c r="E9" t="s">
+        <v>205</v>
+      </c>
+      <c r="F9" t="s">
         <v>206</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>207</v>
-      </c>
-      <c r="G9" t="s">
-        <v>208</v>
       </c>
       <c r="H9">
         <v>5</v>
@@ -3001,7 +3001,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B11" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C11" s="1">
         <v>42788</v>
@@ -3079,7 +3079,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C14" s="1">
         <v>42788</v>
@@ -3105,7 +3105,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C15" s="1">
         <v>42788</v>
@@ -4877,7 +4877,7 @@
     </row>
     <row r="9" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D9">
         <v>25</v>
@@ -5083,7 +5083,7 @@
     </row>
     <row r="10" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D10">
         <v>50</v>
@@ -5289,7 +5289,7 @@
     </row>
     <row r="11" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D11">
         <v>75</v>
@@ -5495,7 +5495,7 @@
     </row>
     <row r="12" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D12">
         <v>90</v>
@@ -5701,7 +5701,7 @@
     </row>
     <row r="13" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D13">
         <v>100</v>
@@ -5907,7 +5907,7 @@
     </row>
     <row r="14" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D14">
         <v>100</v>
@@ -6113,7 +6113,7 @@
     </row>
     <row r="15" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D15">
         <v>110</v>
@@ -6319,7 +6319,7 @@
     </row>
     <row r="16" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D16">
         <v>25</v>
@@ -6525,7 +6525,7 @@
     </row>
     <row r="17" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D17">
         <v>50</v>
@@ -6731,7 +6731,7 @@
     </row>
     <row r="18" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D18">
         <v>75</v>
@@ -6937,7 +6937,7 @@
     </row>
     <row r="19" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D19">
         <v>90</v>
@@ -7143,7 +7143,7 @@
     </row>
     <row r="20" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D20">
         <v>100</v>
@@ -7349,7 +7349,7 @@
     </row>
     <row r="21" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D21">
         <v>100</v>
@@ -7555,7 +7555,7 @@
     </row>
     <row r="22" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D22">
         <v>110</v>
@@ -7761,7 +7761,7 @@
     </row>
     <row r="23" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D23">
         <v>25</v>
@@ -7967,7 +7967,7 @@
     </row>
     <row r="24" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D24">
         <v>50</v>
@@ -8173,7 +8173,7 @@
     </row>
     <row r="25" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D25">
         <v>75</v>
@@ -8379,7 +8379,7 @@
     </row>
     <row r="26" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D26">
         <v>90</v>
@@ -8585,7 +8585,7 @@
     </row>
     <row r="27" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D27">
         <v>100</v>
@@ -8791,7 +8791,7 @@
     </row>
     <row r="28" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D28">
         <v>100</v>
@@ -8997,7 +8997,7 @@
     </row>
     <row r="29" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D29">
         <v>110</v>
@@ -9203,7 +9203,7 @@
     </row>
     <row r="30" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D30">
         <v>25</v>
@@ -9409,7 +9409,7 @@
     </row>
     <row r="31" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D31">
         <v>50</v>
@@ -9615,7 +9615,7 @@
     </row>
     <row r="32" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D32">
         <v>75</v>
@@ -9821,7 +9821,7 @@
     </row>
     <row r="33" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D33">
         <v>90</v>
@@ -10027,7 +10027,7 @@
     </row>
     <row r="34" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D34">
         <v>100</v>
@@ -10233,7 +10233,7 @@
     </row>
     <row r="35" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D35">
         <v>100</v>
@@ -10439,7 +10439,7 @@
     </row>
     <row r="36" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D36">
         <v>110</v>
@@ -10645,7 +10645,7 @@
     </row>
     <row r="37" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D37">
         <v>25</v>
@@ -10845,7 +10845,7 @@
     </row>
     <row r="38" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D38">
         <v>50</v>
@@ -11045,7 +11045,7 @@
     </row>
     <row r="39" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D39">
         <v>75</v>
@@ -11245,7 +11245,7 @@
     </row>
     <row r="40" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D40">
         <v>100</v>
@@ -11445,7 +11445,7 @@
     </row>
     <row r="41" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D41">
         <v>100</v>
@@ -11645,7 +11645,7 @@
     </row>
     <row r="42" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D42">
         <v>110</v>
@@ -11845,7 +11845,7 @@
     </row>
     <row r="43" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D43">
         <v>25</v>
@@ -12045,7 +12045,7 @@
     </row>
     <row r="44" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D44">
         <v>50</v>
@@ -12245,7 +12245,7 @@
     </row>
     <row r="45" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D45">
         <v>75</v>
@@ -12445,7 +12445,7 @@
     </row>
     <row r="46" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D46">
         <v>100</v>
@@ -12645,7 +12645,7 @@
     </row>
     <row r="47" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D47">
         <v>100</v>
@@ -12845,7 +12845,7 @@
     </row>
     <row r="48" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D48">
         <v>110</v>
@@ -13045,7 +13045,7 @@
     </row>
     <row r="49" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D49">
         <v>25</v>
@@ -13159,7 +13159,7 @@
         <v>0.38</v>
       </c>
       <c r="AP49" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AQ49">
         <v>33</v>
@@ -13195,7 +13195,7 @@
         <v>0.43</v>
       </c>
       <c r="BB49" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BC49">
         <v>217</v>
@@ -13245,7 +13245,7 @@
     </row>
     <row r="50" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D50">
         <v>50</v>
@@ -13359,7 +13359,7 @@
         <v>1.06</v>
       </c>
       <c r="AP50" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AQ50">
         <v>32</v>
@@ -13395,7 +13395,7 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="BB50" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BC50">
         <v>311</v>
@@ -13445,7 +13445,7 @@
     </row>
     <row r="51" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D51">
         <v>65</v>
@@ -13559,7 +13559,7 @@
         <v>1.66</v>
       </c>
       <c r="AP51" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AQ51">
         <v>33</v>
@@ -13595,7 +13595,7 @@
         <v>1.68</v>
       </c>
       <c r="BB51" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BC51">
         <v>329</v>
@@ -13645,7 +13645,7 @@
     </row>
     <row r="52" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D52">
         <v>75.599999999999994</v>
@@ -13759,7 +13759,7 @@
         <v>2.06</v>
       </c>
       <c r="AP52" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AQ52">
         <v>32</v>
@@ -13795,7 +13795,7 @@
         <v>2.0699999999999998</v>
       </c>
       <c r="BB52" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BC52">
         <v>349</v>
@@ -13845,7 +13845,7 @@
     </row>
     <row r="53" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D53">
         <v>85</v>
@@ -13959,7 +13959,7 @@
         <v>2.39</v>
       </c>
       <c r="AP53" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AQ53">
         <v>33</v>
@@ -13995,7 +13995,7 @@
         <v>2.4</v>
       </c>
       <c r="BB53" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BC53">
         <v>368</v>
@@ -14045,7 +14045,7 @@
     </row>
     <row r="54" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D54">
         <v>100</v>
@@ -14159,7 +14159,7 @@
         <v>2.92</v>
       </c>
       <c r="AP54" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AQ54">
         <v>31</v>
@@ -14195,7 +14195,7 @@
         <v>2.93</v>
       </c>
       <c r="BB54" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BC54">
         <v>403</v>
@@ -14356,10 +14356,10 @@
         <v>174</v>
       </c>
       <c r="AO55" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AP55" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AQ55">
         <v>33</v>
@@ -14368,7 +14368,7 @@
         <v>135</v>
       </c>
       <c r="AS55" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AT55" t="s">
         <v>177</v>
@@ -14386,7 +14386,7 @@
         <v>174</v>
       </c>
       <c r="BB55" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BD55" t="s">
         <v>135</v>
@@ -14538,7 +14538,7 @@
         <v>3.7699999999999999E-3</v>
       </c>
       <c r="AP56" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AQ56">
         <v>29</v>
@@ -14547,7 +14547,7 @@
         <v>135</v>
       </c>
       <c r="AS56" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AT56" t="s">
         <v>177</v>
@@ -14565,7 +14565,7 @@
         <v>174</v>
       </c>
       <c r="BB56" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BD56" t="s">
         <v>135</v>
@@ -14717,7 +14717,7 @@
         <v>7.2399999999999999E-3</v>
       </c>
       <c r="AP57" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AQ57">
         <v>30</v>
@@ -14726,7 +14726,7 @@
         <v>135</v>
       </c>
       <c r="AS57" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AT57" t="s">
         <v>177</v>
@@ -14744,7 +14744,7 @@
         <v>174</v>
       </c>
       <c r="BB57" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BD57" t="s">
         <v>135</v>
@@ -14896,7 +14896,7 @@
         <v>8.4600000000000005E-3</v>
       </c>
       <c r="AP58" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AQ58">
         <v>31</v>
@@ -14905,7 +14905,7 @@
         <v>135</v>
       </c>
       <c r="AS58" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AT58" t="s">
         <v>177</v>
@@ -14923,7 +14923,7 @@
         <v>174</v>
       </c>
       <c r="BB58" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BD58" t="s">
         <v>135</v>
@@ -15075,7 +15075,7 @@
         <v>1.1010000000000001E-2</v>
       </c>
       <c r="AP59" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AQ59" s="5">
         <v>32</v>
@@ -15084,7 +15084,7 @@
         <v>135</v>
       </c>
       <c r="AS59" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AT59" t="s">
         <v>177</v>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="BA59" s="8"/>
       <c r="BB59" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BD59" t="s">
         <v>135</v>
@@ -15148,7 +15148,7 @@
     </row>
     <row r="60" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B60" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C60" s="12"/>
       <c r="D60" s="10">
@@ -15266,7 +15266,7 @@
         <v>0.40799999999999997</v>
       </c>
       <c r="AP60" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AQ60" s="10">
         <v>30</v>
@@ -15302,7 +15302,7 @@
         <v>0.35699999999999998</v>
       </c>
       <c r="BB60" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BC60" s="10">
         <v>295</v>
@@ -15347,7 +15347,7 @@
     </row>
     <row r="61" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B61" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C61" s="12"/>
       <c r="D61" s="10">
@@ -15465,7 +15465,7 @@
         <v>0.96899999999999997</v>
       </c>
       <c r="AP61" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AQ61" s="10">
         <v>30</v>
@@ -15501,7 +15501,7 @@
         <v>1.02</v>
       </c>
       <c r="BB61" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BC61" s="10">
         <v>325</v>
@@ -15546,7 +15546,7 @@
     </row>
     <row r="62" spans="2:70" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B62" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C62" s="12"/>
       <c r="D62" s="10">
@@ -15664,7 +15664,7 @@
         <v>1.7849999999999999</v>
       </c>
       <c r="AP62" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AQ62" s="10">
         <v>30</v>
@@ -15700,7 +15700,7 @@
         <v>1.7849999999999999</v>
       </c>
       <c r="BB62" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BC62" s="10">
         <v>330</v>
@@ -15745,7 +15745,7 @@
     </row>
     <row r="63" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B63" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C63" s="12"/>
       <c r="D63" s="10">
@@ -15859,7 +15859,7 @@
         <v>1.988</v>
       </c>
       <c r="AP63" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AQ63" s="10">
         <v>28</v>
@@ -15895,7 +15895,7 @@
         <v>2.1920000000000002</v>
       </c>
       <c r="BB63" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BC63" s="10">
         <v>345</v>
@@ -15940,7 +15940,7 @@
     </row>
     <row r="64" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B64" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C64" s="12"/>
       <c r="D64" s="10">
@@ -16058,7 +16058,7 @@
         <v>2.5489999999999999</v>
       </c>
       <c r="AP64" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AQ64" s="10">
         <v>28</v>
@@ -16094,7 +16094,7 @@
         <v>2.7530000000000001</v>
       </c>
       <c r="BB64" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BC64" s="10">
         <v>375</v>
@@ -16139,7 +16139,7 @@
     </row>
     <row r="65" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B65" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C65" s="12"/>
       <c r="D65" s="10">
@@ -16257,7 +16257,7 @@
         <v>2.4980000000000002</v>
       </c>
       <c r="AP65" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AQ65" s="10">
         <v>28</v>
@@ -16293,7 +16293,7 @@
         <v>2.702</v>
       </c>
       <c r="BB65" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BC65" s="10">
         <v>375</v>
@@ -16338,7 +16338,7 @@
     </row>
     <row r="66" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B66" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C66" s="12"/>
       <c r="D66" s="10">
@@ -16456,7 +16456,7 @@
         <v>2.702</v>
       </c>
       <c r="AP66" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AQ66" s="10">
         <v>29</v>
@@ -16492,7 +16492,7 @@
         <v>2.9060000000000001</v>
       </c>
       <c r="BB66" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BC66" s="10">
         <v>390</v>
@@ -16652,10 +16652,10 @@
         <v>174</v>
       </c>
       <c r="AO67" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AP67" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AQ67" s="5">
         <v>18</v>
@@ -16688,10 +16688,10 @@
         <v>174</v>
       </c>
       <c r="BA67" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BB67" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BC67" s="5">
         <v>321.5</v>
@@ -16706,7 +16706,7 @@
         <v>135</v>
       </c>
       <c r="BG67" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BH67" s="5" t="s">
         <v>175</v>
@@ -16730,13 +16730,13 @@
         <v>135</v>
       </c>
       <c r="BO67" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BP67" s="5" t="s">
         <v>135</v>
       </c>
       <c r="BQ67" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BR67" s="5" t="s">
         <v>173</v>
@@ -16860,10 +16860,10 @@
         <v>174</v>
       </c>
       <c r="AO68" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AP68" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AQ68">
         <v>20</v>
@@ -16896,10 +16896,10 @@
         <v>174</v>
       </c>
       <c r="BA68" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BB68" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BC68">
         <v>347.7</v>
@@ -16914,7 +16914,7 @@
         <v>135</v>
       </c>
       <c r="BG68" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BH68" t="s">
         <v>175</v>
@@ -16938,13 +16938,13 @@
         <v>135</v>
       </c>
       <c r="BO68" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BP68" t="s">
         <v>135</v>
       </c>
       <c r="BQ68" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BR68" t="s">
         <v>173</v>
@@ -17066,10 +17066,10 @@
         <v>174</v>
       </c>
       <c r="AO69" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AP69" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AQ69">
         <v>21</v>
@@ -17102,10 +17102,10 @@
         <v>174</v>
       </c>
       <c r="BA69" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BB69" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BC69">
         <v>381.8</v>
@@ -17120,7 +17120,7 @@
         <v>135</v>
       </c>
       <c r="BG69" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BH69" t="s">
         <v>175</v>
@@ -17144,13 +17144,13 @@
         <v>135</v>
       </c>
       <c r="BO69" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BP69" t="s">
         <v>135</v>
       </c>
       <c r="BQ69" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BR69" t="s">
         <v>173</v>
@@ -17272,10 +17272,10 @@
         <v>174</v>
       </c>
       <c r="AO70" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AP70" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AQ70">
         <v>22</v>
@@ -17308,10 +17308,10 @@
         <v>174</v>
       </c>
       <c r="BA70" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BB70" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BC70">
         <v>397.1</v>
@@ -17326,7 +17326,7 @@
         <v>135</v>
       </c>
       <c r="BG70" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BH70" t="s">
         <v>175</v>
@@ -17350,13 +17350,13 @@
         <v>135</v>
       </c>
       <c r="BO70" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BP70" t="s">
         <v>135</v>
       </c>
       <c r="BQ70" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BR70" t="s">
         <v>173</v>
@@ -17478,10 +17478,10 @@
         <v>174</v>
       </c>
       <c r="AO71" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AP71" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AQ71">
         <v>24</v>
@@ -17514,10 +17514,10 @@
         <v>174</v>
       </c>
       <c r="BA71" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BB71" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BC71">
         <v>446.8</v>
@@ -17532,7 +17532,7 @@
         <v>135</v>
       </c>
       <c r="BG71" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BH71" t="s">
         <v>175</v>
@@ -17556,13 +17556,13 @@
         <v>135</v>
       </c>
       <c r="BO71" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BP71" t="s">
         <v>135</v>
       </c>
       <c r="BQ71" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BR71" t="s">
         <v>173</v>
@@ -17684,10 +17684,10 @@
         <v>174</v>
       </c>
       <c r="AO72" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AP72" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AQ72">
         <v>24</v>
@@ -17720,10 +17720,10 @@
         <v>174</v>
       </c>
       <c r="BA72" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BB72" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BC72">
         <v>473.9</v>
@@ -17738,7 +17738,7 @@
         <v>135</v>
       </c>
       <c r="BG72" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BH72" t="s">
         <v>175</v>
@@ -17762,13 +17762,13 @@
         <v>135</v>
       </c>
       <c r="BO72" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BP72" t="s">
         <v>135</v>
       </c>
       <c r="BQ72" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BR72" t="s">
         <v>173</v>
@@ -17890,10 +17890,10 @@
         <v>174</v>
       </c>
       <c r="AO73" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AP73" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AQ73">
         <v>23</v>
@@ -17926,10 +17926,10 @@
         <v>174</v>
       </c>
       <c r="BA73" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BB73" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BC73">
         <v>446.3</v>
@@ -17944,7 +17944,7 @@
         <v>135</v>
       </c>
       <c r="BG73" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BH73" t="s">
         <v>175</v>
@@ -17968,13 +17968,13 @@
         <v>135</v>
       </c>
       <c r="BO73" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BP73" t="s">
         <v>135</v>
       </c>
       <c r="BQ73" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BR73" t="s">
         <v>173</v>
@@ -18014,7 +18014,7 @@
         <v>135</v>
       </c>
       <c r="M74" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="N74" t="s">
         <v>171</v>
@@ -18096,10 +18096,10 @@
         <v>174</v>
       </c>
       <c r="AO74" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AP74" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AQ74" s="5">
         <v>37</v>
@@ -18129,7 +18129,7 @@
       </c>
       <c r="BA74" s="5"/>
       <c r="BB74" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BC74" s="5"/>
       <c r="BD74" t="s">
@@ -18198,7 +18198,7 @@
         <v>135</v>
       </c>
       <c r="M75" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="N75" t="s">
         <v>171</v>
@@ -18279,10 +18279,10 @@
         <v>174</v>
       </c>
       <c r="AO75" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AP75" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AQ75">
         <v>37</v>
@@ -18309,7 +18309,7 @@
         <v>174</v>
       </c>
       <c r="BB75" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BD75" t="s">
         <v>135</v>
@@ -18368,7 +18368,7 @@
         <v>135</v>
       </c>
       <c r="M76" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="N76" t="s">
         <v>171</v>
@@ -18449,10 +18449,10 @@
         <v>174</v>
       </c>
       <c r="AO76" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AP76" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AQ76">
         <v>37</v>
@@ -18479,7 +18479,7 @@
         <v>174</v>
       </c>
       <c r="BB76" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BD76" t="s">
         <v>135</v>
@@ -18541,7 +18541,7 @@
         <v>135</v>
       </c>
       <c r="M77" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="N77" t="s">
         <v>171</v>
@@ -18622,10 +18622,10 @@
         <v>174</v>
       </c>
       <c r="AO77" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AP77" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AQ77">
         <v>37</v>
@@ -18652,7 +18652,7 @@
         <v>174</v>
       </c>
       <c r="BB77" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BD77" t="s">
         <v>135</v>
@@ -18681,7 +18681,7 @@
     </row>
     <row r="78" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B78" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C78" s="5"/>
       <c r="D78" s="5">
@@ -18796,10 +18796,10 @@
         <v>174</v>
       </c>
       <c r="AO78" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AP78" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AQ78" s="5">
         <v>18</v>
@@ -18832,10 +18832,10 @@
         <v>174</v>
       </c>
       <c r="BA78" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BB78" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BC78" s="5">
         <v>321.5</v>
@@ -18850,7 +18850,7 @@
         <v>135</v>
       </c>
       <c r="BG78" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BH78" s="5" t="s">
         <v>175</v>
@@ -18874,13 +18874,13 @@
         <v>135</v>
       </c>
       <c r="BO78" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BP78" s="5" t="s">
         <v>135</v>
       </c>
       <c r="BQ78" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BR78" s="5" t="s">
         <v>173</v>
@@ -18890,7 +18890,7 @@
     </row>
     <row r="79" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B79" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D79">
         <v>50</v>
@@ -19004,10 +19004,10 @@
         <v>174</v>
       </c>
       <c r="AO79" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AP79" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AQ79">
         <v>20</v>
@@ -19040,10 +19040,10 @@
         <v>174</v>
       </c>
       <c r="BA79" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BB79" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BC79">
         <v>347.7</v>
@@ -19058,7 +19058,7 @@
         <v>135</v>
       </c>
       <c r="BG79" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BH79" t="s">
         <v>175</v>
@@ -19082,13 +19082,13 @@
         <v>135</v>
       </c>
       <c r="BO79" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BP79" t="s">
         <v>135</v>
       </c>
       <c r="BQ79" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BR79" t="s">
         <v>173</v>
@@ -19096,7 +19096,7 @@
     </row>
     <row r="80" spans="1:72" x14ac:dyDescent="0.3">
       <c r="B80" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D80">
         <v>75</v>
@@ -19210,10 +19210,10 @@
         <v>174</v>
       </c>
       <c r="AO80" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AP80" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AQ80">
         <v>21</v>
@@ -19246,10 +19246,10 @@
         <v>174</v>
       </c>
       <c r="BA80" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BB80" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BC80">
         <v>381.8</v>
@@ -19264,7 +19264,7 @@
         <v>135</v>
       </c>
       <c r="BG80" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BH80" t="s">
         <v>175</v>
@@ -19288,13 +19288,13 @@
         <v>135</v>
       </c>
       <c r="BO80" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BP80" t="s">
         <v>135</v>
       </c>
       <c r="BQ80" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BR80" t="s">
         <v>173</v>
@@ -19302,7 +19302,7 @@
     </row>
     <row r="81" spans="1:85" x14ac:dyDescent="0.3">
       <c r="B81" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D81">
         <v>85</v>
@@ -19416,10 +19416,10 @@
         <v>174</v>
       </c>
       <c r="AO81" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AP81" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AQ81">
         <v>22</v>
@@ -19452,10 +19452,10 @@
         <v>174</v>
       </c>
       <c r="BA81" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BB81" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BC81">
         <v>397.1</v>
@@ -19470,7 +19470,7 @@
         <v>135</v>
       </c>
       <c r="BG81" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BH81" t="s">
         <v>175</v>
@@ -19494,13 +19494,13 @@
         <v>135</v>
       </c>
       <c r="BO81" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BP81" t="s">
         <v>135</v>
       </c>
       <c r="BQ81" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BR81" t="s">
         <v>173</v>
@@ -19508,7 +19508,7 @@
     </row>
     <row r="82" spans="1:85" x14ac:dyDescent="0.3">
       <c r="B82" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D82">
         <v>100</v>
@@ -19622,10 +19622,10 @@
         <v>174</v>
       </c>
       <c r="AO82" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AP82" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AQ82">
         <v>24</v>
@@ -19658,10 +19658,10 @@
         <v>174</v>
       </c>
       <c r="BA82" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BB82" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BC82">
         <v>446.8</v>
@@ -19676,7 +19676,7 @@
         <v>135</v>
       </c>
       <c r="BG82" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BH82" t="s">
         <v>175</v>
@@ -19700,13 +19700,13 @@
         <v>135</v>
       </c>
       <c r="BO82" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BP82" t="s">
         <v>135</v>
       </c>
       <c r="BQ82" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BR82" t="s">
         <v>173</v>
@@ -19714,7 +19714,7 @@
     </row>
     <row r="83" spans="1:85" x14ac:dyDescent="0.3">
       <c r="B83" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D83">
         <v>110</v>
@@ -19828,10 +19828,10 @@
         <v>174</v>
       </c>
       <c r="AO83" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AP83" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AQ83">
         <v>24</v>
@@ -19864,10 +19864,10 @@
         <v>174</v>
       </c>
       <c r="BA83" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BB83" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BC83">
         <v>473.9</v>
@@ -19882,7 +19882,7 @@
         <v>135</v>
       </c>
       <c r="BG83" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BH83" t="s">
         <v>175</v>
@@ -19906,13 +19906,13 @@
         <v>135</v>
       </c>
       <c r="BO83" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BP83" t="s">
         <v>135</v>
       </c>
       <c r="BQ83" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BR83" t="s">
         <v>173</v>
@@ -19920,7 +19920,7 @@
     </row>
     <row r="84" spans="1:85" x14ac:dyDescent="0.3">
       <c r="B84" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D84">
         <v>100</v>
@@ -20034,10 +20034,10 @@
         <v>174</v>
       </c>
       <c r="AO84" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AP84" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AQ84">
         <v>23</v>
@@ -20070,10 +20070,10 @@
         <v>174</v>
       </c>
       <c r="BA84" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BB84" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BC84">
         <v>446.3</v>
@@ -20088,7 +20088,7 @@
         <v>135</v>
       </c>
       <c r="BG84" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BH84" t="s">
         <v>175</v>
@@ -20112,13 +20112,13 @@
         <v>135</v>
       </c>
       <c r="BO84" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BP84" t="s">
         <v>135</v>
       </c>
       <c r="BQ84" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BR84" t="s">
         <v>173</v>
@@ -20126,7 +20126,7 @@
     </row>
     <row r="85" spans="1:85" x14ac:dyDescent="0.3">
       <c r="B85" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D85" s="14">
         <v>15</v>
@@ -20180,7 +20180,7 @@
         <v>135</v>
       </c>
       <c r="U85" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="V85" t="s">
         <v>173</v>
@@ -20192,13 +20192,13 @@
         <v>174</v>
       </c>
       <c r="Y85" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Z85" t="s">
         <v>174</v>
       </c>
       <c r="AA85" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AB85" t="s">
         <v>174</v>
@@ -20240,10 +20240,10 @@
         <v>174</v>
       </c>
       <c r="AO85" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AP85" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AQ85" s="18">
         <v>30.5</v>
@@ -20264,37 +20264,37 @@
         <v>20</v>
       </c>
       <c r="AW85" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AX85" t="s">
         <v>174</v>
       </c>
       <c r="AY85" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AZ85" t="s">
         <v>174</v>
       </c>
       <c r="BA85" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BB85" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BC85" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BD85" t="s">
         <v>135</v>
       </c>
       <c r="BE85" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BF85" t="s">
         <v>135</v>
       </c>
       <c r="BG85" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BH85" t="s">
         <v>175</v>
@@ -20306,25 +20306,25 @@
         <v>20</v>
       </c>
       <c r="BK85" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BL85" t="s">
         <v>172</v>
       </c>
       <c r="BM85" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BN85" t="s">
         <v>135</v>
       </c>
       <c r="BO85" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BP85" t="s">
         <v>135</v>
       </c>
       <c r="BQ85" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BR85" t="s">
         <v>173</v>
@@ -20333,7 +20333,7 @@
     <row r="86" spans="1:85" x14ac:dyDescent="0.3">
       <c r="A86" s="5"/>
       <c r="B86" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D86" s="17">
         <v>25</v>
@@ -20387,7 +20387,7 @@
         <v>135</v>
       </c>
       <c r="U86" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="V86" t="s">
         <v>173</v>
@@ -20399,13 +20399,13 @@
         <v>174</v>
       </c>
       <c r="Y86" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Z86" t="s">
         <v>174</v>
       </c>
       <c r="AA86" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AB86" t="s">
         <v>174</v>
@@ -20447,10 +20447,10 @@
         <v>174</v>
       </c>
       <c r="AO86" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AP86" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AQ86" s="19">
         <v>31</v>
@@ -20471,37 +20471,37 @@
         <v>20</v>
       </c>
       <c r="AW86" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AX86" t="s">
         <v>174</v>
       </c>
       <c r="AY86" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AZ86" t="s">
         <v>174</v>
       </c>
       <c r="BA86" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BB86" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BC86" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BD86" t="s">
         <v>135</v>
       </c>
       <c r="BE86" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BF86" t="s">
         <v>135</v>
       </c>
       <c r="BG86" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BH86" t="s">
         <v>175</v>
@@ -20513,25 +20513,25 @@
         <v>20</v>
       </c>
       <c r="BK86" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BL86" t="s">
         <v>172</v>
       </c>
       <c r="BM86" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BN86" t="s">
         <v>135</v>
       </c>
       <c r="BO86" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BP86" t="s">
         <v>135</v>
       </c>
       <c r="BQ86" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BR86" t="s">
         <v>173</v>
@@ -20540,7 +20540,7 @@
     <row r="87" spans="1:85" x14ac:dyDescent="0.3">
       <c r="A87" s="5"/>
       <c r="B87" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D87" s="14">
         <v>50</v>
@@ -20594,7 +20594,7 @@
         <v>135</v>
       </c>
       <c r="U87" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="V87" t="s">
         <v>173</v>
@@ -20606,13 +20606,13 @@
         <v>174</v>
       </c>
       <c r="Y87" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Z87" t="s">
         <v>174</v>
       </c>
       <c r="AA87" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AB87" t="s">
         <v>174</v>
@@ -20654,10 +20654,10 @@
         <v>174</v>
       </c>
       <c r="AO87" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AP87" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AQ87" s="18">
         <v>31</v>
@@ -20678,37 +20678,37 @@
         <v>20</v>
       </c>
       <c r="AW87" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AX87" t="s">
         <v>174</v>
       </c>
       <c r="AY87" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AZ87" t="s">
         <v>174</v>
       </c>
       <c r="BA87" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BB87" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BC87" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BD87" t="s">
         <v>135</v>
       </c>
       <c r="BE87" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BF87" t="s">
         <v>135</v>
       </c>
       <c r="BG87" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BH87" t="s">
         <v>175</v>
@@ -20720,25 +20720,25 @@
         <v>20</v>
       </c>
       <c r="BK87" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BL87" t="s">
         <v>172</v>
       </c>
       <c r="BM87" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BN87" t="s">
         <v>135</v>
       </c>
       <c r="BO87" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BP87" t="s">
         <v>135</v>
       </c>
       <c r="BQ87" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BR87" t="s">
         <v>173</v>
@@ -20760,7 +20760,7 @@
     </row>
     <row r="88" spans="1:85" x14ac:dyDescent="0.3">
       <c r="B88" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D88" s="17">
         <v>75</v>
@@ -20814,7 +20814,7 @@
         <v>135</v>
       </c>
       <c r="U88" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="V88" t="s">
         <v>173</v>
@@ -20826,13 +20826,13 @@
         <v>174</v>
       </c>
       <c r="Y88" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Z88" t="s">
         <v>174</v>
       </c>
       <c r="AA88" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AB88" t="s">
         <v>174</v>
@@ -20874,10 +20874,10 @@
         <v>174</v>
       </c>
       <c r="AO88" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AP88" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AQ88" s="19">
         <v>32</v>
@@ -20898,37 +20898,37 @@
         <v>20</v>
       </c>
       <c r="AW88" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AX88" t="s">
         <v>174</v>
       </c>
       <c r="AY88" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AZ88" t="s">
         <v>174</v>
       </c>
       <c r="BA88" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BB88" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BC88" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BD88" t="s">
         <v>135</v>
       </c>
       <c r="BE88" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BF88" t="s">
         <v>135</v>
       </c>
       <c r="BG88" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BH88" t="s">
         <v>175</v>
@@ -20940,25 +20940,25 @@
         <v>20</v>
       </c>
       <c r="BK88" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BL88" t="s">
         <v>172</v>
       </c>
       <c r="BM88" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BN88" t="s">
         <v>135</v>
       </c>
       <c r="BO88" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BP88" t="s">
         <v>135</v>
       </c>
       <c r="BQ88" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BR88" t="s">
         <v>173</v>
@@ -20966,7 +20966,7 @@
     </row>
     <row r="89" spans="1:85" x14ac:dyDescent="0.3">
       <c r="B89" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D89" s="14">
         <v>85</v>
@@ -21020,7 +21020,7 @@
         <v>135</v>
       </c>
       <c r="U89" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="V89" t="s">
         <v>173</v>
@@ -21032,13 +21032,13 @@
         <v>174</v>
       </c>
       <c r="Y89" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Z89" t="s">
         <v>174</v>
       </c>
       <c r="AA89" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AB89" t="s">
         <v>174</v>
@@ -21080,10 +21080,10 @@
         <v>174</v>
       </c>
       <c r="AO89" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AP89" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AQ89" s="18">
         <v>32.5</v>
@@ -21104,37 +21104,37 @@
         <v>20</v>
       </c>
       <c r="AW89" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AX89" t="s">
         <v>174</v>
       </c>
       <c r="AY89" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AZ89" t="s">
         <v>174</v>
       </c>
       <c r="BA89" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BB89" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BC89" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BD89" t="s">
         <v>135</v>
       </c>
       <c r="BE89" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BF89" t="s">
         <v>135</v>
       </c>
       <c r="BG89" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BH89" t="s">
         <v>175</v>
@@ -21146,25 +21146,25 @@
         <v>20</v>
       </c>
       <c r="BK89" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BL89" t="s">
         <v>172</v>
       </c>
       <c r="BM89" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BN89" t="s">
         <v>135</v>
       </c>
       <c r="BO89" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BP89" t="s">
         <v>135</v>
       </c>
       <c r="BQ89" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BR89" t="s">
         <v>173</v>
@@ -21172,7 +21172,7 @@
     </row>
     <row r="90" spans="1:85" x14ac:dyDescent="0.3">
       <c r="B90" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D90" s="17">
         <v>90</v>
@@ -21226,7 +21226,7 @@
         <v>135</v>
       </c>
       <c r="U90" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="V90" t="s">
         <v>173</v>
@@ -21238,13 +21238,13 @@
         <v>174</v>
       </c>
       <c r="Y90" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Z90" t="s">
         <v>174</v>
       </c>
       <c r="AA90" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AB90" t="s">
         <v>174</v>
@@ -21286,10 +21286,10 @@
         <v>174</v>
       </c>
       <c r="AO90" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AP90" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AQ90" s="19">
         <v>32.5</v>
@@ -21310,37 +21310,37 @@
         <v>20</v>
       </c>
       <c r="AW90" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AX90" t="s">
         <v>174</v>
       </c>
       <c r="AY90" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AZ90" t="s">
         <v>174</v>
       </c>
       <c r="BA90" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BB90" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BC90" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BD90" t="s">
         <v>135</v>
       </c>
       <c r="BE90" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BF90" t="s">
         <v>135</v>
       </c>
       <c r="BG90" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BH90" t="s">
         <v>175</v>
@@ -21352,25 +21352,25 @@
         <v>20</v>
       </c>
       <c r="BK90" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BL90" t="s">
         <v>172</v>
       </c>
       <c r="BM90" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BN90" t="s">
         <v>135</v>
       </c>
       <c r="BO90" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BP90" t="s">
         <v>135</v>
       </c>
       <c r="BQ90" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BR90" t="s">
         <v>173</v>
@@ -21378,7 +21378,7 @@
     </row>
     <row r="91" spans="1:85" x14ac:dyDescent="0.3">
       <c r="B91" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C91" s="5"/>
       <c r="D91" s="14">
@@ -21433,7 +21433,7 @@
         <v>135</v>
       </c>
       <c r="U91" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="V91" t="s">
         <v>173</v>
@@ -21445,13 +21445,13 @@
         <v>174</v>
       </c>
       <c r="Y91" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Z91" t="s">
         <v>174</v>
       </c>
       <c r="AA91" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AB91" t="s">
         <v>174</v>
@@ -21493,10 +21493,10 @@
         <v>174</v>
       </c>
       <c r="AO91" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AP91" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AQ91" s="18">
         <v>33</v>
@@ -21517,37 +21517,37 @@
         <v>20</v>
       </c>
       <c r="AW91" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AX91" t="s">
         <v>174</v>
       </c>
       <c r="AY91" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AZ91" t="s">
         <v>174</v>
       </c>
       <c r="BA91" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BB91" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BC91" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BD91" t="s">
         <v>135</v>
       </c>
       <c r="BE91" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BF91" t="s">
         <v>135</v>
       </c>
       <c r="BG91" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BH91" t="s">
         <v>175</v>
@@ -21559,25 +21559,25 @@
         <v>20</v>
       </c>
       <c r="BK91" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BL91" t="s">
         <v>172</v>
       </c>
       <c r="BM91" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BN91" t="s">
         <v>135</v>
       </c>
       <c r="BO91" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BP91" t="s">
         <v>135</v>
       </c>
       <c r="BQ91" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BR91" t="s">
         <v>173</v>
@@ -21586,7 +21586,7 @@
     </row>
     <row r="92" spans="1:85" x14ac:dyDescent="0.3">
       <c r="B92" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D92" s="17">
         <v>100</v>
@@ -21640,7 +21640,7 @@
         <v>135</v>
       </c>
       <c r="U92" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="V92" t="s">
         <v>173</v>
@@ -21652,13 +21652,13 @@
         <v>174</v>
       </c>
       <c r="Y92" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Z92" t="s">
         <v>174</v>
       </c>
       <c r="AA92" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AB92" t="s">
         <v>174</v>
@@ -21700,10 +21700,10 @@
         <v>174</v>
       </c>
       <c r="AO92" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AP92" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AQ92" s="19">
         <v>33</v>
@@ -21724,37 +21724,37 @@
         <v>20</v>
       </c>
       <c r="AW92" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AX92" t="s">
         <v>174</v>
       </c>
       <c r="AY92" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AZ92" t="s">
         <v>174</v>
       </c>
       <c r="BA92" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BB92" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BC92" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BD92" t="s">
         <v>135</v>
       </c>
       <c r="BE92" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BF92" t="s">
         <v>135</v>
       </c>
       <c r="BG92" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BH92" t="s">
         <v>175</v>
@@ -21766,25 +21766,25 @@
         <v>20</v>
       </c>
       <c r="BK92" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BL92" t="s">
         <v>172</v>
       </c>
       <c r="BM92" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BN92" t="s">
         <v>135</v>
       </c>
       <c r="BO92" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BP92" t="s">
         <v>135</v>
       </c>
       <c r="BQ92" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BR92" t="s">
         <v>173</v>
@@ -21792,7 +21792,7 @@
     </row>
     <row r="93" spans="1:85" x14ac:dyDescent="0.3">
       <c r="B93" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D93" s="14">
         <v>110</v>
@@ -21846,7 +21846,7 @@
         <v>135</v>
       </c>
       <c r="U93" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="V93" t="s">
         <v>173</v>
@@ -21858,13 +21858,13 @@
         <v>174</v>
       </c>
       <c r="Y93" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Z93" t="s">
         <v>174</v>
       </c>
       <c r="AA93" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AB93" t="s">
         <v>174</v>
@@ -21906,10 +21906,10 @@
         <v>174</v>
       </c>
       <c r="AO93" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AP93" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AQ93" s="18">
         <v>32.5</v>
@@ -21930,37 +21930,37 @@
         <v>20</v>
       </c>
       <c r="AW93" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AX93" t="s">
         <v>174</v>
       </c>
       <c r="AY93" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AZ93" t="s">
         <v>174</v>
       </c>
       <c r="BA93" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BB93" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BC93" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BD93" t="s">
         <v>135</v>
       </c>
       <c r="BE93" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BF93" t="s">
         <v>135</v>
       </c>
       <c r="BG93" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BH93" t="s">
         <v>175</v>
@@ -21972,25 +21972,25 @@
         <v>20</v>
       </c>
       <c r="BK93" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BL93" t="s">
         <v>172</v>
       </c>
       <c r="BM93" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BN93" t="s">
         <v>135</v>
       </c>
       <c r="BO93" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BP93" t="s">
         <v>135</v>
       </c>
       <c r="BQ93" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BR93" t="s">
         <v>173</v>
